--- a/src/main/resources/be/vlaanderen/omgeving/data/id/conceptscheme/rie-iepr/rie-iepr.xlsx
+++ b/src/main/resources/be/vlaanderen/omgeving/data/id/conceptscheme/rie-iepr/rie-iepr.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AJ275"/>
+  <dimension ref="A1:AK282"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -503,9 +503,12 @@
         <v>isMultiselect</v>
       </c>
       <c r="AI1" t="str">
+        <v>relevantFeatureClass</v>
+      </c>
+      <c r="AJ1" t="str">
         <v>hasTopConcept</v>
       </c>
-      <c r="AJ1" t="str">
+      <c r="AK1" t="str">
         <v>hasPart</v>
       </c>
     </row>
@@ -618,6 +621,9 @@
       <c r="AJ2" t="str">
         <v>null</v>
       </c>
+      <c r="AK2" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -728,6 +734,9 @@
       <c r="AJ3" t="str">
         <v>null</v>
       </c>
+      <c r="AK3" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -838,6 +847,9 @@
       <c r="AJ4" t="str">
         <v>null</v>
       </c>
+      <c r="AK4" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -948,6 +960,9 @@
       <c r="AJ5" t="str">
         <v>null</v>
       </c>
+      <c r="AK5" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -1058,6 +1073,9 @@
       <c r="AJ6" t="str">
         <v>null</v>
       </c>
+      <c r="AK6" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
@@ -1168,6 +1186,9 @@
       <c r="AJ7" t="str">
         <v>null</v>
       </c>
+      <c r="AK7" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
@@ -1278,6 +1299,9 @@
       <c r="AJ8" t="str">
         <v>null</v>
       </c>
+      <c r="AK8" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
@@ -1388,6 +1412,9 @@
       <c r="AJ9" t="str">
         <v>null</v>
       </c>
+      <c r="AK9" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
@@ -1498,6 +1525,9 @@
       <c r="AJ10" t="str">
         <v>null</v>
       </c>
+      <c r="AK10" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
@@ -1608,6 +1638,9 @@
       <c r="AJ11" t="str">
         <v>null</v>
       </c>
+      <c r="AK11" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
@@ -1718,6 +1751,9 @@
       <c r="AJ12" t="str">
         <v>null</v>
       </c>
+      <c r="AK12" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
@@ -1828,6 +1864,9 @@
       <c r="AJ13" t="str">
         <v>null</v>
       </c>
+      <c r="AK13" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
@@ -1938,6 +1977,9 @@
       <c r="AJ14" t="str">
         <v>null</v>
       </c>
+      <c r="AK14" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
@@ -2048,6 +2090,9 @@
       <c r="AJ15" t="str">
         <v>null</v>
       </c>
+      <c r="AK15" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
@@ -2158,6 +2203,9 @@
       <c r="AJ16" t="str">
         <v>null</v>
       </c>
+      <c r="AK16" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
@@ -2268,6 +2316,9 @@
       <c r="AJ17" t="str">
         <v>null</v>
       </c>
+      <c r="AK17" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
@@ -2378,6 +2429,9 @@
       <c r="AJ18" t="str">
         <v>null</v>
       </c>
+      <c r="AK18" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
@@ -2488,6 +2542,9 @@
       <c r="AJ19" t="str">
         <v>null</v>
       </c>
+      <c r="AK19" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
@@ -2598,6 +2655,9 @@
       <c r="AJ20" t="str">
         <v>null</v>
       </c>
+      <c r="AK20" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
@@ -2708,6 +2768,9 @@
       <c r="AJ21" t="str">
         <v>null</v>
       </c>
+      <c r="AK21" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
@@ -2818,6 +2881,9 @@
       <c r="AJ22" t="str">
         <v>null</v>
       </c>
+      <c r="AK22" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
@@ -2928,6 +2994,9 @@
       <c r="AJ23" t="str">
         <v>null</v>
       </c>
+      <c r="AK23" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
@@ -3038,6 +3107,9 @@
       <c r="AJ24" t="str">
         <v>null</v>
       </c>
+      <c r="AK24" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
@@ -3148,6 +3220,9 @@
       <c r="AJ25" t="str">
         <v>null</v>
       </c>
+      <c r="AK25" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
@@ -3258,6 +3333,9 @@
       <c r="AJ26" t="str">
         <v>null</v>
       </c>
+      <c r="AK26" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
@@ -3368,6 +3446,9 @@
       <c r="AJ27" t="str">
         <v>null</v>
       </c>
+      <c r="AK27" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
@@ -3478,6 +3559,9 @@
       <c r="AJ28" t="str">
         <v>null</v>
       </c>
+      <c r="AK28" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
@@ -3588,6 +3672,9 @@
       <c r="AJ29" t="str">
         <v>null</v>
       </c>
+      <c r="AK29" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
@@ -3698,6 +3785,9 @@
       <c r="AJ30" t="str">
         <v>null</v>
       </c>
+      <c r="AK30" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
@@ -3808,6 +3898,9 @@
       <c r="AJ31" t="str">
         <v>null</v>
       </c>
+      <c r="AK31" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
@@ -3918,6 +4011,9 @@
       <c r="AJ32" t="str">
         <v>null</v>
       </c>
+      <c r="AK32" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
@@ -4028,6 +4124,9 @@
       <c r="AJ33" t="str">
         <v>null</v>
       </c>
+      <c r="AK33" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
@@ -4138,6 +4237,9 @@
       <c r="AJ34" t="str">
         <v>null</v>
       </c>
+      <c r="AK34" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
@@ -4248,6 +4350,9 @@
       <c r="AJ35" t="str">
         <v>null</v>
       </c>
+      <c r="AK35" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
@@ -4358,6 +4463,9 @@
       <c r="AJ36" t="str">
         <v>null</v>
       </c>
+      <c r="AK36" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
@@ -4468,6 +4576,9 @@
       <c r="AJ37" t="str">
         <v>null</v>
       </c>
+      <c r="AK37" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
@@ -4578,6 +4689,9 @@
       <c r="AJ38" t="str">
         <v>null</v>
       </c>
+      <c r="AK38" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
@@ -4688,6 +4802,9 @@
       <c r="AJ39" t="str">
         <v>null</v>
       </c>
+      <c r="AK39" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
@@ -4798,6 +4915,9 @@
       <c r="AJ40" t="str">
         <v>null</v>
       </c>
+      <c r="AK40" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
@@ -4867,7 +4987,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/verwijderingsrendement</v>
       </c>
       <c r="W41" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X41" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/verwijderingsrendement_percentage|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/verwijderingsrendement_stof</v>
@@ -4906,6 +5026,9 @@
         <v>null</v>
       </c>
       <c r="AJ41" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK41" t="str">
         <v>null</v>
       </c>
     </row>
@@ -4977,7 +5100,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/verwijderingsrendement_percentage</v>
       </c>
       <c r="W42" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X42" t="str">
         <v>null</v>
@@ -5016,6 +5139,9 @@
         <v>null</v>
       </c>
       <c r="AJ42" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK42" t="str">
         <v>null</v>
       </c>
     </row>
@@ -5087,7 +5213,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/verwijderingsrendement_stof</v>
       </c>
       <c r="W43" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X43" t="str">
         <v>null</v>
@@ -5126,6 +5252,9 @@
         <v>null</v>
       </c>
       <c r="AJ43" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK43" t="str">
         <v>null</v>
       </c>
     </row>
@@ -5197,7 +5326,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/waterzuiveringstechniek</v>
       </c>
       <c r="W44" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X44" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/waterzuiveringstechniek_ingebruikvan|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/waterzuiveringstechniek_techniek</v>
@@ -5236,6 +5365,9 @@
         <v>null</v>
       </c>
       <c r="AJ44" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK44" t="str">
         <v>null</v>
       </c>
     </row>
@@ -5307,7 +5439,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/waterzuiveringstechniek_ingebruikvan</v>
       </c>
       <c r="W45" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X45" t="str">
         <v>null</v>
@@ -5346,6 +5478,9 @@
         <v>null</v>
       </c>
       <c r="AJ45" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK45" t="str">
         <v>null</v>
       </c>
     </row>
@@ -5417,7 +5552,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/waterzuiveringstechniek_techniek</v>
       </c>
       <c r="W46" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X46" t="str">
         <v>null</v>
@@ -5456,6 +5591,9 @@
         <v>null</v>
       </c>
       <c r="AJ46" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK46" t="str">
         <v>null</v>
       </c>
     </row>
@@ -5568,6 +5706,9 @@
       <c r="AJ47" t="str">
         <v>null</v>
       </c>
+      <c r="AK47" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
@@ -5678,6 +5819,9 @@
       <c r="AJ48" t="str">
         <v>null</v>
       </c>
+      <c r="AK48" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
@@ -5788,6 +5932,9 @@
       <c r="AJ49" t="str">
         <v>null</v>
       </c>
+      <c r="AK49" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
@@ -5898,6 +6045,9 @@
       <c r="AJ50" t="str">
         <v>null</v>
       </c>
+      <c r="AK50" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
@@ -6008,6 +6158,9 @@
       <c r="AJ51" t="str">
         <v>null</v>
       </c>
+      <c r="AK51" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
@@ -6118,6 +6271,9 @@
       <c r="AJ52" t="str">
         <v>null</v>
       </c>
+      <c r="AK52" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
@@ -6228,6 +6384,9 @@
       <c r="AJ53" t="str">
         <v>null</v>
       </c>
+      <c r="AK53" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
@@ -6338,6 +6497,9 @@
       <c r="AJ54" t="str">
         <v>null</v>
       </c>
+      <c r="AK54" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
@@ -6448,6 +6610,9 @@
       <c r="AJ55" t="str">
         <v>null</v>
       </c>
+      <c r="AK55" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
@@ -6517,7 +6682,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-eigenschappen/referentiepunt</v>
       </c>
       <c r="W56" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X56" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-eigenschappen/referentiepunt_diepte|https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-eigenschappen/referentiepunt_naam</v>
@@ -6556,6 +6721,9 @@
         <v>null</v>
       </c>
       <c r="AJ56" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK56" t="str">
         <v>null</v>
       </c>
     </row>
@@ -6627,7 +6795,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-eigenschappen/referentiepunt_diepte</v>
       </c>
       <c r="W57" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X57" t="str">
         <v>null</v>
@@ -6666,6 +6834,9 @@
         <v>null</v>
       </c>
       <c r="AJ57" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK57" t="str">
         <v>null</v>
       </c>
     </row>
@@ -6737,7 +6908,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-eigenschappen/referentiepunt_naam</v>
       </c>
       <c r="W58" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X58" t="str">
         <v>null</v>
@@ -6776,6 +6947,9 @@
         <v>null</v>
       </c>
       <c r="AJ58" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK58" t="str">
         <v>null</v>
       </c>
     </row>
@@ -6888,6 +7062,9 @@
       <c r="AJ59" t="str">
         <v>null</v>
       </c>
+      <c r="AK59" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
@@ -6998,6 +7175,9 @@
       <c r="AJ60" t="str">
         <v>null</v>
       </c>
+      <c r="AK60" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
@@ -7108,6 +7288,9 @@
       <c r="AJ61" t="str">
         <v>null</v>
       </c>
+      <c r="AK61" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
@@ -7218,6 +7401,9 @@
       <c r="AJ62" t="str">
         <v>null</v>
       </c>
+      <c r="AK62" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
@@ -7328,6 +7514,9 @@
       <c r="AJ63" t="str">
         <v>null</v>
       </c>
+      <c r="AK63" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
@@ -7438,6 +7627,9 @@
       <c r="AJ64" t="str">
         <v>null</v>
       </c>
+      <c r="AK64" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
@@ -7548,6 +7740,9 @@
       <c r="AJ65" t="str">
         <v>null</v>
       </c>
+      <c r="AK65" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
@@ -7658,6 +7853,9 @@
       <c r="AJ66" t="str">
         <v>null</v>
       </c>
+      <c r="AK66" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
@@ -7768,6 +7966,9 @@
       <c r="AJ67" t="str">
         <v>null</v>
       </c>
+      <c r="AK67" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
@@ -7878,6 +8079,9 @@
       <c r="AJ68" t="str">
         <v>null</v>
       </c>
+      <c r="AK68" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
@@ -7988,6 +8192,9 @@
       <c r="AJ69" t="str">
         <v>null</v>
       </c>
+      <c r="AK69" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
@@ -8098,6 +8305,9 @@
       <c r="AJ70" t="str">
         <v>null</v>
       </c>
+      <c r="AK70" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
@@ -8208,6 +8418,9 @@
       <c r="AJ71" t="str">
         <v>null</v>
       </c>
+      <c r="AK71" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
@@ -8318,6 +8531,9 @@
       <c r="AJ72" t="str">
         <v>null</v>
       </c>
+      <c r="AK72" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
@@ -8428,6 +8644,9 @@
       <c r="AJ73" t="str">
         <v>null</v>
       </c>
+      <c r="AK73" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
@@ -8538,6 +8757,9 @@
       <c r="AJ74" t="str">
         <v>null</v>
       </c>
+      <c r="AK74" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
@@ -8648,6 +8870,9 @@
       <c r="AJ75" t="str">
         <v>null</v>
       </c>
+      <c r="AK75" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
@@ -8758,6 +8983,9 @@
       <c r="AJ76" t="str">
         <v>null</v>
       </c>
+      <c r="AK76" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
@@ -8868,6 +9096,9 @@
       <c r="AJ77" t="str">
         <v>null</v>
       </c>
+      <c r="AK77" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
@@ -8978,6 +9209,9 @@
       <c r="AJ78" t="str">
         <v>null</v>
       </c>
+      <c r="AK78" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
@@ -9088,6 +9322,9 @@
       <c r="AJ79" t="str">
         <v>null</v>
       </c>
+      <c r="AK79" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
@@ -9198,6 +9435,9 @@
       <c r="AJ80" t="str">
         <v>null</v>
       </c>
+      <c r="AK80" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
@@ -9267,7 +9507,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-be</v>
       </c>
       <c r="W81" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X81" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-be-naam|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-be-on|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-be-ve</v>
@@ -9306,6 +9546,9 @@
         <v>null</v>
       </c>
       <c r="AJ81" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK81" t="str">
         <v>null</v>
       </c>
     </row>
@@ -9377,7 +9620,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-be-naam</v>
       </c>
       <c r="W82" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X82" t="str">
         <v>null</v>
@@ -9416,6 +9659,9 @@
         <v>null</v>
       </c>
       <c r="AJ82" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK82" t="str">
         <v>null</v>
       </c>
     </row>
@@ -9487,7 +9733,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-be-on</v>
       </c>
       <c r="W83" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X83" t="str">
         <v>null</v>
@@ -9526,6 +9772,9 @@
         <v>null</v>
       </c>
       <c r="AJ83" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK83" t="str">
         <v>null</v>
       </c>
     </row>
@@ -9597,7 +9846,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-be-ve</v>
       </c>
       <c r="W84" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X84" t="str">
         <v>null</v>
@@ -9636,6 +9885,9 @@
         <v>null</v>
       </c>
       <c r="AJ84" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK84" t="str">
         <v>null</v>
       </c>
     </row>
@@ -9707,7 +9959,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-buitenland</v>
       </c>
       <c r="W85" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X85" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-buitenland-btw|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-buitenland-naam</v>
@@ -9746,6 +9998,9 @@
         <v>null</v>
       </c>
       <c r="AJ85" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK85" t="str">
         <v>null</v>
       </c>
     </row>
@@ -9817,7 +10072,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-buitenland-btw</v>
       </c>
       <c r="W86" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X86" t="str">
         <v>null</v>
@@ -9856,6 +10111,9 @@
         <v>null</v>
       </c>
       <c r="AJ86" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK86" t="str">
         <v>null</v>
       </c>
     </row>
@@ -9927,7 +10185,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-buitenland-naam</v>
       </c>
       <c r="W87" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X87" t="str">
         <v>null</v>
@@ -9966,6 +10224,9 @@
         <v>null</v>
       </c>
       <c r="AJ87" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK87" t="str">
         <v>null</v>
       </c>
     </row>
@@ -10037,7 +10298,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-none</v>
       </c>
       <c r="W88" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X88" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-none-adres|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-none-naam</v>
@@ -10076,6 +10337,9 @@
         <v>null</v>
       </c>
       <c r="AJ88" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK88" t="str">
         <v>null</v>
       </c>
     </row>
@@ -10147,7 +10411,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-none-adres</v>
       </c>
       <c r="W89" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X89" t="str">
         <v>null</v>
@@ -10186,6 +10450,9 @@
         <v>null</v>
       </c>
       <c r="AJ89" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK89" t="str">
         <v>null</v>
       </c>
     </row>
@@ -10257,7 +10524,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-none-naam</v>
       </c>
       <c r="W90" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X90" t="str">
         <v>null</v>
@@ -10296,6 +10563,9 @@
         <v>null</v>
       </c>
       <c r="AJ90" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK90" t="str">
         <v>null</v>
       </c>
     </row>
@@ -10367,7 +10637,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-werf</v>
       </c>
       <c r="W91" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X91" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-werf-naam</v>
@@ -10406,6 +10676,9 @@
         <v>null</v>
       </c>
       <c r="AJ91" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK91" t="str">
         <v>null</v>
       </c>
     </row>
@@ -10477,7 +10750,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-werf-naam</v>
       </c>
       <c r="W92" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X92" t="str">
         <v>null</v>
@@ -10516,6 +10789,9 @@
         <v>null</v>
       </c>
       <c r="AJ92" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK92" t="str">
         <v>null</v>
       </c>
     </row>
@@ -10628,6 +10904,9 @@
       <c r="AJ93" t="str">
         <v>null</v>
       </c>
+      <c r="AK93" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
@@ -10697,7 +10976,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/grondstof</v>
       </c>
       <c r="W94" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X94" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-be|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-buitenland|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-none|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-werf|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/grondstof_bestemming_type|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/grondstof_opmerking|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/grondstof_hoeveelheid|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/grondstof_materiaalcode|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/grondstof_omschrijving|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/grondstof_toepassingswijze</v>
@@ -10715,7 +10994,7 @@
         <v>null</v>
       </c>
       <c r="AC94" t="str">
-        <v>http://www.w3.org/ns/sosa/ObservationCollection</v>
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Observatie</v>
       </c>
       <c r="AD94" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/rie-iepr/true</v>
@@ -10736,6 +11015,9 @@
         <v>null</v>
       </c>
       <c r="AJ94" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK94" t="str">
         <v>null</v>
       </c>
     </row>
@@ -10807,7 +11089,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/grondstof_bestemming_type</v>
       </c>
       <c r="W95" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X95" t="str">
         <v>null</v>
@@ -10825,7 +11107,7 @@
         <v>null</v>
       </c>
       <c r="AC95" t="str">
-        <v>null</v>
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Resultaat</v>
       </c>
       <c r="AD95" t="str">
         <v>null</v>
@@ -10846,6 +11128,9 @@
         <v>null</v>
       </c>
       <c r="AJ95" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK95" t="str">
         <v>null</v>
       </c>
     </row>
@@ -10917,7 +11202,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/grondstof_hoeveelheid</v>
       </c>
       <c r="W96" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X96" t="str">
         <v>null</v>
@@ -10935,7 +11220,7 @@
         <v>null</v>
       </c>
       <c r="AC96" t="str">
-        <v>null</v>
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Resultaat</v>
       </c>
       <c r="AD96" t="str">
         <v>null</v>
@@ -10956,6 +11241,9 @@
         <v>null</v>
       </c>
       <c r="AJ96" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK96" t="str">
         <v>null</v>
       </c>
     </row>
@@ -11027,7 +11315,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/grondstof_materiaalcode</v>
       </c>
       <c r="W97" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X97" t="str">
         <v>null</v>
@@ -11045,7 +11333,7 @@
         <v>null</v>
       </c>
       <c r="AC97" t="str">
-        <v>null</v>
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Resultaat</v>
       </c>
       <c r="AD97" t="str">
         <v>null</v>
@@ -11066,6 +11354,9 @@
         <v>null</v>
       </c>
       <c r="AJ97" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK97" t="str">
         <v>null</v>
       </c>
     </row>
@@ -11137,7 +11428,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/grondstof_omschrijving</v>
       </c>
       <c r="W98" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X98" t="str">
         <v>null</v>
@@ -11155,7 +11446,7 @@
         <v>null</v>
       </c>
       <c r="AC98" t="str">
-        <v>null</v>
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Resultaat</v>
       </c>
       <c r="AD98" t="str">
         <v>null</v>
@@ -11176,6 +11467,9 @@
         <v>null</v>
       </c>
       <c r="AJ98" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK98" t="str">
         <v>null</v>
       </c>
     </row>
@@ -11247,7 +11541,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/grondstof_opmerking</v>
       </c>
       <c r="W99" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X99" t="str">
         <v>null</v>
@@ -11265,7 +11559,7 @@
         <v>null</v>
       </c>
       <c r="AC99" t="str">
-        <v>null</v>
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Resultaat</v>
       </c>
       <c r="AD99" t="str">
         <v>null</v>
@@ -11286,6 +11580,9 @@
         <v>null</v>
       </c>
       <c r="AJ99" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK99" t="str">
         <v>null</v>
       </c>
     </row>
@@ -11357,7 +11654,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/grondstof_toepassingswijze</v>
       </c>
       <c r="W100" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X100" t="str">
         <v>null</v>
@@ -11375,7 +11672,7 @@
         <v>null</v>
       </c>
       <c r="AC100" t="str">
-        <v>null</v>
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Resultaat</v>
       </c>
       <c r="AD100" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_toepassingwijze</v>
@@ -11396,6 +11693,9 @@
         <v>null</v>
       </c>
       <c r="AJ100" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK100" t="str">
         <v>null</v>
       </c>
     </row>
@@ -11467,7 +11767,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/begintoestand</v>
       </c>
       <c r="W101" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X101" t="str">
         <v>null</v>
@@ -11485,7 +11785,7 @@
         <v>null</v>
       </c>
       <c r="AC101" t="str">
-        <v>null</v>
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Observatie</v>
       </c>
       <c r="AD101" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/rie-iepr/NaN</v>
@@ -11506,6 +11806,9 @@
         <v>null</v>
       </c>
       <c r="AJ101" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK101" t="str">
         <v>null</v>
       </c>
     </row>
@@ -11577,7 +11880,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/datum</v>
       </c>
       <c r="W102" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X102" t="str">
         <v>null</v>
@@ -11616,6 +11919,9 @@
         <v>null</v>
       </c>
       <c r="AJ102" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK102" t="str">
         <v>null</v>
       </c>
     </row>
@@ -11687,7 +11993,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/diepte</v>
       </c>
       <c r="W103" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X103" t="str">
         <v>null</v>
@@ -11726,6 +12032,9 @@
         <v>null</v>
       </c>
       <c r="AJ103" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK103" t="str">
         <v>null</v>
       </c>
     </row>
@@ -11797,7 +12106,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/duur-stil</v>
       </c>
       <c r="W104" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X104" t="str">
         <v>null</v>
@@ -11836,6 +12145,9 @@
         <v>null</v>
       </c>
       <c r="AJ104" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK104" t="str">
         <v>null</v>
       </c>
     </row>
@@ -11907,7 +12219,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/eindtoestand</v>
       </c>
       <c r="W105" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X105" t="str">
         <v>null</v>
@@ -11925,7 +12237,7 @@
         <v>null</v>
       </c>
       <c r="AC105" t="str">
-        <v>null</v>
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Observatie</v>
       </c>
       <c r="AD105" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/rie-iepr/NaN</v>
@@ -11946,6 +12258,9 @@
         <v>null</v>
       </c>
       <c r="AJ105" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK105" t="str">
         <v>null</v>
       </c>
     </row>
@@ -12017,7 +12332,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting</v>
       </c>
       <c r="W106" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X106" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-bemonsteringsinstrument|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-labo|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-datum|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting_feature|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-diepte|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-referentiepunt|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-monsternummer|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-parameter|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-techniek</v>
@@ -12035,7 +12350,7 @@
         <v>null</v>
       </c>
       <c r="AC106" t="str">
-        <v>null</v>
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#ObservatieVerzameling</v>
       </c>
       <c r="AD106" t="str">
         <v>null</v>
@@ -12056,6 +12371,9 @@
         <v>null</v>
       </c>
       <c r="AJ106" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK106" t="str">
         <v>null</v>
       </c>
     </row>
@@ -12127,7 +12445,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-bemonsteringsinstrument</v>
       </c>
       <c r="W107" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X107" t="str">
         <v>null</v>
@@ -12166,6 +12484,9 @@
         <v>null</v>
       </c>
       <c r="AJ107" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK107" t="str">
         <v>null</v>
       </c>
     </row>
@@ -12237,7 +12558,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-datum</v>
       </c>
       <c r="W108" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X108" t="str">
         <v>null</v>
@@ -12276,6 +12597,9 @@
         <v>null</v>
       </c>
       <c r="AJ108" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK108" t="str">
         <v>null</v>
       </c>
     </row>
@@ -12347,7 +12671,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-diepte</v>
       </c>
       <c r="W109" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X109" t="str">
         <v>null</v>
@@ -12365,7 +12689,7 @@
         <v>null</v>
       </c>
       <c r="AC109" t="str">
-        <v>null</v>
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Observatie</v>
       </c>
       <c r="AD109" t="str">
         <v>null</v>
@@ -12386,6 +12710,9 @@
         <v>null</v>
       </c>
       <c r="AJ109" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK109" t="str">
         <v>null</v>
       </c>
     </row>
@@ -12457,7 +12784,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-labo</v>
       </c>
       <c r="W110" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X110" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-labo-naam</v>
@@ -12496,6 +12823,9 @@
         <v>null</v>
       </c>
       <c r="AJ110" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK110" t="str">
         <v>null</v>
       </c>
     </row>
@@ -12567,7 +12897,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-labo-naam</v>
       </c>
       <c r="W111" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X111" t="str">
         <v>null</v>
@@ -12606,6 +12936,9 @@
         <v>null</v>
       </c>
       <c r="AJ111" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK111" t="str">
         <v>null</v>
       </c>
     </row>
@@ -12677,7 +13010,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-monsternummer</v>
       </c>
       <c r="W112" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X112" t="str">
         <v>null</v>
@@ -12716,6 +13049,9 @@
         <v>null</v>
       </c>
       <c r="AJ112" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK112" t="str">
         <v>null</v>
       </c>
     </row>
@@ -12787,7 +13123,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-parameter</v>
       </c>
       <c r="W113" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X113" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-parameter-datum|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-parameter-parameter|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-parameter-limiet|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-parameter-meetwaarde|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-parameter-methode</v>
@@ -12826,6 +13162,9 @@
         <v>null</v>
       </c>
       <c r="AJ113" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK113" t="str">
         <v>null</v>
       </c>
     </row>
@@ -12897,7 +13236,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-parameter-datum</v>
       </c>
       <c r="W114" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X114" t="str">
         <v>null</v>
@@ -12936,6 +13275,9 @@
         <v>null</v>
       </c>
       <c r="AJ114" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK114" t="str">
         <v>null</v>
       </c>
     </row>
@@ -13007,7 +13349,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-parameter-limiet</v>
       </c>
       <c r="W115" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X115" t="str">
         <v>null</v>
@@ -13046,6 +13388,9 @@
         <v>null</v>
       </c>
       <c r="AJ115" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK115" t="str">
         <v>null</v>
       </c>
     </row>
@@ -13117,7 +13462,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-parameter-meetwaarde</v>
       </c>
       <c r="W116" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X116" t="str">
         <v>null</v>
@@ -13135,7 +13480,7 @@
         <v>null</v>
       </c>
       <c r="AC116" t="str">
-        <v>null</v>
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Observatie</v>
       </c>
       <c r="AD116" t="str">
         <v>null</v>
@@ -13156,6 +13501,9 @@
         <v>null</v>
       </c>
       <c r="AJ116" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK116" t="str">
         <v>null</v>
       </c>
     </row>
@@ -13227,7 +13575,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-parameter-methode</v>
       </c>
       <c r="W117" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X117" t="str">
         <v>null</v>
@@ -13266,6 +13614,9 @@
         <v>null</v>
       </c>
       <c r="AJ117" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK117" t="str">
         <v>null</v>
       </c>
     </row>
@@ -13337,7 +13688,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-parameter-parameter</v>
       </c>
       <c r="W118" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X118" t="str">
         <v>null</v>
@@ -13376,6 +13727,9 @@
         <v>null</v>
       </c>
       <c r="AJ118" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK118" t="str">
         <v>null</v>
       </c>
     </row>
@@ -13447,7 +13801,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-referentiepunt</v>
       </c>
       <c r="W119" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X119" t="str">
         <v>null</v>
@@ -13486,6 +13840,9 @@
         <v>null</v>
       </c>
       <c r="AJ119" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK119" t="str">
         <v>null</v>
       </c>
     </row>
@@ -13557,7 +13914,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-techniek</v>
       </c>
       <c r="W120" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X120" t="str">
         <v>null</v>
@@ -13596,6 +13953,9 @@
         <v>null</v>
       </c>
       <c r="AJ120" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK120" t="str">
         <v>null</v>
       </c>
     </row>
@@ -13667,7 +14027,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting_feature</v>
       </c>
       <c r="W121" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X121" t="str">
         <v>null</v>
@@ -13706,6 +14066,9 @@
         <v>null</v>
       </c>
       <c r="AJ121" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK121" t="str">
         <v>null</v>
       </c>
     </row>
@@ -13777,7 +14140,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/onttrekking</v>
       </c>
       <c r="W122" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X122" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/begintoestand|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/volume|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/eindtoestand|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/onttrekking_feature|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/periode|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/type-debiet</v>
@@ -13795,7 +14158,7 @@
         <v>null</v>
       </c>
       <c r="AC122" t="str">
-        <v>null</v>
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#ObservatieVerzameling</v>
       </c>
       <c r="AD122" t="str">
         <v>null</v>
@@ -13816,6 +14179,9 @@
         <v>null</v>
       </c>
       <c r="AJ122" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK122" t="str">
         <v>null</v>
       </c>
     </row>
@@ -13887,7 +14253,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/onttrekking_feature</v>
       </c>
       <c r="W123" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X123" t="str">
         <v>null</v>
@@ -13923,9 +14289,12 @@
         <v>null</v>
       </c>
       <c r="AI123" t="str">
-        <v>null</v>
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Onttrekking</v>
       </c>
       <c r="AJ123" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK123" t="str">
         <v>null</v>
       </c>
     </row>
@@ -13997,7 +14366,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/peilmethode</v>
       </c>
       <c r="W124" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X124" t="str">
         <v>null</v>
@@ -14036,6 +14405,9 @@
         <v>null</v>
       </c>
       <c r="AJ124" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK124" t="str">
         <v>null</v>
       </c>
     </row>
@@ -14107,7 +14479,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/peilmeting</v>
       </c>
       <c r="W125" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X125" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/datum|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/peilmeting_feature|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/diepte|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/referentiepunt|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/duur-stil|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/pomptoestand|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/peilmethode|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/volume-rust|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/volume-werking</v>
@@ -14125,7 +14497,7 @@
         <v>null</v>
       </c>
       <c r="AC125" t="str">
-        <v>null</v>
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#ObservatieVerzameling</v>
       </c>
       <c r="AD125" t="str">
         <v>null</v>
@@ -14146,6 +14518,9 @@
         <v>null</v>
       </c>
       <c r="AJ125" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK125" t="str">
         <v>null</v>
       </c>
     </row>
@@ -14217,7 +14592,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/peilmeting_feature</v>
       </c>
       <c r="W126" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X126" t="str">
         <v>null</v>
@@ -14256,6 +14631,9 @@
         <v>null</v>
       </c>
       <c r="AJ126" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK126" t="str">
         <v>null</v>
       </c>
     </row>
@@ -14327,7 +14705,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/periode</v>
       </c>
       <c r="W127" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X127" t="str">
         <v>null</v>
@@ -14366,6 +14744,9 @@
         <v>null</v>
       </c>
       <c r="AJ127" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK127" t="str">
         <v>null</v>
       </c>
     </row>
@@ -14437,7 +14818,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/pomptoestand</v>
       </c>
       <c r="W128" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X128" t="str">
         <v>null</v>
@@ -14476,6 +14857,9 @@
         <v>null</v>
       </c>
       <c r="AJ128" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK128" t="str">
         <v>null</v>
       </c>
     </row>
@@ -14547,7 +14931,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/referentiepunt</v>
       </c>
       <c r="W129" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X129" t="str">
         <v>null</v>
@@ -14586,6 +14970,9 @@
         <v>null</v>
       </c>
       <c r="AJ129" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK129" t="str">
         <v>null</v>
       </c>
     </row>
@@ -14657,7 +15044,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/type-debiet</v>
       </c>
       <c r="W130" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X130" t="str">
         <v>null</v>
@@ -14696,6 +15083,9 @@
         <v>null</v>
       </c>
       <c r="AJ130" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK130" t="str">
         <v>null</v>
       </c>
     </row>
@@ -14767,7 +15157,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/volume</v>
       </c>
       <c r="W131" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X131" t="str">
         <v>null</v>
@@ -14785,7 +15175,7 @@
         <v>null</v>
       </c>
       <c r="AC131" t="str">
-        <v>null</v>
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Observatie</v>
       </c>
       <c r="AD131" t="str">
         <v>null</v>
@@ -14806,6 +15196,9 @@
         <v>null</v>
       </c>
       <c r="AJ131" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK131" t="str">
         <v>null</v>
       </c>
     </row>
@@ -14877,7 +15270,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/volume-rust</v>
       </c>
       <c r="W132" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X132" t="str">
         <v>null</v>
@@ -14916,6 +15309,9 @@
         <v>null</v>
       </c>
       <c r="AJ132" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK132" t="str">
         <v>null</v>
       </c>
     </row>
@@ -14987,7 +15383,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/volume-werking</v>
       </c>
       <c r="W133" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X133" t="str">
         <v>null</v>
@@ -15026,6 +15422,9 @@
         <v>null</v>
       </c>
       <c r="AJ133" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK133" t="str">
         <v>null</v>
       </c>
     </row>
@@ -15097,7 +15496,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/afvalproduct</v>
       </c>
       <c r="W134" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X134" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/afvalproduct_aard|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/afvalproduct_hoeveelheid|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/afvalproduct_naam</v>
@@ -15115,7 +15514,7 @@
         <v>null</v>
       </c>
       <c r="AC134" t="str">
-        <v>http://www.w3.org/ns/sosa/ObservationCollection</v>
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Observatie</v>
       </c>
       <c r="AD134" t="str">
         <v>null</v>
@@ -15133,9 +15532,12 @@
         <v>null</v>
       </c>
       <c r="AI134" t="str">
-        <v>null</v>
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Verbruik</v>
       </c>
       <c r="AJ134" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK134" t="str">
         <v>null</v>
       </c>
     </row>
@@ -15207,7 +15609,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/afvalproduct_aard</v>
       </c>
       <c r="W135" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X135" t="str">
         <v>null</v>
@@ -15225,7 +15627,7 @@
         <v>null</v>
       </c>
       <c r="AC135" t="str">
-        <v>http://www.w3.org/ns/sosa/Result</v>
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Resultaat</v>
       </c>
       <c r="AD135" t="str">
         <v>null</v>
@@ -15246,6 +15648,9 @@
         <v>null</v>
       </c>
       <c r="AJ135" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK135" t="str">
         <v>null</v>
       </c>
     </row>
@@ -15317,7 +15722,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/afvalproduct_hoeveelheid</v>
       </c>
       <c r="W136" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X136" t="str">
         <v>null</v>
@@ -15335,7 +15740,7 @@
         <v>null</v>
       </c>
       <c r="AC136" t="str">
-        <v>http://www.w3.org/ns/sosa/Result</v>
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Resultaat</v>
       </c>
       <c r="AD136" t="str">
         <v>null</v>
@@ -15356,6 +15761,9 @@
         <v>null</v>
       </c>
       <c r="AJ136" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK136" t="str">
         <v>null</v>
       </c>
     </row>
@@ -15427,7 +15835,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/afvalproduct_naam</v>
       </c>
       <c r="W137" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X137" t="str">
         <v>null</v>
@@ -15445,7 +15853,7 @@
         <v>null</v>
       </c>
       <c r="AC137" t="str">
-        <v>null</v>
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Resultaat</v>
       </c>
       <c r="AD137" t="str">
         <v>null</v>
@@ -15466,6 +15874,9 @@
         <v>null</v>
       </c>
       <c r="AJ137" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK137" t="str">
         <v>null</v>
       </c>
     </row>
@@ -15537,7 +15948,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/brandstof</v>
       </c>
       <c r="W138" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X138" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/brandstof_as|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/brandstof_naam|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/brandstof_s|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/brandstof_verbruik</v>
@@ -15555,7 +15966,7 @@
         <v>null</v>
       </c>
       <c r="AC138" t="str">
-        <v>http://www.w3.org/ns/sosa/ObservationCollection</v>
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#ObservatieVerzameling</v>
       </c>
       <c r="AD138" t="str">
         <v>null</v>
@@ -15573,9 +15984,12 @@
         <v>null</v>
       </c>
       <c r="AI138" t="str">
-        <v>null</v>
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Verbruik</v>
       </c>
       <c r="AJ138" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK138" t="str">
         <v>null</v>
       </c>
     </row>
@@ -15647,7 +16061,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/brandstof_as</v>
       </c>
       <c r="W139" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X139" t="str">
         <v>null</v>
@@ -15665,7 +16079,7 @@
         <v>null</v>
       </c>
       <c r="AC139" t="str">
-        <v>http://www.w3.org/ns/sosa/Result</v>
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Observatie</v>
       </c>
       <c r="AD139" t="str">
         <v>null</v>
@@ -15686,6 +16100,9 @@
         <v>null</v>
       </c>
       <c r="AJ139" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK139" t="str">
         <v>null</v>
       </c>
     </row>
@@ -15757,7 +16174,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/brandstof_naam</v>
       </c>
       <c r="W140" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X140" t="str">
         <v>null</v>
@@ -15796,6 +16213,9 @@
         <v>null</v>
       </c>
       <c r="AJ140" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK140" t="str">
         <v>null</v>
       </c>
     </row>
@@ -15867,7 +16287,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/brandstof_s</v>
       </c>
       <c r="W141" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X141" t="str">
         <v>null</v>
@@ -15885,7 +16305,7 @@
         <v>null</v>
       </c>
       <c r="AC141" t="str">
-        <v>http://www.w3.org/ns/sosa/Result</v>
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Observatie</v>
       </c>
       <c r="AD141" t="str">
         <v>null</v>
@@ -15906,6 +16326,9 @@
         <v>null</v>
       </c>
       <c r="AJ141" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK141" t="str">
         <v>null</v>
       </c>
     </row>
@@ -15977,7 +16400,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/brandstof_verbruik</v>
       </c>
       <c r="W142" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X142" t="str">
         <v>null</v>
@@ -15995,7 +16418,7 @@
         <v>null</v>
       </c>
       <c r="AC142" t="str">
-        <v>null</v>
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Observatie</v>
       </c>
       <c r="AD142" t="str">
         <v>null</v>
@@ -16016,6 +16439,9 @@
         <v>null</v>
       </c>
       <c r="AJ142" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK142" t="str">
         <v>null</v>
       </c>
     </row>
@@ -16087,7 +16513,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie</v>
       </c>
       <c r="W143" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X143" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie_luchtoverschot|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie_parameter|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie_temperatuur|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie_vochtgehalte|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie_zuurstofgehalte|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissieduur|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissieperiode|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissieritme|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissietoestand|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissietype</v>
@@ -16105,27 +16531,30 @@
         <v>null</v>
       </c>
       <c r="AC143" t="str">
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#ObservatieVerzameling</v>
+      </c>
+      <c r="AD143" t="str">
+        <v>null</v>
+      </c>
+      <c r="AE143" t="str">
+        <v>null</v>
+      </c>
+      <c r="AF143" t="str">
+        <v>null</v>
+      </c>
+      <c r="AG143" t="str">
+        <v>null</v>
+      </c>
+      <c r="AH143" t="str">
+        <v>null</v>
+      </c>
+      <c r="AI143" t="str">
         <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Emissie</v>
       </c>
-      <c r="AD143" t="str">
-        <v>null</v>
-      </c>
-      <c r="AE143" t="str">
-        <v>null</v>
-      </c>
-      <c r="AF143" t="str">
-        <v>null</v>
-      </c>
-      <c r="AG143" t="str">
-        <v>null</v>
-      </c>
-      <c r="AH143" t="str">
-        <v>null</v>
-      </c>
-      <c r="AI143" t="str">
-        <v>null</v>
-      </c>
       <c r="AJ143" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK143" t="str">
         <v>null</v>
       </c>
     </row>
@@ -16197,7 +16626,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie_luchtoverschot</v>
       </c>
       <c r="W144" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X144" t="str">
         <v>null</v>
@@ -16215,7 +16644,7 @@
         <v>null</v>
       </c>
       <c r="AC144" t="str">
-        <v>null</v>
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Observatie</v>
       </c>
       <c r="AD144" t="str">
         <v>null</v>
@@ -16236,6 +16665,9 @@
         <v>null</v>
       </c>
       <c r="AJ144" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK144" t="str">
         <v>null</v>
       </c>
     </row>
@@ -16307,7 +16739,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie_parameter</v>
       </c>
       <c r="W145" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X145" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie_parameter_massastroom|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie_parameter_meetfrequentie|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie_parameter_parameter|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie_parameter_standaardafwijking</v>
@@ -16346,6 +16778,9 @@
         <v>null</v>
       </c>
       <c r="AJ145" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK145" t="str">
         <v>null</v>
       </c>
     </row>
@@ -16417,7 +16852,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie_parameter_massastroom</v>
       </c>
       <c r="W146" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X146" t="str">
         <v>null</v>
@@ -16456,6 +16891,9 @@
         <v>null</v>
       </c>
       <c r="AJ146" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK146" t="str">
         <v>null</v>
       </c>
     </row>
@@ -16527,7 +16965,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie_parameter_meetfrequentie</v>
       </c>
       <c r="W147" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X147" t="str">
         <v>null</v>
@@ -16566,6 +17004,9 @@
         <v>null</v>
       </c>
       <c r="AJ147" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK147" t="str">
         <v>null</v>
       </c>
     </row>
@@ -16637,7 +17078,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie_parameter_parameter</v>
       </c>
       <c r="W148" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X148" t="str">
         <v>null</v>
@@ -16676,6 +17117,9 @@
         <v>null</v>
       </c>
       <c r="AJ148" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK148" t="str">
         <v>null</v>
       </c>
     </row>
@@ -16747,7 +17191,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie_parameter_standaardafwijking</v>
       </c>
       <c r="W149" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X149" t="str">
         <v>null</v>
@@ -16786,6 +17230,9 @@
         <v>null</v>
       </c>
       <c r="AJ149" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK149" t="str">
         <v>null</v>
       </c>
     </row>
@@ -16857,7 +17304,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie_temperatuur</v>
       </c>
       <c r="W150" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X150" t="str">
         <v>null</v>
@@ -16875,7 +17322,7 @@
         <v>null</v>
       </c>
       <c r="AC150" t="str">
-        <v>null</v>
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Observatie</v>
       </c>
       <c r="AD150" t="str">
         <v>null</v>
@@ -16896,6 +17343,9 @@
         <v>null</v>
       </c>
       <c r="AJ150" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK150" t="str">
         <v>null</v>
       </c>
     </row>
@@ -16967,7 +17417,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie_vochtgehalte</v>
       </c>
       <c r="W151" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X151" t="str">
         <v>null</v>
@@ -16985,7 +17435,7 @@
         <v>null</v>
       </c>
       <c r="AC151" t="str">
-        <v>null</v>
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Observatie</v>
       </c>
       <c r="AD151" t="str">
         <v>null</v>
@@ -17006,6 +17456,9 @@
         <v>null</v>
       </c>
       <c r="AJ151" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK151" t="str">
         <v>null</v>
       </c>
     </row>
@@ -17077,7 +17530,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie_zuurstofgehalte</v>
       </c>
       <c r="W152" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X152" t="str">
         <v>null</v>
@@ -17095,7 +17548,7 @@
         <v>null</v>
       </c>
       <c r="AC152" t="str">
-        <v>null</v>
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Observatie</v>
       </c>
       <c r="AD152" t="str">
         <v>null</v>
@@ -17116,6 +17569,9 @@
         <v>null</v>
       </c>
       <c r="AJ152" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK152" t="str">
         <v>null</v>
       </c>
     </row>
@@ -17187,7 +17643,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissieduur</v>
       </c>
       <c r="W153" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X153" t="str">
         <v>null</v>
@@ -17226,6 +17682,9 @@
         <v>null</v>
       </c>
       <c r="AJ153" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK153" t="str">
         <v>null</v>
       </c>
     </row>
@@ -17297,7 +17756,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissieperiode</v>
       </c>
       <c r="W154" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X154" t="str">
         <v>null</v>
@@ -17336,6 +17795,9 @@
         <v>null</v>
       </c>
       <c r="AJ154" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK154" t="str">
         <v>null</v>
       </c>
     </row>
@@ -17407,7 +17869,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissieritme</v>
       </c>
       <c r="W155" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X155" t="str">
         <v>null</v>
@@ -17446,6 +17908,9 @@
         <v>null</v>
       </c>
       <c r="AJ155" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK155" t="str">
         <v>null</v>
       </c>
     </row>
@@ -17517,7 +17982,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissietoestand</v>
       </c>
       <c r="W156" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X156" t="str">
         <v>null</v>
@@ -17556,6 +18021,9 @@
         <v>null</v>
       </c>
       <c r="AJ156" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK156" t="str">
         <v>null</v>
       </c>
     </row>
@@ -17627,7 +18095,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissietype</v>
       </c>
       <c r="W157" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X157" t="str">
         <v>null</v>
@@ -17666,6 +18134,9 @@
         <v>null</v>
       </c>
       <c r="AJ157" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK157" t="str">
         <v>null</v>
       </c>
     </row>
@@ -17778,6 +18249,9 @@
       <c r="AJ158" t="str">
         <v>null</v>
       </c>
+      <c r="AK158" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
@@ -17888,6 +18362,9 @@
       <c r="AJ159" t="str">
         <v>null</v>
       </c>
+      <c r="AK159" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
@@ -17957,7 +18434,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/geproduceerde_stof</v>
       </c>
       <c r="W160" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X160" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/geproduceerde_stof_aard|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/geproduceerde_stof_hoeveelheid|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/geproduceerde_stof_naam</v>
@@ -17975,7 +18452,7 @@
         <v>null</v>
       </c>
       <c r="AC160" t="str">
-        <v>http://www.w3.org/ns/sosa/ObservationCollection</v>
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Observatie</v>
       </c>
       <c r="AD160" t="str">
         <v>null</v>
@@ -17993,9 +18470,12 @@
         <v>null</v>
       </c>
       <c r="AI160" t="str">
-        <v>null</v>
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Verbruik</v>
       </c>
       <c r="AJ160" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK160" t="str">
         <v>null</v>
       </c>
     </row>
@@ -18067,7 +18547,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/geproduceerde_stof_aard</v>
       </c>
       <c r="W161" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X161" t="str">
         <v>null</v>
@@ -18085,7 +18565,7 @@
         <v>null</v>
       </c>
       <c r="AC161" t="str">
-        <v>http://www.w3.org/ns/sosa/Result</v>
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Resultaat</v>
       </c>
       <c r="AD161" t="str">
         <v>null</v>
@@ -18106,6 +18586,9 @@
         <v>null</v>
       </c>
       <c r="AJ161" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK161" t="str">
         <v>null</v>
       </c>
     </row>
@@ -18177,7 +18660,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/geproduceerde_stof_hoeveelheid</v>
       </c>
       <c r="W162" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X162" t="str">
         <v>null</v>
@@ -18195,7 +18678,7 @@
         <v>null</v>
       </c>
       <c r="AC162" t="str">
-        <v>http://www.w3.org/ns/sosa/Result</v>
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Resultaat</v>
       </c>
       <c r="AD162" t="str">
         <v>null</v>
@@ -18216,6 +18699,9 @@
         <v>null</v>
       </c>
       <c r="AJ162" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK162" t="str">
         <v>null</v>
       </c>
     </row>
@@ -18287,7 +18773,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/geproduceerde_stof_naam</v>
       </c>
       <c r="W163" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X163" t="str">
         <v>null</v>
@@ -18305,7 +18791,7 @@
         <v>null</v>
       </c>
       <c r="AC163" t="str">
-        <v>null</v>
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Resultaat</v>
       </c>
       <c r="AD163" t="str">
         <v>null</v>
@@ -18326,6 +18812,9 @@
         <v>null</v>
       </c>
       <c r="AJ163" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK163" t="str">
         <v>null</v>
       </c>
     </row>
@@ -18397,7 +18886,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/verbruikte_stof</v>
       </c>
       <c r="W164" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X164" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/verbruikte_stof_aard|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/verbruikte_stof_hoeveelheid|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/verbruikte_stof_naam</v>
@@ -18415,7 +18904,7 @@
         <v>null</v>
       </c>
       <c r="AC164" t="str">
-        <v>http://www.w3.org/ns/sosa/ObservationCollection</v>
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Observatie</v>
       </c>
       <c r="AD164" t="str">
         <v>null</v>
@@ -18433,9 +18922,12 @@
         <v>null</v>
       </c>
       <c r="AI164" t="str">
-        <v>null</v>
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Verbruik</v>
       </c>
       <c r="AJ164" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK164" t="str">
         <v>null</v>
       </c>
     </row>
@@ -18507,7 +18999,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/verbruikte_stof_aard</v>
       </c>
       <c r="W165" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X165" t="str">
         <v>null</v>
@@ -18525,7 +19017,7 @@
         <v>null</v>
       </c>
       <c r="AC165" t="str">
-        <v>http://www.w3.org/ns/sosa/Result</v>
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Resultaat</v>
       </c>
       <c r="AD165" t="str">
         <v>null</v>
@@ -18546,6 +19038,9 @@
         <v>null</v>
       </c>
       <c r="AJ165" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK165" t="str">
         <v>null</v>
       </c>
     </row>
@@ -18617,7 +19112,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/verbruikte_stof_hoeveelheid</v>
       </c>
       <c r="W166" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X166" t="str">
         <v>null</v>
@@ -18635,7 +19130,7 @@
         <v>null</v>
       </c>
       <c r="AC166" t="str">
-        <v>http://www.w3.org/ns/sosa/Result</v>
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Resultaat</v>
       </c>
       <c r="AD166" t="str">
         <v>null</v>
@@ -18656,6 +19151,9 @@
         <v>null</v>
       </c>
       <c r="AJ166" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK166" t="str">
         <v>null</v>
       </c>
     </row>
@@ -18727,7 +19225,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/verbruikte_stof_naam</v>
       </c>
       <c r="W167" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X167" t="str">
         <v>null</v>
@@ -18745,7 +19243,7 @@
         <v>null</v>
       </c>
       <c r="AC167" t="str">
-        <v>http://www.w3.org/ns/sosa/Result</v>
+        <v>null</v>
       </c>
       <c r="AD167" t="str">
         <v>null</v>
@@ -18766,6 +19264,9 @@
         <v>null</v>
       </c>
       <c r="AJ167" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK167" t="str">
         <v>null</v>
       </c>
     </row>
@@ -18878,6 +19379,9 @@
       <c r="AJ168" t="str">
         <v>null</v>
       </c>
+      <c r="AK168" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
@@ -18988,6 +19492,9 @@
       <c r="AJ169" t="str">
         <v>null</v>
       </c>
+      <c r="AK169" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
@@ -19098,6 +19605,9 @@
       <c r="AJ170" t="str">
         <v>null</v>
       </c>
+      <c r="AK170" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
@@ -19208,6 +19718,9 @@
       <c r="AJ171" t="str">
         <v>null</v>
       </c>
+      <c r="AK171" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
@@ -19318,6 +19831,9 @@
       <c r="AJ172" t="str">
         <v>null</v>
       </c>
+      <c r="AK172" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
@@ -19428,6 +19944,9 @@
       <c r="AJ173" t="str">
         <v>null</v>
       </c>
+      <c r="AK173" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
@@ -19538,6 +20057,9 @@
       <c r="AJ174" t="str">
         <v>null</v>
       </c>
+      <c r="AK174" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
@@ -19648,6 +20170,9 @@
       <c r="AJ175" t="str">
         <v>null</v>
       </c>
+      <c r="AK175" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
@@ -19758,6 +20283,9 @@
       <c r="AJ176" t="str">
         <v>null</v>
       </c>
+      <c r="AK176" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
@@ -19868,6 +20396,9 @@
       <c r="AJ177" t="str">
         <v>null</v>
       </c>
+      <c r="AK177" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
@@ -19937,7 +20468,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-toestand-indicator/droog</v>
       </c>
       <c r="W178" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X178" t="str">
         <v>null</v>
@@ -19976,6 +20507,9 @@
         <v>null</v>
       </c>
       <c r="AJ178" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK178" t="str">
         <v>null</v>
       </c>
     </row>
@@ -20047,7 +20581,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-toestand-indicator/nat</v>
       </c>
       <c r="W179" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X179" t="str">
         <v>null</v>
@@ -20086,6 +20620,9 @@
         <v>null</v>
       </c>
       <c r="AJ179" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK179" t="str">
         <v>null</v>
       </c>
     </row>
@@ -20157,7 +20694,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/abnormale-lozing</v>
       </c>
       <c r="W180" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X180" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/abnormale-lozing-jaarvracht|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/abnormale-lozing-lozingsduur|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/abnormale-lozing-stof|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/abnormale-lozing-verklaring</v>
@@ -20175,7 +20712,7 @@
         <v>null</v>
       </c>
       <c r="AC180" t="str">
-        <v>http://www.w3.org/ns/sosa/ObservationCollection</v>
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Observatie</v>
       </c>
       <c r="AD180" t="str">
         <v>null</v>
@@ -20196,6 +20733,9 @@
         <v>null</v>
       </c>
       <c r="AJ180" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK180" t="str">
         <v>null</v>
       </c>
     </row>
@@ -20267,7 +20807,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/abnormale-lozing-jaarvracht</v>
       </c>
       <c r="W181" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X181" t="str">
         <v>null</v>
@@ -20306,6 +20846,9 @@
         <v>null</v>
       </c>
       <c r="AJ181" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK181" t="str">
         <v>null</v>
       </c>
     </row>
@@ -20377,7 +20920,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/abnormale-lozing-lozingsduur</v>
       </c>
       <c r="W182" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X182" t="str">
         <v>null</v>
@@ -20416,6 +20959,9 @@
         <v>null</v>
       </c>
       <c r="AJ182" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK182" t="str">
         <v>null</v>
       </c>
     </row>
@@ -20487,7 +21033,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/abnormale-lozing-stof</v>
       </c>
       <c r="W183" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X183" t="str">
         <v>null</v>
@@ -20526,6 +21072,9 @@
         <v>null</v>
       </c>
       <c r="AJ183" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK183" t="str">
         <v>null</v>
       </c>
     </row>
@@ -20597,7 +21146,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/abnormale-lozing-verklaring</v>
       </c>
       <c r="W184" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X184" t="str">
         <v>null</v>
@@ -20636,6 +21185,9 @@
         <v>null</v>
       </c>
       <c r="AJ184" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK184" t="str">
         <v>null</v>
       </c>
     </row>
@@ -20748,6 +21300,9 @@
       <c r="AJ185" t="str">
         <v>null</v>
       </c>
+      <c r="AK185" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
@@ -20817,7 +21372,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing</v>
       </c>
       <c r="W186" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X186" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing-bepalingsmethode|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing-jaarvracht|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing-bepalingsmethodeclassificatie|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing-concentratie|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing-meetfrequentie|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing-dagen|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing-debiet|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing-stof</v>
@@ -20835,7 +21390,7 @@
         <v>null</v>
       </c>
       <c r="AC186" t="str">
-        <v>http://www.w3.org/ns/sosa/ObservationCollection</v>
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#ObservatieVerzameling</v>
       </c>
       <c r="AD186" t="str">
         <v>null</v>
@@ -20853,9 +21408,12 @@
         <v>null</v>
       </c>
       <c r="AI186" t="str">
-        <v>null</v>
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Emissie</v>
       </c>
       <c r="AJ186" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK186" t="str">
         <v>null</v>
       </c>
     </row>
@@ -20927,7 +21485,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing-bepalingsmethode</v>
       </c>
       <c r="W187" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X187" t="str">
         <v>null</v>
@@ -20966,6 +21524,9 @@
         <v>null</v>
       </c>
       <c r="AJ187" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK187" t="str">
         <v>null</v>
       </c>
     </row>
@@ -21037,7 +21598,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing-bepalingsmethodeclassificatie</v>
       </c>
       <c r="W188" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X188" t="str">
         <v>null</v>
@@ -21076,6 +21637,9 @@
         <v>null</v>
       </c>
       <c r="AJ188" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK188" t="str">
         <v>null</v>
       </c>
     </row>
@@ -21147,7 +21711,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing-concentratie</v>
       </c>
       <c r="W189" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X189" t="str">
         <v>null</v>
@@ -21165,7 +21729,7 @@
         <v>null</v>
       </c>
       <c r="AC189" t="str">
-        <v>null</v>
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Observatie</v>
       </c>
       <c r="AD189" t="str">
         <v>null</v>
@@ -21186,6 +21750,9 @@
         <v>null</v>
       </c>
       <c r="AJ189" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK189" t="str">
         <v>null</v>
       </c>
     </row>
@@ -21257,7 +21824,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing-dagen</v>
       </c>
       <c r="W190" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X190" t="str">
         <v>null</v>
@@ -21296,6 +21863,9 @@
         <v>null</v>
       </c>
       <c r="AJ190" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK190" t="str">
         <v>null</v>
       </c>
     </row>
@@ -21367,7 +21937,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing-debiet</v>
       </c>
       <c r="W191" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X191" t="str">
         <v>null</v>
@@ -21406,6 +21976,9 @@
         <v>null</v>
       </c>
       <c r="AJ191" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK191" t="str">
         <v>null</v>
       </c>
     </row>
@@ -21477,7 +22050,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing-jaarvracht</v>
       </c>
       <c r="W192" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X192" t="str">
         <v>null</v>
@@ -21495,7 +22068,7 @@
         <v>null</v>
       </c>
       <c r="AC192" t="str">
-        <v>null</v>
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Observatie</v>
       </c>
       <c r="AD192" t="str">
         <v>null</v>
@@ -21516,6 +22089,9 @@
         <v>null</v>
       </c>
       <c r="AJ192" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK192" t="str">
         <v>null</v>
       </c>
     </row>
@@ -21548,7 +22124,7 @@
         <v>null</v>
       </c>
       <c r="J193" t="str">
-        <v>http://TODO</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_zelfcontrole_meetfrequentie</v>
       </c>
       <c r="K193" t="str">
         <v>null</v>
@@ -21587,7 +22163,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing-meetfrequentie</v>
       </c>
       <c r="W193" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X193" t="str">
         <v>null</v>
@@ -21626,6 +22202,9 @@
         <v>null</v>
       </c>
       <c r="AJ193" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK193" t="str">
         <v>null</v>
       </c>
     </row>
@@ -21697,7 +22276,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing-stof</v>
       </c>
       <c r="W194" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X194" t="str">
         <v>null</v>
@@ -21715,7 +22294,7 @@
         <v>null</v>
       </c>
       <c r="AC194" t="str">
-        <v>http://www.w3.org/ns/sosa/Observation</v>
+        <v>null</v>
       </c>
       <c r="AD194" t="str">
         <v>null</v>
@@ -21736,6 +22315,9 @@
         <v>null</v>
       </c>
       <c r="AJ194" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK194" t="str">
         <v>null</v>
       </c>
     </row>
@@ -21807,7 +22389,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/datum</v>
       </c>
       <c r="W195" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X195" t="str">
         <v>null</v>
@@ -21846,6 +22428,9 @@
         <v>null</v>
       </c>
       <c r="AJ195" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK195" t="str">
         <v>null</v>
       </c>
     </row>
@@ -21958,6 +22543,9 @@
       <c r="AJ196" t="str">
         <v>null</v>
       </c>
+      <c r="AK196" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
@@ -22027,7 +22615,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/labo</v>
       </c>
       <c r="W197" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X197" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/labo-id|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/labo-naam</v>
@@ -22045,7 +22633,7 @@
         <v>null</v>
       </c>
       <c r="AC197" t="str">
-        <v>null</v>
+        <v>http://www.w3.org/ns/prov#Agent</v>
       </c>
       <c r="AD197" t="str">
         <v>null</v>
@@ -22066,6 +22654,9 @@
         <v>null</v>
       </c>
       <c r="AJ197" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK197" t="str">
         <v>null</v>
       </c>
     </row>
@@ -22137,7 +22728,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/labo-id</v>
       </c>
       <c r="W198" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X198" t="str">
         <v>null</v>
@@ -22176,6 +22767,9 @@
         <v>null</v>
       </c>
       <c r="AJ198" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK198" t="str">
         <v>null</v>
       </c>
     </row>
@@ -22247,7 +22841,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/labo-naam</v>
       </c>
       <c r="W199" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X199" t="str">
         <v>null</v>
@@ -22286,6 +22880,9 @@
         <v>null</v>
       </c>
       <c r="AJ199" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK199" t="str">
         <v>null</v>
       </c>
     </row>
@@ -22357,7 +22954,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/meting</v>
       </c>
       <c r="W200" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X200" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/datum|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/labo|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/parameter</v>
@@ -22375,7 +22972,7 @@
         <v>null</v>
       </c>
       <c r="AC200" t="str">
-        <v>null</v>
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Observatie</v>
       </c>
       <c r="AD200" t="str">
         <v>null</v>
@@ -22393,9 +22990,12 @@
         <v>null</v>
       </c>
       <c r="AI200" t="str">
-        <v>null</v>
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Emissie</v>
       </c>
       <c r="AJ200" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK200" t="str">
         <v>null</v>
       </c>
     </row>
@@ -22467,7 +23067,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/parameter</v>
       </c>
       <c r="W201" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X201" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/parameter-concentratie|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/parameter-parameter|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/parameter-meetfrequentie|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/parameter-meetonzekerheid|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/parameter-soort</v>
@@ -22506,6 +23106,9 @@
         <v>null</v>
       </c>
       <c r="AJ201" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK201" t="str">
         <v>null</v>
       </c>
     </row>
@@ -22577,7 +23180,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/parameter-concentratie</v>
       </c>
       <c r="W202" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X202" t="str">
         <v>null</v>
@@ -22616,6 +23219,9 @@
         <v>null</v>
       </c>
       <c r="AJ202" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK202" t="str">
         <v>null</v>
       </c>
     </row>
@@ -22687,7 +23293,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/parameter-meetfrequentie</v>
       </c>
       <c r="W203" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X203" t="str">
         <v>null</v>
@@ -22726,6 +23332,9 @@
         <v>null</v>
       </c>
       <c r="AJ203" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK203" t="str">
         <v>null</v>
       </c>
     </row>
@@ -22797,7 +23406,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/parameter-meetonzekerheid</v>
       </c>
       <c r="W204" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X204" t="str">
         <v>null</v>
@@ -22836,6 +23445,9 @@
         <v>null</v>
       </c>
       <c r="AJ204" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK204" t="str">
         <v>null</v>
       </c>
     </row>
@@ -22907,7 +23519,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/parameter-parameter</v>
       </c>
       <c r="W205" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X205" t="str">
         <v>null</v>
@@ -22946,6 +23558,9 @@
         <v>null</v>
       </c>
       <c r="AJ205" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK205" t="str">
         <v>null</v>
       </c>
     </row>
@@ -23017,7 +23632,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/parameter-soort</v>
       </c>
       <c r="W206" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X206" t="str">
         <v>null</v>
@@ -23056,6 +23671,9 @@
         <v>null</v>
       </c>
       <c r="AJ206" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK206" t="str">
         <v>null</v>
       </c>
     </row>
@@ -23127,7 +23745,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/datum</v>
       </c>
       <c r="W207" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X207" t="str">
         <v>null</v>
@@ -23166,6 +23784,9 @@
         <v>null</v>
       </c>
       <c r="AJ207" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK207" t="str">
         <v>null</v>
       </c>
     </row>
@@ -23278,6 +23899,9 @@
       <c r="AJ208" t="str">
         <v>null</v>
       </c>
+      <c r="AK208" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
@@ -23347,7 +23971,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/labo</v>
       </c>
       <c r="W209" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X209" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/labo-id|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/labo-naam</v>
@@ -23386,6 +24010,9 @@
         <v>null</v>
       </c>
       <c r="AJ209" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK209" t="str">
         <v>null</v>
       </c>
     </row>
@@ -23457,7 +24084,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/labo-id</v>
       </c>
       <c r="W210" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X210" t="str">
         <v>null</v>
@@ -23496,6 +24123,9 @@
         <v>null</v>
       </c>
       <c r="AJ210" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK210" t="str">
         <v>null</v>
       </c>
     </row>
@@ -23567,7 +24197,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/labo-naam</v>
       </c>
       <c r="W211" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X211" t="str">
         <v>null</v>
@@ -23606,6 +24236,9 @@
         <v>null</v>
       </c>
       <c r="AJ211" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK211" t="str">
         <v>null</v>
       </c>
     </row>
@@ -23677,7 +24310,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/meting</v>
       </c>
       <c r="W212" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X212" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/datum</v>
@@ -23716,6 +24349,9 @@
         <v>null</v>
       </c>
       <c r="AJ212" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK212" t="str">
         <v>null</v>
       </c>
     </row>
@@ -23787,7 +24423,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/parameter</v>
       </c>
       <c r="W213" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X213" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/parameter-concentratie|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/parameter-parameter|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/parameter-meetfrequentie|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/parameter-meetonzekerheid|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/parameter-soort</v>
@@ -23826,6 +24462,9 @@
         <v>null</v>
       </c>
       <c r="AJ213" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK213" t="str">
         <v>null</v>
       </c>
     </row>
@@ -23897,7 +24536,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/parameter-concentratie</v>
       </c>
       <c r="W214" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X214" t="str">
         <v>null</v>
@@ -23936,6 +24575,9 @@
         <v>null</v>
       </c>
       <c r="AJ214" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK214" t="str">
         <v>null</v>
       </c>
     </row>
@@ -24007,7 +24649,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/parameter-meetfrequentie</v>
       </c>
       <c r="W215" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X215" t="str">
         <v>null</v>
@@ -24046,6 +24688,9 @@
         <v>null</v>
       </c>
       <c r="AJ215" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK215" t="str">
         <v>null</v>
       </c>
     </row>
@@ -24117,7 +24762,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/parameter-meetonzekerheid</v>
       </c>
       <c r="W216" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X216" t="str">
         <v>null</v>
@@ -24156,6 +24801,9 @@
         <v>null</v>
       </c>
       <c r="AJ216" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK216" t="str">
         <v>null</v>
       </c>
     </row>
@@ -24227,7 +24875,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/parameter-parameter</v>
       </c>
       <c r="W217" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X217" t="str">
         <v>null</v>
@@ -24266,6 +24914,9 @@
         <v>null</v>
       </c>
       <c r="AJ217" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK217" t="str">
         <v>null</v>
       </c>
     </row>
@@ -24337,7 +24988,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/parameter-soort</v>
       </c>
       <c r="W218" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X218" t="str">
         <v>null</v>
@@ -24376,6 +25027,9 @@
         <v>null</v>
       </c>
       <c r="AJ218" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK218" t="str">
         <v>null</v>
       </c>
     </row>
@@ -24488,6 +25142,9 @@
       <c r="AJ219" t="str">
         <v>null</v>
       </c>
+      <c r="AK219" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
@@ -24598,6 +25255,9 @@
       <c r="AJ220" t="str">
         <v>null</v>
       </c>
+      <c r="AK220" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
@@ -24708,6 +25368,9 @@
       <c r="AJ221" t="str">
         <v>null</v>
       </c>
+      <c r="AK221" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
@@ -24818,6 +25481,9 @@
       <c r="AJ222" t="str">
         <v>null</v>
       </c>
+      <c r="AK222" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
@@ -24928,6 +25594,9 @@
       <c r="AJ223" t="str">
         <v>null</v>
       </c>
+      <c r="AK223" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
@@ -25038,6 +25707,9 @@
       <c r="AJ224" t="str">
         <v>null</v>
       </c>
+      <c r="AK224" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
@@ -25148,6 +25820,9 @@
       <c r="AJ225" t="str">
         <v>null</v>
       </c>
+      <c r="AK225" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
@@ -25258,31 +25933,34 @@
       <c r="AJ226" t="str">
         <v>null</v>
       </c>
+      <c r="AK226" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/thema-type/grondstoffen</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/definitief_uit_dienst</v>
       </c>
       <c r="B227" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C227" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/thema_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
       </c>
       <c r="D227" t="str">
-        <v>THEMA_GRONDSTOFFEN</v>
+        <v>DEFINITIEF_UIT_DIENST</v>
       </c>
       <c r="E227" t="str">
-        <v>Grondstoffen</v>
+        <v>Definitief uit dienst</v>
       </c>
       <c r="F227" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/thema_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
       </c>
       <c r="G227" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_grondstoffen</v>
+        <v>http://purl.org/adms/status/Withdrawn</v>
       </c>
       <c r="H227" t="str">
-        <v>null</v>
+        <v>http://www.w3.org/ns/adms#</v>
       </c>
       <c r="I227" t="str">
         <v>null</v>
@@ -25297,10 +25975,10 @@
         <v>null</v>
       </c>
       <c r="M227" t="str">
-        <v>null</v>
+        <v>De status definitief uit dienst geeft aan dat een entiteit definitief buiten gebruik is.</v>
       </c>
       <c r="N227" t="str">
-        <v>null</v>
+        <v>De status definitief uit dienst geeft aan dat een entiteit definitief buiten gebruik is.</v>
       </c>
       <c r="O227" t="str">
         <v>null</v>
@@ -25324,10 +26002,10 @@
         <v>null</v>
       </c>
       <c r="V227" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/definitief_uit_dienst</v>
       </c>
       <c r="W227" t="str">
-        <v>null</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X227" t="str">
         <v>null</v>
@@ -25366,33 +26044,36 @@
         <v>null</v>
       </c>
       <c r="AJ227" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK227" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/thema-type/grondwater</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/in_dienst</v>
       </c>
       <c r="B228" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C228" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/thema_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
       </c>
       <c r="D228" t="str">
-        <v>THEMA_GRONDWATER</v>
+        <v>IN_DIENST</v>
       </c>
       <c r="E228" t="str">
-        <v>Grondwater</v>
+        <v>In dienst</v>
       </c>
       <c r="F228" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/thema_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
       </c>
       <c r="G228" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_grondwater</v>
+        <v>http://purl.org/adms/status/Completed</v>
       </c>
       <c r="H228" t="str">
-        <v>null</v>
+        <v>http://www.w3.org/ns/adms#</v>
       </c>
       <c r="I228" t="str">
         <v>null</v>
@@ -25407,10 +26088,10 @@
         <v>null</v>
       </c>
       <c r="M228" t="str">
-        <v>null</v>
+        <v>De status in dienst geeft aan dat een entiteit momenteel in gebruik is.</v>
       </c>
       <c r="N228" t="str">
-        <v>null</v>
+        <v>De status in dienst geeft aan dat een entiteit momenteel in gebruik is.</v>
       </c>
       <c r="O228" t="str">
         <v>null</v>
@@ -25434,10 +26115,10 @@
         <v>null</v>
       </c>
       <c r="V228" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/in_dienst</v>
       </c>
       <c r="W228" t="str">
-        <v>null</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X228" t="str">
         <v>null</v>
@@ -25476,33 +26157,36 @@
         <v>null</v>
       </c>
       <c r="AJ228" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK228" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/thema-type/lucht</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/ontmanteld</v>
       </c>
       <c r="B229" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C229" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/thema_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
       </c>
       <c r="D229" t="str">
-        <v>THEMA_LUCHT</v>
+        <v>ONTMANTELD</v>
       </c>
       <c r="E229" t="str">
-        <v>Lucht</v>
+        <v>Ontmanteld</v>
       </c>
       <c r="F229" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/thema_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
       </c>
       <c r="G229" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_lucht</v>
+        <v>http://purl.org/adms/status/Withdrawn</v>
       </c>
       <c r="H229" t="str">
-        <v>null</v>
+        <v>http://www.w3.org/ns/adms#</v>
       </c>
       <c r="I229" t="str">
         <v>null</v>
@@ -25517,10 +26201,10 @@
         <v>null</v>
       </c>
       <c r="M229" t="str">
-        <v>null</v>
+        <v>De status ontmanteld geeft aan dat een entiteit niet meer bestaat.</v>
       </c>
       <c r="N229" t="str">
-        <v>null</v>
+        <v>De status ontmanteld geeft aan dat een entiteit niet meer bestaat.</v>
       </c>
       <c r="O229" t="str">
         <v>null</v>
@@ -25544,10 +26228,10 @@
         <v>null</v>
       </c>
       <c r="V229" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/ontmanteld</v>
       </c>
       <c r="W229" t="str">
-        <v>null</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X229" t="str">
         <v>null</v>
@@ -25586,33 +26270,36 @@
         <v>null</v>
       </c>
       <c r="AJ229" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK229" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/thema-type/water</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/tijdelijk_uit_dienst</v>
       </c>
       <c r="B230" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C230" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/thema_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
       </c>
       <c r="D230" t="str">
-        <v>THEMA_WATER</v>
+        <v>TIJDELIJK_UIT_DIENST</v>
       </c>
       <c r="E230" t="str">
-        <v>Water</v>
+        <v>Tijdelijk uit dienst</v>
       </c>
       <c r="F230" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/thema_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
       </c>
       <c r="G230" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_water</v>
+        <v>http://purl.org/adms/status/Deprecated</v>
       </c>
       <c r="H230" t="str">
-        <v>null</v>
+        <v>http://www.w3.org/ns/adms#</v>
       </c>
       <c r="I230" t="str">
         <v>null</v>
@@ -25627,10 +26314,10 @@
         <v>null</v>
       </c>
       <c r="M230" t="str">
-        <v>null</v>
+        <v>De status tijdelijk uit dienst geeft aan dat een entiteit tijden buiten gebruik is.</v>
       </c>
       <c r="N230" t="str">
-        <v>null</v>
+        <v>De status tijdelijk uit dienst geeft aan dat een entiteit tijden buiten gebruik is.</v>
       </c>
       <c r="O230" t="str">
         <v>null</v>
@@ -25654,10 +26341,10 @@
         <v>null</v>
       </c>
       <c r="V230" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/tijdelijk_uit_dienst</v>
       </c>
       <c r="W230" t="str">
-        <v>null</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X230" t="str">
         <v>null</v>
@@ -25696,33 +26383,36 @@
         <v>null</v>
       </c>
       <c r="AJ230" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK230" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/thema-type/zelfcontrole-lucht</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/verkeerde_registratie</v>
       </c>
       <c r="B231" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C231" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/thema_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
       </c>
       <c r="D231" t="str">
-        <v>THEMA_ZELFCONTROLE_LUCHT</v>
+        <v>VERKEERDE_REGISTRATIE</v>
       </c>
       <c r="E231" t="str">
-        <v>Zelfcontrole lucht</v>
+        <v>Verkeerde Registratie</v>
       </c>
       <c r="F231" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/thema_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
       </c>
       <c r="G231" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_zelfcontrole_lucht</v>
+        <v>http://purl.org/adms/status/Withdrawn</v>
       </c>
       <c r="H231" t="str">
-        <v>null</v>
+        <v>http://www.w3.org/ns/adms#</v>
       </c>
       <c r="I231" t="str">
         <v>null</v>
@@ -25737,10 +26427,10 @@
         <v>null</v>
       </c>
       <c r="M231" t="str">
-        <v>null</v>
+        <v>De status verkeerde registratie  geeft aan deze entiteit verkeerd werd geregistreerd en dus niet van toepassing is</v>
       </c>
       <c r="N231" t="str">
-        <v>null</v>
+        <v>De status verkeerde registratie  geeft aan deze entiteit verkeerd werd geregistreerd en dus niet van toepassing is</v>
       </c>
       <c r="O231" t="str">
         <v>null</v>
@@ -25764,10 +26454,10 @@
         <v>null</v>
       </c>
       <c r="V231" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/verkeerde_registratie</v>
       </c>
       <c r="W231" t="str">
-        <v>null</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X231" t="str">
         <v>null</v>
@@ -25806,33 +26496,36 @@
         <v>null</v>
       </c>
       <c r="AJ231" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK231" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/thema-type/zelfcontrole-water</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/voorgesteld</v>
       </c>
       <c r="B232" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C232" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/thema_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
       </c>
       <c r="D232" t="str">
-        <v>THEMA_ZELFCONTROLE_WATER</v>
+        <v>VOORGESTELD</v>
       </c>
       <c r="E232" t="str">
-        <v>Zelfcontrole water</v>
+        <v>Voorgesteld Ontwerp</v>
       </c>
       <c r="F232" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/thema_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
       </c>
       <c r="G232" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_zelfcontrole_water</v>
+        <v>http://purl.org/adms/status/UnderDevelopment</v>
       </c>
       <c r="H232" t="str">
-        <v>null</v>
+        <v>http://www.w3.org/ns/adms#</v>
       </c>
       <c r="I232" t="str">
         <v>null</v>
@@ -25847,10 +26540,10 @@
         <v>null</v>
       </c>
       <c r="M232" t="str">
-        <v>null</v>
+        <v>De status voorgesteld geeft aan dat een entiteit voorsgesteld is door de Vlaamse Overheid.</v>
       </c>
       <c r="N232" t="str">
-        <v>null</v>
+        <v>De status voorgesteld geeft aan dat een entiteit voorsgesteld is door de Vlaamse Overheid.</v>
       </c>
       <c r="O232" t="str">
         <v>null</v>
@@ -25874,10 +26567,10 @@
         <v>null</v>
       </c>
       <c r="V232" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/voorgesteld</v>
       </c>
       <c r="W232" t="str">
-        <v>null</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X232" t="str">
         <v>null</v>
@@ -25916,36 +26609,39 @@
         <v>null</v>
       </c>
       <c r="AJ232" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK232" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/uitwisselpunt-type/uitwisselpunt</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/thema-type/grondstoffen</v>
       </c>
       <c r="B233" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C233" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/uitwisselpunt_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/thema_type</v>
       </c>
       <c r="D233" t="str">
-        <v>stookinstallatie</v>
+        <v>THEMA_GRONDSTOFFEN</v>
       </c>
       <c r="E233" t="str">
-        <v>Uitwisselingspunt</v>
+        <v>Grondstoffen</v>
       </c>
       <c r="F233" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/uitwisselpunt_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/thema_type</v>
       </c>
       <c r="G233" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_grondstoffen</v>
       </c>
       <c r="H233" t="str">
         <v>null</v>
       </c>
       <c r="I233" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_type</v>
+        <v>null</v>
       </c>
       <c r="J233" t="str">
         <v>null</v>
@@ -26026,30 +26722,33 @@
         <v>null</v>
       </c>
       <c r="AJ233" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK233" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/aangifte_status</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/thema-type/grondwater</v>
       </c>
       <c r="B234" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
+        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C234" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/thema_type</v>
       </c>
       <c r="D234" t="str">
-        <v>null</v>
+        <v>THEMA_GRONDWATER</v>
       </c>
       <c r="E234" t="str">
-        <v>Aangifte status</v>
+        <v>Grondwater</v>
       </c>
       <c r="F234" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/thema_type</v>
       </c>
       <c r="G234" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_grondwater</v>
       </c>
       <c r="H234" t="str">
         <v>null</v>
@@ -26133,33 +26832,36 @@
         <v>null</v>
       </c>
       <c r="AI234" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/aangifte-status/concept|https://data.omgeving.vlaanderen.be/id/concept/riepr/aangifte-status/gefaald|https://data.omgeving.vlaanderen.be/id/concept/riepr/aangifte-status/ingediend|https://data.omgeving.vlaanderen.be/id/concept/riepr/aangifte-status/ingetrokken</v>
+        <v>null</v>
       </c>
       <c r="AJ234" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK234" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/aangifte_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/thema-type/lucht</v>
       </c>
       <c r="B235" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
+        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C235" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/thema_type</v>
       </c>
       <c r="D235" t="str">
-        <v>null</v>
+        <v>THEMA_LUCHT</v>
       </c>
       <c r="E235" t="str">
-        <v>Aangifte types</v>
+        <v>Lucht</v>
       </c>
       <c r="F235" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/thema_type</v>
       </c>
       <c r="G235" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_lucht</v>
       </c>
       <c r="H235" t="str">
         <v>null</v>
@@ -26177,10 +26879,10 @@
         <v>null</v>
       </c>
       <c r="M235" t="str">
-        <v>Een typering van verschillende aangiftes</v>
+        <v>null</v>
       </c>
       <c r="N235" t="str">
-        <v>Een typering van verschillende aangiftes</v>
+        <v>null</v>
       </c>
       <c r="O235" t="str">
         <v>null</v>
@@ -26243,33 +26945,36 @@
         <v>null</v>
       </c>
       <c r="AI235" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/aangifte-type/operationeel|https://data.omgeving.vlaanderen.be/id/concept/riepr/aangifte-type/structuur</v>
+        <v>null</v>
       </c>
       <c r="AJ235" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK235" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/eenheden</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/thema-type/water</v>
       </c>
       <c r="B236" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
+        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C236" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/thema_type</v>
       </c>
       <c r="D236" t="str">
-        <v>null</v>
+        <v>THEMA_WATER</v>
       </c>
       <c r="E236" t="str">
-        <v>null</v>
+        <v>Water</v>
       </c>
       <c r="F236" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/thema_type</v>
       </c>
       <c r="G236" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_water</v>
       </c>
       <c r="H236" t="str">
         <v>null</v>
@@ -26353,39 +27058,42 @@
         <v>null</v>
       </c>
       <c r="AI236" t="str">
-        <v>http://qudt.org/vocab/unit/DEG_C|http://qudt.org/vocab/unit/K|http://qudt.org/vocab/unit/M3|http://qudt.org/vocab/unit/M|http://qudt.org/vocab/unit/MegaW|http://qudt.org/vocab/unit/MicroGM-PER-L|http://qudt.org/vocab/unit/MilliGM-PER-L|http://qudt.org/vocab/unit/NanoGM-PER-L|http://qudt.org/vocab/unit/PERCENT|http://qudt.org/vocab/unit/PPB|http://qudt.org/vocab/unit/PPM</v>
+        <v>null</v>
       </c>
       <c r="AJ236" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK236" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_eigenschappen</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/thema-type/zelfcontrole-lucht</v>
       </c>
       <c r="B237" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
+        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C237" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/thema_type</v>
       </c>
       <c r="D237" t="str">
-        <v>null</v>
+        <v>THEMA_ZELFCONTROLE_LUCHT</v>
       </c>
       <c r="E237" t="str">
-        <v>Emissiepunt eigenschappen</v>
+        <v>Zelfcontrole lucht</v>
       </c>
       <c r="F237" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/thema_type</v>
       </c>
       <c r="G237" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_zelfcontrole_lucht</v>
       </c>
       <c r="H237" t="str">
         <v>null</v>
       </c>
       <c r="I237" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_eigenschappen</v>
+        <v>null</v>
       </c>
       <c r="J237" t="str">
         <v>null</v>
@@ -26397,10 +27105,10 @@
         <v>null</v>
       </c>
       <c r="M237" t="str">
-        <v>Een typering van verschillende eigenschappen voor emissiepunten.</v>
+        <v>null</v>
       </c>
       <c r="N237" t="str">
-        <v>Een typering van verschillende eigenschappen voor emissiepunten.</v>
+        <v>null</v>
       </c>
       <c r="O237" t="str">
         <v>null</v>
@@ -26463,39 +27171,42 @@
         <v>null</v>
       </c>
       <c r="AI237" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-eigenschappen/lozingspunt-lozingsplaats|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-eigenschappen/schouw-diameter|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-eigenschappen/schouw-hoogte</v>
+        <v>null</v>
       </c>
       <c r="AJ237" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK237" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/thema-type/zelfcontrole-water</v>
       </c>
       <c r="B238" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
+        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C238" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/thema_type</v>
       </c>
       <c r="D238" t="str">
-        <v>null</v>
+        <v>THEMA_ZELFCONTROLE_WATER</v>
       </c>
       <c r="E238" t="str">
-        <v>Emissiepunt types</v>
+        <v>Zelfcontrole water</v>
       </c>
       <c r="F238" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/thema_type</v>
       </c>
       <c r="G238" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_zelfcontrole_water</v>
       </c>
       <c r="H238" t="str">
         <v>null</v>
       </c>
       <c r="I238" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_type</v>
+        <v>null</v>
       </c>
       <c r="J238" t="str">
         <v>null</v>
@@ -26507,10 +27218,10 @@
         <v>null</v>
       </c>
       <c r="M238" t="str">
-        <v>Een typering van verschillende soorten emissiepunten.</v>
+        <v>null</v>
       </c>
       <c r="N238" t="str">
-        <v>Een typering van verschillende soorten emissiepunten.</v>
+        <v>null</v>
       </c>
       <c r="O238" t="str">
         <v>null</v>
@@ -26573,30 +27284,33 @@
         <v>null</v>
       </c>
       <c r="AI238" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/lozingspunt|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/emissiepunt|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/fakkel|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/gebouw</v>
+        <v>null</v>
       </c>
       <c r="AJ238" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK238" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/filter_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/uitwisselpunt-type/uitwisselpunt</v>
       </c>
       <c r="B239" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
+        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C239" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/uitwisselpunt_type</v>
       </c>
       <c r="D239" t="str">
-        <v>null</v>
+        <v>stookinstallatie</v>
       </c>
       <c r="E239" t="str">
-        <v>Filter type</v>
+        <v>Uitwisselingspunt</v>
       </c>
       <c r="F239" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/uitwisselpunt_type</v>
       </c>
       <c r="G239" t="str">
         <v>null</v>
@@ -26605,7 +27319,7 @@
         <v>null</v>
       </c>
       <c r="I239" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_type</v>
       </c>
       <c r="J239" t="str">
         <v>null</v>
@@ -26683,15 +27397,18 @@
         <v>null</v>
       </c>
       <c r="AI239" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/filter-type/injectie|https://data.omgeving.vlaanderen.be/id/concept/riepr/filter-type/omkeerbaar|https://data.omgeving.vlaanderen.be/id/concept/riepr/filter-type/peil|https://data.omgeving.vlaanderen.be/id/concept/riepr/filter-type/pomp</v>
+        <v>null</v>
       </c>
       <c r="AJ239" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK239" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_eigenschappen</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/aangifte_status</v>
       </c>
       <c r="B240" t="str">
         <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
@@ -26703,7 +27420,7 @@
         <v>null</v>
       </c>
       <c r="E240" t="str">
-        <v>Installatie eigenschappen</v>
+        <v>Aangifte status</v>
       </c>
       <c r="F240" t="str">
         <v>null</v>
@@ -26715,7 +27432,7 @@
         <v>null</v>
       </c>
       <c r="I240" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_eigenschappen</v>
+        <v>null</v>
       </c>
       <c r="J240" t="str">
         <v>null</v>
@@ -26727,10 +27444,10 @@
         <v>null</v>
       </c>
       <c r="M240" t="str">
-        <v>Een typering van verschillende eigenschappen voor installaties.</v>
+        <v>null</v>
       </c>
       <c r="N240" t="str">
-        <v>Een typering van verschillende eigenschappen voor installaties.</v>
+        <v>null</v>
       </c>
       <c r="O240" t="str">
         <v>null</v>
@@ -26754,10 +27471,10 @@
         <v>null</v>
       </c>
       <c r="V240" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_eigenschappen</v>
+        <v>null</v>
       </c>
       <c r="W240" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>null</v>
       </c>
       <c r="X240" t="str">
         <v>null</v>
@@ -26793,15 +27510,18 @@
         <v>null</v>
       </c>
       <c r="AI240" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/geinstalleerd_vermogen|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/geinstalleerde_opslagcapaciteit|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/geinstalleerde_productiecapaciteit|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/luchtzuiverings_techniek|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/type_energie_productie|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/verwijderingsrendement|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/waterzuiveringstechniek</v>
+        <v>null</v>
       </c>
       <c r="AJ240" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/aangifte-status/concept|https://data.omgeving.vlaanderen.be/id/concept/riepr/aangifte-status/gefaald|https://data.omgeving.vlaanderen.be/id/concept/riepr/aangifte-status/ingediend|https://data.omgeving.vlaanderen.be/id/concept/riepr/aangifte-status/ingetrokken</v>
+      </c>
+      <c r="AK240" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/aangifte_type</v>
       </c>
       <c r="B241" t="str">
         <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
@@ -26813,7 +27533,7 @@
         <v>null</v>
       </c>
       <c r="E241" t="str">
-        <v>Installatie types</v>
+        <v>Aangifte types</v>
       </c>
       <c r="F241" t="str">
         <v>null</v>
@@ -26825,7 +27545,7 @@
         <v>null</v>
       </c>
       <c r="I241" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_type</v>
+        <v>null</v>
       </c>
       <c r="J241" t="str">
         <v>null</v>
@@ -26837,10 +27557,10 @@
         <v>null</v>
       </c>
       <c r="M241" t="str">
-        <v>Een typering van verschillende soorten installaties.</v>
+        <v>Een typering van verschillende aangiftes</v>
       </c>
       <c r="N241" t="str">
-        <v>Een typering van verschillende soorten installaties.</v>
+        <v>Een typering van verschillende aangiftes</v>
       </c>
       <c r="O241" t="str">
         <v>null</v>
@@ -26903,15 +27623,18 @@
         <v>null</v>
       </c>
       <c r="AI241" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/stookinstallatie|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/opslag_overslag|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/luchtzuivering|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/waterzuivering|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/geothermisch|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/gpbv|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/installatie</v>
+        <v>null</v>
       </c>
       <c r="AJ241" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/aangifte-type/operationeel|https://data.omgeving.vlaanderen.be/id/concept/riepr/aangifte-type/structuur</v>
+      </c>
+      <c r="AK241" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/lozingspunt_lozingsplaats</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/eenheden</v>
       </c>
       <c r="B242" t="str">
         <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
@@ -27013,15 +27736,18 @@
         <v>null</v>
       </c>
       <c r="AI242" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-eigenschappen-selectiemogelijkheden/grondwater|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-eigenschappen-selectiemogelijkheden/oppervlaktewater|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-eigenschappen-selectiemogelijkheden/riool</v>
+        <v>null</v>
       </c>
       <c r="AJ242" t="str">
+        <v>http://qudt.org/vocab/unit/DEG_C|http://qudt.org/vocab/unit/K|http://qudt.org/vocab/unit/M3|http://qudt.org/vocab/unit/M|http://qudt.org/vocab/unit/MegaW|http://qudt.org/vocab/unit/MicroGM-PER-L|http://qudt.org/vocab/unit/MilliGM-PER-L|http://qudt.org/vocab/unit/NanoGM-PER-L|http://qudt.org/vocab/unit/PERCENT|http://qudt.org/vocab/unit/PPB|http://qudt.org/vocab/unit/PPM</v>
+      </c>
+      <c r="AK242" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/meetpunt_eigenschappen</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_eigenschappen</v>
       </c>
       <c r="B243" t="str">
         <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
@@ -27033,7 +27759,7 @@
         <v>null</v>
       </c>
       <c r="E243" t="str">
-        <v>Meetpunt eigenschappen</v>
+        <v>Emissiepunt eigenschappen</v>
       </c>
       <c r="F243" t="str">
         <v>null</v>
@@ -27057,10 +27783,10 @@
         <v>null</v>
       </c>
       <c r="M243" t="str">
-        <v>Een typering van verschillende eigenschappen voor meetpunten.</v>
+        <v>Een typering van verschillende eigenschappen voor emissiepunten.</v>
       </c>
       <c r="N243" t="str">
-        <v>Een typering van verschillende eigenschappen voor meetpunten.</v>
+        <v>Een typering van verschillende eigenschappen voor emissiepunten.</v>
       </c>
       <c r="O243" t="str">
         <v>null</v>
@@ -27084,10 +27810,10 @@
         <v>null</v>
       </c>
       <c r="V243" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/meetpunt_eigenschappen</v>
+        <v>null</v>
       </c>
       <c r="W243" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>null</v>
       </c>
       <c r="X243" t="str">
         <v>null</v>
@@ -27123,15 +27849,18 @@
         <v>null</v>
       </c>
       <c r="AI243" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-eigenschappen/diepte|https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-eigenschappen/referentiepunt</v>
+        <v>null</v>
       </c>
       <c r="AJ243" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-eigenschappen/lozingspunt-lozingsplaats|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-eigenschappen/schouw-diameter|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-eigenschappen/schouw-hoogte</v>
+      </c>
+      <c r="AK243" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/meetpunt_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
       </c>
       <c r="B244" t="str">
         <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
@@ -27143,7 +27872,7 @@
         <v>null</v>
       </c>
       <c r="E244" t="str">
-        <v>Meetpunt types</v>
+        <v>Emissiepunt types</v>
       </c>
       <c r="F244" t="str">
         <v>null</v>
@@ -27155,7 +27884,7 @@
         <v>null</v>
       </c>
       <c r="I244" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_type</v>
       </c>
       <c r="J244" t="str">
         <v>null</v>
@@ -27167,10 +27896,10 @@
         <v>null</v>
       </c>
       <c r="M244" t="str">
-        <v>null</v>
+        <v>Een typering van verschillende soorten emissiepunten.</v>
       </c>
       <c r="N244" t="str">
-        <v>null</v>
+        <v>Een typering van verschillende soorten emissiepunten.</v>
       </c>
       <c r="O244" t="str">
         <v>null</v>
@@ -27233,15 +27962,18 @@
         <v>null</v>
       </c>
       <c r="AI244" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-type/peilput|https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-type/controleinrichting|https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-type/debietmeter</v>
+        <v>null</v>
       </c>
       <c r="AJ244" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/lozingspunt|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/emissiepunt|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/fakkel|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/gebouw</v>
+      </c>
+      <c r="AK244" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/onttrekkingspunt_eigenschappen</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/filter_type</v>
       </c>
       <c r="B245" t="str">
         <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
@@ -27253,7 +27985,7 @@
         <v>null</v>
       </c>
       <c r="E245" t="str">
-        <v>Onttrekkingspunt eigenschappen</v>
+        <v>Filter type</v>
       </c>
       <c r="F245" t="str">
         <v>null</v>
@@ -27265,7 +27997,7 @@
         <v>null</v>
       </c>
       <c r="I245" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_eigenschappen</v>
+        <v>null</v>
       </c>
       <c r="J245" t="str">
         <v>null</v>
@@ -27277,10 +28009,10 @@
         <v>null</v>
       </c>
       <c r="M245" t="str">
-        <v>Een typering van verschillende eigenschappen voor onttrekkingspunten.</v>
+        <v>null</v>
       </c>
       <c r="N245" t="str">
-        <v>Een typering van verschillende eigenschappen voor onttrekkingspunten.</v>
+        <v>null</v>
       </c>
       <c r="O245" t="str">
         <v>null</v>
@@ -27343,15 +28075,18 @@
         <v>null</v>
       </c>
       <c r="AI245" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/onttrekkingspunt-eigenschappen/diepte|https://data.omgeving.vlaanderen.be/id/concept/riepr/onttrekkingspunt-eigenschappen/watervoerendelaag</v>
+        <v>null</v>
       </c>
       <c r="AJ245" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/filter-type/injectie|https://data.omgeving.vlaanderen.be/id/concept/riepr/filter-type/omkeerbaar|https://data.omgeving.vlaanderen.be/id/concept/riepr/filter-type/peil|https://data.omgeving.vlaanderen.be/id/concept/riepr/filter-type/pomp</v>
+      </c>
+      <c r="AK245" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/onttrekkingspunt_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_eigenschappen</v>
       </c>
       <c r="B246" t="str">
         <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
@@ -27363,7 +28098,7 @@
         <v>null</v>
       </c>
       <c r="E246" t="str">
-        <v>Onttrekkingspunt types</v>
+        <v>Installatie eigenschappen</v>
       </c>
       <c r="F246" t="str">
         <v>null</v>
@@ -27375,7 +28110,7 @@
         <v>null</v>
       </c>
       <c r="I246" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_eigenschappen</v>
       </c>
       <c r="J246" t="str">
         <v>null</v>
@@ -27387,10 +28122,10 @@
         <v>null</v>
       </c>
       <c r="M246" t="str">
-        <v>Een typering van verschillende soorten onttrekkingspunten.</v>
+        <v>Een typering van verschillende eigenschappen voor installaties.</v>
       </c>
       <c r="N246" t="str">
-        <v>Een typering van verschillende soorten onttrekkingspunten.</v>
+        <v>Een typering van verschillende eigenschappen voor installaties.</v>
       </c>
       <c r="O246" t="str">
         <v>null</v>
@@ -27414,10 +28149,10 @@
         <v>null</v>
       </c>
       <c r="V246" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_eigenschappen</v>
       </c>
       <c r="W246" t="str">
-        <v>null</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X246" t="str">
         <v>null</v>
@@ -27453,15 +28188,18 @@
         <v>null</v>
       </c>
       <c r="AI246" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/onttrekkingspunt-type/pompput|https://data.omgeving.vlaanderen.be/id/concept/riepr/onttrekkingspunt-type/opnamepunt</v>
+        <v>null</v>
       </c>
       <c r="AJ246" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/geinstalleerd_vermogen|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/geinstalleerde_opslagcapaciteit|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/geinstalleerde_productiecapaciteit|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/luchtzuiverings_techniek|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/type_energie_productie|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/verwijderingsrendement|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/waterzuiveringstechniek</v>
+      </c>
+      <c r="AK246" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_bepalingsmethode</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_type</v>
       </c>
       <c r="B247" t="str">
         <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
@@ -27473,7 +28211,7 @@
         <v>null</v>
       </c>
       <c r="E247" t="str">
-        <v>Bepalingsmethode</v>
+        <v>Installatie types</v>
       </c>
       <c r="F247" t="str">
         <v>null</v>
@@ -27485,7 +28223,7 @@
         <v>null</v>
       </c>
       <c r="I247" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_type</v>
       </c>
       <c r="J247" t="str">
         <v>null</v>
@@ -27497,10 +28235,10 @@
         <v>null</v>
       </c>
       <c r="M247" t="str">
-        <v>null</v>
+        <v>Een typering van verschillende soorten installaties.</v>
       </c>
       <c r="N247" t="str">
-        <v>null</v>
+        <v>Een typering van verschillende soorten installaties.</v>
       </c>
       <c r="O247" t="str">
         <v>null</v>
@@ -27563,15 +28301,18 @@
         <v>null</v>
       </c>
       <c r="AI247" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-bepalingsmethode/berekend|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-bepalingsmethode/gemeten|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-bepalingsmethode/geschat|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-bepalingsmethode/voorgesteld</v>
+        <v>null</v>
       </c>
       <c r="AJ247" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/stookinstallatie|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/opslag_overslag|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/luchtzuivering|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/waterzuivering|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/geothermisch|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/gpbv|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/installatie</v>
+      </c>
+      <c r="AK247" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_bepalingsmethodeclassificatie</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/lozingspunt_lozingsplaats</v>
       </c>
       <c r="B248" t="str">
         <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
@@ -27583,7 +28324,7 @@
         <v>null</v>
       </c>
       <c r="E248" t="str">
-        <v>Bepalingsmethodeclassificatie</v>
+        <v>null</v>
       </c>
       <c r="F248" t="str">
         <v>null</v>
@@ -27673,15 +28414,18 @@
         <v>null</v>
       </c>
       <c r="AI248" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-bepalingsmethodeclassificatie/vrachten</v>
+        <v>null</v>
       </c>
       <c r="AJ248" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-eigenschappen-selectiemogelijkheden/grondwater|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-eigenschappen-selectiemogelijkheden/oppervlaktewater|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-eigenschappen-selectiemogelijkheden/riool</v>
+      </c>
+      <c r="AK248" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_bestemmingstype</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/meetpunt_eigenschappen</v>
       </c>
       <c r="B249" t="str">
         <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
@@ -27693,7 +28437,7 @@
         <v>null</v>
       </c>
       <c r="E249" t="str">
-        <v>Bestemmingstype</v>
+        <v>Meetpunt eigenschappen</v>
       </c>
       <c r="F249" t="str">
         <v>null</v>
@@ -27705,7 +28449,7 @@
         <v>null</v>
       </c>
       <c r="I249" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_eigenschappen</v>
       </c>
       <c r="J249" t="str">
         <v>null</v>
@@ -27717,10 +28461,10 @@
         <v>null</v>
       </c>
       <c r="M249" t="str">
-        <v>null</v>
+        <v>Een typering van verschillende eigenschappen voor meetpunten.</v>
       </c>
       <c r="N249" t="str">
-        <v>null</v>
+        <v>Een typering van verschillende eigenschappen voor meetpunten.</v>
       </c>
       <c r="O249" t="str">
         <v>null</v>
@@ -27744,10 +28488,10 @@
         <v>null</v>
       </c>
       <c r="V249" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/meetpunt_eigenschappen</v>
       </c>
       <c r="W249" t="str">
-        <v>null</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X249" t="str">
         <v>null</v>
@@ -27783,15 +28527,18 @@
         <v>null</v>
       </c>
       <c r="AI249" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-bestemmingstype/belgisch|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-bestemmingstype/buitenlands|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-bestemmingstype/dispers|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-bestemmingstype/geen_onderneming|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-bestemmingstype/particulier|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-bestemmingstype/werf</v>
+        <v>null</v>
       </c>
       <c r="AJ249" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-eigenschappen/diepte|https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-eigenschappen/referentiepunt</v>
+      </c>
+      <c r="AK249" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_debiet_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/meetpunt_type</v>
       </c>
       <c r="B250" t="str">
         <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
@@ -27803,7 +28550,7 @@
         <v>null</v>
       </c>
       <c r="E250" t="str">
-        <v>Type debiet</v>
+        <v>Meetpunt types</v>
       </c>
       <c r="F250" t="str">
         <v>null</v>
@@ -27893,15 +28640,18 @@
         <v>null</v>
       </c>
       <c r="AI250" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-debiet-type/infiltratie|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-debiet-type/onttrekking|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-debiet-type/spui|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-debiet-type/totaal_rondgepompd</v>
+        <v>null</v>
       </c>
       <c r="AJ250" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-type/peilput|https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-type/controleinrichting|https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-type/debietmeter</v>
+      </c>
+      <c r="AK250" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_grondstoffen</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/onttrekkingspunt_eigenschappen</v>
       </c>
       <c r="B251" t="str">
         <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
@@ -27913,7 +28663,7 @@
         <v>null</v>
       </c>
       <c r="E251" t="str">
-        <v>Operationeel grondstoffen</v>
+        <v>Onttrekkingspunt eigenschappen</v>
       </c>
       <c r="F251" t="str">
         <v>null</v>
@@ -27925,7 +28675,7 @@
         <v>null</v>
       </c>
       <c r="I251" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_eigenschappen</v>
       </c>
       <c r="J251" t="str">
         <v>null</v>
@@ -27937,10 +28687,10 @@
         <v>null</v>
       </c>
       <c r="M251" t="str">
-        <v>null</v>
+        <v>Een typering van verschillende eigenschappen voor onttrekkingspunten.</v>
       </c>
       <c r="N251" t="str">
-        <v>null</v>
+        <v>Een typering van verschillende eigenschappen voor onttrekkingspunten.</v>
       </c>
       <c r="O251" t="str">
         <v>null</v>
@@ -27964,10 +28714,10 @@
         <v>null</v>
       </c>
       <c r="V251" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_grondstoffen</v>
+        <v>null</v>
       </c>
       <c r="W251" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>null</v>
       </c>
       <c r="X251" t="str">
         <v>null</v>
@@ -28003,15 +28753,18 @@
         <v>null</v>
       </c>
       <c r="AI251" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/grondstof|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/geproduceerd</v>
+        <v>null</v>
       </c>
       <c r="AJ251" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/onttrekkingspunt-eigenschappen/diepte|https://data.omgeving.vlaanderen.be/id/concept/riepr/onttrekkingspunt-eigenschappen/watervoerendelaag</v>
+      </c>
+      <c r="AK251" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_grondwater</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/onttrekkingspunt_type</v>
       </c>
       <c r="B252" t="str">
         <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
@@ -28023,7 +28776,7 @@
         <v>null</v>
       </c>
       <c r="E252" t="str">
-        <v>null</v>
+        <v>Onttrekkingspunt types</v>
       </c>
       <c r="F252" t="str">
         <v>null</v>
@@ -28047,10 +28800,10 @@
         <v>null</v>
       </c>
       <c r="M252" t="str">
-        <v>null</v>
+        <v>Een typering van verschillende soorten onttrekkingspunten.</v>
       </c>
       <c r="N252" t="str">
-        <v>null</v>
+        <v>Een typering van verschillende soorten onttrekkingspunten.</v>
       </c>
       <c r="O252" t="str">
         <v>null</v>
@@ -28074,10 +28827,10 @@
         <v>null</v>
       </c>
       <c r="V252" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_grondwater</v>
+        <v>null</v>
       </c>
       <c r="W252" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>null</v>
       </c>
       <c r="X252" t="str">
         <v>null</v>
@@ -28113,15 +28866,18 @@
         <v>null</v>
       </c>
       <c r="AI252" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/onttrekking|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/peilmeting|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting</v>
+        <v>null</v>
       </c>
       <c r="AJ252" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/onttrekkingspunt-type/pompput|https://data.omgeving.vlaanderen.be/id/concept/riepr/onttrekkingspunt-type/opnamepunt</v>
+      </c>
+      <c r="AK252" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_lucht</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_bepalingsmethode</v>
       </c>
       <c r="B253" t="str">
         <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
@@ -28133,7 +28889,7 @@
         <v>null</v>
       </c>
       <c r="E253" t="str">
-        <v>Operationele gegevens</v>
+        <v>Bepalingsmethode</v>
       </c>
       <c r="F253" t="str">
         <v>null</v>
@@ -28223,15 +28979,18 @@
         <v>null</v>
       </c>
       <c r="AI253" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/feature_ep</v>
+        <v>null</v>
       </c>
       <c r="AJ253" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-bepalingsmethode/berekend|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-bepalingsmethode/gemeten|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-bepalingsmethode/geschat|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-bepalingsmethode/voorgesteld</v>
+      </c>
+      <c r="AK253" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_lucht_bron</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_bepalingsmethodeclassificatie</v>
       </c>
       <c r="B254" t="str">
         <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
@@ -28243,7 +29002,7 @@
         <v>null</v>
       </c>
       <c r="E254" t="str">
-        <v>null</v>
+        <v>Bepalingsmethodeclassificatie</v>
       </c>
       <c r="F254" t="str">
         <v>null</v>
@@ -28333,15 +29092,18 @@
         <v>null</v>
       </c>
       <c r="AI254" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/feature_bron</v>
+        <v>null</v>
       </c>
       <c r="AJ254" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-bepalingsmethodeclassificatie/vrachten</v>
+      </c>
+      <c r="AK254" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_lucht_emissie</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_bestemmingstype</v>
       </c>
       <c r="B255" t="str">
         <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
@@ -28353,7 +29115,7 @@
         <v>null</v>
       </c>
       <c r="E255" t="str">
-        <v>null</v>
+        <v>Bestemmingstype</v>
       </c>
       <c r="F255" t="str">
         <v>null</v>
@@ -28404,10 +29166,10 @@
         <v>null</v>
       </c>
       <c r="V255" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_lucht_emissie</v>
+        <v>null</v>
       </c>
       <c r="W255" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>null</v>
       </c>
       <c r="X255" t="str">
         <v>null</v>
@@ -28443,15 +29205,18 @@
         <v>null</v>
       </c>
       <c r="AI255" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie</v>
+        <v>null</v>
       </c>
       <c r="AJ255" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-bestemmingstype/belgisch|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-bestemmingstype/buitenlands|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-bestemmingstype/dispers|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-bestemmingstype/geen_onderneming|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-bestemmingstype/particulier|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-bestemmingstype/werf</v>
+      </c>
+      <c r="AK255" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_lucht_rapportering</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_debiet_type</v>
       </c>
       <c r="B256" t="str">
         <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
@@ -28463,7 +29228,7 @@
         <v>null</v>
       </c>
       <c r="E256" t="str">
-        <v>null</v>
+        <v>Type debiet</v>
       </c>
       <c r="F256" t="str">
         <v>null</v>
@@ -28514,10 +29279,10 @@
         <v>null</v>
       </c>
       <c r="V256" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_lucht_rapportering</v>
+        <v>null</v>
       </c>
       <c r="W256" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>null</v>
       </c>
       <c r="X256" t="str">
         <v>null</v>
@@ -28553,15 +29318,18 @@
         <v>null</v>
       </c>
       <c r="AI256" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/afvalproduct|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/geproduceerde_stof|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/brandstof|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/verbruikte_stof</v>
+        <v>null</v>
       </c>
       <c r="AJ256" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-debiet-type/infiltratie|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-debiet-type/onttrekking|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-debiet-type/spui|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-debiet-type/totaal_rondgepompd</v>
+      </c>
+      <c r="AK256" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_peilmethode</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_grondstoffen</v>
       </c>
       <c r="B257" t="str">
         <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
@@ -28573,7 +29341,7 @@
         <v>null</v>
       </c>
       <c r="E257" t="str">
-        <v>Peilmethode</v>
+        <v>Operationeel grondstoffen</v>
       </c>
       <c r="F257" t="str">
         <v>null</v>
@@ -28624,10 +29392,10 @@
         <v>null</v>
       </c>
       <c r="V257" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_grondstoffen</v>
       </c>
       <c r="W257" t="str">
-        <v>null</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X257" t="str">
         <v>null</v>
@@ -28663,15 +29431,18 @@
         <v>null</v>
       </c>
       <c r="AI257" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-peilmethode/automatische_sonde|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-peilmethode/overige|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-peilmethode/peillint</v>
+        <v>null</v>
       </c>
       <c r="AJ257" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/grondstof|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/geproduceerd</v>
+      </c>
+      <c r="AK257" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_pomptoestand</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_grondwater</v>
       </c>
       <c r="B258" t="str">
         <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
@@ -28683,7 +29454,7 @@
         <v>null</v>
       </c>
       <c r="E258" t="str">
-        <v>Pomptoestand</v>
+        <v>null</v>
       </c>
       <c r="F258" t="str">
         <v>null</v>
@@ -28734,10 +29505,10 @@
         <v>null</v>
       </c>
       <c r="V258" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_grondwater</v>
       </c>
       <c r="W258" t="str">
-        <v>null</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X258" t="str">
         <v>null</v>
@@ -28773,15 +29544,18 @@
         <v>null</v>
       </c>
       <c r="AI258" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-pomptoestand/rust|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-pomptoestand/werking</v>
+        <v>null</v>
       </c>
       <c r="AJ258" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/onttrekking|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/peilmeting|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting</v>
+      </c>
+      <c r="AK258" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_techniekmonstername</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_lucht</v>
       </c>
       <c r="B259" t="str">
         <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
@@ -28793,7 +29567,7 @@
         <v>null</v>
       </c>
       <c r="E259" t="str">
-        <v>Techniek monstername</v>
+        <v>Operationele gegevens</v>
       </c>
       <c r="F259" t="str">
         <v>null</v>
@@ -28883,15 +29657,18 @@
         <v>null</v>
       </c>
       <c r="AI259" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-techniekmonstername/aftap</v>
+        <v>null</v>
       </c>
       <c r="AJ259" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/feature_ep</v>
+      </c>
+      <c r="AK259" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_toepassingwijze</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_lucht_bron</v>
       </c>
       <c r="B260" t="str">
         <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
@@ -28903,7 +29680,7 @@
         <v>null</v>
       </c>
       <c r="E260" t="str">
-        <v>Toepassingswijze</v>
+        <v>null</v>
       </c>
       <c r="F260" t="str">
         <v>null</v>
@@ -28993,15 +29770,18 @@
         <v>null</v>
       </c>
       <c r="AI260" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-toepassingswijze/brandstof|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-toepassingswijze/dispers|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-toepassingswijze/overige</v>
+        <v>null</v>
       </c>
       <c r="AJ260" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/feature_bron</v>
+      </c>
+      <c r="AK260" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_toestand_indicator</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_lucht_emissie</v>
       </c>
       <c r="B261" t="str">
         <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
@@ -29064,10 +29844,10 @@
         <v>null</v>
       </c>
       <c r="V261" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_toestand_indicator</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_lucht_emissie</v>
       </c>
       <c r="W261" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X261" t="str">
         <v>null</v>
@@ -29103,15 +29883,18 @@
         <v>null</v>
       </c>
       <c r="AI261" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-toestand-indicator/droog|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-toestand-indicator/nat</v>
+        <v>null</v>
       </c>
       <c r="AJ261" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie</v>
+      </c>
+      <c r="AK261" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_water</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_lucht_rapportering</v>
       </c>
       <c r="B262" t="str">
         <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
@@ -29123,7 +29906,7 @@
         <v>null</v>
       </c>
       <c r="E262" t="str">
-        <v>Operationele gegevens</v>
+        <v>null</v>
       </c>
       <c r="F262" t="str">
         <v>null</v>
@@ -29147,10 +29930,10 @@
         <v>null</v>
       </c>
       <c r="M262" t="str">
-        <v>Selecteer de controleinrichting waarop je de lozing wil rapporteren.</v>
+        <v>null</v>
       </c>
       <c r="N262" t="str">
-        <v>Selecteer de controleinrichting waarop je de lozing wil rapporteren.</v>
+        <v>null</v>
       </c>
       <c r="O262" t="str">
         <v>null</v>
@@ -29174,10 +29957,10 @@
         <v>null</v>
       </c>
       <c r="V262" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_lucht_rapportering</v>
       </c>
       <c r="W262" t="str">
-        <v>null</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X262" t="str">
         <v>null</v>
@@ -29213,15 +29996,18 @@
         <v>null</v>
       </c>
       <c r="AI262" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/feature</v>
+        <v>null</v>
       </c>
       <c r="AJ262" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/afvalproduct|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/geproduceerde_stof|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/brandstof|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/verbruikte_stof</v>
+      </c>
+      <c r="AK262" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_water_lozing</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_peilmethode</v>
       </c>
       <c r="B263" t="str">
         <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
@@ -29233,7 +30019,7 @@
         <v>null</v>
       </c>
       <c r="E263" t="str">
-        <v>null</v>
+        <v>Peilmethode</v>
       </c>
       <c r="F263" t="str">
         <v>null</v>
@@ -29284,10 +30070,10 @@
         <v>null</v>
       </c>
       <c r="V263" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_water_lozing</v>
+        <v>null</v>
       </c>
       <c r="W263" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>null</v>
       </c>
       <c r="X263" t="str">
         <v>null</v>
@@ -29323,15 +30109,18 @@
         <v>null</v>
       </c>
       <c r="AI263" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/abnormale-lozing|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing</v>
+        <v>null</v>
       </c>
       <c r="AJ263" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-peilmethode/automatische_sonde|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-peilmethode/overige|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-peilmethode/peillint</v>
+      </c>
+      <c r="AK263" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_zelfcontrole_lucht</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_pomptoestand</v>
       </c>
       <c r="B264" t="str">
         <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
@@ -29343,7 +30132,7 @@
         <v>null</v>
       </c>
       <c r="E264" t="str">
-        <v>Operationele gegevens</v>
+        <v>Pomptoestand</v>
       </c>
       <c r="F264" t="str">
         <v>null</v>
@@ -29433,15 +30222,18 @@
         <v>null</v>
       </c>
       <c r="AI264" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/feature</v>
+        <v>null</v>
       </c>
       <c r="AJ264" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-pomptoestand/rust|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-pomptoestand/werking</v>
+      </c>
+      <c r="AK264" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_zelfcontrole_lucht_meting</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_techniekmonstername</v>
       </c>
       <c r="B265" t="str">
         <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
@@ -29453,7 +30245,7 @@
         <v>null</v>
       </c>
       <c r="E265" t="str">
-        <v>null</v>
+        <v>Techniek monstername</v>
       </c>
       <c r="F265" t="str">
         <v>null</v>
@@ -29504,10 +30296,10 @@
         <v>null</v>
       </c>
       <c r="V265" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_zelfcontrole_lucht_meting</v>
+        <v>null</v>
       </c>
       <c r="W265" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>null</v>
       </c>
       <c r="X265" t="str">
         <v>null</v>
@@ -29543,15 +30335,18 @@
         <v>null</v>
       </c>
       <c r="AI265" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/meting</v>
+        <v>null</v>
       </c>
       <c r="AJ265" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-techniekmonstername/aftap</v>
+      </c>
+      <c r="AK265" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_zelfcontrole_meetfrequentie</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_toepassingwijze</v>
       </c>
       <c r="B266" t="str">
         <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
@@ -29563,7 +30358,7 @@
         <v>null</v>
       </c>
       <c r="E266" t="str">
-        <v>Meetfrequentie</v>
+        <v>Toepassingswijze</v>
       </c>
       <c r="F266" t="str">
         <v>null</v>
@@ -29653,15 +30448,18 @@
         <v>null</v>
       </c>
       <c r="AI266" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-meetfrequentie/test</v>
+        <v>null</v>
       </c>
       <c r="AJ266" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-toepassingswijze/brandstof|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-toepassingswijze/dispers|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-toepassingswijze/overige</v>
+      </c>
+      <c r="AK266" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_zelfcontrole_water</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_toestand_indicator</v>
       </c>
       <c r="B267" t="str">
         <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
@@ -29673,7 +30471,7 @@
         <v>null</v>
       </c>
       <c r="E267" t="str">
-        <v>Operationele gegevens</v>
+        <v>null</v>
       </c>
       <c r="F267" t="str">
         <v>null</v>
@@ -29724,10 +30522,10 @@
         <v>null</v>
       </c>
       <c r="V267" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_toestand_indicator</v>
       </c>
       <c r="W267" t="str">
-        <v>null</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X267" t="str">
         <v>null</v>
@@ -29763,15 +30561,18 @@
         <v>null</v>
       </c>
       <c r="AI267" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/feature</v>
+        <v>null</v>
       </c>
       <c r="AJ267" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-toestand-indicator/droog|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-toestand-indicator/nat</v>
+      </c>
+      <c r="AK267" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_zelfcontrole_water_meting</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_water</v>
       </c>
       <c r="B268" t="str">
         <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
@@ -29783,7 +30584,7 @@
         <v>null</v>
       </c>
       <c r="E268" t="str">
-        <v>null</v>
+        <v>Operationele gegevens</v>
       </c>
       <c r="F268" t="str">
         <v>null</v>
@@ -29807,10 +30608,10 @@
         <v>null</v>
       </c>
       <c r="M268" t="str">
-        <v>null</v>
+        <v>Selecteer de controleinrichting waarop je de lozing wil rapporteren.</v>
       </c>
       <c r="N268" t="str">
-        <v>null</v>
+        <v>Selecteer de controleinrichting waarop je de lozing wil rapporteren.</v>
       </c>
       <c r="O268" t="str">
         <v>null</v>
@@ -29834,10 +30635,10 @@
         <v>null</v>
       </c>
       <c r="V268" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_zelfcontrole_water_meting</v>
+        <v>null</v>
       </c>
       <c r="W268" t="str">
-        <v>2026-08-24T08:16:17.128Z</v>
+        <v>null</v>
       </c>
       <c r="X268" t="str">
         <v>null</v>
@@ -29873,15 +30674,18 @@
         <v>null</v>
       </c>
       <c r="AI268" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/meting|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/labo|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/parameter</v>
+        <v>null</v>
       </c>
       <c r="AJ268" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/feature</v>
+      </c>
+      <c r="AK268" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_water_lozing</v>
       </c>
       <c r="B269" t="str">
         <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
@@ -29893,7 +30697,7 @@
         <v>null</v>
       </c>
       <c r="E269" t="str">
-        <v>Procedure types</v>
+        <v>null</v>
       </c>
       <c r="F269" t="str">
         <v>null</v>
@@ -29917,10 +30721,10 @@
         <v>null</v>
       </c>
       <c r="M269" t="str">
-        <v>Een typering van verschillende procedures.</v>
+        <v>null</v>
       </c>
       <c r="N269" t="str">
-        <v>Een typering van verschillende procedures.</v>
+        <v>null</v>
       </c>
       <c r="O269" t="str">
         <v>null</v>
@@ -29944,10 +30748,10 @@
         <v>null</v>
       </c>
       <c r="V269" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_water_lozing</v>
       </c>
       <c r="W269" t="str">
-        <v>null</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X269" t="str">
         <v>null</v>
@@ -29983,15 +30787,18 @@
         <v>null</v>
       </c>
       <c r="AI269" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/emissie|https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/hoofdactiviteit|https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/meting|https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/onttrekking|https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/transport|https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/uitwissel|https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/verwerking</v>
+        <v>null</v>
       </c>
       <c r="AJ269" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/abnormale-lozing|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing</v>
+      </c>
+      <c r="AK269" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/rubriek_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_zelfcontrole_lucht</v>
       </c>
       <c r="B270" t="str">
         <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
@@ -30003,7 +30810,7 @@
         <v>null</v>
       </c>
       <c r="E270" t="str">
-        <v>Rubriek types</v>
+        <v>Operationele gegevens</v>
       </c>
       <c r="F270" t="str">
         <v>null</v>
@@ -30093,18 +30900,21 @@
         <v>null</v>
       </c>
       <c r="AI270" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/rubriek-type/vlarem</v>
+        <v>null</v>
       </c>
       <c r="AJ270" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/feature</v>
+      </c>
+      <c r="AK270" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_eigenschappen</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_zelfcontrole_lucht_meting</v>
       </c>
       <c r="B271" t="str">
-        <v>null</v>
+        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
       </c>
       <c r="C271" t="str">
         <v>null</v>
@@ -30164,10 +30974,10 @@
         <v>null</v>
       </c>
       <c r="V271" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_zelfcontrole_lucht_meting</v>
       </c>
       <c r="W271" t="str">
-        <v>null</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X271" t="str">
         <v>null</v>
@@ -30206,15 +31016,18 @@
         <v>null</v>
       </c>
       <c r="AJ271" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-eigenschappen/lozingspunt-lozingsplaats|https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_eigenschappen|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-eigenschappen/schouw-diameter|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-eigenschappen/schouw-hoogte|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/geinstalleerd_vermogen|https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_eigenschappen|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/geinstalleerde_opslagcapaciteit|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/geinstalleerde_productiecapaciteit|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/luchtzuiverings_techniek|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/type_energie_productie|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/verwijderingsrendement|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/waterzuiveringstechniek|https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-eigenschappen/diepte|https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/meetpunt_eigenschappen|https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-eigenschappen/referentiepunt|https://data.omgeving.vlaanderen.be/id/concept/riepr/onttrekkingspunt-eigenschappen/diepte|https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/onttrekkingspunt_eigenschappen|https://data.omgeving.vlaanderen.be/id/concept/riepr/onttrekkingspunt-eigenschappen/watervoerendelaag|https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/uitwisselpunt_eigenschappen</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/meting</v>
+      </c>
+      <c r="AK271" t="str">
+        <v>null</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_zelfcontrole_meetfrequentie</v>
       </c>
       <c r="B272" t="str">
-        <v>null</v>
+        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
       </c>
       <c r="C272" t="str">
         <v>null</v>
@@ -30223,7 +31036,7 @@
         <v>null</v>
       </c>
       <c r="E272" t="str">
-        <v>null</v>
+        <v>Meetfrequentie</v>
       </c>
       <c r="F272" t="str">
         <v>null</v>
@@ -30316,12 +31129,15 @@
         <v>null</v>
       </c>
       <c r="AJ272" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/lozingspunt|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/emissiepunt|https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/fakkel|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/gebouw|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/stookinstallatie|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/opslag_overslag|https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_type|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/luchtzuivering|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/waterzuivering|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/geothermisch|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/gpbv|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/installatie|https://data.omgeving.vlaanderen.be/id/concept/riepr/uitwisselpunt-type/uitwisselpunt|https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/uitwisselpunt_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-meetfrequentie/test</v>
+      </c>
+      <c r="AK272" t="str">
+        <v>null</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/thema_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_zelfcontrole_water</v>
       </c>
       <c r="B273" t="str">
         <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
@@ -30333,7 +31149,7 @@
         <v>null</v>
       </c>
       <c r="E273" t="str">
-        <v>Thematische stroom</v>
+        <v>Operationele gegevens</v>
       </c>
       <c r="F273" t="str">
         <v>null</v>
@@ -30423,15 +31239,18 @@
         <v>null</v>
       </c>
       <c r="AI273" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/thema-type/grondstoffen|https://data.omgeving.vlaanderen.be/id/concept/riepr/thema-type/grondwater|https://data.omgeving.vlaanderen.be/id/concept/riepr/thema-type/lucht|https://data.omgeving.vlaanderen.be/id/concept/riepr/thema-type/water|https://data.omgeving.vlaanderen.be/id/concept/riepr/thema-type/zelfcontrole-lucht|https://data.omgeving.vlaanderen.be/id/concept/riepr/thema-type/zelfcontrole-water</v>
+        <v>null</v>
       </c>
       <c r="AJ273" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/feature</v>
+      </c>
+      <c r="AK273" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/uitwisselpunt_eigenschappen</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_zelfcontrole_water_meting</v>
       </c>
       <c r="B274" t="str">
         <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
@@ -30443,7 +31262,7 @@
         <v>null</v>
       </c>
       <c r="E274" t="str">
-        <v>Uitwisselpunt eigenschappen</v>
+        <v>null</v>
       </c>
       <c r="F274" t="str">
         <v>null</v>
@@ -30455,7 +31274,7 @@
         <v>null</v>
       </c>
       <c r="I274" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_eigenschappen</v>
+        <v>null</v>
       </c>
       <c r="J274" t="str">
         <v>null</v>
@@ -30467,10 +31286,10 @@
         <v>null</v>
       </c>
       <c r="M274" t="str">
-        <v>Een typering van verschillende eigenschappen voor installaties.</v>
+        <v>null</v>
       </c>
       <c r="N274" t="str">
-        <v>Een typering van verschillende eigenschappen voor installaties.</v>
+        <v>null</v>
       </c>
       <c r="O274" t="str">
         <v>null</v>
@@ -30494,10 +31313,10 @@
         <v>null</v>
       </c>
       <c r="V274" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_zelfcontrole_water_meting</v>
       </c>
       <c r="W274" t="str">
-        <v>null</v>
+        <v>2026-08-27T08:27:38.700Z</v>
       </c>
       <c r="X274" t="str">
         <v>null</v>
@@ -30536,12 +31355,15 @@
         <v>null</v>
       </c>
       <c r="AJ274" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/meting|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/labo|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/parameter</v>
+      </c>
+      <c r="AK274" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/uitwisselpunt_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
       </c>
       <c r="B275" t="str">
         <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
@@ -30553,105 +31375,899 @@
         <v>null</v>
       </c>
       <c r="E275" t="str">
+        <v>Procedure types</v>
+      </c>
+      <c r="F275" t="str">
+        <v>null</v>
+      </c>
+      <c r="G275" t="str">
+        <v>null</v>
+      </c>
+      <c r="H275" t="str">
+        <v>null</v>
+      </c>
+      <c r="I275" t="str">
+        <v>null</v>
+      </c>
+      <c r="J275" t="str">
+        <v>null</v>
+      </c>
+      <c r="K275" t="str">
+        <v>null</v>
+      </c>
+      <c r="L275" t="str">
+        <v>null</v>
+      </c>
+      <c r="M275" t="str">
+        <v>Een typering van verschillende procedures.</v>
+      </c>
+      <c r="N275" t="str">
+        <v>Een typering van verschillende procedures.</v>
+      </c>
+      <c r="O275" t="str">
+        <v>null</v>
+      </c>
+      <c r="P275" t="str">
+        <v>null</v>
+      </c>
+      <c r="Q275" t="str">
+        <v>null</v>
+      </c>
+      <c r="R275" t="str">
+        <v>null</v>
+      </c>
+      <c r="S275" t="str">
+        <v>null</v>
+      </c>
+      <c r="T275" t="str">
+        <v>null</v>
+      </c>
+      <c r="U275" t="str">
+        <v>null</v>
+      </c>
+      <c r="V275" t="str">
+        <v>null</v>
+      </c>
+      <c r="W275" t="str">
+        <v>null</v>
+      </c>
+      <c r="X275" t="str">
+        <v>null</v>
+      </c>
+      <c r="Y275" t="str">
+        <v>null</v>
+      </c>
+      <c r="Z275" t="str">
+        <v>null</v>
+      </c>
+      <c r="AA275" t="str">
+        <v>null</v>
+      </c>
+      <c r="AB275" t="str">
+        <v>null</v>
+      </c>
+      <c r="AC275" t="str">
+        <v>null</v>
+      </c>
+      <c r="AD275" t="str">
+        <v>null</v>
+      </c>
+      <c r="AE275" t="str">
+        <v>null</v>
+      </c>
+      <c r="AF275" t="str">
+        <v>null</v>
+      </c>
+      <c r="AG275" t="str">
+        <v>null</v>
+      </c>
+      <c r="AH275" t="str">
+        <v>null</v>
+      </c>
+      <c r="AI275" t="str">
+        <v>null</v>
+      </c>
+      <c r="AJ275" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/emissie|https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/hoofdactiviteit|https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/meting|https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/onttrekking|https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/transport|https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/uitwissel|https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/verwerking</v>
+      </c>
+      <c r="AK275" t="str">
+        <v>null</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/rubriek_type</v>
+      </c>
+      <c r="B276" t="str">
+        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
+      </c>
+      <c r="C276" t="str">
+        <v>null</v>
+      </c>
+      <c r="D276" t="str">
+        <v>null</v>
+      </c>
+      <c r="E276" t="str">
+        <v>Rubriek types</v>
+      </c>
+      <c r="F276" t="str">
+        <v>null</v>
+      </c>
+      <c r="G276" t="str">
+        <v>null</v>
+      </c>
+      <c r="H276" t="str">
+        <v>null</v>
+      </c>
+      <c r="I276" t="str">
+        <v>null</v>
+      </c>
+      <c r="J276" t="str">
+        <v>null</v>
+      </c>
+      <c r="K276" t="str">
+        <v>null</v>
+      </c>
+      <c r="L276" t="str">
+        <v>null</v>
+      </c>
+      <c r="M276" t="str">
+        <v>null</v>
+      </c>
+      <c r="N276" t="str">
+        <v>null</v>
+      </c>
+      <c r="O276" t="str">
+        <v>null</v>
+      </c>
+      <c r="P276" t="str">
+        <v>null</v>
+      </c>
+      <c r="Q276" t="str">
+        <v>null</v>
+      </c>
+      <c r="R276" t="str">
+        <v>null</v>
+      </c>
+      <c r="S276" t="str">
+        <v>null</v>
+      </c>
+      <c r="T276" t="str">
+        <v>null</v>
+      </c>
+      <c r="U276" t="str">
+        <v>null</v>
+      </c>
+      <c r="V276" t="str">
+        <v>null</v>
+      </c>
+      <c r="W276" t="str">
+        <v>null</v>
+      </c>
+      <c r="X276" t="str">
+        <v>null</v>
+      </c>
+      <c r="Y276" t="str">
+        <v>null</v>
+      </c>
+      <c r="Z276" t="str">
+        <v>null</v>
+      </c>
+      <c r="AA276" t="str">
+        <v>null</v>
+      </c>
+      <c r="AB276" t="str">
+        <v>null</v>
+      </c>
+      <c r="AC276" t="str">
+        <v>null</v>
+      </c>
+      <c r="AD276" t="str">
+        <v>null</v>
+      </c>
+      <c r="AE276" t="str">
+        <v>null</v>
+      </c>
+      <c r="AF276" t="str">
+        <v>null</v>
+      </c>
+      <c r="AG276" t="str">
+        <v>null</v>
+      </c>
+      <c r="AH276" t="str">
+        <v>null</v>
+      </c>
+      <c r="AI276" t="str">
+        <v>null</v>
+      </c>
+      <c r="AJ276" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/rubriek-type/vlarem</v>
+      </c>
+      <c r="AK276" t="str">
+        <v>null</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
+      </c>
+      <c r="B277" t="str">
+        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
+      </c>
+      <c r="C277" t="str">
+        <v>null</v>
+      </c>
+      <c r="D277" t="str">
+        <v>null</v>
+      </c>
+      <c r="E277" t="str">
+        <v>Status types</v>
+      </c>
+      <c r="F277" t="str">
+        <v>null</v>
+      </c>
+      <c r="G277" t="str">
+        <v>null</v>
+      </c>
+      <c r="H277" t="str">
+        <v>null</v>
+      </c>
+      <c r="I277" t="str">
+        <v>null</v>
+      </c>
+      <c r="J277" t="str">
+        <v>null</v>
+      </c>
+      <c r="K277" t="str">
+        <v>null</v>
+      </c>
+      <c r="L277" t="str">
+        <v>null</v>
+      </c>
+      <c r="M277" t="str">
+        <v>Een typering van verschillende statussen (actief, inactief, ...).</v>
+      </c>
+      <c r="N277" t="str">
+        <v>Een typering van verschillende statussen (actief, inactief, ...).</v>
+      </c>
+      <c r="O277" t="str">
+        <v>null</v>
+      </c>
+      <c r="P277" t="str">
+        <v>null</v>
+      </c>
+      <c r="Q277" t="str">
+        <v>null</v>
+      </c>
+      <c r="R277" t="str">
+        <v>null</v>
+      </c>
+      <c r="S277" t="str">
+        <v>null</v>
+      </c>
+      <c r="T277" t="str">
+        <v>null</v>
+      </c>
+      <c r="U277" t="str">
+        <v>null</v>
+      </c>
+      <c r="V277" t="str">
+        <v>null</v>
+      </c>
+      <c r="W277" t="str">
+        <v>null</v>
+      </c>
+      <c r="X277" t="str">
+        <v>null</v>
+      </c>
+      <c r="Y277" t="str">
+        <v>null</v>
+      </c>
+      <c r="Z277" t="str">
+        <v>null</v>
+      </c>
+      <c r="AA277" t="str">
+        <v>null</v>
+      </c>
+      <c r="AB277" t="str">
+        <v>null</v>
+      </c>
+      <c r="AC277" t="str">
+        <v>null</v>
+      </c>
+      <c r="AD277" t="str">
+        <v>null</v>
+      </c>
+      <c r="AE277" t="str">
+        <v>null</v>
+      </c>
+      <c r="AF277" t="str">
+        <v>null</v>
+      </c>
+      <c r="AG277" t="str">
+        <v>null</v>
+      </c>
+      <c r="AH277" t="str">
+        <v>null</v>
+      </c>
+      <c r="AI277" t="str">
+        <v>null</v>
+      </c>
+      <c r="AJ277" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/definitief_uit_dienst|https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/in_dienst|https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/ontmanteld|https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/tijdelijk_uit_dienst|https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/verkeerde_registratie|https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/voorgesteld</v>
+      </c>
+      <c r="AK277" t="str">
+        <v>null</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_eigenschappen</v>
+      </c>
+      <c r="B278" t="str">
+        <v>null</v>
+      </c>
+      <c r="C278" t="str">
+        <v>null</v>
+      </c>
+      <c r="D278" t="str">
+        <v>null</v>
+      </c>
+      <c r="E278" t="str">
+        <v>null</v>
+      </c>
+      <c r="F278" t="str">
+        <v>null</v>
+      </c>
+      <c r="G278" t="str">
+        <v>null</v>
+      </c>
+      <c r="H278" t="str">
+        <v>null</v>
+      </c>
+      <c r="I278" t="str">
+        <v>null</v>
+      </c>
+      <c r="J278" t="str">
+        <v>null</v>
+      </c>
+      <c r="K278" t="str">
+        <v>null</v>
+      </c>
+      <c r="L278" t="str">
+        <v>null</v>
+      </c>
+      <c r="M278" t="str">
+        <v>null</v>
+      </c>
+      <c r="N278" t="str">
+        <v>null</v>
+      </c>
+      <c r="O278" t="str">
+        <v>null</v>
+      </c>
+      <c r="P278" t="str">
+        <v>null</v>
+      </c>
+      <c r="Q278" t="str">
+        <v>null</v>
+      </c>
+      <c r="R278" t="str">
+        <v>null</v>
+      </c>
+      <c r="S278" t="str">
+        <v>null</v>
+      </c>
+      <c r="T278" t="str">
+        <v>null</v>
+      </c>
+      <c r="U278" t="str">
+        <v>null</v>
+      </c>
+      <c r="V278" t="str">
+        <v>null</v>
+      </c>
+      <c r="W278" t="str">
+        <v>null</v>
+      </c>
+      <c r="X278" t="str">
+        <v>null</v>
+      </c>
+      <c r="Y278" t="str">
+        <v>null</v>
+      </c>
+      <c r="Z278" t="str">
+        <v>null</v>
+      </c>
+      <c r="AA278" t="str">
+        <v>null</v>
+      </c>
+      <c r="AB278" t="str">
+        <v>null</v>
+      </c>
+      <c r="AC278" t="str">
+        <v>null</v>
+      </c>
+      <c r="AD278" t="str">
+        <v>null</v>
+      </c>
+      <c r="AE278" t="str">
+        <v>null</v>
+      </c>
+      <c r="AF278" t="str">
+        <v>null</v>
+      </c>
+      <c r="AG278" t="str">
+        <v>null</v>
+      </c>
+      <c r="AH278" t="str">
+        <v>null</v>
+      </c>
+      <c r="AI278" t="str">
+        <v>null</v>
+      </c>
+      <c r="AJ278" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK278" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-eigenschappen/lozingspunt-lozingsplaats|https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_eigenschappen|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-eigenschappen/schouw-diameter|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-eigenschappen/schouw-hoogte|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/geinstalleerd_vermogen|https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_eigenschappen|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/geinstalleerde_opslagcapaciteit|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/geinstalleerde_productiecapaciteit|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/luchtzuiverings_techniek|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/type_energie_productie|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/verwijderingsrendement|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/waterzuiveringstechniek|https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-eigenschappen/diepte|https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/meetpunt_eigenschappen|https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-eigenschappen/referentiepunt|https://data.omgeving.vlaanderen.be/id/concept/riepr/onttrekkingspunt-eigenschappen/diepte|https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/onttrekkingspunt_eigenschappen|https://data.omgeving.vlaanderen.be/id/concept/riepr/onttrekkingspunt-eigenschappen/watervoerendelaag|https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/uitwisselpunt_eigenschappen</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_type</v>
+      </c>
+      <c r="B279" t="str">
+        <v>null</v>
+      </c>
+      <c r="C279" t="str">
+        <v>null</v>
+      </c>
+      <c r="D279" t="str">
+        <v>null</v>
+      </c>
+      <c r="E279" t="str">
+        <v>null</v>
+      </c>
+      <c r="F279" t="str">
+        <v>null</v>
+      </c>
+      <c r="G279" t="str">
+        <v>null</v>
+      </c>
+      <c r="H279" t="str">
+        <v>null</v>
+      </c>
+      <c r="I279" t="str">
+        <v>null</v>
+      </c>
+      <c r="J279" t="str">
+        <v>null</v>
+      </c>
+      <c r="K279" t="str">
+        <v>null</v>
+      </c>
+      <c r="L279" t="str">
+        <v>null</v>
+      </c>
+      <c r="M279" t="str">
+        <v>null</v>
+      </c>
+      <c r="N279" t="str">
+        <v>null</v>
+      </c>
+      <c r="O279" t="str">
+        <v>null</v>
+      </c>
+      <c r="P279" t="str">
+        <v>null</v>
+      </c>
+      <c r="Q279" t="str">
+        <v>null</v>
+      </c>
+      <c r="R279" t="str">
+        <v>null</v>
+      </c>
+      <c r="S279" t="str">
+        <v>null</v>
+      </c>
+      <c r="T279" t="str">
+        <v>null</v>
+      </c>
+      <c r="U279" t="str">
+        <v>null</v>
+      </c>
+      <c r="V279" t="str">
+        <v>null</v>
+      </c>
+      <c r="W279" t="str">
+        <v>null</v>
+      </c>
+      <c r="X279" t="str">
+        <v>null</v>
+      </c>
+      <c r="Y279" t="str">
+        <v>null</v>
+      </c>
+      <c r="Z279" t="str">
+        <v>null</v>
+      </c>
+      <c r="AA279" t="str">
+        <v>null</v>
+      </c>
+      <c r="AB279" t="str">
+        <v>null</v>
+      </c>
+      <c r="AC279" t="str">
+        <v>null</v>
+      </c>
+      <c r="AD279" t="str">
+        <v>null</v>
+      </c>
+      <c r="AE279" t="str">
+        <v>null</v>
+      </c>
+      <c r="AF279" t="str">
+        <v>null</v>
+      </c>
+      <c r="AG279" t="str">
+        <v>null</v>
+      </c>
+      <c r="AH279" t="str">
+        <v>null</v>
+      </c>
+      <c r="AI279" t="str">
+        <v>null</v>
+      </c>
+      <c r="AJ279" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK279" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/lozingspunt|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/emissiepunt|https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/fakkel|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/gebouw|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/stookinstallatie|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/opslag_overslag|https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_type|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/luchtzuivering|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/waterzuivering|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/geothermisch|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/gpbv|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/installatie|https://data.omgeving.vlaanderen.be/id/concept/riepr/uitwisselpunt-type/uitwisselpunt|https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/uitwisselpunt_type</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/thema_type</v>
+      </c>
+      <c r="B280" t="str">
+        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
+      </c>
+      <c r="C280" t="str">
+        <v>null</v>
+      </c>
+      <c r="D280" t="str">
+        <v>null</v>
+      </c>
+      <c r="E280" t="str">
+        <v>Thematische stroom</v>
+      </c>
+      <c r="F280" t="str">
+        <v>null</v>
+      </c>
+      <c r="G280" t="str">
+        <v>null</v>
+      </c>
+      <c r="H280" t="str">
+        <v>null</v>
+      </c>
+      <c r="I280" t="str">
+        <v>null</v>
+      </c>
+      <c r="J280" t="str">
+        <v>null</v>
+      </c>
+      <c r="K280" t="str">
+        <v>null</v>
+      </c>
+      <c r="L280" t="str">
+        <v>null</v>
+      </c>
+      <c r="M280" t="str">
+        <v>null</v>
+      </c>
+      <c r="N280" t="str">
+        <v>null</v>
+      </c>
+      <c r="O280" t="str">
+        <v>null</v>
+      </c>
+      <c r="P280" t="str">
+        <v>null</v>
+      </c>
+      <c r="Q280" t="str">
+        <v>null</v>
+      </c>
+      <c r="R280" t="str">
+        <v>null</v>
+      </c>
+      <c r="S280" t="str">
+        <v>null</v>
+      </c>
+      <c r="T280" t="str">
+        <v>null</v>
+      </c>
+      <c r="U280" t="str">
+        <v>null</v>
+      </c>
+      <c r="V280" t="str">
+        <v>null</v>
+      </c>
+      <c r="W280" t="str">
+        <v>null</v>
+      </c>
+      <c r="X280" t="str">
+        <v>null</v>
+      </c>
+      <c r="Y280" t="str">
+        <v>null</v>
+      </c>
+      <c r="Z280" t="str">
+        <v>null</v>
+      </c>
+      <c r="AA280" t="str">
+        <v>null</v>
+      </c>
+      <c r="AB280" t="str">
+        <v>null</v>
+      </c>
+      <c r="AC280" t="str">
+        <v>null</v>
+      </c>
+      <c r="AD280" t="str">
+        <v>null</v>
+      </c>
+      <c r="AE280" t="str">
+        <v>null</v>
+      </c>
+      <c r="AF280" t="str">
+        <v>null</v>
+      </c>
+      <c r="AG280" t="str">
+        <v>null</v>
+      </c>
+      <c r="AH280" t="str">
+        <v>null</v>
+      </c>
+      <c r="AI280" t="str">
+        <v>null</v>
+      </c>
+      <c r="AJ280" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/thema-type/grondstoffen|https://data.omgeving.vlaanderen.be/id/concept/riepr/thema-type/grondwater|https://data.omgeving.vlaanderen.be/id/concept/riepr/thema-type/lucht|https://data.omgeving.vlaanderen.be/id/concept/riepr/thema-type/water|https://data.omgeving.vlaanderen.be/id/concept/riepr/thema-type/zelfcontrole-lucht|https://data.omgeving.vlaanderen.be/id/concept/riepr/thema-type/zelfcontrole-water</v>
+      </c>
+      <c r="AK280" t="str">
+        <v>null</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/uitwisselpunt_eigenschappen</v>
+      </c>
+      <c r="B281" t="str">
+        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
+      </c>
+      <c r="C281" t="str">
+        <v>null</v>
+      </c>
+      <c r="D281" t="str">
+        <v>null</v>
+      </c>
+      <c r="E281" t="str">
+        <v>Uitwisselpunt eigenschappen</v>
+      </c>
+      <c r="F281" t="str">
+        <v>null</v>
+      </c>
+      <c r="G281" t="str">
+        <v>null</v>
+      </c>
+      <c r="H281" t="str">
+        <v>null</v>
+      </c>
+      <c r="I281" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_eigenschappen</v>
+      </c>
+      <c r="J281" t="str">
+        <v>null</v>
+      </c>
+      <c r="K281" t="str">
+        <v>null</v>
+      </c>
+      <c r="L281" t="str">
+        <v>null</v>
+      </c>
+      <c r="M281" t="str">
+        <v>Een typering van verschillende eigenschappen voor installaties.</v>
+      </c>
+      <c r="N281" t="str">
+        <v>Een typering van verschillende eigenschappen voor installaties.</v>
+      </c>
+      <c r="O281" t="str">
+        <v>null</v>
+      </c>
+      <c r="P281" t="str">
+        <v>null</v>
+      </c>
+      <c r="Q281" t="str">
+        <v>null</v>
+      </c>
+      <c r="R281" t="str">
+        <v>null</v>
+      </c>
+      <c r="S281" t="str">
+        <v>null</v>
+      </c>
+      <c r="T281" t="str">
+        <v>null</v>
+      </c>
+      <c r="U281" t="str">
+        <v>null</v>
+      </c>
+      <c r="V281" t="str">
+        <v>null</v>
+      </c>
+      <c r="W281" t="str">
+        <v>null</v>
+      </c>
+      <c r="X281" t="str">
+        <v>null</v>
+      </c>
+      <c r="Y281" t="str">
+        <v>null</v>
+      </c>
+      <c r="Z281" t="str">
+        <v>null</v>
+      </c>
+      <c r="AA281" t="str">
+        <v>null</v>
+      </c>
+      <c r="AB281" t="str">
+        <v>null</v>
+      </c>
+      <c r="AC281" t="str">
+        <v>null</v>
+      </c>
+      <c r="AD281" t="str">
+        <v>null</v>
+      </c>
+      <c r="AE281" t="str">
+        <v>null</v>
+      </c>
+      <c r="AF281" t="str">
+        <v>null</v>
+      </c>
+      <c r="AG281" t="str">
+        <v>null</v>
+      </c>
+      <c r="AH281" t="str">
+        <v>null</v>
+      </c>
+      <c r="AI281" t="str">
+        <v>null</v>
+      </c>
+      <c r="AJ281" t="str">
+        <v>null</v>
+      </c>
+      <c r="AK281" t="str">
+        <v>null</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/uitwisselpunt_type</v>
+      </c>
+      <c r="B282" t="str">
+        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
+      </c>
+      <c r="C282" t="str">
+        <v>null</v>
+      </c>
+      <c r="D282" t="str">
+        <v>null</v>
+      </c>
+      <c r="E282" t="str">
         <v>Uitwisselpunt types</v>
       </c>
-      <c r="F275" t="str">
-        <v>null</v>
-      </c>
-      <c r="G275" t="str">
-        <v>null</v>
-      </c>
-      <c r="H275" t="str">
-        <v>null</v>
-      </c>
-      <c r="I275" t="str">
+      <c r="F282" t="str">
+        <v>null</v>
+      </c>
+      <c r="G282" t="str">
+        <v>null</v>
+      </c>
+      <c r="H282" t="str">
+        <v>null</v>
+      </c>
+      <c r="I282" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_type</v>
       </c>
-      <c r="J275" t="str">
-        <v>null</v>
-      </c>
-      <c r="K275" t="str">
-        <v>null</v>
-      </c>
-      <c r="L275" t="str">
-        <v>null</v>
-      </c>
-      <c r="M275" t="str">
+      <c r="J282" t="str">
+        <v>null</v>
+      </c>
+      <c r="K282" t="str">
+        <v>null</v>
+      </c>
+      <c r="L282" t="str">
+        <v>null</v>
+      </c>
+      <c r="M282" t="str">
         <v>Een typering van verschillende soorten installaties.</v>
       </c>
-      <c r="N275" t="str">
+      <c r="N282" t="str">
         <v>Een typering van verschillende soorten installaties.</v>
       </c>
-      <c r="O275" t="str">
-        <v>null</v>
-      </c>
-      <c r="P275" t="str">
-        <v>null</v>
-      </c>
-      <c r="Q275" t="str">
-        <v>null</v>
-      </c>
-      <c r="R275" t="str">
-        <v>null</v>
-      </c>
-      <c r="S275" t="str">
-        <v>null</v>
-      </c>
-      <c r="T275" t="str">
-        <v>null</v>
-      </c>
-      <c r="U275" t="str">
-        <v>null</v>
-      </c>
-      <c r="V275" t="str">
-        <v>null</v>
-      </c>
-      <c r="W275" t="str">
-        <v>null</v>
-      </c>
-      <c r="X275" t="str">
-        <v>null</v>
-      </c>
-      <c r="Y275" t="str">
-        <v>null</v>
-      </c>
-      <c r="Z275" t="str">
-        <v>null</v>
-      </c>
-      <c r="AA275" t="str">
-        <v>null</v>
-      </c>
-      <c r="AB275" t="str">
-        <v>null</v>
-      </c>
-      <c r="AC275" t="str">
-        <v>null</v>
-      </c>
-      <c r="AD275" t="str">
-        <v>null</v>
-      </c>
-      <c r="AE275" t="str">
-        <v>null</v>
-      </c>
-      <c r="AF275" t="str">
-        <v>null</v>
-      </c>
-      <c r="AG275" t="str">
-        <v>null</v>
-      </c>
-      <c r="AH275" t="str">
-        <v>null</v>
-      </c>
-      <c r="AI275" t="str">
+      <c r="O282" t="str">
+        <v>null</v>
+      </c>
+      <c r="P282" t="str">
+        <v>null</v>
+      </c>
+      <c r="Q282" t="str">
+        <v>null</v>
+      </c>
+      <c r="R282" t="str">
+        <v>null</v>
+      </c>
+      <c r="S282" t="str">
+        <v>null</v>
+      </c>
+      <c r="T282" t="str">
+        <v>null</v>
+      </c>
+      <c r="U282" t="str">
+        <v>null</v>
+      </c>
+      <c r="V282" t="str">
+        <v>null</v>
+      </c>
+      <c r="W282" t="str">
+        <v>null</v>
+      </c>
+      <c r="X282" t="str">
+        <v>null</v>
+      </c>
+      <c r="Y282" t="str">
+        <v>null</v>
+      </c>
+      <c r="Z282" t="str">
+        <v>null</v>
+      </c>
+      <c r="AA282" t="str">
+        <v>null</v>
+      </c>
+      <c r="AB282" t="str">
+        <v>null</v>
+      </c>
+      <c r="AC282" t="str">
+        <v>null</v>
+      </c>
+      <c r="AD282" t="str">
+        <v>null</v>
+      </c>
+      <c r="AE282" t="str">
+        <v>null</v>
+      </c>
+      <c r="AF282" t="str">
+        <v>null</v>
+      </c>
+      <c r="AG282" t="str">
+        <v>null</v>
+      </c>
+      <c r="AH282" t="str">
+        <v>null</v>
+      </c>
+      <c r="AI282" t="str">
+        <v>null</v>
+      </c>
+      <c r="AJ282" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/uitwisselpunt-type/uitwisselpunt</v>
       </c>
-      <c r="AJ275" t="str">
+      <c r="AK282" t="str">
         <v>null</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AJ275"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AK282"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/src/main/resources/be/vlaanderen/omgeving/data/id/conceptscheme/rie-iepr/rie-iepr.xlsx
+++ b/src/main/resources/be/vlaanderen/omgeving/data/id/conceptscheme/rie-iepr/rie-iepr.xlsx
@@ -4987,7 +4987,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/verwijderingsrendement</v>
       </c>
       <c r="W41" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X41" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/verwijderingsrendement_percentage|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/verwijderingsrendement_stof</v>
@@ -5100,7 +5100,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/verwijderingsrendement_percentage</v>
       </c>
       <c r="W42" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X42" t="str">
         <v>null</v>
@@ -5213,7 +5213,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/verwijderingsrendement_stof</v>
       </c>
       <c r="W43" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X43" t="str">
         <v>null</v>
@@ -5326,7 +5326,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/waterzuiveringstechniek</v>
       </c>
       <c r="W44" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X44" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/waterzuiveringstechniek_ingebruikvan|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/waterzuiveringstechniek_techniek</v>
@@ -5439,7 +5439,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/waterzuiveringstechniek_ingebruikvan</v>
       </c>
       <c r="W45" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X45" t="str">
         <v>null</v>
@@ -5552,7 +5552,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/waterzuiveringstechniek_techniek</v>
       </c>
       <c r="W46" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X46" t="str">
         <v>null</v>
@@ -6682,7 +6682,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-eigenschappen/referentiepunt</v>
       </c>
       <c r="W56" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X56" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-eigenschappen/referentiepunt_diepte|https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-eigenschappen/referentiepunt_naam</v>
@@ -6795,7 +6795,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-eigenschappen/referentiepunt_diepte</v>
       </c>
       <c r="W57" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X57" t="str">
         <v>null</v>
@@ -6908,7 +6908,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-eigenschappen/referentiepunt_naam</v>
       </c>
       <c r="W58" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X58" t="str">
         <v>null</v>
@@ -9507,7 +9507,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-be</v>
       </c>
       <c r="W81" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X81" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-be-naam|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-be-on|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-be-ve</v>
@@ -9620,7 +9620,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-be-naam</v>
       </c>
       <c r="W82" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X82" t="str">
         <v>null</v>
@@ -9733,7 +9733,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-be-on</v>
       </c>
       <c r="W83" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X83" t="str">
         <v>null</v>
@@ -9846,7 +9846,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-be-ve</v>
       </c>
       <c r="W84" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X84" t="str">
         <v>null</v>
@@ -9959,7 +9959,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-buitenland</v>
       </c>
       <c r="W85" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X85" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-buitenland-btw|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-buitenland-naam</v>
@@ -10072,7 +10072,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-buitenland-btw</v>
       </c>
       <c r="W86" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X86" t="str">
         <v>null</v>
@@ -10185,7 +10185,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-buitenland-naam</v>
       </c>
       <c r="W87" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X87" t="str">
         <v>null</v>
@@ -10298,7 +10298,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-none</v>
       </c>
       <c r="W88" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X88" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-none-adres|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-none-naam</v>
@@ -10411,7 +10411,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-none-adres</v>
       </c>
       <c r="W89" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X89" t="str">
         <v>null</v>
@@ -10524,7 +10524,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-none-naam</v>
       </c>
       <c r="W90" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X90" t="str">
         <v>null</v>
@@ -10637,7 +10637,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-werf</v>
       </c>
       <c r="W91" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X91" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-werf-naam</v>
@@ -10750,7 +10750,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-werf-naam</v>
       </c>
       <c r="W92" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X92" t="str">
         <v>null</v>
@@ -10976,7 +10976,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/grondstof</v>
       </c>
       <c r="W94" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X94" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-be|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-buitenland|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-none|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-werf|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/grondstof_bestemming_type|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/grondstof_opmerking|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/grondstof_hoeveelheid|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/grondstof_materiaalcode|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/grondstof_omschrijving|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/grondstof_toepassingswijze</v>
@@ -11089,7 +11089,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/grondstof_bestemming_type</v>
       </c>
       <c r="W95" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X95" t="str">
         <v>null</v>
@@ -11202,7 +11202,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/grondstof_hoeveelheid</v>
       </c>
       <c r="W96" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X96" t="str">
         <v>null</v>
@@ -11315,7 +11315,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/grondstof_materiaalcode</v>
       </c>
       <c r="W97" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X97" t="str">
         <v>null</v>
@@ -11428,7 +11428,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/grondstof_omschrijving</v>
       </c>
       <c r="W98" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X98" t="str">
         <v>null</v>
@@ -11541,7 +11541,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/grondstof_opmerking</v>
       </c>
       <c r="W99" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X99" t="str">
         <v>null</v>
@@ -11654,7 +11654,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/grondstof_toepassingswijze</v>
       </c>
       <c r="W100" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X100" t="str">
         <v>null</v>
@@ -11767,7 +11767,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/begintoestand</v>
       </c>
       <c r="W101" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X101" t="str">
         <v>null</v>
@@ -11880,7 +11880,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/datum</v>
       </c>
       <c r="W102" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X102" t="str">
         <v>null</v>
@@ -11993,7 +11993,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/diepte</v>
       </c>
       <c r="W103" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X103" t="str">
         <v>null</v>
@@ -12106,7 +12106,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/duur-stil</v>
       </c>
       <c r="W104" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X104" t="str">
         <v>null</v>
@@ -12219,7 +12219,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/eindtoestand</v>
       </c>
       <c r="W105" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X105" t="str">
         <v>null</v>
@@ -12332,7 +12332,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting</v>
       </c>
       <c r="W106" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X106" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-bemonsteringsinstrument|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-labo|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-datum|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting_feature|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-diepte|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-referentiepunt|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-monsternummer|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-parameter|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-techniek</v>
@@ -12445,7 +12445,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-bemonsteringsinstrument</v>
       </c>
       <c r="W107" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X107" t="str">
         <v>null</v>
@@ -12558,7 +12558,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-datum</v>
       </c>
       <c r="W108" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X108" t="str">
         <v>null</v>
@@ -12671,7 +12671,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-diepte</v>
       </c>
       <c r="W109" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X109" t="str">
         <v>null</v>
@@ -12784,7 +12784,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-labo</v>
       </c>
       <c r="W110" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X110" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-labo-naam</v>
@@ -12897,7 +12897,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-labo-naam</v>
       </c>
       <c r="W111" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X111" t="str">
         <v>null</v>
@@ -13010,7 +13010,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-monsternummer</v>
       </c>
       <c r="W112" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X112" t="str">
         <v>null</v>
@@ -13123,7 +13123,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-parameter</v>
       </c>
       <c r="W113" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X113" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-parameter-datum|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-parameter-parameter|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-parameter-limiet|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-parameter-meetwaarde|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-parameter-methode</v>
@@ -13236,7 +13236,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-parameter-datum</v>
       </c>
       <c r="W114" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X114" t="str">
         <v>null</v>
@@ -13349,7 +13349,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-parameter-limiet</v>
       </c>
       <c r="W115" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X115" t="str">
         <v>null</v>
@@ -13462,7 +13462,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-parameter-meetwaarde</v>
       </c>
       <c r="W116" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X116" t="str">
         <v>null</v>
@@ -13575,7 +13575,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-parameter-methode</v>
       </c>
       <c r="W117" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X117" t="str">
         <v>null</v>
@@ -13688,7 +13688,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-parameter-parameter</v>
       </c>
       <c r="W118" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X118" t="str">
         <v>null</v>
@@ -13801,7 +13801,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-referentiepunt</v>
       </c>
       <c r="W119" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X119" t="str">
         <v>null</v>
@@ -13914,7 +13914,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-techniek</v>
       </c>
       <c r="W120" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X120" t="str">
         <v>null</v>
@@ -14027,7 +14027,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting_feature</v>
       </c>
       <c r="W121" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X121" t="str">
         <v>null</v>
@@ -14140,7 +14140,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/onttrekking</v>
       </c>
       <c r="W122" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X122" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/begintoestand|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/volume|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/eindtoestand|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/onttrekking_feature|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/periode|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/type-debiet</v>
@@ -14253,7 +14253,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/onttrekking_feature</v>
       </c>
       <c r="W123" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X123" t="str">
         <v>null</v>
@@ -14366,7 +14366,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/peilmethode</v>
       </c>
       <c r="W124" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X124" t="str">
         <v>null</v>
@@ -14479,7 +14479,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/peilmeting</v>
       </c>
       <c r="W125" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X125" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/datum|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/peilmeting_feature|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/diepte|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/referentiepunt|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/duur-stil|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/pomptoestand|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/peilmethode|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/volume-rust|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/volume-werking</v>
@@ -14592,7 +14592,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/peilmeting_feature</v>
       </c>
       <c r="W126" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X126" t="str">
         <v>null</v>
@@ -14705,7 +14705,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/periode</v>
       </c>
       <c r="W127" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X127" t="str">
         <v>null</v>
@@ -14818,7 +14818,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/pomptoestand</v>
       </c>
       <c r="W128" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X128" t="str">
         <v>null</v>
@@ -14931,7 +14931,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/referentiepunt</v>
       </c>
       <c r="W129" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X129" t="str">
         <v>null</v>
@@ -15044,7 +15044,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/type-debiet</v>
       </c>
       <c r="W130" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X130" t="str">
         <v>null</v>
@@ -15157,7 +15157,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/volume</v>
       </c>
       <c r="W131" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X131" t="str">
         <v>null</v>
@@ -15270,7 +15270,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/volume-rust</v>
       </c>
       <c r="W132" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X132" t="str">
         <v>null</v>
@@ -15383,7 +15383,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/volume-werking</v>
       </c>
       <c r="W133" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X133" t="str">
         <v>null</v>
@@ -15496,7 +15496,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/afvalproduct</v>
       </c>
       <c r="W134" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X134" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/afvalproduct_aard|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/afvalproduct_hoeveelheid|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/afvalproduct_naam</v>
@@ -15609,7 +15609,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/afvalproduct_aard</v>
       </c>
       <c r="W135" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X135" t="str">
         <v>null</v>
@@ -15722,7 +15722,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/afvalproduct_hoeveelheid</v>
       </c>
       <c r="W136" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X136" t="str">
         <v>null</v>
@@ -15835,7 +15835,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/afvalproduct_naam</v>
       </c>
       <c r="W137" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X137" t="str">
         <v>null</v>
@@ -15948,7 +15948,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/brandstof</v>
       </c>
       <c r="W138" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X138" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/brandstof_as|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/brandstof_naam|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/brandstof_s|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/brandstof_verbruik</v>
@@ -16061,7 +16061,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/brandstof_as</v>
       </c>
       <c r="W139" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X139" t="str">
         <v>null</v>
@@ -16174,7 +16174,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/brandstof_naam</v>
       </c>
       <c r="W140" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X140" t="str">
         <v>null</v>
@@ -16287,7 +16287,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/brandstof_s</v>
       </c>
       <c r="W141" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X141" t="str">
         <v>null</v>
@@ -16400,7 +16400,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/brandstof_verbruik</v>
       </c>
       <c r="W142" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X142" t="str">
         <v>null</v>
@@ -16513,7 +16513,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie</v>
       </c>
       <c r="W143" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X143" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie_luchtoverschot|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie_parameter|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie_temperatuur|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie_vochtgehalte|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie_zuurstofgehalte|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissieduur|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissieperiode|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissieritme|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissietoestand|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissietype</v>
@@ -16626,7 +16626,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie_luchtoverschot</v>
       </c>
       <c r="W144" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X144" t="str">
         <v>null</v>
@@ -16739,7 +16739,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie_parameter</v>
       </c>
       <c r="W145" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X145" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie_parameter_massastroom|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie_parameter_meetfrequentie|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie_parameter_parameter|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie_parameter_standaardafwijking</v>
@@ -16852,7 +16852,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie_parameter_massastroom</v>
       </c>
       <c r="W146" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X146" t="str">
         <v>null</v>
@@ -16965,7 +16965,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie_parameter_meetfrequentie</v>
       </c>
       <c r="W147" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X147" t="str">
         <v>null</v>
@@ -17078,7 +17078,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie_parameter_parameter</v>
       </c>
       <c r="W148" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X148" t="str">
         <v>null</v>
@@ -17191,7 +17191,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie_parameter_standaardafwijking</v>
       </c>
       <c r="W149" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X149" t="str">
         <v>null</v>
@@ -17304,7 +17304,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie_temperatuur</v>
       </c>
       <c r="W150" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X150" t="str">
         <v>null</v>
@@ -17417,7 +17417,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie_vochtgehalte</v>
       </c>
       <c r="W151" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X151" t="str">
         <v>null</v>
@@ -17530,7 +17530,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie_zuurstofgehalte</v>
       </c>
       <c r="W152" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X152" t="str">
         <v>null</v>
@@ -17643,7 +17643,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissieduur</v>
       </c>
       <c r="W153" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X153" t="str">
         <v>null</v>
@@ -17756,7 +17756,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissieperiode</v>
       </c>
       <c r="W154" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X154" t="str">
         <v>null</v>
@@ -17869,7 +17869,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissieritme</v>
       </c>
       <c r="W155" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X155" t="str">
         <v>null</v>
@@ -17982,7 +17982,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissietoestand</v>
       </c>
       <c r="W156" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X156" t="str">
         <v>null</v>
@@ -18095,7 +18095,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissietype</v>
       </c>
       <c r="W157" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X157" t="str">
         <v>null</v>
@@ -18434,7 +18434,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/geproduceerde_stof</v>
       </c>
       <c r="W160" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X160" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/geproduceerde_stof_aard|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/geproduceerde_stof_hoeveelheid|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/geproduceerde_stof_naam</v>
@@ -18547,7 +18547,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/geproduceerde_stof_aard</v>
       </c>
       <c r="W161" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X161" t="str">
         <v>null</v>
@@ -18660,7 +18660,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/geproduceerde_stof_hoeveelheid</v>
       </c>
       <c r="W162" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X162" t="str">
         <v>null</v>
@@ -18773,7 +18773,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/geproduceerde_stof_naam</v>
       </c>
       <c r="W163" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X163" t="str">
         <v>null</v>
@@ -18886,7 +18886,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/verbruikte_stof</v>
       </c>
       <c r="W164" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X164" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/verbruikte_stof_aard|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/verbruikte_stof_hoeveelheid|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/verbruikte_stof_naam</v>
@@ -18999,7 +18999,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/verbruikte_stof_aard</v>
       </c>
       <c r="W165" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X165" t="str">
         <v>null</v>
@@ -19112,7 +19112,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/verbruikte_stof_hoeveelheid</v>
       </c>
       <c r="W166" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X166" t="str">
         <v>null</v>
@@ -19225,7 +19225,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/verbruikte_stof_naam</v>
       </c>
       <c r="W167" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X167" t="str">
         <v>null</v>
@@ -20468,7 +20468,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-toestand-indicator/droog</v>
       </c>
       <c r="W178" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X178" t="str">
         <v>null</v>
@@ -20581,7 +20581,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-toestand-indicator/nat</v>
       </c>
       <c r="W179" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X179" t="str">
         <v>null</v>
@@ -20694,7 +20694,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/abnormale-lozing</v>
       </c>
       <c r="W180" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X180" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/abnormale-lozing-jaarvracht|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/abnormale-lozing-lozingsduur|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/abnormale-lozing-stof|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/abnormale-lozing-verklaring</v>
@@ -20807,7 +20807,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/abnormale-lozing-jaarvracht</v>
       </c>
       <c r="W181" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X181" t="str">
         <v>null</v>
@@ -20920,7 +20920,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/abnormale-lozing-lozingsduur</v>
       </c>
       <c r="W182" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X182" t="str">
         <v>null</v>
@@ -21033,7 +21033,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/abnormale-lozing-stof</v>
       </c>
       <c r="W183" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X183" t="str">
         <v>null</v>
@@ -21146,7 +21146,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/abnormale-lozing-verklaring</v>
       </c>
       <c r="W184" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X184" t="str">
         <v>null</v>
@@ -21372,7 +21372,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing</v>
       </c>
       <c r="W186" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X186" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing-bepalingsmethode|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing-jaarvracht|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing-bepalingsmethodeclassificatie|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing-concentratie|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing-meetfrequentie|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing-dagen|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing-debiet|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing-stof</v>
@@ -21485,7 +21485,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing-bepalingsmethode</v>
       </c>
       <c r="W187" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X187" t="str">
         <v>null</v>
@@ -21598,7 +21598,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing-bepalingsmethodeclassificatie</v>
       </c>
       <c r="W188" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X188" t="str">
         <v>null</v>
@@ -21711,7 +21711,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing-concentratie</v>
       </c>
       <c r="W189" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X189" t="str">
         <v>null</v>
@@ -21824,7 +21824,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing-dagen</v>
       </c>
       <c r="W190" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X190" t="str">
         <v>null</v>
@@ -21937,7 +21937,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing-debiet</v>
       </c>
       <c r="W191" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X191" t="str">
         <v>null</v>
@@ -22050,7 +22050,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing-jaarvracht</v>
       </c>
       <c r="W192" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X192" t="str">
         <v>null</v>
@@ -22163,7 +22163,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing-meetfrequentie</v>
       </c>
       <c r="W193" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X193" t="str">
         <v>null</v>
@@ -22276,7 +22276,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing-stof</v>
       </c>
       <c r="W194" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X194" t="str">
         <v>null</v>
@@ -22389,7 +22389,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/datum</v>
       </c>
       <c r="W195" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X195" t="str">
         <v>null</v>
@@ -22615,7 +22615,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/labo</v>
       </c>
       <c r="W197" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X197" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/labo-id|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/labo-naam</v>
@@ -22728,7 +22728,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/labo-id</v>
       </c>
       <c r="W198" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X198" t="str">
         <v>null</v>
@@ -22841,7 +22841,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/labo-naam</v>
       </c>
       <c r="W199" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X199" t="str">
         <v>null</v>
@@ -22954,7 +22954,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/meting</v>
       </c>
       <c r="W200" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X200" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/datum|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/labo|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/parameter</v>
@@ -23067,7 +23067,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/parameter</v>
       </c>
       <c r="W201" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X201" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/parameter-concentratie|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/parameter-parameter|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/parameter-meetfrequentie|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/parameter-meetonzekerheid|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/parameter-soort</v>
@@ -23180,7 +23180,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/parameter-concentratie</v>
       </c>
       <c r="W202" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X202" t="str">
         <v>null</v>
@@ -23293,7 +23293,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/parameter-meetfrequentie</v>
       </c>
       <c r="W203" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X203" t="str">
         <v>null</v>
@@ -23406,7 +23406,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/parameter-meetonzekerheid</v>
       </c>
       <c r="W204" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X204" t="str">
         <v>null</v>
@@ -23519,7 +23519,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/parameter-parameter</v>
       </c>
       <c r="W205" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X205" t="str">
         <v>null</v>
@@ -23632,7 +23632,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/parameter-soort</v>
       </c>
       <c r="W206" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X206" t="str">
         <v>null</v>
@@ -23745,7 +23745,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/datum</v>
       </c>
       <c r="W207" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X207" t="str">
         <v>null</v>
@@ -23971,7 +23971,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/labo</v>
       </c>
       <c r="W209" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X209" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/labo-id|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/labo-naam</v>
@@ -24084,7 +24084,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/labo-id</v>
       </c>
       <c r="W210" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X210" t="str">
         <v>null</v>
@@ -24197,7 +24197,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/labo-naam</v>
       </c>
       <c r="W211" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X211" t="str">
         <v>null</v>
@@ -24310,7 +24310,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/meting</v>
       </c>
       <c r="W212" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X212" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/datum</v>
@@ -24423,7 +24423,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/parameter</v>
       </c>
       <c r="W213" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X213" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/parameter-concentratie|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/parameter-parameter|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/parameter-meetfrequentie|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/parameter-meetonzekerheid|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/parameter-soort</v>
@@ -24536,7 +24536,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/parameter-concentratie</v>
       </c>
       <c r="W214" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X214" t="str">
         <v>null</v>
@@ -24649,7 +24649,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/parameter-meetfrequentie</v>
       </c>
       <c r="W215" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X215" t="str">
         <v>null</v>
@@ -24762,7 +24762,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/parameter-meetonzekerheid</v>
       </c>
       <c r="W216" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X216" t="str">
         <v>null</v>
@@ -24875,7 +24875,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/parameter-parameter</v>
       </c>
       <c r="W217" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X217" t="str">
         <v>null</v>
@@ -24988,7 +24988,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/parameter-soort</v>
       </c>
       <c r="W218" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X218" t="str">
         <v>null</v>
@@ -26005,7 +26005,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/definitief_uit_dienst</v>
       </c>
       <c r="W227" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X227" t="str">
         <v>null</v>
@@ -26118,7 +26118,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/in_dienst</v>
       </c>
       <c r="W228" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X228" t="str">
         <v>null</v>
@@ -26231,7 +26231,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/ontmanteld</v>
       </c>
       <c r="W229" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X229" t="str">
         <v>null</v>
@@ -26344,7 +26344,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/tijdelijk_uit_dienst</v>
       </c>
       <c r="W230" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X230" t="str">
         <v>null</v>
@@ -26457,7 +26457,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/verkeerde_registratie</v>
       </c>
       <c r="W231" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X231" t="str">
         <v>null</v>
@@ -26570,7 +26570,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/voorgesteld</v>
       </c>
       <c r="W232" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X232" t="str">
         <v>null</v>
@@ -28152,7 +28152,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_eigenschappen</v>
       </c>
       <c r="W246" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X246" t="str">
         <v>null</v>
@@ -28491,7 +28491,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/meetpunt_eigenschappen</v>
       </c>
       <c r="W249" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X249" t="str">
         <v>null</v>
@@ -29395,7 +29395,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_grondstoffen</v>
       </c>
       <c r="W257" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X257" t="str">
         <v>null</v>
@@ -29508,7 +29508,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_grondwater</v>
       </c>
       <c r="W258" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X258" t="str">
         <v>null</v>
@@ -29847,7 +29847,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_lucht_emissie</v>
       </c>
       <c r="W261" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X261" t="str">
         <v>null</v>
@@ -29960,7 +29960,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_lucht_rapportering</v>
       </c>
       <c r="W262" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X262" t="str">
         <v>null</v>
@@ -30525,7 +30525,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_toestand_indicator</v>
       </c>
       <c r="W267" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X267" t="str">
         <v>null</v>
@@ -30751,7 +30751,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_water_lozing</v>
       </c>
       <c r="W269" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X269" t="str">
         <v>null</v>
@@ -30977,7 +30977,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_zelfcontrole_lucht_meting</v>
       </c>
       <c r="W271" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X271" t="str">
         <v>null</v>
@@ -31316,7 +31316,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_zelfcontrole_water_meting</v>
       </c>
       <c r="W274" t="str">
-        <v>2026-08-27T08:27:38.700Z</v>
+        <v>2026-08-27T12:39:31.063Z</v>
       </c>
       <c r="X274" t="str">
         <v>null</v>

--- a/src/main/resources/be/vlaanderen/omgeving/data/id/conceptscheme/rie-iepr/rie-iepr.xlsx
+++ b/src/main/resources/be/vlaanderen/omgeving/data/id/conceptscheme/rie-iepr/rie-iepr.xlsx
@@ -443,67 +443,67 @@
         <v>note</v>
       </c>
       <c r="O1" t="str">
+        <v>isVersionOf</v>
+      </c>
+      <c r="P1" t="str">
+        <v>modified</v>
+      </c>
+      <c r="Q1" t="str">
         <v>narrower</v>
       </c>
-      <c r="P1" t="str">
+      <c r="R1" t="str">
         <v>narrowerTransitive</v>
       </c>
-      <c r="Q1" t="str">
+      <c r="S1" t="str">
         <v>semanticRelation</v>
       </c>
-      <c r="R1" t="str">
+      <c r="T1" t="str">
+        <v>broader</v>
+      </c>
+      <c r="U1" t="str">
+        <v>broaderTransitive</v>
+      </c>
+      <c r="V1" t="str">
+        <v>isVerplicht</v>
+      </c>
+      <c r="W1" t="str">
+        <v>narrowerPartitive</v>
+      </c>
+      <c r="X1" t="str">
+        <v>isMeervoudig</v>
+      </c>
+      <c r="Y1" t="str">
+        <v>broaderPartitive</v>
+      </c>
+      <c r="Z1" t="str">
+        <v>isOnzichtbaar</v>
+      </c>
+      <c r="AA1" t="str">
+        <v>related</v>
+      </c>
+      <c r="AB1" t="str">
+        <v>relevantClass</v>
+      </c>
+      <c r="AC1" t="str">
+        <v>conditionValue</v>
+      </c>
+      <c r="AD1" t="str">
+        <v>conditionPath</v>
+      </c>
+      <c r="AE1" t="str">
+        <v>_ui_after</v>
+      </c>
+      <c r="AF1" t="str">
+        <v>_ui_first</v>
+      </c>
+      <c r="AG1" t="str">
+        <v>isMultiselect</v>
+      </c>
+      <c r="AH1" t="str">
+        <v>relevantFeatureClass</v>
+      </c>
+      <c r="AI1" t="str">
         <v>isMeetbaar</v>
-      </c>
-      <c r="S1" t="str">
-        <v>broader</v>
-      </c>
-      <c r="T1" t="str">
-        <v>broaderTransitive</v>
-      </c>
-      <c r="U1" t="str">
-        <v>isVerplicht</v>
-      </c>
-      <c r="V1" t="str">
-        <v>isVersionOf</v>
-      </c>
-      <c r="W1" t="str">
-        <v>modified</v>
-      </c>
-      <c r="X1" t="str">
-        <v>narrowerPartitive</v>
-      </c>
-      <c r="Y1" t="str">
-        <v>isMeervoudig</v>
-      </c>
-      <c r="Z1" t="str">
-        <v>broaderPartitive</v>
-      </c>
-      <c r="AA1" t="str">
-        <v>isOnzichtbaar</v>
-      </c>
-      <c r="AB1" t="str">
-        <v>related</v>
-      </c>
-      <c r="AC1" t="str">
-        <v>relevantClass</v>
-      </c>
-      <c r="AD1" t="str">
-        <v>conditionValue</v>
-      </c>
-      <c r="AE1" t="str">
-        <v>conditionPath</v>
-      </c>
-      <c r="AF1" t="str">
-        <v>_ui_after</v>
-      </c>
-      <c r="AG1" t="str">
-        <v>_ui_first</v>
-      </c>
-      <c r="AH1" t="str">
-        <v>isMultiselect</v>
-      </c>
-      <c r="AI1" t="str">
-        <v>relevantFeatureClass</v>
       </c>
       <c r="AJ1" t="str">
         <v>hasTopConcept</v>
@@ -3607,19 +3607,19 @@
         <v>Een schoorsteen.</v>
       </c>
       <c r="O29" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_horizontale_uitstroom|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_verticale_uitstroom</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen</v>
       </c>
       <c r="P29" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_horizontale_uitstroom|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_verticale_uitstroom</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q29" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_horizontale_uitstroom|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_verticale_uitstroom</v>
       </c>
       <c r="R29" t="str">
-        <v>true</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_horizontale_uitstroom|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_verticale_uitstroom</v>
       </c>
       <c r="S29" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_horizontale_uitstroom|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_verticale_uitstroom</v>
       </c>
       <c r="T29" t="str">
         <v>null</v>
@@ -3726,7 +3726,7 @@
         <v>null</v>
       </c>
       <c r="Q30" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen</v>
+        <v>null</v>
       </c>
       <c r="R30" t="str">
         <v>null</v>
@@ -3738,7 +3738,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen</v>
       </c>
       <c r="U30" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen</v>
       </c>
       <c r="V30" t="str">
         <v>null</v>
@@ -3839,7 +3839,7 @@
         <v>null</v>
       </c>
       <c r="Q31" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen</v>
+        <v>null</v>
       </c>
       <c r="R31" t="str">
         <v>null</v>
@@ -3851,7 +3851,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen</v>
       </c>
       <c r="U31" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen</v>
       </c>
       <c r="V31" t="str">
         <v>null</v>
@@ -3946,16 +3946,16 @@
         <v>null</v>
       </c>
       <c r="O32" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/filter-type/injectie</v>
       </c>
       <c r="P32" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q32" t="str">
         <v>null</v>
       </c>
       <c r="R32" t="str">
-        <v>true</v>
+        <v>null</v>
       </c>
       <c r="S32" t="str">
         <v>null</v>
@@ -4059,16 +4059,16 @@
         <v>null</v>
       </c>
       <c r="O33" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/filter-type/omkeerbaar</v>
       </c>
       <c r="P33" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q33" t="str">
         <v>null</v>
       </c>
       <c r="R33" t="str">
-        <v>true</v>
+        <v>null</v>
       </c>
       <c r="S33" t="str">
         <v>null</v>
@@ -4172,16 +4172,16 @@
         <v>null</v>
       </c>
       <c r="O34" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/filter-type/peil</v>
       </c>
       <c r="P34" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q34" t="str">
         <v>null</v>
       </c>
       <c r="R34" t="str">
-        <v>true</v>
+        <v>null</v>
       </c>
       <c r="S34" t="str">
         <v>null</v>
@@ -4285,16 +4285,16 @@
         <v>null</v>
       </c>
       <c r="O35" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/filter-type/pomp</v>
       </c>
       <c r="P35" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q35" t="str">
         <v>null</v>
       </c>
       <c r="R35" t="str">
-        <v>true</v>
+        <v>null</v>
       </c>
       <c r="S35" t="str">
         <v>null</v>
@@ -4416,10 +4416,10 @@
         <v>null</v>
       </c>
       <c r="U36" t="str">
+        <v>null</v>
+      </c>
+      <c r="V36" t="str">
         <v>true</v>
-      </c>
-      <c r="V36" t="str">
-        <v>null</v>
       </c>
       <c r="W36" t="str">
         <v>null</v>
@@ -4963,10 +4963,10 @@
         <v>Samengestelde eigenschap voor verwijderingsrendement (stof en percentage).</v>
       </c>
       <c r="O41" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/verwijderingsrendement</v>
       </c>
       <c r="P41" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q41" t="str">
         <v>null</v>
@@ -4984,16 +4984,16 @@
         <v>null</v>
       </c>
       <c r="V41" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/verwijderingsrendement</v>
+        <v>null</v>
       </c>
       <c r="W41" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/verwijderingsrendement_percentage|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/verwijderingsrendement_stof</v>
       </c>
       <c r="X41" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/verwijderingsrendement_percentage|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/verwijderingsrendement_stof</v>
+        <v>true</v>
       </c>
       <c r="Y41" t="str">
-        <v>true</v>
+        <v>null</v>
       </c>
       <c r="Z41" t="str">
         <v>null</v>
@@ -5076,10 +5076,10 @@
         <v>Het % waarmee de verontreinigende stof door de luchtzuivering wordt verwijderd</v>
       </c>
       <c r="O42" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/verwijderingsrendement_percentage</v>
       </c>
       <c r="P42" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q42" t="str">
         <v>null</v>
@@ -5097,19 +5097,19 @@
         <v>null</v>
       </c>
       <c r="V42" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/verwijderingsrendement_percentage</v>
+        <v>null</v>
       </c>
       <c r="W42" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X42" t="str">
         <v>null</v>
       </c>
       <c r="Y42" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/verwijderingsrendement</v>
       </c>
       <c r="Z42" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/verwijderingsrendement</v>
+        <v>null</v>
       </c>
       <c r="AA42" t="str">
         <v>null</v>
@@ -5189,10 +5189,10 @@
         <v>De verontreinigende stoffen en broeikasgassen die door de luchtzuivering verwijderd worden</v>
       </c>
       <c r="O43" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/verwijderingsrendement_stof</v>
       </c>
       <c r="P43" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q43" t="str">
         <v>null</v>
@@ -5210,19 +5210,19 @@
         <v>null</v>
       </c>
       <c r="V43" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/verwijderingsrendement_stof</v>
+        <v>null</v>
       </c>
       <c r="W43" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X43" t="str">
         <v>null</v>
       </c>
       <c r="Y43" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/verwijderingsrendement</v>
       </c>
       <c r="Z43" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/verwijderingsrendement</v>
+        <v>null</v>
       </c>
       <c r="AA43" t="str">
         <v>null</v>
@@ -5302,10 +5302,10 @@
         <v>Samengestelde eigenschap voor waterzuiveringstechniek.</v>
       </c>
       <c r="O44" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/waterzuiveringstechniek</v>
       </c>
       <c r="P44" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q44" t="str">
         <v>null</v>
@@ -5323,16 +5323,16 @@
         <v>null</v>
       </c>
       <c r="V44" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/waterzuiveringstechniek</v>
+        <v>null</v>
       </c>
       <c r="W44" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/waterzuiveringstechniek_ingebruikvan|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/waterzuiveringstechniek_techniek</v>
       </c>
       <c r="X44" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/waterzuiveringstechniek_ingebruikvan|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/waterzuiveringstechniek_techniek</v>
+        <v>true</v>
       </c>
       <c r="Y44" t="str">
-        <v>true</v>
+        <v>null</v>
       </c>
       <c r="Z44" t="str">
         <v>null</v>
@@ -5415,10 +5415,10 @@
         <v>De datum van ingebruikname van de waterzuiveringstechniek.</v>
       </c>
       <c r="O45" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/waterzuiveringstechniek_ingebruikvan</v>
       </c>
       <c r="P45" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q45" t="str">
         <v>null</v>
@@ -5433,22 +5433,22 @@
         <v>null</v>
       </c>
       <c r="U45" t="str">
+        <v>null</v>
+      </c>
+      <c r="V45" t="str">
         <v>true</v>
       </c>
-      <c r="V45" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/waterzuiveringstechniek_ingebruikvan</v>
-      </c>
       <c r="W45" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X45" t="str">
         <v>null</v>
       </c>
       <c r="Y45" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/waterzuiveringstechniek</v>
       </c>
       <c r="Z45" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/waterzuiveringstechniek</v>
+        <v>null</v>
       </c>
       <c r="AA45" t="str">
         <v>null</v>
@@ -5528,10 +5528,10 @@
         <v>De techniek gebruikt voor de zuivering van water</v>
       </c>
       <c r="O46" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/waterzuiveringstechniek_techniek</v>
       </c>
       <c r="P46" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q46" t="str">
         <v>null</v>
@@ -5546,22 +5546,22 @@
         <v>null</v>
       </c>
       <c r="U46" t="str">
+        <v>null</v>
+      </c>
+      <c r="V46" t="str">
         <v>true</v>
       </c>
-      <c r="V46" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/waterzuiveringstechniek_techniek</v>
-      </c>
       <c r="W46" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X46" t="str">
         <v>null</v>
       </c>
       <c r="Y46" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/waterzuiveringstechniek</v>
       </c>
       <c r="Z46" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/waterzuiveringstechniek</v>
+        <v>null</v>
       </c>
       <c r="AA46" t="str">
         <v>null</v>
@@ -5647,7 +5647,7 @@
         <v>null</v>
       </c>
       <c r="Q47" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/stookinstallatie</v>
+        <v>null</v>
       </c>
       <c r="R47" t="str">
         <v>null</v>
@@ -5659,7 +5659,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/stookinstallatie</v>
       </c>
       <c r="U47" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/stookinstallatie</v>
       </c>
       <c r="V47" t="str">
         <v>null</v>
@@ -5900,10 +5900,10 @@
         <v>null</v>
       </c>
       <c r="Z49" t="str">
-        <v>null</v>
+        <v>true</v>
       </c>
       <c r="AA49" t="str">
-        <v>true</v>
+        <v>null</v>
       </c>
       <c r="AB49" t="str">
         <v>null</v>
@@ -6013,10 +6013,10 @@
         <v>null</v>
       </c>
       <c r="Z50" t="str">
-        <v>null</v>
+        <v>true</v>
       </c>
       <c r="AA50" t="str">
-        <v>true</v>
+        <v>null</v>
       </c>
       <c r="AB50" t="str">
         <v>null</v>
@@ -6319,19 +6319,19 @@
         <v>null</v>
       </c>
       <c r="O53" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/directe_stookinstallatie</v>
+        <v>null</v>
       </c>
       <c r="P53" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/directe_stookinstallatie</v>
+        <v>null</v>
       </c>
       <c r="Q53" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/directe_stookinstallatie</v>
       </c>
       <c r="R53" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/directe_stookinstallatie</v>
       </c>
       <c r="S53" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/directe_stookinstallatie</v>
       </c>
       <c r="T53" t="str">
         <v>null</v>
@@ -6563,10 +6563,10 @@
         <v>null</v>
       </c>
       <c r="U55" t="str">
+        <v>null</v>
+      </c>
+      <c r="V55" t="str">
         <v>true</v>
-      </c>
-      <c r="V55" t="str">
-        <v>null</v>
       </c>
       <c r="W55" t="str">
         <v>null</v>
@@ -6658,10 +6658,10 @@
         <v>Samengestelde eigenschap voor referentiepunt (naam en hoogte in meter).</v>
       </c>
       <c r="O56" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-eigenschappen/referentiepunt</v>
       </c>
       <c r="P56" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q56" t="str">
         <v>null</v>
@@ -6679,16 +6679,16 @@
         <v>null</v>
       </c>
       <c r="V56" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-eigenschappen/referentiepunt</v>
+        <v>null</v>
       </c>
       <c r="W56" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-eigenschappen/referentiepunt_diepte|https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-eigenschappen/referentiepunt_naam</v>
       </c>
       <c r="X56" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-eigenschappen/referentiepunt_diepte|https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-eigenschappen/referentiepunt_naam</v>
+        <v>true</v>
       </c>
       <c r="Y56" t="str">
-        <v>true</v>
+        <v>null</v>
       </c>
       <c r="Z56" t="str">
         <v>null</v>
@@ -6771,10 +6771,10 @@
         <v>null</v>
       </c>
       <c r="O57" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-eigenschappen/referentiepunt_diepte</v>
       </c>
       <c r="P57" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q57" t="str">
         <v>null</v>
@@ -6792,19 +6792,19 @@
         <v>null</v>
       </c>
       <c r="V57" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-eigenschappen/referentiepunt_diepte</v>
+        <v>null</v>
       </c>
       <c r="W57" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X57" t="str">
-        <v>null</v>
+        <v>false</v>
       </c>
       <c r="Y57" t="str">
-        <v>false</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-eigenschappen/referentiepunt</v>
       </c>
       <c r="Z57" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-eigenschappen/referentiepunt</v>
+        <v>null</v>
       </c>
       <c r="AA57" t="str">
         <v>null</v>
@@ -6884,10 +6884,10 @@
         <v>null</v>
       </c>
       <c r="O58" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-eigenschappen/referentiepunt_naam</v>
       </c>
       <c r="P58" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q58" t="str">
         <v>null</v>
@@ -6905,19 +6905,19 @@
         <v>null</v>
       </c>
       <c r="V58" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-eigenschappen/referentiepunt_naam</v>
+        <v>null</v>
       </c>
       <c r="W58" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X58" t="str">
-        <v>null</v>
+        <v>false</v>
       </c>
       <c r="Y58" t="str">
-        <v>false</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-eigenschappen/referentiepunt</v>
       </c>
       <c r="Z58" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-eigenschappen/referentiepunt</v>
+        <v>null</v>
       </c>
       <c r="AA58" t="str">
         <v>null</v>
@@ -6997,16 +6997,16 @@
         <v>Een controleinrichting is een meetpunt voorafgaand een lozingspunt of na een opnamepunt.</v>
       </c>
       <c r="O59" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-type/controleinrichting</v>
       </c>
       <c r="P59" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q59" t="str">
         <v>null</v>
       </c>
       <c r="R59" t="str">
-        <v>true</v>
+        <v>null</v>
       </c>
       <c r="S59" t="str">
         <v>null</v>
@@ -7110,16 +7110,16 @@
         <v>Een meetinrichting is een meetpunt voor een pompput.</v>
       </c>
       <c r="O60" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-type/debietmeter</v>
       </c>
       <c r="P60" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q60" t="str">
         <v>null</v>
       </c>
       <c r="R60" t="str">
-        <v>true</v>
+        <v>null</v>
       </c>
       <c r="S60" t="str">
         <v>null</v>
@@ -7223,16 +7223,16 @@
         <v>Een peilput is een put voor het meting van het grondwaterpeil en de kwaliteit van het grondwater</v>
       </c>
       <c r="O61" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-type/peilput</v>
       </c>
       <c r="P61" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q61" t="str">
         <v>null</v>
       </c>
       <c r="R61" t="str">
-        <v>true</v>
+        <v>null</v>
       </c>
       <c r="S61" t="str">
         <v>null</v>
@@ -8160,10 +8160,10 @@
         <v>null</v>
       </c>
       <c r="Z69" t="str">
-        <v>null</v>
+        <v>true</v>
       </c>
       <c r="AA69" t="str">
-        <v>true</v>
+        <v>null</v>
       </c>
       <c r="AB69" t="str">
         <v>null</v>
@@ -9483,20 +9483,20 @@
         <v>null</v>
       </c>
       <c r="O81" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-be</v>
       </c>
       <c r="P81" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q81" t="str">
+        <v>null</v>
+      </c>
+      <c r="R81" t="str">
+        <v>null</v>
+      </c>
+      <c r="S81" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-buitenland|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-none|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-werf</v>
       </c>
-      <c r="R81" t="str">
-        <v>null</v>
-      </c>
-      <c r="S81" t="str">
-        <v>null</v>
-      </c>
       <c r="T81" t="str">
         <v>null</v>
       </c>
@@ -9504,37 +9504,37 @@
         <v>null</v>
       </c>
       <c r="V81" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-be</v>
+        <v>null</v>
       </c>
       <c r="W81" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-be-naam|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-be-on|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-be-ve</v>
       </c>
       <c r="X81" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-be-naam|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-be-on|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-be-ve</v>
+        <v>null</v>
       </c>
       <c r="Y81" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/grondstof</v>
       </c>
       <c r="Z81" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/grondstof</v>
+        <v>null</v>
       </c>
       <c r="AA81" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-buitenland|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-none|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-werf</v>
       </c>
       <c r="AB81" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-buitenland|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-none|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-werf</v>
+        <v>http://www.w3.org/ns/prov#Agent</v>
       </c>
       <c r="AC81" t="str">
-        <v>http://www.w3.org/ns/prov#Agent</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-bestemmingstype/belgisch</v>
       </c>
       <c r="AD81" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-bestemmingstype/belgisch</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/grondstof_bestemming_type</v>
       </c>
       <c r="AE81" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/grondstof_bestemming_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/grondstof_opmerking</v>
       </c>
       <c r="AF81" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/grondstof_opmerking</v>
+        <v>null</v>
       </c>
       <c r="AG81" t="str">
         <v>null</v>
@@ -9596,10 +9596,10 @@
         <v>null</v>
       </c>
       <c r="O82" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-be-naam</v>
       </c>
       <c r="P82" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q82" t="str">
         <v>null</v>
@@ -9614,22 +9614,22 @@
         <v>null</v>
       </c>
       <c r="U82" t="str">
+        <v>null</v>
+      </c>
+      <c r="V82" t="str">
         <v>false</v>
       </c>
-      <c r="V82" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-be-naam</v>
-      </c>
       <c r="W82" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X82" t="str">
         <v>null</v>
       </c>
       <c r="Y82" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-be</v>
       </c>
       <c r="Z82" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-be</v>
+        <v>null</v>
       </c>
       <c r="AA82" t="str">
         <v>null</v>
@@ -9647,10 +9647,10 @@
         <v>null</v>
       </c>
       <c r="AF82" t="str">
-        <v>null</v>
+        <v>true</v>
       </c>
       <c r="AG82" t="str">
-        <v>true</v>
+        <v>null</v>
       </c>
       <c r="AH82" t="str">
         <v>null</v>
@@ -9709,10 +9709,10 @@
         <v>null</v>
       </c>
       <c r="O83" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-be-on</v>
       </c>
       <c r="P83" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q83" t="str">
         <v>null</v>
@@ -9727,22 +9727,22 @@
         <v>null</v>
       </c>
       <c r="U83" t="str">
+        <v>null</v>
+      </c>
+      <c r="V83" t="str">
         <v>true</v>
       </c>
-      <c r="V83" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-be-on</v>
-      </c>
       <c r="W83" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X83" t="str">
         <v>null</v>
       </c>
       <c r="Y83" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-be</v>
       </c>
       <c r="Z83" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-be</v>
+        <v>null</v>
       </c>
       <c r="AA83" t="str">
         <v>null</v>
@@ -9757,10 +9757,10 @@
         <v>null</v>
       </c>
       <c r="AE83" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-be-naam</v>
       </c>
       <c r="AF83" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-be-naam</v>
+        <v>null</v>
       </c>
       <c r="AG83" t="str">
         <v>null</v>
@@ -9822,10 +9822,10 @@
         <v>null</v>
       </c>
       <c r="O84" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-be-ve</v>
       </c>
       <c r="P84" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q84" t="str">
         <v>null</v>
@@ -9840,22 +9840,22 @@
         <v>null</v>
       </c>
       <c r="U84" t="str">
+        <v>null</v>
+      </c>
+      <c r="V84" t="str">
         <v>true</v>
       </c>
-      <c r="V84" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-be-ve</v>
-      </c>
       <c r="W84" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X84" t="str">
         <v>null</v>
       </c>
       <c r="Y84" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-be</v>
       </c>
       <c r="Z84" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-be</v>
+        <v>null</v>
       </c>
       <c r="AA84" t="str">
         <v>null</v>
@@ -9870,10 +9870,10 @@
         <v>null</v>
       </c>
       <c r="AE84" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-be-on</v>
       </c>
       <c r="AF84" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-be-on</v>
+        <v>null</v>
       </c>
       <c r="AG84" t="str">
         <v>null</v>
@@ -9935,20 +9935,20 @@
         <v>null</v>
       </c>
       <c r="O85" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-buitenland</v>
       </c>
       <c r="P85" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q85" t="str">
+        <v>null</v>
+      </c>
+      <c r="R85" t="str">
+        <v>null</v>
+      </c>
+      <c r="S85" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-be|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-none|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-werf</v>
       </c>
-      <c r="R85" t="str">
-        <v>null</v>
-      </c>
-      <c r="S85" t="str">
-        <v>null</v>
-      </c>
       <c r="T85" t="str">
         <v>null</v>
       </c>
@@ -9956,37 +9956,37 @@
         <v>null</v>
       </c>
       <c r="V85" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-buitenland</v>
+        <v>null</v>
       </c>
       <c r="W85" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-buitenland-btw|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-buitenland-naam</v>
       </c>
       <c r="X85" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-buitenland-btw|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-buitenland-naam</v>
+        <v>null</v>
       </c>
       <c r="Y85" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/grondstof</v>
       </c>
       <c r="Z85" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/grondstof</v>
+        <v>null</v>
       </c>
       <c r="AA85" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-be|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-none|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-werf</v>
       </c>
       <c r="AB85" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-be|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-none|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-werf</v>
+        <v>http://www.w3.org/ns/prov#Agent</v>
       </c>
       <c r="AC85" t="str">
-        <v>http://www.w3.org/ns/prov#Agent</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-bestemmingstype/buitenlands</v>
       </c>
       <c r="AD85" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-bestemmingstype/buitenlands</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/grondstof_bestemming_type</v>
       </c>
       <c r="AE85" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/grondstof_bestemming_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-be</v>
       </c>
       <c r="AF85" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-be</v>
+        <v>null</v>
       </c>
       <c r="AG85" t="str">
         <v>null</v>
@@ -10048,10 +10048,10 @@
         <v>null</v>
       </c>
       <c r="O86" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-buitenland-btw</v>
       </c>
       <c r="P86" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q86" t="str">
         <v>null</v>
@@ -10066,22 +10066,22 @@
         <v>null</v>
       </c>
       <c r="U86" t="str">
+        <v>null</v>
+      </c>
+      <c r="V86" t="str">
         <v>true</v>
       </c>
-      <c r="V86" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-buitenland-btw</v>
-      </c>
       <c r="W86" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X86" t="str">
         <v>null</v>
       </c>
       <c r="Y86" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-buitenland</v>
       </c>
       <c r="Z86" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-buitenland</v>
+        <v>null</v>
       </c>
       <c r="AA86" t="str">
         <v>null</v>
@@ -10096,10 +10096,10 @@
         <v>null</v>
       </c>
       <c r="AE86" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-buitenland-naam</v>
       </c>
       <c r="AF86" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-buitenland-naam</v>
+        <v>null</v>
       </c>
       <c r="AG86" t="str">
         <v>null</v>
@@ -10161,10 +10161,10 @@
         <v>null</v>
       </c>
       <c r="O87" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-buitenland-naam</v>
       </c>
       <c r="P87" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q87" t="str">
         <v>null</v>
@@ -10179,22 +10179,22 @@
         <v>null</v>
       </c>
       <c r="U87" t="str">
+        <v>null</v>
+      </c>
+      <c r="V87" t="str">
         <v>false</v>
       </c>
-      <c r="V87" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-buitenland-naam</v>
-      </c>
       <c r="W87" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X87" t="str">
         <v>null</v>
       </c>
       <c r="Y87" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-buitenland</v>
       </c>
       <c r="Z87" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-buitenland</v>
+        <v>null</v>
       </c>
       <c r="AA87" t="str">
         <v>null</v>
@@ -10212,10 +10212,10 @@
         <v>null</v>
       </c>
       <c r="AF87" t="str">
-        <v>null</v>
+        <v>true</v>
       </c>
       <c r="AG87" t="str">
-        <v>true</v>
+        <v>null</v>
       </c>
       <c r="AH87" t="str">
         <v>null</v>
@@ -10274,20 +10274,20 @@
         <v>null</v>
       </c>
       <c r="O88" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-none</v>
       </c>
       <c r="P88" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q88" t="str">
+        <v>null</v>
+      </c>
+      <c r="R88" t="str">
+        <v>null</v>
+      </c>
+      <c r="S88" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-be|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-buitenland|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-werf</v>
       </c>
-      <c r="R88" t="str">
-        <v>null</v>
-      </c>
-      <c r="S88" t="str">
-        <v>null</v>
-      </c>
       <c r="T88" t="str">
         <v>null</v>
       </c>
@@ -10295,37 +10295,37 @@
         <v>null</v>
       </c>
       <c r="V88" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-none</v>
+        <v>null</v>
       </c>
       <c r="W88" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-none-adres|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-none-naam</v>
       </c>
       <c r="X88" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-none-adres|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-none-naam</v>
+        <v>null</v>
       </c>
       <c r="Y88" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/grondstof</v>
       </c>
       <c r="Z88" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/grondstof</v>
+        <v>null</v>
       </c>
       <c r="AA88" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-be|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-buitenland|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-werf</v>
       </c>
       <c r="AB88" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-be|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-buitenland|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-werf</v>
+        <v>http://www.w3.org/ns/prov#Agent</v>
       </c>
       <c r="AC88" t="str">
-        <v>http://www.w3.org/ns/prov#Agent</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-bestemmingstype/geen_onderneming</v>
       </c>
       <c r="AD88" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-bestemmingstype/geen_onderneming</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/grondstof_bestemming_type</v>
       </c>
       <c r="AE88" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/grondstof_bestemming_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-werf</v>
       </c>
       <c r="AF88" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-werf</v>
+        <v>null</v>
       </c>
       <c r="AG88" t="str">
         <v>null</v>
@@ -10387,10 +10387,10 @@
         <v>null</v>
       </c>
       <c r="O89" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-none-adres</v>
       </c>
       <c r="P89" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q89" t="str">
         <v>null</v>
@@ -10405,22 +10405,22 @@
         <v>null</v>
       </c>
       <c r="U89" t="str">
+        <v>null</v>
+      </c>
+      <c r="V89" t="str">
         <v>true</v>
       </c>
-      <c r="V89" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-none-adres</v>
-      </c>
       <c r="W89" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X89" t="str">
         <v>null</v>
       </c>
       <c r="Y89" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-none</v>
       </c>
       <c r="Z89" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-none</v>
+        <v>null</v>
       </c>
       <c r="AA89" t="str">
         <v>null</v>
@@ -10435,10 +10435,10 @@
         <v>null</v>
       </c>
       <c r="AE89" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-none-naam</v>
       </c>
       <c r="AF89" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-none-naam</v>
+        <v>null</v>
       </c>
       <c r="AG89" t="str">
         <v>null</v>
@@ -10500,10 +10500,10 @@
         <v>null</v>
       </c>
       <c r="O90" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-none-naam</v>
       </c>
       <c r="P90" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q90" t="str">
         <v>null</v>
@@ -10518,22 +10518,22 @@
         <v>null</v>
       </c>
       <c r="U90" t="str">
+        <v>null</v>
+      </c>
+      <c r="V90" t="str">
         <v>true</v>
       </c>
-      <c r="V90" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-none-naam</v>
-      </c>
       <c r="W90" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X90" t="str">
         <v>null</v>
       </c>
       <c r="Y90" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-none</v>
       </c>
       <c r="Z90" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-none</v>
+        <v>null</v>
       </c>
       <c r="AA90" t="str">
         <v>null</v>
@@ -10551,10 +10551,10 @@
         <v>null</v>
       </c>
       <c r="AF90" t="str">
-        <v>null</v>
+        <v>true</v>
       </c>
       <c r="AG90" t="str">
-        <v>true</v>
+        <v>null</v>
       </c>
       <c r="AH90" t="str">
         <v>null</v>
@@ -10613,20 +10613,20 @@
         <v>null</v>
       </c>
       <c r="O91" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-werf</v>
       </c>
       <c r="P91" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q91" t="str">
+        <v>null</v>
+      </c>
+      <c r="R91" t="str">
+        <v>null</v>
+      </c>
+      <c r="S91" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-be|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-buitenland|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-none</v>
       </c>
-      <c r="R91" t="str">
-        <v>null</v>
-      </c>
-      <c r="S91" t="str">
-        <v>null</v>
-      </c>
       <c r="T91" t="str">
         <v>null</v>
       </c>
@@ -10634,37 +10634,37 @@
         <v>null</v>
       </c>
       <c r="V91" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-werf</v>
+        <v>null</v>
       </c>
       <c r="W91" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-werf-naam</v>
       </c>
       <c r="X91" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-werf-naam</v>
+        <v>null</v>
       </c>
       <c r="Y91" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/grondstof</v>
       </c>
       <c r="Z91" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/grondstof</v>
+        <v>null</v>
       </c>
       <c r="AA91" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-be|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-buitenland|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-none</v>
       </c>
       <c r="AB91" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-be|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-buitenland|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-none</v>
+        <v>http://www.w3.org/ns/prov#Agent</v>
       </c>
       <c r="AC91" t="str">
-        <v>http://www.w3.org/ns/prov#Agent</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-bestemmingstype/werf</v>
       </c>
       <c r="AD91" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-bestemmingstype/werf</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/grondstof_bestemming_type</v>
       </c>
       <c r="AE91" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/grondstof_bestemming_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-buitenland</v>
       </c>
       <c r="AF91" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-buitenland</v>
+        <v>null</v>
       </c>
       <c r="AG91" t="str">
         <v>null</v>
@@ -10726,10 +10726,10 @@
         <v>null</v>
       </c>
       <c r="O92" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-werf-naam</v>
       </c>
       <c r="P92" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q92" t="str">
         <v>null</v>
@@ -10744,22 +10744,22 @@
         <v>null</v>
       </c>
       <c r="U92" t="str">
+        <v>null</v>
+      </c>
+      <c r="V92" t="str">
         <v>false</v>
       </c>
-      <c r="V92" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-werf-naam</v>
-      </c>
       <c r="W92" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X92" t="str">
         <v>null</v>
       </c>
       <c r="Y92" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-werf</v>
       </c>
       <c r="Z92" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-werf</v>
+        <v>null</v>
       </c>
       <c r="AA92" t="str">
         <v>null</v>
@@ -10777,10 +10777,10 @@
         <v>null</v>
       </c>
       <c r="AF92" t="str">
-        <v>null</v>
+        <v>true</v>
       </c>
       <c r="AG92" t="str">
-        <v>true</v>
+        <v>null</v>
       </c>
       <c r="AH92" t="str">
         <v>null</v>
@@ -10890,10 +10890,10 @@
         <v>null</v>
       </c>
       <c r="AF93" t="str">
-        <v>null</v>
+        <v>true</v>
       </c>
       <c r="AG93" t="str">
-        <v>true</v>
+        <v>null</v>
       </c>
       <c r="AH93" t="str">
         <v>null</v>
@@ -10952,10 +10952,10 @@
         <v>null</v>
       </c>
       <c r="O94" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/grondstof</v>
       </c>
       <c r="P94" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q94" t="str">
         <v>null</v>
@@ -10973,16 +10973,16 @@
         <v>null</v>
       </c>
       <c r="V94" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/grondstof</v>
+        <v>null</v>
       </c>
       <c r="W94" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-be|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-buitenland|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-none|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-werf|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/grondstof_bestemming_type|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/grondstof_opmerking|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/grondstof_hoeveelheid|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/grondstof_materiaalcode|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/grondstof_omschrijving|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/grondstof_toepassingswijze</v>
       </c>
       <c r="X94" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-be|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-buitenland|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-none|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-werf|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/grondstof_bestemming_type|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/grondstof_opmerking|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/grondstof_hoeveelheid|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/grondstof_materiaalcode|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/grondstof_omschrijving|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/grondstof_toepassingswijze</v>
+        <v>true</v>
       </c>
       <c r="Y94" t="str">
-        <v>true</v>
+        <v>null</v>
       </c>
       <c r="Z94" t="str">
         <v>null</v>
@@ -10991,19 +10991,19 @@
         <v>null</v>
       </c>
       <c r="AB94" t="str">
-        <v>null</v>
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Observatie</v>
       </c>
       <c r="AC94" t="str">
-        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Observatie</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/rie-iepr/true</v>
       </c>
       <c r="AD94" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/rie-iepr/true</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/geproduceerd</v>
       </c>
       <c r="AE94" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/geproduceerd</v>
       </c>
       <c r="AF94" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/geproduceerd</v>
+        <v>null</v>
       </c>
       <c r="AG94" t="str">
         <v>null</v>
@@ -11065,10 +11065,10 @@
         <v>null</v>
       </c>
       <c r="O95" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/grondstof_bestemming_type</v>
       </c>
       <c r="P95" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q95" t="str">
         <v>null</v>
@@ -11083,40 +11083,40 @@
         <v>null</v>
       </c>
       <c r="U95" t="str">
+        <v>null</v>
+      </c>
+      <c r="V95" t="str">
         <v>true</v>
       </c>
-      <c r="V95" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/grondstof_bestemming_type</v>
-      </c>
       <c r="W95" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X95" t="str">
         <v>null</v>
       </c>
       <c r="Y95" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/grondstof</v>
       </c>
       <c r="Z95" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/grondstof</v>
+        <v>null</v>
       </c>
       <c r="AA95" t="str">
         <v>null</v>
       </c>
       <c r="AB95" t="str">
-        <v>null</v>
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Resultaat</v>
       </c>
       <c r="AC95" t="str">
-        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Resultaat</v>
+        <v>null</v>
       </c>
       <c r="AD95" t="str">
         <v>null</v>
       </c>
       <c r="AE95" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/grondstof_toepassingswijze</v>
       </c>
       <c r="AF95" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/grondstof_toepassingswijze</v>
+        <v>null</v>
       </c>
       <c r="AG95" t="str">
         <v>null</v>
@@ -11178,10 +11178,10 @@
         <v>null</v>
       </c>
       <c r="O96" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/grondstof_hoeveelheid</v>
       </c>
       <c r="P96" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q96" t="str">
         <v>null</v>
@@ -11196,40 +11196,40 @@
         <v>null</v>
       </c>
       <c r="U96" t="str">
+        <v>null</v>
+      </c>
+      <c r="V96" t="str">
         <v>true</v>
       </c>
-      <c r="V96" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/grondstof_hoeveelheid</v>
-      </c>
       <c r="W96" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X96" t="str">
         <v>null</v>
       </c>
       <c r="Y96" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/grondstof</v>
       </c>
       <c r="Z96" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/grondstof</v>
+        <v>null</v>
       </c>
       <c r="AA96" t="str">
         <v>null</v>
       </c>
       <c r="AB96" t="str">
-        <v>null</v>
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Resultaat</v>
       </c>
       <c r="AC96" t="str">
-        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Resultaat</v>
+        <v>null</v>
       </c>
       <c r="AD96" t="str">
         <v>null</v>
       </c>
       <c r="AE96" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/grondstof_omschrijving</v>
       </c>
       <c r="AF96" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/grondstof_omschrijving</v>
+        <v>null</v>
       </c>
       <c r="AG96" t="str">
         <v>null</v>
@@ -11291,10 +11291,10 @@
         <v>null</v>
       </c>
       <c r="O97" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/grondstof_materiaalcode</v>
       </c>
       <c r="P97" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q97" t="str">
         <v>null</v>
@@ -11312,28 +11312,28 @@
         <v>null</v>
       </c>
       <c r="V97" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/grondstof_materiaalcode</v>
+        <v>null</v>
       </c>
       <c r="W97" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X97" t="str">
         <v>null</v>
       </c>
       <c r="Y97" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/grondstof</v>
       </c>
       <c r="Z97" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/grondstof</v>
+        <v>null</v>
       </c>
       <c r="AA97" t="str">
         <v>null</v>
       </c>
       <c r="AB97" t="str">
-        <v>null</v>
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Resultaat</v>
       </c>
       <c r="AC97" t="str">
-        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Resultaat</v>
+        <v>null</v>
       </c>
       <c r="AD97" t="str">
         <v>null</v>
@@ -11342,10 +11342,10 @@
         <v>null</v>
       </c>
       <c r="AF97" t="str">
-        <v>null</v>
+        <v>true</v>
       </c>
       <c r="AG97" t="str">
-        <v>true</v>
+        <v>null</v>
       </c>
       <c r="AH97" t="str">
         <v>null</v>
@@ -11404,10 +11404,10 @@
         <v>null</v>
       </c>
       <c r="O98" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/grondstof_omschrijving</v>
       </c>
       <c r="P98" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q98" t="str">
         <v>null</v>
@@ -11422,40 +11422,40 @@
         <v>null</v>
       </c>
       <c r="U98" t="str">
+        <v>null</v>
+      </c>
+      <c r="V98" t="str">
         <v>false</v>
       </c>
-      <c r="V98" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/grondstof_omschrijving</v>
-      </c>
       <c r="W98" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X98" t="str">
         <v>null</v>
       </c>
       <c r="Y98" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/grondstof</v>
       </c>
       <c r="Z98" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/grondstof</v>
+        <v>null</v>
       </c>
       <c r="AA98" t="str">
         <v>null</v>
       </c>
       <c r="AB98" t="str">
-        <v>null</v>
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Resultaat</v>
       </c>
       <c r="AC98" t="str">
-        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Resultaat</v>
+        <v>null</v>
       </c>
       <c r="AD98" t="str">
         <v>null</v>
       </c>
       <c r="AE98" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/grondstof_materiaalcode</v>
       </c>
       <c r="AF98" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/grondstof_materiaalcode</v>
+        <v>null</v>
       </c>
       <c r="AG98" t="str">
         <v>null</v>
@@ -11517,10 +11517,10 @@
         <v>null</v>
       </c>
       <c r="O99" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/grondstof_opmerking</v>
       </c>
       <c r="P99" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q99" t="str">
         <v>null</v>
@@ -11535,40 +11535,40 @@
         <v>null</v>
       </c>
       <c r="U99" t="str">
+        <v>null</v>
+      </c>
+      <c r="V99" t="str">
         <v>false</v>
       </c>
-      <c r="V99" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/grondstof_opmerking</v>
-      </c>
       <c r="W99" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X99" t="str">
         <v>null</v>
       </c>
       <c r="Y99" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/grondstof</v>
       </c>
       <c r="Z99" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/grondstof</v>
+        <v>null</v>
       </c>
       <c r="AA99" t="str">
         <v>null</v>
       </c>
       <c r="AB99" t="str">
-        <v>null</v>
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Resultaat</v>
       </c>
       <c r="AC99" t="str">
-        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Resultaat</v>
+        <v>null</v>
       </c>
       <c r="AD99" t="str">
         <v>null</v>
       </c>
       <c r="AE99" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/grondstof_bestemming_type</v>
       </c>
       <c r="AF99" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/grondstof_bestemming_type</v>
+        <v>null</v>
       </c>
       <c r="AG99" t="str">
         <v>null</v>
@@ -11630,10 +11630,10 @@
         <v>null</v>
       </c>
       <c r="O100" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/grondstof_toepassingswijze</v>
       </c>
       <c r="P100" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q100" t="str">
         <v>null</v>
@@ -11651,37 +11651,37 @@
         <v>null</v>
       </c>
       <c r="V100" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/grondstof_toepassingswijze</v>
+        <v>null</v>
       </c>
       <c r="W100" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X100" t="str">
         <v>null</v>
       </c>
       <c r="Y100" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/grondstof</v>
       </c>
       <c r="Z100" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/grondstof</v>
+        <v>null</v>
       </c>
       <c r="AA100" t="str">
         <v>null</v>
       </c>
       <c r="AB100" t="str">
-        <v>null</v>
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Resultaat</v>
       </c>
       <c r="AC100" t="str">
-        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Resultaat</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_toepassingwijze</v>
       </c>
       <c r="AD100" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_toepassingwijze</v>
+        <v>null</v>
       </c>
       <c r="AE100" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/grondstof_hoeveelheid</v>
       </c>
       <c r="AF100" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/grondstof_hoeveelheid</v>
+        <v>null</v>
       </c>
       <c r="AG100" t="str">
         <v>null</v>
@@ -11743,10 +11743,10 @@
         <v>Begintoestand van de debietmeter om het volume te berekenen.</v>
       </c>
       <c r="O101" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/begintoestand</v>
       </c>
       <c r="P101" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q101" t="str">
         <v>null</v>
@@ -11761,40 +11761,40 @@
         <v>null</v>
       </c>
       <c r="U101" t="str">
+        <v>null</v>
+      </c>
+      <c r="V101" t="str">
         <v>false</v>
       </c>
-      <c r="V101" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/begintoestand</v>
-      </c>
       <c r="W101" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X101" t="str">
         <v>null</v>
       </c>
       <c r="Y101" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/onttrekking</v>
       </c>
       <c r="Z101" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/onttrekking</v>
+        <v>null</v>
       </c>
       <c r="AA101" t="str">
         <v>null</v>
       </c>
       <c r="AB101" t="str">
-        <v>null</v>
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Observatie</v>
       </c>
       <c r="AC101" t="str">
-        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Observatie</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/rie-iepr/NaN</v>
       </c>
       <c r="AD101" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/rie-iepr/NaN</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/volume</v>
       </c>
       <c r="AE101" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/volume</v>
       </c>
       <c r="AF101" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/volume</v>
+        <v>null</v>
       </c>
       <c r="AG101" t="str">
         <v>null</v>
@@ -11856,10 +11856,10 @@
         <v>null</v>
       </c>
       <c r="O102" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/datum</v>
       </c>
       <c r="P102" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q102" t="str">
         <v>null</v>
@@ -11877,19 +11877,19 @@
         <v>null</v>
       </c>
       <c r="V102" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/datum</v>
+        <v>null</v>
       </c>
       <c r="W102" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X102" t="str">
         <v>null</v>
       </c>
       <c r="Y102" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/peilmeting</v>
       </c>
       <c r="Z102" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/peilmeting</v>
+        <v>null</v>
       </c>
       <c r="AA102" t="str">
         <v>null</v>
@@ -11904,10 +11904,10 @@
         <v>null</v>
       </c>
       <c r="AE102" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/peilmeting_feature</v>
       </c>
       <c r="AF102" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/peilmeting_feature</v>
+        <v>null</v>
       </c>
       <c r="AG102" t="str">
         <v>null</v>
@@ -11969,10 +11969,10 @@
         <v>null</v>
       </c>
       <c r="O103" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/diepte</v>
       </c>
       <c r="P103" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q103" t="str">
         <v>null</v>
@@ -11990,19 +11990,19 @@
         <v>null</v>
       </c>
       <c r="V103" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/diepte</v>
+        <v>null</v>
       </c>
       <c r="W103" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X103" t="str">
         <v>null</v>
       </c>
       <c r="Y103" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/peilmeting</v>
       </c>
       <c r="Z103" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/peilmeting</v>
+        <v>null</v>
       </c>
       <c r="AA103" t="str">
         <v>null</v>
@@ -12017,10 +12017,10 @@
         <v>null</v>
       </c>
       <c r="AE103" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/referentiepunt</v>
       </c>
       <c r="AF103" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/referentiepunt</v>
+        <v>null</v>
       </c>
       <c r="AG103" t="str">
         <v>null</v>
@@ -12082,10 +12082,10 @@
         <v>null</v>
       </c>
       <c r="O104" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/duur-stil</v>
       </c>
       <c r="P104" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q104" t="str">
         <v>null</v>
@@ -12103,19 +12103,19 @@
         <v>null</v>
       </c>
       <c r="V104" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/duur-stil</v>
+        <v>null</v>
       </c>
       <c r="W104" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X104" t="str">
         <v>null</v>
       </c>
       <c r="Y104" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/peilmeting</v>
       </c>
       <c r="Z104" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/peilmeting</v>
+        <v>null</v>
       </c>
       <c r="AA104" t="str">
         <v>null</v>
@@ -12124,16 +12124,16 @@
         <v>null</v>
       </c>
       <c r="AC104" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-pomptoestand/rust</v>
       </c>
       <c r="AD104" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-pomptoestand/rust</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/pomptoestand</v>
       </c>
       <c r="AE104" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/pomptoestand</v>
       </c>
       <c r="AF104" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/pomptoestand</v>
+        <v>null</v>
       </c>
       <c r="AG104" t="str">
         <v>null</v>
@@ -12195,10 +12195,10 @@
         <v>Eindtoestand van de debietmeter om het volume te berekenen.</v>
       </c>
       <c r="O105" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/eindtoestand</v>
       </c>
       <c r="P105" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q105" t="str">
         <v>null</v>
@@ -12213,40 +12213,40 @@
         <v>null</v>
       </c>
       <c r="U105" t="str">
+        <v>null</v>
+      </c>
+      <c r="V105" t="str">
         <v>false</v>
       </c>
-      <c r="V105" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/eindtoestand</v>
-      </c>
       <c r="W105" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X105" t="str">
         <v>null</v>
       </c>
       <c r="Y105" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/onttrekking</v>
       </c>
       <c r="Z105" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/onttrekking</v>
+        <v>null</v>
       </c>
       <c r="AA105" t="str">
         <v>null</v>
       </c>
       <c r="AB105" t="str">
-        <v>null</v>
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Observatie</v>
       </c>
       <c r="AC105" t="str">
-        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Observatie</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/rie-iepr/NaN</v>
       </c>
       <c r="AD105" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/rie-iepr/NaN</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/volume</v>
       </c>
       <c r="AE105" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/volume</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/begintoestand</v>
       </c>
       <c r="AF105" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/begintoestand</v>
+        <v>null</v>
       </c>
       <c r="AG105" t="str">
         <v>null</v>
@@ -12308,10 +12308,10 @@
         <v>Een kwaliteitsmeting van een pomp- of peilput.</v>
       </c>
       <c r="O106" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting</v>
       </c>
       <c r="P106" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q106" t="str">
         <v>null</v>
@@ -12329,16 +12329,16 @@
         <v>null</v>
       </c>
       <c r="V106" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting</v>
+        <v>null</v>
       </c>
       <c r="W106" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-bemonsteringsinstrument|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-labo|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-datum|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting_feature|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-diepte|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-referentiepunt|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-monsternummer|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-parameter|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-techniek</v>
       </c>
       <c r="X106" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-bemonsteringsinstrument|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-labo|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-datum|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting_feature|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-diepte|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-referentiepunt|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-monsternummer|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-parameter|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-techniek</v>
+        <v>true</v>
       </c>
       <c r="Y106" t="str">
-        <v>true</v>
+        <v>null</v>
       </c>
       <c r="Z106" t="str">
         <v>null</v>
@@ -12347,19 +12347,19 @@
         <v>null</v>
       </c>
       <c r="AB106" t="str">
-        <v>null</v>
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#ObservatieVerzameling</v>
       </c>
       <c r="AC106" t="str">
-        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#ObservatieVerzameling</v>
+        <v>null</v>
       </c>
       <c r="AD106" t="str">
         <v>null</v>
       </c>
       <c r="AE106" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/peilmeting</v>
       </c>
       <c r="AF106" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/peilmeting</v>
+        <v>null</v>
       </c>
       <c r="AG106" t="str">
         <v>null</v>
@@ -12421,10 +12421,10 @@
         <v>null</v>
       </c>
       <c r="O107" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-bemonsteringsinstrument</v>
       </c>
       <c r="P107" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q107" t="str">
         <v>null</v>
@@ -12442,19 +12442,19 @@
         <v>null</v>
       </c>
       <c r="V107" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-bemonsteringsinstrument</v>
+        <v>null</v>
       </c>
       <c r="W107" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X107" t="str">
         <v>null</v>
       </c>
       <c r="Y107" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting</v>
       </c>
       <c r="Z107" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting</v>
+        <v>null</v>
       </c>
       <c r="AA107" t="str">
         <v>null</v>
@@ -12469,10 +12469,10 @@
         <v>null</v>
       </c>
       <c r="AE107" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-labo</v>
       </c>
       <c r="AF107" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-labo</v>
+        <v>null</v>
       </c>
       <c r="AG107" t="str">
         <v>null</v>
@@ -12534,10 +12534,10 @@
         <v>null</v>
       </c>
       <c r="O108" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-datum</v>
       </c>
       <c r="P108" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q108" t="str">
         <v>null</v>
@@ -12555,19 +12555,19 @@
         <v>null</v>
       </c>
       <c r="V108" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-datum</v>
+        <v>null</v>
       </c>
       <c r="W108" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X108" t="str">
         <v>null</v>
       </c>
       <c r="Y108" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting</v>
       </c>
       <c r="Z108" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting</v>
+        <v>null</v>
       </c>
       <c r="AA108" t="str">
         <v>null</v>
@@ -12582,10 +12582,10 @@
         <v>null</v>
       </c>
       <c r="AE108" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting_feature</v>
       </c>
       <c r="AF108" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting_feature</v>
+        <v>null</v>
       </c>
       <c r="AG108" t="str">
         <v>null</v>
@@ -12647,10 +12647,10 @@
         <v>null</v>
       </c>
       <c r="O109" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-diepte</v>
       </c>
       <c r="P109" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q109" t="str">
         <v>null</v>
@@ -12668,37 +12668,37 @@
         <v>null</v>
       </c>
       <c r="V109" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-diepte</v>
+        <v>null</v>
       </c>
       <c r="W109" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X109" t="str">
         <v>null</v>
       </c>
       <c r="Y109" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting</v>
       </c>
       <c r="Z109" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting</v>
+        <v>null</v>
       </c>
       <c r="AA109" t="str">
         <v>null</v>
       </c>
       <c r="AB109" t="str">
-        <v>null</v>
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Observatie</v>
       </c>
       <c r="AC109" t="str">
-        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Observatie</v>
+        <v>null</v>
       </c>
       <c r="AD109" t="str">
         <v>null</v>
       </c>
       <c r="AE109" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-referentiepunt</v>
       </c>
       <c r="AF109" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-referentiepunt</v>
+        <v>null</v>
       </c>
       <c r="AG109" t="str">
         <v>null</v>
@@ -12760,10 +12760,10 @@
         <v>Labo dat de meting uitvoerde.</v>
       </c>
       <c r="O110" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-labo</v>
       </c>
       <c r="P110" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q110" t="str">
         <v>null</v>
@@ -12778,40 +12778,40 @@
         <v>null</v>
       </c>
       <c r="U110" t="str">
+        <v>null</v>
+      </c>
+      <c r="V110" t="str">
         <v>true</v>
       </c>
-      <c r="V110" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-labo</v>
-      </c>
       <c r="W110" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-labo-naam</v>
       </c>
       <c r="X110" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-labo-naam</v>
+        <v>null</v>
       </c>
       <c r="Y110" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting</v>
       </c>
       <c r="Z110" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting</v>
+        <v>null</v>
       </c>
       <c r="AA110" t="str">
         <v>null</v>
       </c>
       <c r="AB110" t="str">
-        <v>null</v>
+        <v>http://www.w3.org/ns/prov#Agent</v>
       </c>
       <c r="AC110" t="str">
-        <v>http://www.w3.org/ns/prov#Agent</v>
+        <v>null</v>
       </c>
       <c r="AD110" t="str">
         <v>null</v>
       </c>
       <c r="AE110" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-monsternummer</v>
       </c>
       <c r="AF110" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-monsternummer</v>
+        <v>null</v>
       </c>
       <c r="AG110" t="str">
         <v>null</v>
@@ -12873,10 +12873,10 @@
         <v>null</v>
       </c>
       <c r="O111" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-labo-naam</v>
       </c>
       <c r="P111" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q111" t="str">
         <v>null</v>
@@ -12891,22 +12891,22 @@
         <v>null</v>
       </c>
       <c r="U111" t="str">
+        <v>null</v>
+      </c>
+      <c r="V111" t="str">
         <v>true</v>
       </c>
-      <c r="V111" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-labo-naam</v>
-      </c>
       <c r="W111" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X111" t="str">
         <v>null</v>
       </c>
       <c r="Y111" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-labo</v>
       </c>
       <c r="Z111" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-labo</v>
+        <v>null</v>
       </c>
       <c r="AA111" t="str">
         <v>null</v>
@@ -12924,10 +12924,10 @@
         <v>null</v>
       </c>
       <c r="AF111" t="str">
-        <v>null</v>
+        <v>true</v>
       </c>
       <c r="AG111" t="str">
-        <v>true</v>
+        <v>null</v>
       </c>
       <c r="AH111" t="str">
         <v>null</v>
@@ -12986,10 +12986,10 @@
         <v>null</v>
       </c>
       <c r="O112" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-monsternummer</v>
       </c>
       <c r="P112" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q112" t="str">
         <v>null</v>
@@ -13007,19 +13007,19 @@
         <v>null</v>
       </c>
       <c r="V112" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-monsternummer</v>
+        <v>null</v>
       </c>
       <c r="W112" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X112" t="str">
         <v>null</v>
       </c>
       <c r="Y112" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting</v>
       </c>
       <c r="Z112" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting</v>
+        <v>null</v>
       </c>
       <c r="AA112" t="str">
         <v>null</v>
@@ -13034,10 +13034,10 @@
         <v>null</v>
       </c>
       <c r="AE112" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-datum</v>
       </c>
       <c r="AF112" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-datum</v>
+        <v>null</v>
       </c>
       <c r="AG112" t="str">
         <v>null</v>
@@ -13099,10 +13099,10 @@
         <v>null</v>
       </c>
       <c r="O113" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-parameter</v>
       </c>
       <c r="P113" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q113" t="str">
         <v>null</v>
@@ -13120,19 +13120,19 @@
         <v>null</v>
       </c>
       <c r="V113" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-parameter</v>
+        <v>null</v>
       </c>
       <c r="W113" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-parameter-datum|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-parameter-parameter|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-parameter-limiet|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-parameter-meetwaarde|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-parameter-methode</v>
       </c>
       <c r="X113" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-parameter-datum|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-parameter-parameter|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-parameter-limiet|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-parameter-meetwaarde|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-parameter-methode</v>
+        <v>true</v>
       </c>
       <c r="Y113" t="str">
-        <v>true</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting</v>
       </c>
       <c r="Z113" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting</v>
+        <v>null</v>
       </c>
       <c r="AA113" t="str">
         <v>null</v>
@@ -13147,10 +13147,10 @@
         <v>null</v>
       </c>
       <c r="AE113" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-techniek</v>
       </c>
       <c r="AF113" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-techniek</v>
+        <v>null</v>
       </c>
       <c r="AG113" t="str">
         <v>null</v>
@@ -13212,10 +13212,10 @@
         <v>null</v>
       </c>
       <c r="O114" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-parameter-datum</v>
       </c>
       <c r="P114" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q114" t="str">
         <v>null</v>
@@ -13233,19 +13233,19 @@
         <v>null</v>
       </c>
       <c r="V114" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-parameter-datum</v>
+        <v>null</v>
       </c>
       <c r="W114" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X114" t="str">
         <v>null</v>
       </c>
       <c r="Y114" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-parameter</v>
       </c>
       <c r="Z114" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-parameter</v>
+        <v>null</v>
       </c>
       <c r="AA114" t="str">
         <v>null</v>
@@ -13260,10 +13260,10 @@
         <v>null</v>
       </c>
       <c r="AE114" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-parameter-parameter</v>
       </c>
       <c r="AF114" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-parameter-parameter</v>
+        <v>null</v>
       </c>
       <c r="AG114" t="str">
         <v>null</v>
@@ -13325,10 +13325,10 @@
         <v>null</v>
       </c>
       <c r="O115" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-parameter-limiet</v>
       </c>
       <c r="P115" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q115" t="str">
         <v>null</v>
@@ -13346,19 +13346,19 @@
         <v>null</v>
       </c>
       <c r="V115" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-parameter-limiet</v>
+        <v>null</v>
       </c>
       <c r="W115" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X115" t="str">
         <v>null</v>
       </c>
       <c r="Y115" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-parameter</v>
       </c>
       <c r="Z115" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-parameter</v>
+        <v>null</v>
       </c>
       <c r="AA115" t="str">
         <v>null</v>
@@ -13373,10 +13373,10 @@
         <v>null</v>
       </c>
       <c r="AE115" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-parameter-datum</v>
       </c>
       <c r="AF115" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-parameter-datum</v>
+        <v>null</v>
       </c>
       <c r="AG115" t="str">
         <v>null</v>
@@ -13438,10 +13438,10 @@
         <v>null</v>
       </c>
       <c r="O116" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-parameter-meetwaarde</v>
       </c>
       <c r="P116" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q116" t="str">
         <v>null</v>
@@ -13459,37 +13459,37 @@
         <v>null</v>
       </c>
       <c r="V116" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-parameter-meetwaarde</v>
+        <v>null</v>
       </c>
       <c r="W116" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X116" t="str">
         <v>null</v>
       </c>
       <c r="Y116" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-parameter</v>
       </c>
       <c r="Z116" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-parameter</v>
+        <v>null</v>
       </c>
       <c r="AA116" t="str">
         <v>null</v>
       </c>
       <c r="AB116" t="str">
-        <v>null</v>
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Observatie</v>
       </c>
       <c r="AC116" t="str">
-        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Observatie</v>
+        <v>null</v>
       </c>
       <c r="AD116" t="str">
         <v>null</v>
       </c>
       <c r="AE116" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-parameter-limiet</v>
       </c>
       <c r="AF116" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-parameter-limiet</v>
+        <v>null</v>
       </c>
       <c r="AG116" t="str">
         <v>null</v>
@@ -13551,10 +13551,10 @@
         <v>null</v>
       </c>
       <c r="O117" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-parameter-methode</v>
       </c>
       <c r="P117" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q117" t="str">
         <v>null</v>
@@ -13572,19 +13572,19 @@
         <v>null</v>
       </c>
       <c r="V117" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-parameter-methode</v>
+        <v>null</v>
       </c>
       <c r="W117" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X117" t="str">
         <v>null</v>
       </c>
       <c r="Y117" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-parameter</v>
       </c>
       <c r="Z117" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-parameter</v>
+        <v>null</v>
       </c>
       <c r="AA117" t="str">
         <v>null</v>
@@ -13599,10 +13599,10 @@
         <v>null</v>
       </c>
       <c r="AE117" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-parameter-meetwaarde</v>
       </c>
       <c r="AF117" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-parameter-meetwaarde</v>
+        <v>null</v>
       </c>
       <c r="AG117" t="str">
         <v>null</v>
@@ -13664,10 +13664,10 @@
         <v>null</v>
       </c>
       <c r="O118" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-parameter-parameter</v>
       </c>
       <c r="P118" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q118" t="str">
         <v>null</v>
@@ -13685,19 +13685,19 @@
         <v>null</v>
       </c>
       <c r="V118" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-parameter-parameter</v>
+        <v>null</v>
       </c>
       <c r="W118" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X118" t="str">
         <v>null</v>
       </c>
       <c r="Y118" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-parameter</v>
       </c>
       <c r="Z118" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-parameter</v>
+        <v>null</v>
       </c>
       <c r="AA118" t="str">
         <v>null</v>
@@ -13709,16 +13709,16 @@
         <v>null</v>
       </c>
       <c r="AD118" t="str">
-        <v>null</v>
+        <v>http://TODO</v>
       </c>
       <c r="AE118" t="str">
-        <v>http://TODO</v>
+        <v>null</v>
       </c>
       <c r="AF118" t="str">
-        <v>null</v>
+        <v>true</v>
       </c>
       <c r="AG118" t="str">
-        <v>true</v>
+        <v>null</v>
       </c>
       <c r="AH118" t="str">
         <v>null</v>
@@ -13777,10 +13777,10 @@
         <v>null</v>
       </c>
       <c r="O119" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-referentiepunt</v>
       </c>
       <c r="P119" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q119" t="str">
         <v>null</v>
@@ -13795,22 +13795,22 @@
         <v>null</v>
       </c>
       <c r="U119" t="str">
+        <v>null</v>
+      </c>
+      <c r="V119" t="str">
         <v>true</v>
       </c>
-      <c r="V119" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-referentiepunt</v>
-      </c>
       <c r="W119" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X119" t="str">
-        <v>null</v>
+        <v>true</v>
       </c>
       <c r="Y119" t="str">
-        <v>true</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting</v>
       </c>
       <c r="Z119" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting</v>
+        <v>null</v>
       </c>
       <c r="AA119" t="str">
         <v>null</v>
@@ -13825,10 +13825,10 @@
         <v>null</v>
       </c>
       <c r="AE119" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-bemonsteringsinstrument</v>
       </c>
       <c r="AF119" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-bemonsteringsinstrument</v>
+        <v>null</v>
       </c>
       <c r="AG119" t="str">
         <v>null</v>
@@ -13890,10 +13890,10 @@
         <v>null</v>
       </c>
       <c r="O120" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-techniek</v>
       </c>
       <c r="P120" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q120" t="str">
         <v>null</v>
@@ -13911,19 +13911,19 @@
         <v>null</v>
       </c>
       <c r="V120" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-techniek</v>
+        <v>null</v>
       </c>
       <c r="W120" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X120" t="str">
         <v>null</v>
       </c>
       <c r="Y120" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting</v>
       </c>
       <c r="Z120" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting</v>
+        <v>null</v>
       </c>
       <c r="AA120" t="str">
         <v>null</v>
@@ -13938,10 +13938,10 @@
         <v>null</v>
       </c>
       <c r="AE120" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-diepte</v>
       </c>
       <c r="AF120" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-diepte</v>
+        <v>null</v>
       </c>
       <c r="AG120" t="str">
         <v>null</v>
@@ -13991,7 +13991,7 @@
         <v>null</v>
       </c>
       <c r="K121" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/filter-type/peil,riepr-filter-type:pomp</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/filter-type/peil|https://data.omgeving.vlaanderen.be/id/concept/riepr/filter-type/pomp</v>
       </c>
       <c r="L121" t="str">
         <v>null</v>
@@ -14003,10 +14003,10 @@
         <v>Actieve peil- en pompfilters in het productiejaar.</v>
       </c>
       <c r="O121" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting_feature</v>
       </c>
       <c r="P121" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q121" t="str">
         <v>null</v>
@@ -14024,28 +14024,28 @@
         <v>null</v>
       </c>
       <c r="V121" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting_feature</v>
+        <v>null</v>
       </c>
       <c r="W121" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X121" t="str">
         <v>null</v>
       </c>
       <c r="Y121" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting</v>
       </c>
       <c r="Z121" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting</v>
+        <v>null</v>
       </c>
       <c r="AA121" t="str">
         <v>null</v>
       </c>
       <c r="AB121" t="str">
-        <v>null</v>
+        <v>http://www.w3.org/ns/sosa/FeatureOfInterest</v>
       </c>
       <c r="AC121" t="str">
-        <v>http://www.w3.org/ns/sosa/FeatureOfInterest</v>
+        <v>null</v>
       </c>
       <c r="AD121" t="str">
         <v>null</v>
@@ -14054,13 +14054,13 @@
         <v>null</v>
       </c>
       <c r="AF121" t="str">
-        <v>null</v>
+        <v>true</v>
       </c>
       <c r="AG121" t="str">
         <v>true</v>
       </c>
       <c r="AH121" t="str">
-        <v>true</v>
+        <v>null</v>
       </c>
       <c r="AI121" t="str">
         <v>null</v>
@@ -14116,10 +14116,10 @@
         <v>Een meting van de onttrekking van een pompput.</v>
       </c>
       <c r="O122" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/onttrekking</v>
       </c>
       <c r="P122" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q122" t="str">
         <v>null</v>
@@ -14137,40 +14137,40 @@
         <v>null</v>
       </c>
       <c r="V122" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/onttrekking</v>
+        <v>null</v>
       </c>
       <c r="W122" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/begintoestand|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/volume|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/eindtoestand|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/onttrekking_feature|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/periode|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/type-debiet</v>
       </c>
       <c r="X122" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/begintoestand|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/volume|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/eindtoestand|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/onttrekking_feature|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/periode|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/type-debiet</v>
+        <v>true</v>
       </c>
       <c r="Y122" t="str">
+        <v>null</v>
+      </c>
+      <c r="Z122" t="str">
+        <v>null</v>
+      </c>
+      <c r="AA122" t="str">
+        <v>null</v>
+      </c>
+      <c r="AB122" t="str">
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#ObservatieVerzameling</v>
+      </c>
+      <c r="AC122" t="str">
+        <v>null</v>
+      </c>
+      <c r="AD122" t="str">
+        <v>null</v>
+      </c>
+      <c r="AE122" t="str">
+        <v>null</v>
+      </c>
+      <c r="AF122" t="str">
         <v>true</v>
       </c>
-      <c r="Z122" t="str">
-        <v>null</v>
-      </c>
-      <c r="AA122" t="str">
-        <v>null</v>
-      </c>
-      <c r="AB122" t="str">
-        <v>null</v>
-      </c>
-      <c r="AC122" t="str">
-        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#ObservatieVerzameling</v>
-      </c>
-      <c r="AD122" t="str">
-        <v>null</v>
-      </c>
-      <c r="AE122" t="str">
-        <v>null</v>
-      </c>
-      <c r="AF122" t="str">
-        <v>null</v>
-      </c>
       <c r="AG122" t="str">
-        <v>true</v>
+        <v>null</v>
       </c>
       <c r="AH122" t="str">
         <v>null</v>
@@ -14229,10 +14229,10 @@
         <v>Actieve debietmeters in het productiejaar.</v>
       </c>
       <c r="O123" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/onttrekking_feature</v>
       </c>
       <c r="P123" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q123" t="str">
         <v>null</v>
@@ -14250,28 +14250,28 @@
         <v>null</v>
       </c>
       <c r="V123" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/onttrekking_feature</v>
+        <v>null</v>
       </c>
       <c r="W123" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X123" t="str">
         <v>null</v>
       </c>
       <c r="Y123" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/onttrekking</v>
       </c>
       <c r="Z123" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/onttrekking</v>
+        <v>null</v>
       </c>
       <c r="AA123" t="str">
         <v>null</v>
       </c>
       <c r="AB123" t="str">
-        <v>null</v>
+        <v>http://www.w3.org/ns/sosa/FeatureOfInterest</v>
       </c>
       <c r="AC123" t="str">
-        <v>http://www.w3.org/ns/sosa/FeatureOfInterest</v>
+        <v>null</v>
       </c>
       <c r="AD123" t="str">
         <v>null</v>
@@ -14280,16 +14280,16 @@
         <v>null</v>
       </c>
       <c r="AF123" t="str">
-        <v>null</v>
+        <v>true</v>
       </c>
       <c r="AG123" t="str">
-        <v>true</v>
+        <v>null</v>
       </c>
       <c r="AH123" t="str">
-        <v>null</v>
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Onttrekking</v>
       </c>
       <c r="AI123" t="str">
-        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Onttrekking</v>
+        <v>null</v>
       </c>
       <c r="AJ123" t="str">
         <v>null</v>
@@ -14342,10 +14342,10 @@
         <v>null</v>
       </c>
       <c r="O124" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/peilmethode</v>
       </c>
       <c r="P124" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q124" t="str">
         <v>null</v>
@@ -14363,19 +14363,19 @@
         <v>null</v>
       </c>
       <c r="V124" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/peilmethode</v>
+        <v>null</v>
       </c>
       <c r="W124" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X124" t="str">
         <v>null</v>
       </c>
       <c r="Y124" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/peilmeting</v>
       </c>
       <c r="Z124" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/peilmeting</v>
+        <v>null</v>
       </c>
       <c r="AA124" t="str">
         <v>null</v>
@@ -14390,10 +14390,10 @@
         <v>null</v>
       </c>
       <c r="AE124" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/diepte</v>
       </c>
       <c r="AF124" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/diepte</v>
+        <v>null</v>
       </c>
       <c r="AG124" t="str">
         <v>null</v>
@@ -14455,10 +14455,10 @@
         <v>Een peilmeting van een pomp- of peilput.</v>
       </c>
       <c r="O125" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/peilmeting</v>
       </c>
       <c r="P125" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q125" t="str">
         <v>null</v>
@@ -14476,16 +14476,16 @@
         <v>null</v>
       </c>
       <c r="V125" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/peilmeting</v>
+        <v>null</v>
       </c>
       <c r="W125" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/datum|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/peilmeting_feature|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/diepte|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/referentiepunt|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/duur-stil|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/pomptoestand|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/peilmethode|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/volume-rust|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/volume-werking</v>
       </c>
       <c r="X125" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/datum|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/peilmeting_feature|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/diepte|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/referentiepunt|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/duur-stil|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/pomptoestand|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/peilmethode|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/volume-rust|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/volume-werking</v>
+        <v>true</v>
       </c>
       <c r="Y125" t="str">
-        <v>true</v>
+        <v>null</v>
       </c>
       <c r="Z125" t="str">
         <v>null</v>
@@ -14494,19 +14494,19 @@
         <v>null</v>
       </c>
       <c r="AB125" t="str">
-        <v>null</v>
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#ObservatieVerzameling</v>
       </c>
       <c r="AC125" t="str">
-        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#ObservatieVerzameling</v>
+        <v>null</v>
       </c>
       <c r="AD125" t="str">
         <v>null</v>
       </c>
       <c r="AE125" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/onttrekking</v>
       </c>
       <c r="AF125" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/onttrekking</v>
+        <v>null</v>
       </c>
       <c r="AG125" t="str">
         <v>null</v>
@@ -14556,7 +14556,7 @@
         <v>null</v>
       </c>
       <c r="K126" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/filter-type/peil,riepr-filter-type:pomp</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/filter-type/peil|https://data.omgeving.vlaanderen.be/id/concept/riepr/filter-type/pomp</v>
       </c>
       <c r="L126" t="str">
         <v>null</v>
@@ -14568,10 +14568,10 @@
         <v>Actieve peil- en pompfilters in het productiejaar.</v>
       </c>
       <c r="O126" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/peilmeting_feature</v>
       </c>
       <c r="P126" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q126" t="str">
         <v>null</v>
@@ -14589,28 +14589,28 @@
         <v>null</v>
       </c>
       <c r="V126" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/peilmeting_feature</v>
+        <v>null</v>
       </c>
       <c r="W126" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X126" t="str">
         <v>null</v>
       </c>
       <c r="Y126" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/peilmeting</v>
       </c>
       <c r="Z126" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/peilmeting</v>
+        <v>null</v>
       </c>
       <c r="AA126" t="str">
         <v>null</v>
       </c>
       <c r="AB126" t="str">
-        <v>null</v>
+        <v>http://www.w3.org/ns/sosa/FeatureOfInterest</v>
       </c>
       <c r="AC126" t="str">
-        <v>http://www.w3.org/ns/sosa/FeatureOfInterest</v>
+        <v>null</v>
       </c>
       <c r="AD126" t="str">
         <v>null</v>
@@ -14619,10 +14619,10 @@
         <v>null</v>
       </c>
       <c r="AF126" t="str">
-        <v>null</v>
+        <v>true</v>
       </c>
       <c r="AG126" t="str">
-        <v>true</v>
+        <v>null</v>
       </c>
       <c r="AH126" t="str">
         <v>null</v>
@@ -14681,10 +14681,10 @@
         <v>null</v>
       </c>
       <c r="O127" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/periode</v>
       </c>
       <c r="P127" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q127" t="str">
         <v>null</v>
@@ -14702,19 +14702,19 @@
         <v>null</v>
       </c>
       <c r="V127" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/periode</v>
+        <v>null</v>
       </c>
       <c r="W127" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X127" t="str">
         <v>null</v>
       </c>
       <c r="Y127" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/onttrekking</v>
       </c>
       <c r="Z127" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/onttrekking</v>
+        <v>null</v>
       </c>
       <c r="AA127" t="str">
         <v>null</v>
@@ -14729,10 +14729,10 @@
         <v>null</v>
       </c>
       <c r="AE127" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/onttrekking_feature</v>
       </c>
       <c r="AF127" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/onttrekking_feature</v>
+        <v>null</v>
       </c>
       <c r="AG127" t="str">
         <v>null</v>
@@ -14794,10 +14794,10 @@
         <v>null</v>
       </c>
       <c r="O128" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/pomptoestand</v>
       </c>
       <c r="P128" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q128" t="str">
         <v>null</v>
@@ -14815,19 +14815,19 @@
         <v>null</v>
       </c>
       <c r="V128" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/pomptoestand</v>
+        <v>null</v>
       </c>
       <c r="W128" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X128" t="str">
         <v>null</v>
       </c>
       <c r="Y128" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/peilmeting</v>
       </c>
       <c r="Z128" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/peilmeting</v>
+        <v>null</v>
       </c>
       <c r="AA128" t="str">
         <v>null</v>
@@ -14842,10 +14842,10 @@
         <v>null</v>
       </c>
       <c r="AE128" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/peilmethode</v>
       </c>
       <c r="AF128" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/peilmethode</v>
+        <v>null</v>
       </c>
       <c r="AG128" t="str">
         <v>null</v>
@@ -14907,10 +14907,10 @@
         <v>null</v>
       </c>
       <c r="O129" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/referentiepunt</v>
       </c>
       <c r="P129" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q129" t="str">
         <v>null</v>
@@ -14925,22 +14925,22 @@
         <v>null</v>
       </c>
       <c r="U129" t="str">
+        <v>null</v>
+      </c>
+      <c r="V129" t="str">
         <v>true</v>
       </c>
-      <c r="V129" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/referentiepunt</v>
-      </c>
       <c r="W129" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X129" t="str">
-        <v>null</v>
+        <v>true</v>
       </c>
       <c r="Y129" t="str">
-        <v>true</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/peilmeting</v>
       </c>
       <c r="Z129" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/peilmeting</v>
+        <v>null</v>
       </c>
       <c r="AA129" t="str">
         <v>null</v>
@@ -14955,10 +14955,10 @@
         <v>null</v>
       </c>
       <c r="AE129" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/datum</v>
       </c>
       <c r="AF129" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/datum</v>
+        <v>null</v>
       </c>
       <c r="AG129" t="str">
         <v>null</v>
@@ -15020,10 +15020,10 @@
         <v>null</v>
       </c>
       <c r="O130" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/type-debiet</v>
       </c>
       <c r="P130" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q130" t="str">
         <v>null</v>
@@ -15041,19 +15041,19 @@
         <v>null</v>
       </c>
       <c r="V130" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/type-debiet</v>
+        <v>null</v>
       </c>
       <c r="W130" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X130" t="str">
         <v>null</v>
       </c>
       <c r="Y130" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/onttrekking</v>
       </c>
       <c r="Z130" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/onttrekking</v>
+        <v>null</v>
       </c>
       <c r="AA130" t="str">
         <v>null</v>
@@ -15062,16 +15062,16 @@
         <v>null</v>
       </c>
       <c r="AC130" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_debiet_type</v>
       </c>
       <c r="AD130" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_debiet_type</v>
+        <v>null</v>
       </c>
       <c r="AE130" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/periode</v>
       </c>
       <c r="AF130" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/periode</v>
+        <v>null</v>
       </c>
       <c r="AG130" t="str">
         <v>null</v>
@@ -15133,10 +15133,10 @@
         <v>null</v>
       </c>
       <c r="O131" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/volume</v>
       </c>
       <c r="P131" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q131" t="str">
         <v>null</v>
@@ -15151,40 +15151,40 @@
         <v>null</v>
       </c>
       <c r="U131" t="str">
+        <v>null</v>
+      </c>
+      <c r="V131" t="str">
         <v>true</v>
       </c>
-      <c r="V131" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/volume</v>
-      </c>
       <c r="W131" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X131" t="str">
         <v>null</v>
       </c>
       <c r="Y131" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/onttrekking</v>
       </c>
       <c r="Z131" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/onttrekking</v>
+        <v>null</v>
       </c>
       <c r="AA131" t="str">
         <v>null</v>
       </c>
       <c r="AB131" t="str">
-        <v>null</v>
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Observatie</v>
       </c>
       <c r="AC131" t="str">
-        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Observatie</v>
+        <v>null</v>
       </c>
       <c r="AD131" t="str">
         <v>null</v>
       </c>
       <c r="AE131" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/type-debiet</v>
       </c>
       <c r="AF131" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/type-debiet</v>
+        <v>null</v>
       </c>
       <c r="AG131" t="str">
         <v>null</v>
@@ -15246,10 +15246,10 @@
         <v>null</v>
       </c>
       <c r="O132" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/volume-rust</v>
       </c>
       <c r="P132" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q132" t="str">
         <v>null</v>
@@ -15267,19 +15267,19 @@
         <v>null</v>
       </c>
       <c r="V132" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/volume-rust</v>
+        <v>null</v>
       </c>
       <c r="W132" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X132" t="str">
         <v>null</v>
       </c>
       <c r="Y132" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/peilmeting</v>
       </c>
       <c r="Z132" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/peilmeting</v>
+        <v>null</v>
       </c>
       <c r="AA132" t="str">
         <v>null</v>
@@ -15288,16 +15288,16 @@
         <v>null</v>
       </c>
       <c r="AC132" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-pomptoestand/rust</v>
       </c>
       <c r="AD132" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-pomptoestand/rust</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/pomptoestand</v>
       </c>
       <c r="AE132" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/pomptoestand</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/duur-stil</v>
       </c>
       <c r="AF132" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/duur-stil</v>
+        <v>null</v>
       </c>
       <c r="AG132" t="str">
         <v>null</v>
@@ -15359,10 +15359,10 @@
         <v>null</v>
       </c>
       <c r="O133" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/volume-werking</v>
       </c>
       <c r="P133" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q133" t="str">
         <v>null</v>
@@ -15380,19 +15380,19 @@
         <v>null</v>
       </c>
       <c r="V133" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/volume-werking</v>
+        <v>null</v>
       </c>
       <c r="W133" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X133" t="str">
         <v>null</v>
       </c>
       <c r="Y133" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/peilmeting</v>
       </c>
       <c r="Z133" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/peilmeting</v>
+        <v>null</v>
       </c>
       <c r="AA133" t="str">
         <v>null</v>
@@ -15401,16 +15401,16 @@
         <v>null</v>
       </c>
       <c r="AC133" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-pomptoestand/werking</v>
       </c>
       <c r="AD133" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-pomptoestand/werking</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/pomptoestand</v>
       </c>
       <c r="AE133" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/pomptoestand</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/volume-rust</v>
       </c>
       <c r="AF133" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/volume-rust</v>
+        <v>null</v>
       </c>
       <c r="AG133" t="str">
         <v>null</v>
@@ -15472,10 +15472,10 @@
         <v>Afvalproduct</v>
       </c>
       <c r="O134" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/afvalproduct</v>
       </c>
       <c r="P134" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q134" t="str">
         <v>null</v>
@@ -15493,16 +15493,16 @@
         <v>null</v>
       </c>
       <c r="V134" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/afvalproduct</v>
+        <v>null</v>
       </c>
       <c r="W134" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/afvalproduct_aard|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/afvalproduct_hoeveelheid|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/afvalproduct_naam</v>
       </c>
       <c r="X134" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/afvalproduct_aard|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/afvalproduct_hoeveelheid|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/afvalproduct_naam</v>
+        <v>true</v>
       </c>
       <c r="Y134" t="str">
-        <v>true</v>
+        <v>null</v>
       </c>
       <c r="Z134" t="str">
         <v>null</v>
@@ -15511,28 +15511,28 @@
         <v>null</v>
       </c>
       <c r="AB134" t="str">
-        <v>null</v>
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Observatie</v>
       </c>
       <c r="AC134" t="str">
-        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Observatie</v>
+        <v>null</v>
       </c>
       <c r="AD134" t="str">
         <v>null</v>
       </c>
       <c r="AE134" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/geproduceerde_stof</v>
       </c>
       <c r="AF134" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/geproduceerde_stof</v>
+        <v>null</v>
       </c>
       <c r="AG134" t="str">
         <v>null</v>
       </c>
       <c r="AH134" t="str">
-        <v>null</v>
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Verbruik</v>
       </c>
       <c r="AI134" t="str">
-        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Verbruik</v>
+        <v>null</v>
       </c>
       <c r="AJ134" t="str">
         <v>null</v>
@@ -15585,10 +15585,10 @@
         <v>Aard van de afvalproduct.</v>
       </c>
       <c r="O135" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/afvalproduct_aard</v>
       </c>
       <c r="P135" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q135" t="str">
         <v>null</v>
@@ -15603,40 +15603,40 @@
         <v>null</v>
       </c>
       <c r="U135" t="str">
+        <v>null</v>
+      </c>
+      <c r="V135" t="str">
         <v>true</v>
       </c>
-      <c r="V135" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/afvalproduct_aard</v>
-      </c>
       <c r="W135" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X135" t="str">
         <v>null</v>
       </c>
       <c r="Y135" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/afvalproduct</v>
       </c>
       <c r="Z135" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/afvalproduct</v>
+        <v>null</v>
       </c>
       <c r="AA135" t="str">
         <v>null</v>
       </c>
       <c r="AB135" t="str">
-        <v>null</v>
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Resultaat</v>
       </c>
       <c r="AC135" t="str">
-        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Resultaat</v>
+        <v>null</v>
       </c>
       <c r="AD135" t="str">
         <v>null</v>
       </c>
       <c r="AE135" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/afvalproduct_naam</v>
       </c>
       <c r="AF135" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/afvalproduct_naam</v>
+        <v>null</v>
       </c>
       <c r="AG135" t="str">
         <v>null</v>
@@ -15698,10 +15698,10 @@
         <v>null</v>
       </c>
       <c r="O136" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/afvalproduct_hoeveelheid</v>
       </c>
       <c r="P136" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q136" t="str">
         <v>null</v>
@@ -15719,37 +15719,37 @@
         <v>null</v>
       </c>
       <c r="V136" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/afvalproduct_hoeveelheid</v>
+        <v>null</v>
       </c>
       <c r="W136" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X136" t="str">
         <v>null</v>
       </c>
       <c r="Y136" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/afvalproduct</v>
       </c>
       <c r="Z136" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/afvalproduct</v>
+        <v>null</v>
       </c>
       <c r="AA136" t="str">
         <v>null</v>
       </c>
       <c r="AB136" t="str">
-        <v>null</v>
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Resultaat</v>
       </c>
       <c r="AC136" t="str">
-        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Resultaat</v>
+        <v>null</v>
       </c>
       <c r="AD136" t="str">
         <v>null</v>
       </c>
       <c r="AE136" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/afvalproduct_aard</v>
       </c>
       <c r="AF136" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/afvalproduct_aard</v>
+        <v>null</v>
       </c>
       <c r="AG136" t="str">
         <v>null</v>
@@ -15811,10 +15811,10 @@
         <v>Naam van het afvalproduct.</v>
       </c>
       <c r="O137" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/afvalproduct_naam</v>
       </c>
       <c r="P137" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q137" t="str">
         <v>null</v>
@@ -15829,31 +15829,31 @@
         <v>null</v>
       </c>
       <c r="U137" t="str">
+        <v>null</v>
+      </c>
+      <c r="V137" t="str">
         <v>true</v>
       </c>
-      <c r="V137" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/afvalproduct_naam</v>
-      </c>
       <c r="W137" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X137" t="str">
         <v>null</v>
       </c>
       <c r="Y137" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/afvalproduct</v>
       </c>
       <c r="Z137" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/afvalproduct</v>
+        <v>null</v>
       </c>
       <c r="AA137" t="str">
         <v>null</v>
       </c>
       <c r="AB137" t="str">
-        <v>null</v>
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Resultaat</v>
       </c>
       <c r="AC137" t="str">
-        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Resultaat</v>
+        <v>null</v>
       </c>
       <c r="AD137" t="str">
         <v>null</v>
@@ -15862,10 +15862,10 @@
         <v>null</v>
       </c>
       <c r="AF137" t="str">
-        <v>null</v>
+        <v>true</v>
       </c>
       <c r="AG137" t="str">
-        <v>true</v>
+        <v>null</v>
       </c>
       <c r="AH137" t="str">
         <v>null</v>
@@ -15924,10 +15924,10 @@
         <v>Geef de verbruikte brondstoffen op.</v>
       </c>
       <c r="O138" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/brandstof</v>
       </c>
       <c r="P138" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q138" t="str">
         <v>null</v>
@@ -15945,46 +15945,46 @@
         <v>null</v>
       </c>
       <c r="V138" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/brandstof</v>
+        <v>null</v>
       </c>
       <c r="W138" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/brandstof_as|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/brandstof_naam|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/brandstof_s|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/brandstof_verbruik</v>
       </c>
       <c r="X138" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/brandstof_as|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/brandstof_naam|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/brandstof_s|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/brandstof_verbruik</v>
+        <v>true</v>
       </c>
       <c r="Y138" t="str">
+        <v>null</v>
+      </c>
+      <c r="Z138" t="str">
+        <v>null</v>
+      </c>
+      <c r="AA138" t="str">
+        <v>null</v>
+      </c>
+      <c r="AB138" t="str">
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#ObservatieVerzameling</v>
+      </c>
+      <c r="AC138" t="str">
+        <v>null</v>
+      </c>
+      <c r="AD138" t="str">
+        <v>null</v>
+      </c>
+      <c r="AE138" t="str">
+        <v>null</v>
+      </c>
+      <c r="AF138" t="str">
         <v>true</v>
       </c>
-      <c r="Z138" t="str">
-        <v>null</v>
-      </c>
-      <c r="AA138" t="str">
-        <v>null</v>
-      </c>
-      <c r="AB138" t="str">
-        <v>null</v>
-      </c>
-      <c r="AC138" t="str">
-        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#ObservatieVerzameling</v>
-      </c>
-      <c r="AD138" t="str">
-        <v>null</v>
-      </c>
-      <c r="AE138" t="str">
-        <v>null</v>
-      </c>
-      <c r="AF138" t="str">
-        <v>null</v>
-      </c>
       <c r="AG138" t="str">
-        <v>true</v>
+        <v>null</v>
       </c>
       <c r="AH138" t="str">
-        <v>null</v>
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Verbruik</v>
       </c>
       <c r="AI138" t="str">
-        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Verbruik</v>
+        <v>null</v>
       </c>
       <c r="AJ138" t="str">
         <v>null</v>
@@ -16037,10 +16037,10 @@
         <v>null</v>
       </c>
       <c r="O139" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/brandstof_as</v>
       </c>
       <c r="P139" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q139" t="str">
         <v>null</v>
@@ -16055,40 +16055,40 @@
         <v>null</v>
       </c>
       <c r="U139" t="str">
+        <v>null</v>
+      </c>
+      <c r="V139" t="str">
         <v>true</v>
       </c>
-      <c r="V139" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/brandstof_as</v>
-      </c>
       <c r="W139" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X139" t="str">
         <v>null</v>
       </c>
       <c r="Y139" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/brandstof</v>
       </c>
       <c r="Z139" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/brandstof</v>
+        <v>null</v>
       </c>
       <c r="AA139" t="str">
         <v>null</v>
       </c>
       <c r="AB139" t="str">
-        <v>null</v>
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Observatie</v>
       </c>
       <c r="AC139" t="str">
-        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Observatie</v>
+        <v>null</v>
       </c>
       <c r="AD139" t="str">
         <v>null</v>
       </c>
       <c r="AE139" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/brandstof_s</v>
       </c>
       <c r="AF139" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/brandstof_s</v>
+        <v>null</v>
       </c>
       <c r="AG139" t="str">
         <v>null</v>
@@ -16150,10 +16150,10 @@
         <v>Naam van de brandstof.</v>
       </c>
       <c r="O140" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/brandstof_naam</v>
       </c>
       <c r="P140" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q140" t="str">
         <v>null</v>
@@ -16168,22 +16168,22 @@
         <v>null</v>
       </c>
       <c r="U140" t="str">
+        <v>null</v>
+      </c>
+      <c r="V140" t="str">
         <v>true</v>
       </c>
-      <c r="V140" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/brandstof_naam</v>
-      </c>
       <c r="W140" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X140" t="str">
         <v>null</v>
       </c>
       <c r="Y140" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/brandstof</v>
       </c>
       <c r="Z140" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/brandstof</v>
+        <v>null</v>
       </c>
       <c r="AA140" t="str">
         <v>null</v>
@@ -16201,10 +16201,10 @@
         <v>null</v>
       </c>
       <c r="AF140" t="str">
-        <v>null</v>
+        <v>true</v>
       </c>
       <c r="AG140" t="str">
-        <v>true</v>
+        <v>null</v>
       </c>
       <c r="AH140" t="str">
         <v>null</v>
@@ -16263,10 +16263,10 @@
         <v>null</v>
       </c>
       <c r="O141" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/brandstof_s</v>
       </c>
       <c r="P141" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q141" t="str">
         <v>null</v>
@@ -16281,40 +16281,40 @@
         <v>null</v>
       </c>
       <c r="U141" t="str">
+        <v>null</v>
+      </c>
+      <c r="V141" t="str">
         <v>true</v>
       </c>
-      <c r="V141" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/brandstof_s</v>
-      </c>
       <c r="W141" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X141" t="str">
         <v>null</v>
       </c>
       <c r="Y141" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/brandstof</v>
       </c>
       <c r="Z141" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/brandstof</v>
+        <v>null</v>
       </c>
       <c r="AA141" t="str">
         <v>null</v>
       </c>
       <c r="AB141" t="str">
-        <v>null</v>
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Observatie</v>
       </c>
       <c r="AC141" t="str">
-        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Observatie</v>
+        <v>null</v>
       </c>
       <c r="AD141" t="str">
         <v>null</v>
       </c>
       <c r="AE141" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/brandstof_naam</v>
       </c>
       <c r="AF141" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/brandstof_naam</v>
+        <v>null</v>
       </c>
       <c r="AG141" t="str">
         <v>null</v>
@@ -16376,10 +16376,10 @@
         <v>Verbruik van de brandstof in GJ</v>
       </c>
       <c r="O142" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/brandstof_verbruik</v>
       </c>
       <c r="P142" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q142" t="str">
         <v>null</v>
@@ -16394,40 +16394,40 @@
         <v>null</v>
       </c>
       <c r="U142" t="str">
+        <v>null</v>
+      </c>
+      <c r="V142" t="str">
         <v>true</v>
       </c>
-      <c r="V142" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/brandstof_verbruik</v>
-      </c>
       <c r="W142" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X142" t="str">
         <v>null</v>
       </c>
       <c r="Y142" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/brandstof</v>
       </c>
       <c r="Z142" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/brandstof</v>
+        <v>null</v>
       </c>
       <c r="AA142" t="str">
         <v>null</v>
       </c>
       <c r="AB142" t="str">
-        <v>null</v>
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Observatie</v>
       </c>
       <c r="AC142" t="str">
-        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Observatie</v>
+        <v>null</v>
       </c>
       <c r="AD142" t="str">
         <v>null</v>
       </c>
       <c r="AE142" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/brandstof_as</v>
       </c>
       <c r="AF142" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/brandstof_as</v>
+        <v>null</v>
       </c>
       <c r="AG142" t="str">
         <v>null</v>
@@ -16489,10 +16489,10 @@
         <v>null</v>
       </c>
       <c r="O143" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie</v>
       </c>
       <c r="P143" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q143" t="str">
         <v>null</v>
@@ -16510,16 +16510,16 @@
         <v>null</v>
       </c>
       <c r="V143" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie</v>
+        <v>null</v>
       </c>
       <c r="W143" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie_luchtoverschot|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie_parameter|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie_temperatuur|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie_vochtgehalte|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie_zuurstofgehalte|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissieduur|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissieperiode|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissieritme|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissietoestand|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissietype</v>
       </c>
       <c r="X143" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie_luchtoverschot|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie_parameter|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie_temperatuur|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie_vochtgehalte|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie_zuurstofgehalte|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissieduur|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissieperiode|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissieritme|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissietoestand|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissietype</v>
+        <v>true</v>
       </c>
       <c r="Y143" t="str">
-        <v>true</v>
+        <v>null</v>
       </c>
       <c r="Z143" t="str">
         <v>null</v>
@@ -16528,10 +16528,10 @@
         <v>null</v>
       </c>
       <c r="AB143" t="str">
-        <v>null</v>
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#ObservatieVerzameling</v>
       </c>
       <c r="AC143" t="str">
-        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#ObservatieVerzameling</v>
+        <v>null</v>
       </c>
       <c r="AD143" t="str">
         <v>null</v>
@@ -16546,10 +16546,10 @@
         <v>null</v>
       </c>
       <c r="AH143" t="str">
-        <v>null</v>
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Emissie</v>
       </c>
       <c r="AI143" t="str">
-        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Emissie</v>
+        <v>null</v>
       </c>
       <c r="AJ143" t="str">
         <v>null</v>
@@ -16602,10 +16602,10 @@
         <v>null</v>
       </c>
       <c r="O144" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie_luchtoverschot</v>
       </c>
       <c r="P144" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q144" t="str">
         <v>null</v>
@@ -16623,28 +16623,28 @@
         <v>null</v>
       </c>
       <c r="V144" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie_luchtoverschot</v>
+        <v>null</v>
       </c>
       <c r="W144" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X144" t="str">
         <v>null</v>
       </c>
       <c r="Y144" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie</v>
       </c>
       <c r="Z144" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie</v>
+        <v>null</v>
       </c>
       <c r="AA144" t="str">
         <v>null</v>
       </c>
       <c r="AB144" t="str">
-        <v>null</v>
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Observatie</v>
       </c>
       <c r="AC144" t="str">
-        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Observatie</v>
+        <v>null</v>
       </c>
       <c r="AD144" t="str">
         <v>null</v>
@@ -16715,10 +16715,10 @@
         <v>null</v>
       </c>
       <c r="O145" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie_parameter</v>
       </c>
       <c r="P145" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q145" t="str">
         <v>null</v>
@@ -16736,19 +16736,19 @@
         <v>null</v>
       </c>
       <c r="V145" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie_parameter</v>
+        <v>null</v>
       </c>
       <c r="W145" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie_parameter_massastroom|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie_parameter_meetfrequentie|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie_parameter_parameter|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie_parameter_standaardafwijking</v>
       </c>
       <c r="X145" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie_parameter_massastroom|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie_parameter_meetfrequentie|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie_parameter_parameter|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie_parameter_standaardafwijking</v>
+        <v>true</v>
       </c>
       <c r="Y145" t="str">
-        <v>true</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie</v>
       </c>
       <c r="Z145" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie</v>
+        <v>null</v>
       </c>
       <c r="AA145" t="str">
         <v>null</v>
@@ -16828,10 +16828,10 @@
         <v>null</v>
       </c>
       <c r="O146" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie_parameter_massastroom</v>
       </c>
       <c r="P146" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q146" t="str">
         <v>null</v>
@@ -16849,19 +16849,19 @@
         <v>null</v>
       </c>
       <c r="V146" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie_parameter_massastroom</v>
+        <v>null</v>
       </c>
       <c r="W146" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X146" t="str">
         <v>null</v>
       </c>
       <c r="Y146" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie_parameter</v>
       </c>
       <c r="Z146" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie_parameter</v>
+        <v>null</v>
       </c>
       <c r="AA146" t="str">
         <v>null</v>
@@ -16941,10 +16941,10 @@
         <v>null</v>
       </c>
       <c r="O147" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie_parameter_meetfrequentie</v>
       </c>
       <c r="P147" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q147" t="str">
         <v>null</v>
@@ -16962,19 +16962,19 @@
         <v>null</v>
       </c>
       <c r="V147" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie_parameter_meetfrequentie</v>
+        <v>null</v>
       </c>
       <c r="W147" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X147" t="str">
         <v>null</v>
       </c>
       <c r="Y147" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie_parameter</v>
       </c>
       <c r="Z147" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie_parameter</v>
+        <v>null</v>
       </c>
       <c r="AA147" t="str">
         <v>null</v>
@@ -17054,10 +17054,10 @@
         <v>null</v>
       </c>
       <c r="O148" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie_parameter_parameter</v>
       </c>
       <c r="P148" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q148" t="str">
         <v>null</v>
@@ -17075,19 +17075,19 @@
         <v>null</v>
       </c>
       <c r="V148" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie_parameter_parameter</v>
+        <v>null</v>
       </c>
       <c r="W148" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X148" t="str">
         <v>null</v>
       </c>
       <c r="Y148" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie_parameter</v>
       </c>
       <c r="Z148" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie_parameter</v>
+        <v>null</v>
       </c>
       <c r="AA148" t="str">
         <v>null</v>
@@ -17167,10 +17167,10 @@
         <v>null</v>
       </c>
       <c r="O149" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie_parameter_standaardafwijking</v>
       </c>
       <c r="P149" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q149" t="str">
         <v>null</v>
@@ -17188,19 +17188,19 @@
         <v>null</v>
       </c>
       <c r="V149" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie_parameter_standaardafwijking</v>
+        <v>null</v>
       </c>
       <c r="W149" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X149" t="str">
         <v>null</v>
       </c>
       <c r="Y149" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie_parameter</v>
       </c>
       <c r="Z149" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie_parameter</v>
+        <v>null</v>
       </c>
       <c r="AA149" t="str">
         <v>null</v>
@@ -17280,10 +17280,10 @@
         <v>null</v>
       </c>
       <c r="O150" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie_temperatuur</v>
       </c>
       <c r="P150" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q150" t="str">
         <v>null</v>
@@ -17301,28 +17301,28 @@
         <v>null</v>
       </c>
       <c r="V150" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie_temperatuur</v>
+        <v>null</v>
       </c>
       <c r="W150" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X150" t="str">
         <v>null</v>
       </c>
       <c r="Y150" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie</v>
       </c>
       <c r="Z150" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie</v>
+        <v>null</v>
       </c>
       <c r="AA150" t="str">
         <v>null</v>
       </c>
       <c r="AB150" t="str">
-        <v>null</v>
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Observatie</v>
       </c>
       <c r="AC150" t="str">
-        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Observatie</v>
+        <v>null</v>
       </c>
       <c r="AD150" t="str">
         <v>null</v>
@@ -17393,10 +17393,10 @@
         <v>null</v>
       </c>
       <c r="O151" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie_vochtgehalte</v>
       </c>
       <c r="P151" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q151" t="str">
         <v>null</v>
@@ -17414,28 +17414,28 @@
         <v>null</v>
       </c>
       <c r="V151" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie_vochtgehalte</v>
+        <v>null</v>
       </c>
       <c r="W151" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X151" t="str">
         <v>null</v>
       </c>
       <c r="Y151" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie</v>
       </c>
       <c r="Z151" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie</v>
+        <v>null</v>
       </c>
       <c r="AA151" t="str">
         <v>null</v>
       </c>
       <c r="AB151" t="str">
-        <v>null</v>
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Observatie</v>
       </c>
       <c r="AC151" t="str">
-        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Observatie</v>
+        <v>null</v>
       </c>
       <c r="AD151" t="str">
         <v>null</v>
@@ -17506,10 +17506,10 @@
         <v>null</v>
       </c>
       <c r="O152" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie_zuurstofgehalte</v>
       </c>
       <c r="P152" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q152" t="str">
         <v>null</v>
@@ -17527,28 +17527,28 @@
         <v>null</v>
       </c>
       <c r="V152" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie_zuurstofgehalte</v>
+        <v>null</v>
       </c>
       <c r="W152" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X152" t="str">
         <v>null</v>
       </c>
       <c r="Y152" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie</v>
       </c>
       <c r="Z152" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie</v>
+        <v>null</v>
       </c>
       <c r="AA152" t="str">
         <v>null</v>
       </c>
       <c r="AB152" t="str">
-        <v>null</v>
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Observatie</v>
       </c>
       <c r="AC152" t="str">
-        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Observatie</v>
+        <v>null</v>
       </c>
       <c r="AD152" t="str">
         <v>null</v>
@@ -17619,10 +17619,10 @@
         <v>null</v>
       </c>
       <c r="O153" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissieduur</v>
       </c>
       <c r="P153" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q153" t="str">
         <v>null</v>
@@ -17640,19 +17640,19 @@
         <v>null</v>
       </c>
       <c r="V153" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissieduur</v>
+        <v>null</v>
       </c>
       <c r="W153" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X153" t="str">
         <v>null</v>
       </c>
       <c r="Y153" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie</v>
       </c>
       <c r="Z153" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie</v>
+        <v>null</v>
       </c>
       <c r="AA153" t="str">
         <v>null</v>
@@ -17732,10 +17732,10 @@
         <v>null</v>
       </c>
       <c r="O154" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissieperiode</v>
       </c>
       <c r="P154" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q154" t="str">
         <v>null</v>
@@ -17753,19 +17753,19 @@
         <v>null</v>
       </c>
       <c r="V154" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissieperiode</v>
+        <v>null</v>
       </c>
       <c r="W154" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X154" t="str">
         <v>null</v>
       </c>
       <c r="Y154" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie</v>
       </c>
       <c r="Z154" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie</v>
+        <v>null</v>
       </c>
       <c r="AA154" t="str">
         <v>null</v>
@@ -17845,10 +17845,10 @@
         <v>null</v>
       </c>
       <c r="O155" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissieritme</v>
       </c>
       <c r="P155" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q155" t="str">
         <v>null</v>
@@ -17866,19 +17866,19 @@
         <v>null</v>
       </c>
       <c r="V155" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissieritme</v>
+        <v>null</v>
       </c>
       <c r="W155" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X155" t="str">
         <v>null</v>
       </c>
       <c r="Y155" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie</v>
       </c>
       <c r="Z155" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie</v>
+        <v>null</v>
       </c>
       <c r="AA155" t="str">
         <v>null</v>
@@ -17958,10 +17958,10 @@
         <v>null</v>
       </c>
       <c r="O156" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissietoestand</v>
       </c>
       <c r="P156" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q156" t="str">
         <v>null</v>
@@ -17979,19 +17979,19 @@
         <v>null</v>
       </c>
       <c r="V156" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissietoestand</v>
+        <v>null</v>
       </c>
       <c r="W156" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X156" t="str">
         <v>null</v>
       </c>
       <c r="Y156" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie</v>
       </c>
       <c r="Z156" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie</v>
+        <v>null</v>
       </c>
       <c r="AA156" t="str">
         <v>null</v>
@@ -18071,10 +18071,10 @@
         <v>null</v>
       </c>
       <c r="O157" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissietype</v>
       </c>
       <c r="P157" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q157" t="str">
         <v>null</v>
@@ -18092,19 +18092,19 @@
         <v>null</v>
       </c>
       <c r="V157" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissietype</v>
+        <v>null</v>
       </c>
       <c r="W157" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X157" t="str">
         <v>null</v>
       </c>
       <c r="Y157" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie</v>
       </c>
       <c r="Z157" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie</v>
+        <v>null</v>
       </c>
       <c r="AA157" t="str">
         <v>null</v>
@@ -18223,10 +18223,10 @@
         <v>null</v>
       </c>
       <c r="AB158" t="str">
-        <v>null</v>
+        <v>http://www.w3.org/ns/sosa/FeatureOfInterest</v>
       </c>
       <c r="AC158" t="str">
-        <v>http://www.w3.org/ns/sosa/FeatureOfInterest</v>
+        <v>null</v>
       </c>
       <c r="AD158" t="str">
         <v>null</v>
@@ -18235,13 +18235,13 @@
         <v>null</v>
       </c>
       <c r="AF158" t="str">
-        <v>null</v>
+        <v>true</v>
       </c>
       <c r="AG158" t="str">
         <v>true</v>
       </c>
       <c r="AH158" t="str">
-        <v>true</v>
+        <v>null</v>
       </c>
       <c r="AI158" t="str">
         <v>null</v>
@@ -18336,10 +18336,10 @@
         <v>null</v>
       </c>
       <c r="AB159" t="str">
-        <v>null</v>
+        <v>http://www.w3.org/ns/sosa/FeatureOfInterest</v>
       </c>
       <c r="AC159" t="str">
-        <v>http://www.w3.org/ns/sosa/FeatureOfInterest</v>
+        <v>null</v>
       </c>
       <c r="AD159" t="str">
         <v>null</v>
@@ -18348,10 +18348,10 @@
         <v>null</v>
       </c>
       <c r="AF159" t="str">
-        <v>null</v>
+        <v>true</v>
       </c>
       <c r="AG159" t="str">
-        <v>true</v>
+        <v>null</v>
       </c>
       <c r="AH159" t="str">
         <v>null</v>
@@ -18410,10 +18410,10 @@
         <v>Geproduceerde stof.</v>
       </c>
       <c r="O160" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/geproduceerde_stof</v>
       </c>
       <c r="P160" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q160" t="str">
         <v>null</v>
@@ -18431,16 +18431,16 @@
         <v>null</v>
       </c>
       <c r="V160" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/geproduceerde_stof</v>
+        <v>null</v>
       </c>
       <c r="W160" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/geproduceerde_stof_aard|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/geproduceerde_stof_hoeveelheid|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/geproduceerde_stof_naam</v>
       </c>
       <c r="X160" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/geproduceerde_stof_aard|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/geproduceerde_stof_hoeveelheid|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/geproduceerde_stof_naam</v>
+        <v>true</v>
       </c>
       <c r="Y160" t="str">
-        <v>true</v>
+        <v>null</v>
       </c>
       <c r="Z160" t="str">
         <v>null</v>
@@ -18449,28 +18449,28 @@
         <v>null</v>
       </c>
       <c r="AB160" t="str">
-        <v>null</v>
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Observatie</v>
       </c>
       <c r="AC160" t="str">
-        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Observatie</v>
+        <v>null</v>
       </c>
       <c r="AD160" t="str">
         <v>null</v>
       </c>
       <c r="AE160" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/verbruikte_stof</v>
       </c>
       <c r="AF160" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/verbruikte_stof</v>
+        <v>null</v>
       </c>
       <c r="AG160" t="str">
         <v>null</v>
       </c>
       <c r="AH160" t="str">
-        <v>null</v>
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Verbruik</v>
       </c>
       <c r="AI160" t="str">
-        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Verbruik</v>
+        <v>null</v>
       </c>
       <c r="AJ160" t="str">
         <v>null</v>
@@ -18523,10 +18523,10 @@
         <v>Aard van de geproduceerde stof.</v>
       </c>
       <c r="O161" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/geproduceerde_stof_aard</v>
       </c>
       <c r="P161" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q161" t="str">
         <v>null</v>
@@ -18541,40 +18541,40 @@
         <v>null</v>
       </c>
       <c r="U161" t="str">
+        <v>null</v>
+      </c>
+      <c r="V161" t="str">
         <v>true</v>
       </c>
-      <c r="V161" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/geproduceerde_stof_aard</v>
-      </c>
       <c r="W161" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X161" t="str">
         <v>null</v>
       </c>
       <c r="Y161" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/geproduceerde_stof</v>
       </c>
       <c r="Z161" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/geproduceerde_stof</v>
+        <v>null</v>
       </c>
       <c r="AA161" t="str">
         <v>null</v>
       </c>
       <c r="AB161" t="str">
-        <v>null</v>
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Resultaat</v>
       </c>
       <c r="AC161" t="str">
-        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Resultaat</v>
+        <v>null</v>
       </c>
       <c r="AD161" t="str">
         <v>null</v>
       </c>
       <c r="AE161" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/geproduceerde_stof_naam</v>
       </c>
       <c r="AF161" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/geproduceerde_stof_naam</v>
+        <v>null</v>
       </c>
       <c r="AG161" t="str">
         <v>null</v>
@@ -18636,10 +18636,10 @@
         <v>null</v>
       </c>
       <c r="O162" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/geproduceerde_stof_hoeveelheid</v>
       </c>
       <c r="P162" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q162" t="str">
         <v>null</v>
@@ -18657,37 +18657,37 @@
         <v>null</v>
       </c>
       <c r="V162" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/geproduceerde_stof_hoeveelheid</v>
+        <v>null</v>
       </c>
       <c r="W162" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X162" t="str">
         <v>null</v>
       </c>
       <c r="Y162" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/geproduceerde_stof</v>
       </c>
       <c r="Z162" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/geproduceerde_stof</v>
+        <v>null</v>
       </c>
       <c r="AA162" t="str">
         <v>null</v>
       </c>
       <c r="AB162" t="str">
-        <v>null</v>
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Resultaat</v>
       </c>
       <c r="AC162" t="str">
-        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Resultaat</v>
+        <v>null</v>
       </c>
       <c r="AD162" t="str">
         <v>null</v>
       </c>
       <c r="AE162" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/geproduceerde_stof_aard</v>
       </c>
       <c r="AF162" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/geproduceerde_stof_aard</v>
+        <v>null</v>
       </c>
       <c r="AG162" t="str">
         <v>null</v>
@@ -18749,10 +18749,10 @@
         <v>Naam van de geproduceerde stof.</v>
       </c>
       <c r="O163" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/geproduceerde_stof_naam</v>
       </c>
       <c r="P163" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q163" t="str">
         <v>null</v>
@@ -18767,31 +18767,31 @@
         <v>null</v>
       </c>
       <c r="U163" t="str">
+        <v>null</v>
+      </c>
+      <c r="V163" t="str">
         <v>true</v>
       </c>
-      <c r="V163" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/geproduceerde_stof_naam</v>
-      </c>
       <c r="W163" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X163" t="str">
         <v>null</v>
       </c>
       <c r="Y163" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/geproduceerde_stof</v>
       </c>
       <c r="Z163" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/geproduceerde_stof</v>
+        <v>null</v>
       </c>
       <c r="AA163" t="str">
         <v>null</v>
       </c>
       <c r="AB163" t="str">
-        <v>null</v>
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Resultaat</v>
       </c>
       <c r="AC163" t="str">
-        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Resultaat</v>
+        <v>null</v>
       </c>
       <c r="AD163" t="str">
         <v>null</v>
@@ -18800,10 +18800,10 @@
         <v>null</v>
       </c>
       <c r="AF163" t="str">
-        <v>null</v>
+        <v>true</v>
       </c>
       <c r="AG163" t="str">
-        <v>true</v>
+        <v>null</v>
       </c>
       <c r="AH163" t="str">
         <v>null</v>
@@ -18862,10 +18862,10 @@
         <v>Geef de verbruikte stoffen op.</v>
       </c>
       <c r="O164" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/verbruikte_stof</v>
       </c>
       <c r="P164" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q164" t="str">
         <v>null</v>
@@ -18883,16 +18883,16 @@
         <v>null</v>
       </c>
       <c r="V164" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/verbruikte_stof</v>
+        <v>null</v>
       </c>
       <c r="W164" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/verbruikte_stof_aard|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/verbruikte_stof_hoeveelheid|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/verbruikte_stof_naam</v>
       </c>
       <c r="X164" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/verbruikte_stof_aard|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/verbruikte_stof_hoeveelheid|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/verbruikte_stof_naam</v>
+        <v>true</v>
       </c>
       <c r="Y164" t="str">
-        <v>true</v>
+        <v>null</v>
       </c>
       <c r="Z164" t="str">
         <v>null</v>
@@ -18901,28 +18901,28 @@
         <v>null</v>
       </c>
       <c r="AB164" t="str">
-        <v>null</v>
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Observatie</v>
       </c>
       <c r="AC164" t="str">
-        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Observatie</v>
+        <v>null</v>
       </c>
       <c r="AD164" t="str">
         <v>null</v>
       </c>
       <c r="AE164" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/brandstof</v>
       </c>
       <c r="AF164" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/brandstof</v>
+        <v>null</v>
       </c>
       <c r="AG164" t="str">
         <v>null</v>
       </c>
       <c r="AH164" t="str">
-        <v>null</v>
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Verbruik</v>
       </c>
       <c r="AI164" t="str">
-        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Verbruik</v>
+        <v>null</v>
       </c>
       <c r="AJ164" t="str">
         <v>null</v>
@@ -18975,10 +18975,10 @@
         <v>Aard van het verbruik.</v>
       </c>
       <c r="O165" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/verbruikte_stof_aard</v>
       </c>
       <c r="P165" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q165" t="str">
         <v>null</v>
@@ -18993,40 +18993,40 @@
         <v>null</v>
       </c>
       <c r="U165" t="str">
+        <v>null</v>
+      </c>
+      <c r="V165" t="str">
         <v>true</v>
       </c>
-      <c r="V165" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/verbruikte_stof_aard</v>
-      </c>
       <c r="W165" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X165" t="str">
         <v>null</v>
       </c>
       <c r="Y165" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/verbruikte_stof</v>
       </c>
       <c r="Z165" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/verbruikte_stof</v>
+        <v>null</v>
       </c>
       <c r="AA165" t="str">
         <v>null</v>
       </c>
       <c r="AB165" t="str">
-        <v>null</v>
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Resultaat</v>
       </c>
       <c r="AC165" t="str">
-        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Resultaat</v>
+        <v>null</v>
       </c>
       <c r="AD165" t="str">
         <v>null</v>
       </c>
       <c r="AE165" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/verbruikte_stof_naam</v>
       </c>
       <c r="AF165" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/verbruikte_stof_naam</v>
+        <v>null</v>
       </c>
       <c r="AG165" t="str">
         <v>null</v>
@@ -19088,10 +19088,10 @@
         <v>null</v>
       </c>
       <c r="O166" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/verbruikte_stof_hoeveelheid</v>
       </c>
       <c r="P166" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q166" t="str">
         <v>null</v>
@@ -19106,40 +19106,40 @@
         <v>null</v>
       </c>
       <c r="U166" t="str">
+        <v>null</v>
+      </c>
+      <c r="V166" t="str">
         <v>true</v>
       </c>
-      <c r="V166" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/verbruikte_stof_hoeveelheid</v>
-      </c>
       <c r="W166" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X166" t="str">
         <v>null</v>
       </c>
       <c r="Y166" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/verbruikte_stof</v>
       </c>
       <c r="Z166" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/verbruikte_stof</v>
+        <v>null</v>
       </c>
       <c r="AA166" t="str">
         <v>null</v>
       </c>
       <c r="AB166" t="str">
-        <v>null</v>
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Resultaat</v>
       </c>
       <c r="AC166" t="str">
-        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Resultaat</v>
+        <v>null</v>
       </c>
       <c r="AD166" t="str">
         <v>null</v>
       </c>
       <c r="AE166" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/verbruikte_stof_aard</v>
       </c>
       <c r="AF166" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/verbruikte_stof_aard</v>
+        <v>null</v>
       </c>
       <c r="AG166" t="str">
         <v>null</v>
@@ -19201,10 +19201,10 @@
         <v>Naam van de verbruikte stof.</v>
       </c>
       <c r="O167" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/verbruikte_stof_naam</v>
       </c>
       <c r="P167" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q167" t="str">
         <v>null</v>
@@ -19219,22 +19219,22 @@
         <v>null</v>
       </c>
       <c r="U167" t="str">
+        <v>null</v>
+      </c>
+      <c r="V167" t="str">
         <v>true</v>
       </c>
-      <c r="V167" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/verbruikte_stof_naam</v>
-      </c>
       <c r="W167" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X167" t="str">
         <v>null</v>
       </c>
       <c r="Y167" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/verbruikte_stof</v>
       </c>
       <c r="Z167" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/verbruikte_stof</v>
+        <v>null</v>
       </c>
       <c r="AA167" t="str">
         <v>null</v>
@@ -19252,10 +19252,10 @@
         <v>null</v>
       </c>
       <c r="AF167" t="str">
-        <v>null</v>
+        <v>true</v>
       </c>
       <c r="AG167" t="str">
-        <v>true</v>
+        <v>null</v>
       </c>
       <c r="AH167" t="str">
         <v>null</v>
@@ -20444,10 +20444,10 @@
         <v>null</v>
       </c>
       <c r="O178" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-toestand-indicator/droog</v>
       </c>
       <c r="P178" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q178" t="str">
         <v>null</v>
@@ -20465,10 +20465,10 @@
         <v>null</v>
       </c>
       <c r="V178" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-toestand-indicator/droog</v>
+        <v>null</v>
       </c>
       <c r="W178" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X178" t="str">
         <v>null</v>
@@ -20557,10 +20557,10 @@
         <v>null</v>
       </c>
       <c r="O179" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-toestand-indicator/nat</v>
       </c>
       <c r="P179" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q179" t="str">
         <v>null</v>
@@ -20578,10 +20578,10 @@
         <v>null</v>
       </c>
       <c r="V179" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-toestand-indicator/nat</v>
+        <v>null</v>
       </c>
       <c r="W179" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X179" t="str">
         <v>null</v>
@@ -20670,10 +20670,10 @@
         <v>null</v>
       </c>
       <c r="O180" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/abnormale-lozing</v>
       </c>
       <c r="P180" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q180" t="str">
         <v>null</v>
@@ -20688,19 +20688,19 @@
         <v>null</v>
       </c>
       <c r="U180" t="str">
+        <v>null</v>
+      </c>
+      <c r="V180" t="str">
         <v>false</v>
       </c>
-      <c r="V180" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/abnormale-lozing</v>
-      </c>
       <c r="W180" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/abnormale-lozing-jaarvracht|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/abnormale-lozing-lozingsduur|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/abnormale-lozing-stof|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/abnormale-lozing-verklaring</v>
       </c>
       <c r="X180" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/abnormale-lozing-jaarvracht|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/abnormale-lozing-lozingsduur|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/abnormale-lozing-stof|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/abnormale-lozing-verklaring</v>
+        <v>true</v>
       </c>
       <c r="Y180" t="str">
-        <v>true</v>
+        <v>null</v>
       </c>
       <c r="Z180" t="str">
         <v>null</v>
@@ -20709,19 +20709,19 @@
         <v>null</v>
       </c>
       <c r="AB180" t="str">
-        <v>null</v>
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Observatie</v>
       </c>
       <c r="AC180" t="str">
-        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Observatie</v>
+        <v>null</v>
       </c>
       <c r="AD180" t="str">
         <v>null</v>
       </c>
       <c r="AE180" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing</v>
       </c>
       <c r="AF180" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing</v>
+        <v>null</v>
       </c>
       <c r="AG180" t="str">
         <v>null</v>
@@ -20783,10 +20783,10 @@
         <v>null</v>
       </c>
       <c r="O181" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/abnormale-lozing-jaarvracht</v>
       </c>
       <c r="P181" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q181" t="str">
         <v>null</v>
@@ -20804,19 +20804,19 @@
         <v>null</v>
       </c>
       <c r="V181" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/abnormale-lozing-jaarvracht</v>
+        <v>null</v>
       </c>
       <c r="W181" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X181" t="str">
         <v>null</v>
       </c>
       <c r="Y181" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/abnormale-lozing</v>
       </c>
       <c r="Z181" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/abnormale-lozing</v>
+        <v>null</v>
       </c>
       <c r="AA181" t="str">
         <v>null</v>
@@ -20831,10 +20831,10 @@
         <v>null</v>
       </c>
       <c r="AE181" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/abnormale-lozing-lozingsduur</v>
       </c>
       <c r="AF181" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/abnormale-lozing-lozingsduur</v>
+        <v>null</v>
       </c>
       <c r="AG181" t="str">
         <v>null</v>
@@ -20896,10 +20896,10 @@
         <v>null</v>
       </c>
       <c r="O182" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/abnormale-lozing-lozingsduur</v>
       </c>
       <c r="P182" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q182" t="str">
         <v>null</v>
@@ -20914,22 +20914,22 @@
         <v>null</v>
       </c>
       <c r="U182" t="str">
+        <v>null</v>
+      </c>
+      <c r="V182" t="str">
         <v>true</v>
       </c>
-      <c r="V182" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/abnormale-lozing-lozingsduur</v>
-      </c>
       <c r="W182" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X182" t="str">
         <v>null</v>
       </c>
       <c r="Y182" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/abnormale-lozing</v>
       </c>
       <c r="Z182" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/abnormale-lozing</v>
+        <v>null</v>
       </c>
       <c r="AA182" t="str">
         <v>null</v>
@@ -20944,10 +20944,10 @@
         <v>null</v>
       </c>
       <c r="AE182" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/abnormale-lozing-stof</v>
       </c>
       <c r="AF182" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/abnormale-lozing-stof</v>
+        <v>null</v>
       </c>
       <c r="AG182" t="str">
         <v>null</v>
@@ -21009,10 +21009,10 @@
         <v>null</v>
       </c>
       <c r="O183" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/abnormale-lozing-stof</v>
       </c>
       <c r="P183" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q183" t="str">
         <v>null</v>
@@ -21027,22 +21027,22 @@
         <v>null</v>
       </c>
       <c r="U183" t="str">
+        <v>null</v>
+      </c>
+      <c r="V183" t="str">
         <v>true</v>
       </c>
-      <c r="V183" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/abnormale-lozing-stof</v>
-      </c>
       <c r="W183" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X183" t="str">
         <v>null</v>
       </c>
       <c r="Y183" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/abnormale-lozing</v>
       </c>
       <c r="Z183" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/abnormale-lozing</v>
+        <v>null</v>
       </c>
       <c r="AA183" t="str">
         <v>null</v>
@@ -21060,10 +21060,10 @@
         <v>null</v>
       </c>
       <c r="AF183" t="str">
-        <v>null</v>
+        <v>true</v>
       </c>
       <c r="AG183" t="str">
-        <v>true</v>
+        <v>null</v>
       </c>
       <c r="AH183" t="str">
         <v>null</v>
@@ -21122,10 +21122,10 @@
         <v>null</v>
       </c>
       <c r="O184" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/abnormale-lozing-verklaring</v>
       </c>
       <c r="P184" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q184" t="str">
         <v>null</v>
@@ -21143,19 +21143,19 @@
         <v>null</v>
       </c>
       <c r="V184" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/abnormale-lozing-verklaring</v>
+        <v>null</v>
       </c>
       <c r="W184" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X184" t="str">
         <v>null</v>
       </c>
       <c r="Y184" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/abnormale-lozing</v>
       </c>
       <c r="Z184" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/abnormale-lozing</v>
+        <v>null</v>
       </c>
       <c r="AA184" t="str">
         <v>null</v>
@@ -21170,10 +21170,10 @@
         <v>null</v>
       </c>
       <c r="AE184" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/abnormale-lozing-jaarvracht</v>
       </c>
       <c r="AF184" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/abnormale-lozing-jaarvracht</v>
+        <v>null</v>
       </c>
       <c r="AG184" t="str">
         <v>null</v>
@@ -21253,43 +21253,43 @@
         <v>null</v>
       </c>
       <c r="U185" t="str">
+        <v>null</v>
+      </c>
+      <c r="V185" t="str">
         <v>true</v>
       </c>
-      <c r="V185" t="str">
-        <v>null</v>
-      </c>
       <c r="W185" t="str">
         <v>null</v>
       </c>
       <c r="X185" t="str">
-        <v>null</v>
+        <v>true</v>
       </c>
       <c r="Y185" t="str">
+        <v>null</v>
+      </c>
+      <c r="Z185" t="str">
+        <v>null</v>
+      </c>
+      <c r="AA185" t="str">
+        <v>null</v>
+      </c>
+      <c r="AB185" t="str">
+        <v>http://www.w3.org/ns/sosa/FeatureOfInterest</v>
+      </c>
+      <c r="AC185" t="str">
+        <v>null</v>
+      </c>
+      <c r="AD185" t="str">
+        <v>null</v>
+      </c>
+      <c r="AE185" t="str">
+        <v>null</v>
+      </c>
+      <c r="AF185" t="str">
         <v>true</v>
       </c>
-      <c r="Z185" t="str">
-        <v>null</v>
-      </c>
-      <c r="AA185" t="str">
-        <v>null</v>
-      </c>
-      <c r="AB185" t="str">
-        <v>null</v>
-      </c>
-      <c r="AC185" t="str">
-        <v>http://www.w3.org/ns/sosa/FeatureOfInterest</v>
-      </c>
-      <c r="AD185" t="str">
-        <v>null</v>
-      </c>
-      <c r="AE185" t="str">
-        <v>null</v>
-      </c>
-      <c r="AF185" t="str">
-        <v>null</v>
-      </c>
       <c r="AG185" t="str">
-        <v>true</v>
+        <v>null</v>
       </c>
       <c r="AH185" t="str">
         <v>null</v>
@@ -21348,10 +21348,10 @@
         <v>null</v>
       </c>
       <c r="O186" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing</v>
       </c>
       <c r="P186" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q186" t="str">
         <v>null</v>
@@ -21366,49 +21366,49 @@
         <v>null</v>
       </c>
       <c r="U186" t="str">
+        <v>null</v>
+      </c>
+      <c r="V186" t="str">
         <v>true</v>
       </c>
-      <c r="V186" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing</v>
-      </c>
       <c r="W186" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing-bepalingsmethode|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing-jaarvracht|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing-bepalingsmethodeclassificatie|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing-concentratie|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing-meetfrequentie|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing-dagen|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing-debiet|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing-stof</v>
       </c>
       <c r="X186" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing-bepalingsmethode|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing-jaarvracht|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing-bepalingsmethodeclassificatie|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing-concentratie|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing-meetfrequentie|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing-dagen|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing-debiet|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing-stof</v>
+        <v>true</v>
       </c>
       <c r="Y186" t="str">
+        <v>null</v>
+      </c>
+      <c r="Z186" t="str">
+        <v>null</v>
+      </c>
+      <c r="AA186" t="str">
+        <v>null</v>
+      </c>
+      <c r="AB186" t="str">
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#ObservatieVerzameling</v>
+      </c>
+      <c r="AC186" t="str">
+        <v>null</v>
+      </c>
+      <c r="AD186" t="str">
+        <v>null</v>
+      </c>
+      <c r="AE186" t="str">
+        <v>null</v>
+      </c>
+      <c r="AF186" t="str">
         <v>true</v>
       </c>
-      <c r="Z186" t="str">
-        <v>null</v>
-      </c>
-      <c r="AA186" t="str">
-        <v>null</v>
-      </c>
-      <c r="AB186" t="str">
-        <v>null</v>
-      </c>
-      <c r="AC186" t="str">
-        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#ObservatieVerzameling</v>
-      </c>
-      <c r="AD186" t="str">
-        <v>null</v>
-      </c>
-      <c r="AE186" t="str">
-        <v>null</v>
-      </c>
-      <c r="AF186" t="str">
-        <v>null</v>
-      </c>
       <c r="AG186" t="str">
-        <v>true</v>
+        <v>null</v>
       </c>
       <c r="AH186" t="str">
-        <v>null</v>
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Emissie</v>
       </c>
       <c r="AI186" t="str">
-        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Emissie</v>
+        <v>null</v>
       </c>
       <c r="AJ186" t="str">
         <v>null</v>
@@ -21461,10 +21461,10 @@
         <v>null</v>
       </c>
       <c r="O187" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing-bepalingsmethode</v>
       </c>
       <c r="P187" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q187" t="str">
         <v>null</v>
@@ -21482,19 +21482,19 @@
         <v>null</v>
       </c>
       <c r="V187" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing-bepalingsmethode</v>
+        <v>null</v>
       </c>
       <c r="W187" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X187" t="str">
         <v>null</v>
       </c>
       <c r="Y187" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing</v>
       </c>
       <c r="Z187" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing</v>
+        <v>null</v>
       </c>
       <c r="AA187" t="str">
         <v>null</v>
@@ -21509,10 +21509,10 @@
         <v>null</v>
       </c>
       <c r="AE187" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing-jaarvracht</v>
       </c>
       <c r="AF187" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing-jaarvracht</v>
+        <v>null</v>
       </c>
       <c r="AG187" t="str">
         <v>null</v>
@@ -21574,10 +21574,10 @@
         <v>null</v>
       </c>
       <c r="O188" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing-bepalingsmethodeclassificatie</v>
       </c>
       <c r="P188" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q188" t="str">
         <v>null</v>
@@ -21595,19 +21595,19 @@
         <v>null</v>
       </c>
       <c r="V188" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing-bepalingsmethodeclassificatie</v>
+        <v>null</v>
       </c>
       <c r="W188" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X188" t="str">
         <v>null</v>
       </c>
       <c r="Y188" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing</v>
       </c>
       <c r="Z188" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing</v>
+        <v>null</v>
       </c>
       <c r="AA188" t="str">
         <v>null</v>
@@ -21622,10 +21622,10 @@
         <v>null</v>
       </c>
       <c r="AE188" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing-bepalingsmethode</v>
       </c>
       <c r="AF188" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing-bepalingsmethode</v>
+        <v>null</v>
       </c>
       <c r="AG188" t="str">
         <v>null</v>
@@ -21687,10 +21687,10 @@
         <v>null</v>
       </c>
       <c r="O189" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing-concentratie</v>
       </c>
       <c r="P189" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q189" t="str">
         <v>null</v>
@@ -21708,37 +21708,37 @@
         <v>null</v>
       </c>
       <c r="V189" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing-concentratie</v>
+        <v>null</v>
       </c>
       <c r="W189" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X189" t="str">
         <v>null</v>
       </c>
       <c r="Y189" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing</v>
       </c>
       <c r="Z189" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing</v>
+        <v>null</v>
       </c>
       <c r="AA189" t="str">
         <v>null</v>
       </c>
       <c r="AB189" t="str">
-        <v>null</v>
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Observatie</v>
       </c>
       <c r="AC189" t="str">
-        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Observatie</v>
+        <v>null</v>
       </c>
       <c r="AD189" t="str">
         <v>null</v>
       </c>
       <c r="AE189" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing-meetfrequentie</v>
       </c>
       <c r="AF189" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing-meetfrequentie</v>
+        <v>null</v>
       </c>
       <c r="AG189" t="str">
         <v>null</v>
@@ -21800,10 +21800,10 @@
         <v>null</v>
       </c>
       <c r="O190" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing-dagen</v>
       </c>
       <c r="P190" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q190" t="str">
         <v>null</v>
@@ -21818,22 +21818,22 @@
         <v>null</v>
       </c>
       <c r="U190" t="str">
+        <v>null</v>
+      </c>
+      <c r="V190" t="str">
         <v>true</v>
       </c>
-      <c r="V190" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing-dagen</v>
-      </c>
       <c r="W190" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X190" t="str">
         <v>null</v>
       </c>
       <c r="Y190" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing</v>
       </c>
       <c r="Z190" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing</v>
+        <v>null</v>
       </c>
       <c r="AA190" t="str">
         <v>null</v>
@@ -21848,10 +21848,10 @@
         <v>null</v>
       </c>
       <c r="AE190" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing-debiet</v>
       </c>
       <c r="AF190" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing-debiet</v>
+        <v>null</v>
       </c>
       <c r="AG190" t="str">
         <v>null</v>
@@ -21913,10 +21913,10 @@
         <v>null</v>
       </c>
       <c r="O191" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing-debiet</v>
       </c>
       <c r="P191" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q191" t="str">
         <v>null</v>
@@ -21931,22 +21931,22 @@
         <v>null</v>
       </c>
       <c r="U191" t="str">
+        <v>null</v>
+      </c>
+      <c r="V191" t="str">
         <v>true</v>
       </c>
-      <c r="V191" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing-debiet</v>
-      </c>
       <c r="W191" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X191" t="str">
         <v>null</v>
       </c>
       <c r="Y191" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing</v>
       </c>
       <c r="Z191" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing</v>
+        <v>null</v>
       </c>
       <c r="AA191" t="str">
         <v>null</v>
@@ -21964,10 +21964,10 @@
         <v>null</v>
       </c>
       <c r="AF191" t="str">
-        <v>null</v>
+        <v>true</v>
       </c>
       <c r="AG191" t="str">
-        <v>true</v>
+        <v>null</v>
       </c>
       <c r="AH191" t="str">
         <v>null</v>
@@ -22026,10 +22026,10 @@
         <v>null</v>
       </c>
       <c r="O192" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing-jaarvracht</v>
       </c>
       <c r="P192" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q192" t="str">
         <v>null</v>
@@ -22047,37 +22047,37 @@
         <v>null</v>
       </c>
       <c r="V192" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing-jaarvracht</v>
+        <v>null</v>
       </c>
       <c r="W192" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X192" t="str">
         <v>null</v>
       </c>
       <c r="Y192" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing</v>
       </c>
       <c r="Z192" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing</v>
+        <v>null</v>
       </c>
       <c r="AA192" t="str">
         <v>null</v>
       </c>
       <c r="AB192" t="str">
-        <v>null</v>
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Observatie</v>
       </c>
       <c r="AC192" t="str">
-        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Observatie</v>
+        <v>null</v>
       </c>
       <c r="AD192" t="str">
         <v>null</v>
       </c>
       <c r="AE192" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing-concentratie</v>
       </c>
       <c r="AF192" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing-concentratie</v>
+        <v>null</v>
       </c>
       <c r="AG192" t="str">
         <v>null</v>
@@ -22139,10 +22139,10 @@
         <v>null</v>
       </c>
       <c r="O193" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing-meetfrequentie</v>
       </c>
       <c r="P193" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q193" t="str">
         <v>null</v>
@@ -22160,19 +22160,19 @@
         <v>null</v>
       </c>
       <c r="V193" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing-meetfrequentie</v>
+        <v>null</v>
       </c>
       <c r="W193" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X193" t="str">
         <v>null</v>
       </c>
       <c r="Y193" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing</v>
       </c>
       <c r="Z193" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing</v>
+        <v>null</v>
       </c>
       <c r="AA193" t="str">
         <v>null</v>
@@ -22187,10 +22187,10 @@
         <v>null</v>
       </c>
       <c r="AE193" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing-stof</v>
       </c>
       <c r="AF193" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing-stof</v>
+        <v>null</v>
       </c>
       <c r="AG193" t="str">
         <v>null</v>
@@ -22252,10 +22252,10 @@
         <v>null</v>
       </c>
       <c r="O194" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing-stof</v>
       </c>
       <c r="P194" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q194" t="str">
         <v>null</v>
@@ -22270,22 +22270,22 @@
         <v>null</v>
       </c>
       <c r="U194" t="str">
+        <v>null</v>
+      </c>
+      <c r="V194" t="str">
         <v>true</v>
       </c>
-      <c r="V194" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing-stof</v>
-      </c>
       <c r="W194" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X194" t="str">
         <v>null</v>
       </c>
       <c r="Y194" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing</v>
       </c>
       <c r="Z194" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing</v>
+        <v>null</v>
       </c>
       <c r="AA194" t="str">
         <v>null</v>
@@ -22300,10 +22300,10 @@
         <v>null</v>
       </c>
       <c r="AE194" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing-dagen</v>
       </c>
       <c r="AF194" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing-dagen</v>
+        <v>null</v>
       </c>
       <c r="AG194" t="str">
         <v>null</v>
@@ -22365,10 +22365,10 @@
         <v>Datum van de meting of startdatum indien de meting over meerdere dagen heeft plaatsgevonden.</v>
       </c>
       <c r="O195" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/datum</v>
       </c>
       <c r="P195" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q195" t="str">
         <v>null</v>
@@ -22386,19 +22386,19 @@
         <v>null</v>
       </c>
       <c r="V195" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/datum</v>
+        <v>null</v>
       </c>
       <c r="W195" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X195" t="str">
         <v>null</v>
       </c>
       <c r="Y195" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/meting</v>
       </c>
       <c r="Z195" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/meting</v>
+        <v>null</v>
       </c>
       <c r="AA195" t="str">
         <v>null</v>
@@ -22416,10 +22416,10 @@
         <v>null</v>
       </c>
       <c r="AF195" t="str">
-        <v>null</v>
+        <v>true</v>
       </c>
       <c r="AG195" t="str">
-        <v>true</v>
+        <v>null</v>
       </c>
       <c r="AH195" t="str">
         <v>null</v>
@@ -22496,43 +22496,43 @@
         <v>null</v>
       </c>
       <c r="U196" t="str">
+        <v>null</v>
+      </c>
+      <c r="V196" t="str">
         <v>true</v>
       </c>
-      <c r="V196" t="str">
-        <v>null</v>
-      </c>
       <c r="W196" t="str">
         <v>null</v>
       </c>
       <c r="X196" t="str">
-        <v>null</v>
+        <v>true</v>
       </c>
       <c r="Y196" t="str">
+        <v>null</v>
+      </c>
+      <c r="Z196" t="str">
+        <v>null</v>
+      </c>
+      <c r="AA196" t="str">
+        <v>null</v>
+      </c>
+      <c r="AB196" t="str">
+        <v>http://www.w3.org/ns/sosa/FeatureOfInterest</v>
+      </c>
+      <c r="AC196" t="str">
+        <v>null</v>
+      </c>
+      <c r="AD196" t="str">
+        <v>null</v>
+      </c>
+      <c r="AE196" t="str">
+        <v>null</v>
+      </c>
+      <c r="AF196" t="str">
         <v>true</v>
       </c>
-      <c r="Z196" t="str">
-        <v>null</v>
-      </c>
-      <c r="AA196" t="str">
-        <v>null</v>
-      </c>
-      <c r="AB196" t="str">
-        <v>null</v>
-      </c>
-      <c r="AC196" t="str">
-        <v>http://www.w3.org/ns/sosa/FeatureOfInterest</v>
-      </c>
-      <c r="AD196" t="str">
-        <v>null</v>
-      </c>
-      <c r="AE196" t="str">
-        <v>null</v>
-      </c>
-      <c r="AF196" t="str">
-        <v>null</v>
-      </c>
       <c r="AG196" t="str">
-        <v>true</v>
+        <v>null</v>
       </c>
       <c r="AH196" t="str">
         <v>null</v>
@@ -22591,10 +22591,10 @@
         <v>null</v>
       </c>
       <c r="O197" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/labo</v>
       </c>
       <c r="P197" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q197" t="str">
         <v>null</v>
@@ -22612,37 +22612,37 @@
         <v>null</v>
       </c>
       <c r="V197" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/labo</v>
+        <v>null</v>
       </c>
       <c r="W197" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/labo-id|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/labo-naam</v>
       </c>
       <c r="X197" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/labo-id|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/labo-naam</v>
+        <v>null</v>
       </c>
       <c r="Y197" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/meting</v>
       </c>
       <c r="Z197" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/meting</v>
+        <v>null</v>
       </c>
       <c r="AA197" t="str">
         <v>null</v>
       </c>
       <c r="AB197" t="str">
-        <v>null</v>
+        <v>http://www.w3.org/ns/prov#Agent</v>
       </c>
       <c r="AC197" t="str">
-        <v>http://www.w3.org/ns/prov#Agent</v>
+        <v>null</v>
       </c>
       <c r="AD197" t="str">
         <v>null</v>
       </c>
       <c r="AE197" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/datum</v>
       </c>
       <c r="AF197" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/datum</v>
+        <v>null</v>
       </c>
       <c r="AG197" t="str">
         <v>null</v>
@@ -22704,10 +22704,10 @@
         <v>null</v>
       </c>
       <c r="O198" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/labo-id</v>
       </c>
       <c r="P198" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q198" t="str">
         <v>null</v>
@@ -22725,19 +22725,19 @@
         <v>null</v>
       </c>
       <c r="V198" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/labo-id</v>
+        <v>null</v>
       </c>
       <c r="W198" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X198" t="str">
         <v>null</v>
       </c>
       <c r="Y198" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/labo</v>
       </c>
       <c r="Z198" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/labo</v>
+        <v>null</v>
       </c>
       <c r="AA198" t="str">
         <v>null</v>
@@ -22752,10 +22752,10 @@
         <v>null</v>
       </c>
       <c r="AE198" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/labo-naam</v>
       </c>
       <c r="AF198" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/labo-naam</v>
+        <v>null</v>
       </c>
       <c r="AG198" t="str">
         <v>null</v>
@@ -22817,10 +22817,10 @@
         <v>De naam van het labo.</v>
       </c>
       <c r="O199" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/labo-naam</v>
       </c>
       <c r="P199" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q199" t="str">
         <v>null</v>
@@ -22835,22 +22835,22 @@
         <v>null</v>
       </c>
       <c r="U199" t="str">
+        <v>null</v>
+      </c>
+      <c r="V199" t="str">
         <v>true</v>
       </c>
-      <c r="V199" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/labo-naam</v>
-      </c>
       <c r="W199" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X199" t="str">
         <v>null</v>
       </c>
       <c r="Y199" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/labo</v>
       </c>
       <c r="Z199" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/labo</v>
+        <v>null</v>
       </c>
       <c r="AA199" t="str">
         <v>null</v>
@@ -22868,10 +22868,10 @@
         <v>null</v>
       </c>
       <c r="AF199" t="str">
-        <v>null</v>
+        <v>true</v>
       </c>
       <c r="AG199" t="str">
-        <v>true</v>
+        <v>null</v>
       </c>
       <c r="AH199" t="str">
         <v>null</v>
@@ -22930,10 +22930,10 @@
         <v>null</v>
       </c>
       <c r="O200" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/meting</v>
       </c>
       <c r="P200" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q200" t="str">
         <v>null</v>
@@ -22951,46 +22951,46 @@
         <v>null</v>
       </c>
       <c r="V200" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/meting</v>
+        <v>null</v>
       </c>
       <c r="W200" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/datum|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/labo|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/parameter</v>
       </c>
       <c r="X200" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/datum|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/labo|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/parameter</v>
+        <v>true</v>
       </c>
       <c r="Y200" t="str">
+        <v>null</v>
+      </c>
+      <c r="Z200" t="str">
+        <v>null</v>
+      </c>
+      <c r="AA200" t="str">
+        <v>null</v>
+      </c>
+      <c r="AB200" t="str">
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#ObservatieVerzameling</v>
+      </c>
+      <c r="AC200" t="str">
+        <v>null</v>
+      </c>
+      <c r="AD200" t="str">
+        <v>null</v>
+      </c>
+      <c r="AE200" t="str">
+        <v>null</v>
+      </c>
+      <c r="AF200" t="str">
         <v>true</v>
       </c>
-      <c r="Z200" t="str">
-        <v>null</v>
-      </c>
-      <c r="AA200" t="str">
-        <v>null</v>
-      </c>
-      <c r="AB200" t="str">
-        <v>null</v>
-      </c>
-      <c r="AC200" t="str">
-        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Observatie</v>
-      </c>
-      <c r="AD200" t="str">
-        <v>null</v>
-      </c>
-      <c r="AE200" t="str">
-        <v>null</v>
-      </c>
-      <c r="AF200" t="str">
-        <v>null</v>
-      </c>
       <c r="AG200" t="str">
-        <v>true</v>
+        <v>null</v>
       </c>
       <c r="AH200" t="str">
-        <v>null</v>
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Emissie</v>
       </c>
       <c r="AI200" t="str">
-        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Emissie</v>
+        <v>null</v>
       </c>
       <c r="AJ200" t="str">
         <v>null</v>
@@ -23043,10 +23043,10 @@
         <v>null</v>
       </c>
       <c r="O201" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/parameter</v>
       </c>
       <c r="P201" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q201" t="str">
         <v>null</v>
@@ -23064,25 +23064,25 @@
         <v>null</v>
       </c>
       <c r="V201" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/parameter</v>
+        <v>null</v>
       </c>
       <c r="W201" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/parameter-concentratie|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/parameter-parameter|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/parameter-meetfrequentie|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/parameter-meetonzekerheid|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/parameter-soort</v>
       </c>
       <c r="X201" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/parameter-concentratie|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/parameter-parameter|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/parameter-meetfrequentie|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/parameter-meetonzekerheid|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/parameter-soort</v>
+        <v>true</v>
       </c>
       <c r="Y201" t="str">
-        <v>true</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/meting</v>
       </c>
       <c r="Z201" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/meting</v>
+        <v>null</v>
       </c>
       <c r="AA201" t="str">
         <v>null</v>
       </c>
       <c r="AB201" t="str">
-        <v>null</v>
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Observatie</v>
       </c>
       <c r="AC201" t="str">
         <v>null</v>
@@ -23091,10 +23091,10 @@
         <v>null</v>
       </c>
       <c r="AE201" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/labo</v>
       </c>
       <c r="AF201" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/labo</v>
+        <v>null</v>
       </c>
       <c r="AG201" t="str">
         <v>null</v>
@@ -23135,7 +23135,7 @@
         <v>null</v>
       </c>
       <c r="H202" t="str">
-        <v>null</v>
+        <v>http://www.w3.org/2001/XMLSchema#decimal</v>
       </c>
       <c r="I202" t="str">
         <v>null</v>
@@ -23156,10 +23156,10 @@
         <v>null</v>
       </c>
       <c r="O202" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/parameter-concentratie</v>
       </c>
       <c r="P202" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q202" t="str">
         <v>null</v>
@@ -23177,25 +23177,25 @@
         <v>null</v>
       </c>
       <c r="V202" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/parameter-concentratie</v>
+        <v>null</v>
       </c>
       <c r="W202" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X202" t="str">
         <v>null</v>
       </c>
       <c r="Y202" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/parameter</v>
       </c>
       <c r="Z202" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/parameter</v>
+        <v>null</v>
       </c>
       <c r="AA202" t="str">
         <v>null</v>
       </c>
       <c r="AB202" t="str">
-        <v>null</v>
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Resultaat</v>
       </c>
       <c r="AC202" t="str">
         <v>null</v>
@@ -23204,10 +23204,10 @@
         <v>null</v>
       </c>
       <c r="AE202" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/parameter-parameter</v>
       </c>
       <c r="AF202" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/parameter-parameter</v>
+        <v>null</v>
       </c>
       <c r="AG202" t="str">
         <v>null</v>
@@ -23269,10 +23269,10 @@
         <v>null</v>
       </c>
       <c r="O203" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/parameter-meetfrequentie</v>
       </c>
       <c r="P203" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q203" t="str">
         <v>null</v>
@@ -23290,19 +23290,19 @@
         <v>null</v>
       </c>
       <c r="V203" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/parameter-meetfrequentie</v>
+        <v>null</v>
       </c>
       <c r="W203" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X203" t="str">
         <v>null</v>
       </c>
       <c r="Y203" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/parameter</v>
       </c>
       <c r="Z203" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/parameter</v>
+        <v>null</v>
       </c>
       <c r="AA203" t="str">
         <v>null</v>
@@ -23317,10 +23317,10 @@
         <v>null</v>
       </c>
       <c r="AE203" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/parameter-meetonzekerheid</v>
       </c>
       <c r="AF203" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/parameter-meetonzekerheid</v>
+        <v>null</v>
       </c>
       <c r="AG203" t="str">
         <v>null</v>
@@ -23382,10 +23382,10 @@
         <v>null</v>
       </c>
       <c r="O204" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/parameter-meetonzekerheid</v>
       </c>
       <c r="P204" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q204" t="str">
         <v>null</v>
@@ -23403,25 +23403,25 @@
         <v>null</v>
       </c>
       <c r="V204" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/parameter-meetonzekerheid</v>
+        <v>null</v>
       </c>
       <c r="W204" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X204" t="str">
         <v>null</v>
       </c>
       <c r="Y204" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/parameter</v>
       </c>
       <c r="Z204" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/parameter</v>
+        <v>null</v>
       </c>
       <c r="AA204" t="str">
         <v>null</v>
       </c>
       <c r="AB204" t="str">
-        <v>null</v>
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Resultaat</v>
       </c>
       <c r="AC204" t="str">
         <v>null</v>
@@ -23430,10 +23430,10 @@
         <v>null</v>
       </c>
       <c r="AE204" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/parameter-concentratie</v>
       </c>
       <c r="AF204" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/parameter-concentratie</v>
+        <v>null</v>
       </c>
       <c r="AG204" t="str">
         <v>null</v>
@@ -23495,10 +23495,10 @@
         <v>null</v>
       </c>
       <c r="O205" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/parameter-parameter</v>
       </c>
       <c r="P205" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q205" t="str">
         <v>null</v>
@@ -23516,37 +23516,37 @@
         <v>null</v>
       </c>
       <c r="V205" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/parameter-parameter</v>
+        <v>null</v>
       </c>
       <c r="W205" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X205" t="str">
         <v>null</v>
       </c>
       <c r="Y205" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/parameter</v>
       </c>
       <c r="Z205" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/parameter</v>
+        <v>null</v>
       </c>
       <c r="AA205" t="str">
         <v>null</v>
       </c>
       <c r="AB205" t="str">
-        <v>null</v>
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Resultaat</v>
       </c>
       <c r="AC205" t="str">
         <v>null</v>
       </c>
       <c r="AD205" t="str">
-        <v>null</v>
+        <v>http://TODO</v>
       </c>
       <c r="AE205" t="str">
-        <v>http://TODO</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/parameter-soort</v>
       </c>
       <c r="AF205" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/parameter-soort</v>
+        <v>null</v>
       </c>
       <c r="AG205" t="str">
         <v>null</v>
@@ -23608,10 +23608,10 @@
         <v>null</v>
       </c>
       <c r="O206" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/parameter-soort</v>
       </c>
       <c r="P206" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q206" t="str">
         <v>null</v>
@@ -23629,25 +23629,25 @@
         <v>null</v>
       </c>
       <c r="V206" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/parameter-soort</v>
+        <v>null</v>
       </c>
       <c r="W206" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X206" t="str">
         <v>null</v>
       </c>
       <c r="Y206" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/parameter</v>
       </c>
       <c r="Z206" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/parameter</v>
+        <v>null</v>
       </c>
       <c r="AA206" t="str">
         <v>null</v>
       </c>
       <c r="AB206" t="str">
-        <v>null</v>
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Resultaat</v>
       </c>
       <c r="AC206" t="str">
         <v>null</v>
@@ -23659,10 +23659,10 @@
         <v>null</v>
       </c>
       <c r="AF206" t="str">
-        <v>null</v>
+        <v>true</v>
       </c>
       <c r="AG206" t="str">
-        <v>true</v>
+        <v>null</v>
       </c>
       <c r="AH206" t="str">
         <v>null</v>
@@ -23721,10 +23721,10 @@
         <v>Datum van de meting of startdatum indien de meting over meerdere dagen heeft plaatsgevonden.</v>
       </c>
       <c r="O207" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/datum</v>
       </c>
       <c r="P207" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q207" t="str">
         <v>null</v>
@@ -23742,19 +23742,19 @@
         <v>null</v>
       </c>
       <c r="V207" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/datum</v>
+        <v>null</v>
       </c>
       <c r="W207" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X207" t="str">
         <v>null</v>
       </c>
       <c r="Y207" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/meting</v>
       </c>
       <c r="Z207" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/meting</v>
+        <v>null</v>
       </c>
       <c r="AA207" t="str">
         <v>null</v>
@@ -23772,10 +23772,10 @@
         <v>null</v>
       </c>
       <c r="AF207" t="str">
-        <v>null</v>
+        <v>true</v>
       </c>
       <c r="AG207" t="str">
-        <v>true</v>
+        <v>null</v>
       </c>
       <c r="AH207" t="str">
         <v>null</v>
@@ -23852,43 +23852,43 @@
         <v>null</v>
       </c>
       <c r="U208" t="str">
+        <v>null</v>
+      </c>
+      <c r="V208" t="str">
         <v>true</v>
       </c>
-      <c r="V208" t="str">
-        <v>null</v>
-      </c>
       <c r="W208" t="str">
         <v>null</v>
       </c>
       <c r="X208" t="str">
-        <v>null</v>
+        <v>true</v>
       </c>
       <c r="Y208" t="str">
+        <v>null</v>
+      </c>
+      <c r="Z208" t="str">
+        <v>null</v>
+      </c>
+      <c r="AA208" t="str">
+        <v>null</v>
+      </c>
+      <c r="AB208" t="str">
+        <v>http://www.w3.org/ns/sosa/FeatureOfInterest</v>
+      </c>
+      <c r="AC208" t="str">
+        <v>null</v>
+      </c>
+      <c r="AD208" t="str">
+        <v>null</v>
+      </c>
+      <c r="AE208" t="str">
+        <v>null</v>
+      </c>
+      <c r="AF208" t="str">
         <v>true</v>
       </c>
-      <c r="Z208" t="str">
-        <v>null</v>
-      </c>
-      <c r="AA208" t="str">
-        <v>null</v>
-      </c>
-      <c r="AB208" t="str">
-        <v>null</v>
-      </c>
-      <c r="AC208" t="str">
-        <v>http://www.w3.org/ns/sosa/FeatureOfInterest</v>
-      </c>
-      <c r="AD208" t="str">
-        <v>null</v>
-      </c>
-      <c r="AE208" t="str">
-        <v>null</v>
-      </c>
-      <c r="AF208" t="str">
-        <v>null</v>
-      </c>
       <c r="AG208" t="str">
-        <v>true</v>
+        <v>null</v>
       </c>
       <c r="AH208" t="str">
         <v>null</v>
@@ -23947,10 +23947,10 @@
         <v>null</v>
       </c>
       <c r="O209" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/labo</v>
       </c>
       <c r="P209" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q209" t="str">
         <v>null</v>
@@ -23968,13 +23968,13 @@
         <v>null</v>
       </c>
       <c r="V209" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/labo</v>
+        <v>null</v>
       </c>
       <c r="W209" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/labo-id|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/labo-naam</v>
       </c>
       <c r="X209" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/labo-id|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/labo-naam</v>
+        <v>null</v>
       </c>
       <c r="Y209" t="str">
         <v>null</v>
@@ -23986,7 +23986,7 @@
         <v>null</v>
       </c>
       <c r="AB209" t="str">
-        <v>null</v>
+        <v>http://www.w3.org/ns/prov#Agent</v>
       </c>
       <c r="AC209" t="str">
         <v>null</v>
@@ -23995,10 +23995,10 @@
         <v>null</v>
       </c>
       <c r="AE209" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/meting</v>
       </c>
       <c r="AF209" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/meting</v>
+        <v>null</v>
       </c>
       <c r="AG209" t="str">
         <v>null</v>
@@ -24060,10 +24060,10 @@
         <v>null</v>
       </c>
       <c r="O210" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/labo-id</v>
       </c>
       <c r="P210" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q210" t="str">
         <v>null</v>
@@ -24081,19 +24081,19 @@
         <v>null</v>
       </c>
       <c r="V210" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/labo-id</v>
+        <v>null</v>
       </c>
       <c r="W210" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X210" t="str">
         <v>null</v>
       </c>
       <c r="Y210" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/labo</v>
       </c>
       <c r="Z210" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/labo</v>
+        <v>null</v>
       </c>
       <c r="AA210" t="str">
         <v>null</v>
@@ -24108,10 +24108,10 @@
         <v>null</v>
       </c>
       <c r="AE210" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/labo-naam</v>
       </c>
       <c r="AF210" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/labo-naam</v>
+        <v>null</v>
       </c>
       <c r="AG210" t="str">
         <v>null</v>
@@ -24173,10 +24173,10 @@
         <v>De naam van het labo.</v>
       </c>
       <c r="O211" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/labo-naam</v>
       </c>
       <c r="P211" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q211" t="str">
         <v>null</v>
@@ -24191,22 +24191,22 @@
         <v>null</v>
       </c>
       <c r="U211" t="str">
+        <v>null</v>
+      </c>
+      <c r="V211" t="str">
         <v>true</v>
       </c>
-      <c r="V211" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/labo-naam</v>
-      </c>
       <c r="W211" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X211" t="str">
         <v>null</v>
       </c>
       <c r="Y211" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/labo</v>
       </c>
       <c r="Z211" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/labo</v>
+        <v>null</v>
       </c>
       <c r="AA211" t="str">
         <v>null</v>
@@ -24224,10 +24224,10 @@
         <v>null</v>
       </c>
       <c r="AF211" t="str">
-        <v>null</v>
+        <v>true</v>
       </c>
       <c r="AG211" t="str">
-        <v>true</v>
+        <v>null</v>
       </c>
       <c r="AH211" t="str">
         <v>null</v>
@@ -24286,10 +24286,10 @@
         <v>null</v>
       </c>
       <c r="O212" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/meting</v>
       </c>
       <c r="P212" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q212" t="str">
         <v>null</v>
@@ -24307,40 +24307,40 @@
         <v>null</v>
       </c>
       <c r="V212" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/meting</v>
+        <v>null</v>
       </c>
       <c r="W212" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/datum</v>
       </c>
       <c r="X212" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/datum</v>
+        <v>true</v>
       </c>
       <c r="Y212" t="str">
+        <v>null</v>
+      </c>
+      <c r="Z212" t="str">
+        <v>null</v>
+      </c>
+      <c r="AA212" t="str">
+        <v>null</v>
+      </c>
+      <c r="AB212" t="str">
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#ObservatieVerzameling</v>
+      </c>
+      <c r="AC212" t="str">
+        <v>null</v>
+      </c>
+      <c r="AD212" t="str">
+        <v>null</v>
+      </c>
+      <c r="AE212" t="str">
+        <v>null</v>
+      </c>
+      <c r="AF212" t="str">
         <v>true</v>
       </c>
-      <c r="Z212" t="str">
-        <v>null</v>
-      </c>
-      <c r="AA212" t="str">
-        <v>null</v>
-      </c>
-      <c r="AB212" t="str">
-        <v>null</v>
-      </c>
-      <c r="AC212" t="str">
-        <v>http://www.w3.org/ns/sosa/ObservationCollection</v>
-      </c>
-      <c r="AD212" t="str">
-        <v>null</v>
-      </c>
-      <c r="AE212" t="str">
-        <v>null</v>
-      </c>
-      <c r="AF212" t="str">
-        <v>null</v>
-      </c>
       <c r="AG212" t="str">
-        <v>true</v>
+        <v>null</v>
       </c>
       <c r="AH212" t="str">
         <v>null</v>
@@ -24399,10 +24399,10 @@
         <v>null</v>
       </c>
       <c r="O213" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/parameter</v>
       </c>
       <c r="P213" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q213" t="str">
         <v>null</v>
@@ -24420,16 +24420,16 @@
         <v>null</v>
       </c>
       <c r="V213" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/parameter</v>
+        <v>null</v>
       </c>
       <c r="W213" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/parameter-concentratie|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/parameter-parameter|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/parameter-meetfrequentie|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/parameter-meetonzekerheid|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/parameter-soort</v>
       </c>
       <c r="X213" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/parameter-concentratie|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/parameter-parameter|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/parameter-meetfrequentie|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/parameter-meetonzekerheid|https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/parameter-soort</v>
+        <v>true</v>
       </c>
       <c r="Y213" t="str">
-        <v>true</v>
+        <v>null</v>
       </c>
       <c r="Z213" t="str">
         <v>null</v>
@@ -24438,19 +24438,19 @@
         <v>null</v>
       </c>
       <c r="AB213" t="str">
-        <v>null</v>
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Observatie</v>
       </c>
       <c r="AC213" t="str">
-        <v>http://www.w3.org/ns/sosa/Observation</v>
+        <v>null</v>
       </c>
       <c r="AD213" t="str">
         <v>null</v>
       </c>
       <c r="AE213" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/labo</v>
       </c>
       <c r="AF213" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/labo</v>
+        <v>null</v>
       </c>
       <c r="AG213" t="str">
         <v>null</v>
@@ -24512,10 +24512,10 @@
         <v>null</v>
       </c>
       <c r="O214" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/parameter-concentratie</v>
       </c>
       <c r="P214" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q214" t="str">
         <v>null</v>
@@ -24533,25 +24533,25 @@
         <v>null</v>
       </c>
       <c r="V214" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/parameter-concentratie</v>
+        <v>null</v>
       </c>
       <c r="W214" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X214" t="str">
         <v>null</v>
       </c>
       <c r="Y214" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/parameter</v>
       </c>
       <c r="Z214" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/parameter</v>
+        <v>null</v>
       </c>
       <c r="AA214" t="str">
         <v>null</v>
       </c>
       <c r="AB214" t="str">
-        <v>null</v>
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Resultaat</v>
       </c>
       <c r="AC214" t="str">
         <v>null</v>
@@ -24560,10 +24560,10 @@
         <v>null</v>
       </c>
       <c r="AE214" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/parameter-parameter</v>
       </c>
       <c r="AF214" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/parameter-parameter</v>
+        <v>null</v>
       </c>
       <c r="AG214" t="str">
         <v>null</v>
@@ -24625,10 +24625,10 @@
         <v>null</v>
       </c>
       <c r="O215" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/parameter-meetfrequentie</v>
       </c>
       <c r="P215" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q215" t="str">
         <v>null</v>
@@ -24646,19 +24646,19 @@
         <v>null</v>
       </c>
       <c r="V215" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/parameter-meetfrequentie</v>
+        <v>null</v>
       </c>
       <c r="W215" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X215" t="str">
         <v>null</v>
       </c>
       <c r="Y215" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/parameter</v>
       </c>
       <c r="Z215" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/parameter</v>
+        <v>null</v>
       </c>
       <c r="AA215" t="str">
         <v>null</v>
@@ -24673,10 +24673,10 @@
         <v>null</v>
       </c>
       <c r="AE215" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/parameter-meetonzekerheid</v>
       </c>
       <c r="AF215" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/parameter-meetonzekerheid</v>
+        <v>null</v>
       </c>
       <c r="AG215" t="str">
         <v>null</v>
@@ -24738,10 +24738,10 @@
         <v>null</v>
       </c>
       <c r="O216" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/parameter-meetonzekerheid</v>
       </c>
       <c r="P216" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q216" t="str">
         <v>null</v>
@@ -24759,25 +24759,25 @@
         <v>null</v>
       </c>
       <c r="V216" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/parameter-meetonzekerheid</v>
+        <v>null</v>
       </c>
       <c r="W216" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X216" t="str">
         <v>null</v>
       </c>
       <c r="Y216" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/parameter</v>
       </c>
       <c r="Z216" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/parameter</v>
+        <v>null</v>
       </c>
       <c r="AA216" t="str">
         <v>null</v>
       </c>
       <c r="AB216" t="str">
-        <v>null</v>
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Resultaat</v>
       </c>
       <c r="AC216" t="str">
         <v>null</v>
@@ -24786,10 +24786,10 @@
         <v>null</v>
       </c>
       <c r="AE216" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/parameter-concentratie</v>
       </c>
       <c r="AF216" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/parameter-concentratie</v>
+        <v>null</v>
       </c>
       <c r="AG216" t="str">
         <v>null</v>
@@ -24851,10 +24851,10 @@
         <v>null</v>
       </c>
       <c r="O217" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/parameter-parameter</v>
       </c>
       <c r="P217" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q217" t="str">
         <v>null</v>
@@ -24872,37 +24872,37 @@
         <v>null</v>
       </c>
       <c r="V217" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/parameter-parameter</v>
+        <v>null</v>
       </c>
       <c r="W217" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X217" t="str">
         <v>null</v>
       </c>
       <c r="Y217" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/parameter</v>
       </c>
       <c r="Z217" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/parameter</v>
+        <v>null</v>
       </c>
       <c r="AA217" t="str">
         <v>null</v>
       </c>
       <c r="AB217" t="str">
-        <v>null</v>
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Resultaat</v>
       </c>
       <c r="AC217" t="str">
         <v>null</v>
       </c>
       <c r="AD217" t="str">
-        <v>null</v>
+        <v>http://TODO</v>
       </c>
       <c r="AE217" t="str">
-        <v>http://TODO</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/parameter-soort</v>
       </c>
       <c r="AF217" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/parameter-soort</v>
+        <v>null</v>
       </c>
       <c r="AG217" t="str">
         <v>null</v>
@@ -24964,10 +24964,10 @@
         <v>null</v>
       </c>
       <c r="O218" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/parameter-soort</v>
       </c>
       <c r="P218" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q218" t="str">
         <v>null</v>
@@ -24985,25 +24985,25 @@
         <v>null</v>
       </c>
       <c r="V218" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/parameter-soort</v>
+        <v>null</v>
       </c>
       <c r="W218" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X218" t="str">
         <v>null</v>
       </c>
       <c r="Y218" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/parameter</v>
       </c>
       <c r="Z218" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/parameter</v>
+        <v>null</v>
       </c>
       <c r="AA218" t="str">
         <v>null</v>
       </c>
       <c r="AB218" t="str">
-        <v>null</v>
+        <v>https://data.riepr.omgeving.vlaanderen.be/ns/riepr#Resultaat</v>
       </c>
       <c r="AC218" t="str">
         <v>null</v>
@@ -25015,10 +25015,10 @@
         <v>null</v>
       </c>
       <c r="AF218" t="str">
-        <v>null</v>
+        <v>true</v>
       </c>
       <c r="AG218" t="str">
-        <v>true</v>
+        <v>null</v>
       </c>
       <c r="AH218" t="str">
         <v>null</v>
@@ -25877,58 +25877,58 @@
         <v>null</v>
       </c>
       <c r="R226" t="str">
+        <v>null</v>
+      </c>
+      <c r="S226" t="str">
+        <v>null</v>
+      </c>
+      <c r="T226" t="str">
+        <v>null</v>
+      </c>
+      <c r="U226" t="str">
+        <v>null</v>
+      </c>
+      <c r="V226" t="str">
+        <v>null</v>
+      </c>
+      <c r="W226" t="str">
+        <v>null</v>
+      </c>
+      <c r="X226" t="str">
+        <v>null</v>
+      </c>
+      <c r="Y226" t="str">
+        <v>null</v>
+      </c>
+      <c r="Z226" t="str">
+        <v>null</v>
+      </c>
+      <c r="AA226" t="str">
+        <v>null</v>
+      </c>
+      <c r="AB226" t="str">
+        <v>null</v>
+      </c>
+      <c r="AC226" t="str">
+        <v>null</v>
+      </c>
+      <c r="AD226" t="str">
+        <v>null</v>
+      </c>
+      <c r="AE226" t="str">
+        <v>null</v>
+      </c>
+      <c r="AF226" t="str">
+        <v>null</v>
+      </c>
+      <c r="AG226" t="str">
+        <v>null</v>
+      </c>
+      <c r="AH226" t="str">
+        <v>null</v>
+      </c>
+      <c r="AI226" t="str">
         <v>true</v>
-      </c>
-      <c r="S226" t="str">
-        <v>null</v>
-      </c>
-      <c r="T226" t="str">
-        <v>null</v>
-      </c>
-      <c r="U226" t="str">
-        <v>null</v>
-      </c>
-      <c r="V226" t="str">
-        <v>null</v>
-      </c>
-      <c r="W226" t="str">
-        <v>null</v>
-      </c>
-      <c r="X226" t="str">
-        <v>null</v>
-      </c>
-      <c r="Y226" t="str">
-        <v>null</v>
-      </c>
-      <c r="Z226" t="str">
-        <v>null</v>
-      </c>
-      <c r="AA226" t="str">
-        <v>null</v>
-      </c>
-      <c r="AB226" t="str">
-        <v>null</v>
-      </c>
-      <c r="AC226" t="str">
-        <v>null</v>
-      </c>
-      <c r="AD226" t="str">
-        <v>null</v>
-      </c>
-      <c r="AE226" t="str">
-        <v>null</v>
-      </c>
-      <c r="AF226" t="str">
-        <v>null</v>
-      </c>
-      <c r="AG226" t="str">
-        <v>null</v>
-      </c>
-      <c r="AH226" t="str">
-        <v>null</v>
-      </c>
-      <c r="AI226" t="str">
-        <v>null</v>
       </c>
       <c r="AJ226" t="str">
         <v>null</v>
@@ -25981,10 +25981,10 @@
         <v>De status definitief uit dienst geeft aan dat een entiteit definitief buiten gebruik is.</v>
       </c>
       <c r="O227" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/definitief_uit_dienst</v>
       </c>
       <c r="P227" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q227" t="str">
         <v>null</v>
@@ -26002,10 +26002,10 @@
         <v>null</v>
       </c>
       <c r="V227" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/definitief_uit_dienst</v>
+        <v>null</v>
       </c>
       <c r="W227" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X227" t="str">
         <v>null</v>
@@ -26094,10 +26094,10 @@
         <v>De status in dienst geeft aan dat een entiteit momenteel in gebruik is.</v>
       </c>
       <c r="O228" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/in_dienst</v>
       </c>
       <c r="P228" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q228" t="str">
         <v>null</v>
@@ -26115,10 +26115,10 @@
         <v>null</v>
       </c>
       <c r="V228" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/in_dienst</v>
+        <v>null</v>
       </c>
       <c r="W228" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X228" t="str">
         <v>null</v>
@@ -26207,10 +26207,10 @@
         <v>De status ontmanteld geeft aan dat een entiteit niet meer bestaat.</v>
       </c>
       <c r="O229" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/ontmanteld</v>
       </c>
       <c r="P229" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q229" t="str">
         <v>null</v>
@@ -26228,10 +26228,10 @@
         <v>null</v>
       </c>
       <c r="V229" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/ontmanteld</v>
+        <v>null</v>
       </c>
       <c r="W229" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X229" t="str">
         <v>null</v>
@@ -26320,10 +26320,10 @@
         <v>De status tijdelijk uit dienst geeft aan dat een entiteit tijden buiten gebruik is.</v>
       </c>
       <c r="O230" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/tijdelijk_uit_dienst</v>
       </c>
       <c r="P230" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q230" t="str">
         <v>null</v>
@@ -26341,10 +26341,10 @@
         <v>null</v>
       </c>
       <c r="V230" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/tijdelijk_uit_dienst</v>
+        <v>null</v>
       </c>
       <c r="W230" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X230" t="str">
         <v>null</v>
@@ -26433,10 +26433,10 @@
         <v>De status verkeerde registratie  geeft aan deze entiteit verkeerd werd geregistreerd en dus niet van toepassing is</v>
       </c>
       <c r="O231" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/verkeerde_registratie</v>
       </c>
       <c r="P231" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q231" t="str">
         <v>null</v>
@@ -26454,10 +26454,10 @@
         <v>null</v>
       </c>
       <c r="V231" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/verkeerde_registratie</v>
+        <v>null</v>
       </c>
       <c r="W231" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X231" t="str">
         <v>null</v>
@@ -26546,10 +26546,10 @@
         <v>De status voorgesteld geeft aan dat een entiteit voorsgesteld is door de Vlaamse Overheid.</v>
       </c>
       <c r="O232" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/voorgesteld</v>
       </c>
       <c r="P232" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q232" t="str">
         <v>null</v>
@@ -26567,10 +26567,10 @@
         <v>null</v>
       </c>
       <c r="V232" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/voorgesteld</v>
+        <v>null</v>
       </c>
       <c r="W232" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X232" t="str">
         <v>null</v>
@@ -28128,10 +28128,10 @@
         <v>Een typering van verschillende eigenschappen voor installaties.</v>
       </c>
       <c r="O246" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_eigenschappen</v>
       </c>
       <c r="P246" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q246" t="str">
         <v>null</v>
@@ -28149,10 +28149,10 @@
         <v>null</v>
       </c>
       <c r="V246" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_eigenschappen</v>
+        <v>null</v>
       </c>
       <c r="W246" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X246" t="str">
         <v>null</v>
@@ -28467,10 +28467,10 @@
         <v>Een typering van verschillende eigenschappen voor meetpunten.</v>
       </c>
       <c r="O249" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/meetpunt_eigenschappen</v>
       </c>
       <c r="P249" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q249" t="str">
         <v>null</v>
@@ -28488,10 +28488,10 @@
         <v>null</v>
       </c>
       <c r="V249" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/meetpunt_eigenschappen</v>
+        <v>null</v>
       </c>
       <c r="W249" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X249" t="str">
         <v>null</v>
@@ -29371,10 +29371,10 @@
         <v>null</v>
       </c>
       <c r="O257" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_grondstoffen</v>
       </c>
       <c r="P257" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q257" t="str">
         <v>null</v>
@@ -29392,10 +29392,10 @@
         <v>null</v>
       </c>
       <c r="V257" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_grondstoffen</v>
+        <v>null</v>
       </c>
       <c r="W257" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X257" t="str">
         <v>null</v>
@@ -29484,10 +29484,10 @@
         <v>null</v>
       </c>
       <c r="O258" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_grondwater</v>
       </c>
       <c r="P258" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q258" t="str">
         <v>null</v>
@@ -29505,10 +29505,10 @@
         <v>null</v>
       </c>
       <c r="V258" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_grondwater</v>
+        <v>null</v>
       </c>
       <c r="W258" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X258" t="str">
         <v>null</v>
@@ -29823,10 +29823,10 @@
         <v>null</v>
       </c>
       <c r="O261" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_lucht_emissie</v>
       </c>
       <c r="P261" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q261" t="str">
         <v>null</v>
@@ -29844,10 +29844,10 @@
         <v>null</v>
       </c>
       <c r="V261" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_lucht_emissie</v>
+        <v>null</v>
       </c>
       <c r="W261" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X261" t="str">
         <v>null</v>
@@ -29936,10 +29936,10 @@
         <v>null</v>
       </c>
       <c r="O262" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_lucht_rapportering</v>
       </c>
       <c r="P262" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q262" t="str">
         <v>null</v>
@@ -29957,10 +29957,10 @@
         <v>null</v>
       </c>
       <c r="V262" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_lucht_rapportering</v>
+        <v>null</v>
       </c>
       <c r="W262" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X262" t="str">
         <v>null</v>
@@ -30501,10 +30501,10 @@
         <v>null</v>
       </c>
       <c r="O267" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_toestand_indicator</v>
       </c>
       <c r="P267" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q267" t="str">
         <v>null</v>
@@ -30522,10 +30522,10 @@
         <v>null</v>
       </c>
       <c r="V267" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_toestand_indicator</v>
+        <v>null</v>
       </c>
       <c r="W267" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X267" t="str">
         <v>null</v>
@@ -30727,10 +30727,10 @@
         <v>null</v>
       </c>
       <c r="O269" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_water_lozing</v>
       </c>
       <c r="P269" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q269" t="str">
         <v>null</v>
@@ -30748,10 +30748,10 @@
         <v>null</v>
       </c>
       <c r="V269" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_water_lozing</v>
+        <v>null</v>
       </c>
       <c r="W269" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X269" t="str">
         <v>null</v>
@@ -30953,10 +30953,10 @@
         <v>null</v>
       </c>
       <c r="O271" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_zelfcontrole_lucht_meting</v>
       </c>
       <c r="P271" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q271" t="str">
         <v>null</v>
@@ -30974,10 +30974,10 @@
         <v>null</v>
       </c>
       <c r="V271" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_zelfcontrole_lucht_meting</v>
+        <v>null</v>
       </c>
       <c r="W271" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X271" t="str">
         <v>null</v>
@@ -31292,10 +31292,10 @@
         <v>null</v>
       </c>
       <c r="O274" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_zelfcontrole_water_meting</v>
       </c>
       <c r="P274" t="str">
-        <v>null</v>
+        <v>2026-09-09T10:38:08.410Z</v>
       </c>
       <c r="Q274" t="str">
         <v>null</v>
@@ -31313,10 +31313,10 @@
         <v>null</v>
       </c>
       <c r="V274" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_zelfcontrole_water_meting</v>
+        <v>null</v>
       </c>
       <c r="W274" t="str">
-        <v>2026-08-27T12:39:31.063Z</v>
+        <v>null</v>
       </c>
       <c r="X274" t="str">
         <v>null</v>

--- a/src/main/resources/be/vlaanderen/omgeving/data/id/conceptscheme/rie-iepr/rie-iepr.xlsx
+++ b/src/main/resources/be/vlaanderen/omgeving/data/id/conceptscheme/rie-iepr/rie-iepr.xlsx
@@ -529,7 +529,7 @@
         <v>http://www.w3.org/2004/02/skos/core#Collection</v>
       </c>
       <c r="C2" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="D2" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/csor/eenheid/E_92</v>
@@ -651,7 +651,7 @@
         <v>http://www.w3.org/2004/02/skos/core#Collection</v>
       </c>
       <c r="C3" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="D3" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/csor/variabele/V_1096|https://data.omgeving.vlaanderen.be/id/concept/csor/variabele/V_2217</v>
@@ -1535,7 +1535,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-eigenschappen-selectiemogelijkheden/grondwater</v>
       </c>
       <c r="M10" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N10" t="str">
         <v>null</v>
@@ -1657,7 +1657,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-eigenschappen-selectiemogelijkheden/oppervlaktewater</v>
       </c>
       <c r="M11" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N11" t="str">
         <v>null</v>
@@ -1779,7 +1779,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-eigenschappen-selectiemogelijkheden/riool</v>
       </c>
       <c r="M12" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N12" t="str">
         <v>null</v>
@@ -1871,7 +1871,7 @@
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C13" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="D13" t="str">
         <v>null</v>
@@ -2023,7 +2023,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-eigenschappen/lozingspunt-lozingsplaats</v>
       </c>
       <c r="M14" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N14" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_eigenschappen</v>
@@ -2145,7 +2145,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-eigenschappen/schouw-diameter</v>
       </c>
       <c r="M15" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N15" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_eigenschappen</v>
@@ -2267,7 +2267,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-eigenschappen/schouw-hoogte</v>
       </c>
       <c r="M16" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N16" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_eigenschappen</v>
@@ -2389,7 +2389,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/emissiepunt</v>
       </c>
       <c r="M17" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N17" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_type</v>
@@ -2511,7 +2511,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/fakkel</v>
       </c>
       <c r="M18" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N18" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_type</v>
@@ -2633,7 +2633,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/gebouw</v>
       </c>
       <c r="M19" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N19" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_type</v>
@@ -2755,7 +2755,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/lozingspunt</v>
       </c>
       <c r="M20" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N20" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_type</v>
@@ -2877,7 +2877,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen</v>
       </c>
       <c r="M21" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N21" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_type</v>
@@ -2999,7 +2999,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_horizontale_uitstroom</v>
       </c>
       <c r="M22" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N22" t="str">
         <v>null</v>
@@ -3121,7 +3121,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_verticale_uitstroom</v>
       </c>
       <c r="M23" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N23" t="str">
         <v>null</v>
@@ -3213,7 +3213,7 @@
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C24" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="D24" t="str">
         <v>null</v>
@@ -3335,7 +3335,7 @@
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C25" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="D25" t="str">
         <v>null</v>
@@ -3457,7 +3457,7 @@
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C26" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="D26" t="str">
         <v>null</v>
@@ -3609,7 +3609,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/filter-type/injectie</v>
       </c>
       <c r="M27" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N27" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_type</v>
@@ -3731,7 +3731,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/filter-type/omkeerbaar</v>
       </c>
       <c r="M28" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N28" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_type</v>
@@ -3853,7 +3853,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/filter-type/peil</v>
       </c>
       <c r="M29" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N29" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_type</v>
@@ -3975,7 +3975,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/filter-type/pomp</v>
       </c>
       <c r="M30" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N30" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_type</v>
@@ -4097,7 +4097,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/geinstalleerd_vermogen</v>
       </c>
       <c r="M31" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N31" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_eigenschappen</v>
@@ -4219,7 +4219,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/geinstalleerde_opslagcapaciteit</v>
       </c>
       <c r="M32" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N32" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_eigenschappen</v>
@@ -4341,7 +4341,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/geinstalleerde_productiecapaciteit</v>
       </c>
       <c r="M33" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N33" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_eigenschappen</v>
@@ -4463,7 +4463,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/luchtzuiverings_techniek</v>
       </c>
       <c r="M34" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N34" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_eigenschappen</v>
@@ -4585,7 +4585,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/type_energie_productie</v>
       </c>
       <c r="M35" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N35" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_eigenschappen</v>
@@ -4707,7 +4707,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/verwijderingsrendement</v>
       </c>
       <c r="M36" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N36" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_eigenschappen</v>
@@ -4829,7 +4829,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/verwijderingsrendement_percentage</v>
       </c>
       <c r="M37" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N37" t="str">
         <v>null</v>
@@ -4951,7 +4951,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/verwijderingsrendement_stof</v>
       </c>
       <c r="M38" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N38" t="str">
         <v>null</v>
@@ -5073,7 +5073,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/waterzuiveringstechniek</v>
       </c>
       <c r="M39" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N39" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_eigenschappen</v>
@@ -5195,7 +5195,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/waterzuiveringstechniek_ingebruikvan</v>
       </c>
       <c r="M40" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N40" t="str">
         <v>null</v>
@@ -5317,7 +5317,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/waterzuiveringstechniek_techniek</v>
       </c>
       <c r="M41" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N41" t="str">
         <v>null</v>
@@ -5439,7 +5439,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/directe_stookinstallatie</v>
       </c>
       <c r="M42" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N42" t="str">
         <v>null</v>
@@ -5561,7 +5561,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/geothermisch</v>
       </c>
       <c r="M43" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N43" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_type</v>
@@ -5683,7 +5683,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/gpbv</v>
       </c>
       <c r="M44" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N44" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_type</v>
@@ -5805,7 +5805,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/installatie</v>
       </c>
       <c r="M45" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N45" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_type</v>
@@ -5927,7 +5927,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/luchtzuivering</v>
       </c>
       <c r="M46" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N46" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_type</v>
@@ -6049,7 +6049,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/opslag_overslag</v>
       </c>
       <c r="M47" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N47" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_type</v>
@@ -6171,7 +6171,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/stookinstallatie</v>
       </c>
       <c r="M48" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N48" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_type</v>
@@ -6293,7 +6293,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/waterzuivering</v>
       </c>
       <c r="M49" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N49" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_type</v>
@@ -6415,7 +6415,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-eigenschappen/diepte</v>
       </c>
       <c r="M50" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N50" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_eigenschappen</v>
@@ -6537,7 +6537,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-eigenschappen/referentiepunt</v>
       </c>
       <c r="M51" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N51" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_eigenschappen</v>
@@ -6659,7 +6659,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-eigenschappen/referentiepunt_diepte</v>
       </c>
       <c r="M52" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N52" t="str">
         <v>null</v>
@@ -6781,7 +6781,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-eigenschappen/referentiepunt_naam</v>
       </c>
       <c r="M53" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N53" t="str">
         <v>null</v>
@@ -6903,7 +6903,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-type/controleinrichting</v>
       </c>
       <c r="M54" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N54" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_type</v>
@@ -7025,7 +7025,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-type/debietmeter</v>
       </c>
       <c r="M55" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N55" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_type</v>
@@ -7147,7 +7147,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-type/peilput</v>
       </c>
       <c r="M56" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N56" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_type</v>
@@ -7269,7 +7269,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/onttrekkingspunt-eigenschappen/diepte</v>
       </c>
       <c r="M57" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N57" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_eigenschappen</v>
@@ -7391,7 +7391,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/onttrekkingspunt-eigenschappen/watervoerendelaag</v>
       </c>
       <c r="M58" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N58" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_eigenschappen</v>
@@ -7513,7 +7513,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/onttrekkingspunt-type/opnamepunt</v>
       </c>
       <c r="M59" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N59" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_type</v>
@@ -7635,7 +7635,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/onttrekkingspunt-type/pompput</v>
       </c>
       <c r="M60" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N60" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_type</v>
@@ -9587,7 +9587,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-be</v>
       </c>
       <c r="M76" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N76" t="str">
         <v>null</v>
@@ -9709,7 +9709,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-be-naam</v>
       </c>
       <c r="M77" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N77" t="str">
         <v>null</v>
@@ -9831,7 +9831,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-be-on</v>
       </c>
       <c r="M78" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N78" t="str">
         <v>null</v>
@@ -9953,7 +9953,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-be-ve</v>
       </c>
       <c r="M79" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N79" t="str">
         <v>null</v>
@@ -10075,7 +10075,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-buitenland</v>
       </c>
       <c r="M80" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N80" t="str">
         <v>null</v>
@@ -10197,7 +10197,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-buitenland-btw</v>
       </c>
       <c r="M81" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N81" t="str">
         <v>null</v>
@@ -10319,7 +10319,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-buitenland-naam</v>
       </c>
       <c r="M82" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N82" t="str">
         <v>null</v>
@@ -10441,7 +10441,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-none</v>
       </c>
       <c r="M83" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N83" t="str">
         <v>null</v>
@@ -10563,7 +10563,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-none-adres</v>
       </c>
       <c r="M84" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N84" t="str">
         <v>null</v>
@@ -10685,7 +10685,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-none-naam</v>
       </c>
       <c r="M85" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N85" t="str">
         <v>null</v>
@@ -10807,7 +10807,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-werf</v>
       </c>
       <c r="M86" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N86" t="str">
         <v>null</v>
@@ -10929,7 +10929,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-werf-naam</v>
       </c>
       <c r="M87" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N87" t="str">
         <v>null</v>
@@ -11173,7 +11173,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/grondstof</v>
       </c>
       <c r="M89" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N89" t="str">
         <v>null</v>
@@ -11295,7 +11295,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/grondstof_bestemming_type</v>
       </c>
       <c r="M90" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N90" t="str">
         <v>null</v>
@@ -11417,7 +11417,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/grondstof_hoeveelheid</v>
       </c>
       <c r="M91" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N91" t="str">
         <v>null</v>
@@ -11539,7 +11539,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/grondstof_materiaalcode</v>
       </c>
       <c r="M92" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N92" t="str">
         <v>null</v>
@@ -11661,7 +11661,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/grondstof_omschrijving</v>
       </c>
       <c r="M93" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N93" t="str">
         <v>null</v>
@@ -11783,7 +11783,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/grondstof_opmerking</v>
       </c>
       <c r="M94" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N94" t="str">
         <v>null</v>
@@ -11905,7 +11905,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/grondstof_toepassingswijze</v>
       </c>
       <c r="M95" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N95" t="str">
         <v>null</v>
@@ -12027,7 +12027,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/begintoestand</v>
       </c>
       <c r="M96" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N96" t="str">
         <v>null</v>
@@ -12149,7 +12149,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/datum</v>
       </c>
       <c r="M97" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N97" t="str">
         <v>null</v>
@@ -12271,7 +12271,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/diepte</v>
       </c>
       <c r="M98" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N98" t="str">
         <v>null</v>
@@ -12393,7 +12393,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/duur-stil</v>
       </c>
       <c r="M99" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N99" t="str">
         <v>null</v>
@@ -12515,7 +12515,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/eindtoestand</v>
       </c>
       <c r="M100" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N100" t="str">
         <v>null</v>
@@ -12637,7 +12637,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting</v>
       </c>
       <c r="M101" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N101" t="str">
         <v>null</v>
@@ -12759,7 +12759,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-bemonsteringsinstrument</v>
       </c>
       <c r="M102" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N102" t="str">
         <v>null</v>
@@ -12881,7 +12881,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-datum</v>
       </c>
       <c r="M103" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N103" t="str">
         <v>null</v>
@@ -13003,7 +13003,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-diepte</v>
       </c>
       <c r="M104" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N104" t="str">
         <v>null</v>
@@ -13125,7 +13125,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-labo</v>
       </c>
       <c r="M105" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N105" t="str">
         <v>null</v>
@@ -13247,7 +13247,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-labo-naam</v>
       </c>
       <c r="M106" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N106" t="str">
         <v>null</v>
@@ -13369,7 +13369,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-monsternummer</v>
       </c>
       <c r="M107" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N107" t="str">
         <v>null</v>
@@ -13491,7 +13491,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-parameter</v>
       </c>
       <c r="M108" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N108" t="str">
         <v>null</v>
@@ -13613,7 +13613,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-parameter-datum</v>
       </c>
       <c r="M109" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N109" t="str">
         <v>null</v>
@@ -13735,7 +13735,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-parameter-limiet</v>
       </c>
       <c r="M110" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N110" t="str">
         <v>null</v>
@@ -13857,7 +13857,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-parameter-meetwaarde</v>
       </c>
       <c r="M111" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N111" t="str">
         <v>null</v>
@@ -13979,7 +13979,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-parameter-methode</v>
       </c>
       <c r="M112" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N112" t="str">
         <v>null</v>
@@ -14101,7 +14101,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-parameter-parameter</v>
       </c>
       <c r="M113" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N113" t="str">
         <v>null</v>
@@ -14223,7 +14223,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-referentiepunt</v>
       </c>
       <c r="M114" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N114" t="str">
         <v>null</v>
@@ -14345,7 +14345,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting-techniek</v>
       </c>
       <c r="M115" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N115" t="str">
         <v>null</v>
@@ -14467,7 +14467,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/kwaliteitsmeting_feature</v>
       </c>
       <c r="M116" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N116" t="str">
         <v>null</v>
@@ -14589,7 +14589,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/onttrekking</v>
       </c>
       <c r="M117" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N117" t="str">
         <v>null</v>
@@ -14711,7 +14711,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/onttrekking_feature</v>
       </c>
       <c r="M118" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N118" t="str">
         <v>null</v>
@@ -14833,7 +14833,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/peilmethode</v>
       </c>
       <c r="M119" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N119" t="str">
         <v>null</v>
@@ -14955,7 +14955,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/peilmeting</v>
       </c>
       <c r="M120" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N120" t="str">
         <v>null</v>
@@ -15077,7 +15077,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/peilmeting_feature</v>
       </c>
       <c r="M121" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N121" t="str">
         <v>null</v>
@@ -15199,7 +15199,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/periode</v>
       </c>
       <c r="M122" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N122" t="str">
         <v>null</v>
@@ -15321,7 +15321,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/pomptoestand</v>
       </c>
       <c r="M123" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N123" t="str">
         <v>null</v>
@@ -15443,7 +15443,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/referentiepunt</v>
       </c>
       <c r="M124" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N124" t="str">
         <v>null</v>
@@ -15565,7 +15565,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/type-debiet</v>
       </c>
       <c r="M125" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N125" t="str">
         <v>null</v>
@@ -15687,7 +15687,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/volume</v>
       </c>
       <c r="M126" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N126" t="str">
         <v>null</v>
@@ -15809,7 +15809,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/volume-rust</v>
       </c>
       <c r="M127" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N127" t="str">
         <v>null</v>
@@ -15931,7 +15931,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondwater/volume-werking</v>
       </c>
       <c r="M128" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N128" t="str">
         <v>null</v>
@@ -16053,7 +16053,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/afvalproduct</v>
       </c>
       <c r="M129" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N129" t="str">
         <v>null</v>
@@ -16175,7 +16175,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/afvalproduct_aard</v>
       </c>
       <c r="M130" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N130" t="str">
         <v>null</v>
@@ -16297,7 +16297,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/afvalproduct_hoeveelheid</v>
       </c>
       <c r="M131" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N131" t="str">
         <v>null</v>
@@ -16419,7 +16419,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/afvalproduct_naam</v>
       </c>
       <c r="M132" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N132" t="str">
         <v>null</v>
@@ -16541,7 +16541,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/brandstof</v>
       </c>
       <c r="M133" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N133" t="str">
         <v>null</v>
@@ -16663,7 +16663,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/brandstof_as</v>
       </c>
       <c r="M134" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N134" t="str">
         <v>null</v>
@@ -16785,7 +16785,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/brandstof_naam</v>
       </c>
       <c r="M135" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N135" t="str">
         <v>null</v>
@@ -16907,7 +16907,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/brandstof_s</v>
       </c>
       <c r="M136" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N136" t="str">
         <v>null</v>
@@ -17029,7 +17029,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/brandstof_verbruik</v>
       </c>
       <c r="M137" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N137" t="str">
         <v>null</v>
@@ -17151,7 +17151,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie</v>
       </c>
       <c r="M138" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N138" t="str">
         <v>null</v>
@@ -17273,7 +17273,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie_luchtoverschot</v>
       </c>
       <c r="M139" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N139" t="str">
         <v>null</v>
@@ -17395,7 +17395,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie_parameter</v>
       </c>
       <c r="M140" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N140" t="str">
         <v>null</v>
@@ -17517,7 +17517,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie_parameter_massastroom</v>
       </c>
       <c r="M141" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N141" t="str">
         <v>null</v>
@@ -17639,7 +17639,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie_parameter_meetfrequentie</v>
       </c>
       <c r="M142" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N142" t="str">
         <v>null</v>
@@ -17761,7 +17761,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie_parameter_parameter</v>
       </c>
       <c r="M143" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N143" t="str">
         <v>null</v>
@@ -17883,7 +17883,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie_parameter_standaardafwijking</v>
       </c>
       <c r="M144" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N144" t="str">
         <v>null</v>
@@ -18005,7 +18005,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie_temperatuur</v>
       </c>
       <c r="M145" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N145" t="str">
         <v>null</v>
@@ -18127,7 +18127,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie_vochtgehalte</v>
       </c>
       <c r="M146" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N146" t="str">
         <v>null</v>
@@ -18249,7 +18249,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissie_zuurstofgehalte</v>
       </c>
       <c r="M147" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N147" t="str">
         <v>null</v>
@@ -18371,7 +18371,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissieduur</v>
       </c>
       <c r="M148" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N148" t="str">
         <v>null</v>
@@ -18493,7 +18493,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissieperiode</v>
       </c>
       <c r="M149" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N149" t="str">
         <v>null</v>
@@ -18615,7 +18615,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissieritme</v>
       </c>
       <c r="M150" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N150" t="str">
         <v>null</v>
@@ -18737,7 +18737,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissietoestand</v>
       </c>
       <c r="M151" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N151" t="str">
         <v>null</v>
@@ -18859,7 +18859,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/emissietype</v>
       </c>
       <c r="M152" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N152" t="str">
         <v>null</v>
@@ -19225,7 +19225,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/geproduceerde_stof</v>
       </c>
       <c r="M155" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N155" t="str">
         <v>null</v>
@@ -19347,7 +19347,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/geproduceerde_stof_aard</v>
       </c>
       <c r="M156" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N156" t="str">
         <v>null</v>
@@ -19469,7 +19469,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/geproduceerde_stof_hoeveelheid</v>
       </c>
       <c r="M157" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N157" t="str">
         <v>null</v>
@@ -19591,7 +19591,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/geproduceerde_stof_naam</v>
       </c>
       <c r="M158" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N158" t="str">
         <v>null</v>
@@ -19713,7 +19713,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/verbruikte_stof</v>
       </c>
       <c r="M159" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N159" t="str">
         <v>null</v>
@@ -19835,7 +19835,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/verbruikte_stof_aard</v>
       </c>
       <c r="M160" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N160" t="str">
         <v>null</v>
@@ -19957,7 +19957,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/verbruikte_stof_hoeveelheid</v>
       </c>
       <c r="M161" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N161" t="str">
         <v>null</v>
@@ -20079,7 +20079,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-lucht/verbruikte_stof_naam</v>
       </c>
       <c r="M162" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N162" t="str">
         <v>null</v>
@@ -21421,7 +21421,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-toestand-indicator/droog</v>
       </c>
       <c r="M173" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N173" t="str">
         <v>null</v>
@@ -21543,7 +21543,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-toestand-indicator/nat</v>
       </c>
       <c r="M174" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N174" t="str">
         <v>null</v>
@@ -21665,7 +21665,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/abnormale-lozing</v>
       </c>
       <c r="M175" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N175" t="str">
         <v>null</v>
@@ -21787,7 +21787,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/abnormale-lozing-jaarvracht</v>
       </c>
       <c r="M176" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N176" t="str">
         <v>null</v>
@@ -21909,7 +21909,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/abnormale-lozing-lozingsduur</v>
       </c>
       <c r="M177" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N177" t="str">
         <v>null</v>
@@ -22031,7 +22031,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/abnormale-lozing-stof</v>
       </c>
       <c r="M178" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N178" t="str">
         <v>null</v>
@@ -22153,7 +22153,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/abnormale-lozing-verklaring</v>
       </c>
       <c r="M179" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N179" t="str">
         <v>null</v>
@@ -22397,7 +22397,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing</v>
       </c>
       <c r="M181" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N181" t="str">
         <v>null</v>
@@ -22519,7 +22519,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing-bepalingsmethode</v>
       </c>
       <c r="M182" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N182" t="str">
         <v>null</v>
@@ -22641,7 +22641,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing-bepalingsmethodeclassificatie</v>
       </c>
       <c r="M183" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N183" t="str">
         <v>null</v>
@@ -22763,7 +22763,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing-concentratie</v>
       </c>
       <c r="M184" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N184" t="str">
         <v>null</v>
@@ -22885,7 +22885,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing-dagen</v>
       </c>
       <c r="M185" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N185" t="str">
         <v>null</v>
@@ -23007,7 +23007,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing-debiet</v>
       </c>
       <c r="M186" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N186" t="str">
         <v>null</v>
@@ -23129,7 +23129,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing-jaarvracht</v>
       </c>
       <c r="M187" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N187" t="str">
         <v>null</v>
@@ -23251,7 +23251,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing-meetfrequentie</v>
       </c>
       <c r="M188" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N188" t="str">
         <v>null</v>
@@ -23373,7 +23373,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-water/lozing-stof</v>
       </c>
       <c r="M189" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N189" t="str">
         <v>null</v>
@@ -23495,7 +23495,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/datum</v>
       </c>
       <c r="M190" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N190" t="str">
         <v>null</v>
@@ -23739,7 +23739,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/labo</v>
       </c>
       <c r="M192" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N192" t="str">
         <v>null</v>
@@ -23861,7 +23861,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/labo-id</v>
       </c>
       <c r="M193" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N193" t="str">
         <v>null</v>
@@ -23983,7 +23983,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/labo-naam</v>
       </c>
       <c r="M194" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N194" t="str">
         <v>null</v>
@@ -24105,7 +24105,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/meting</v>
       </c>
       <c r="M195" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N195" t="str">
         <v>null</v>
@@ -24227,7 +24227,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/parameter</v>
       </c>
       <c r="M196" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N196" t="str">
         <v>null</v>
@@ -24349,7 +24349,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/parameter-concentratie</v>
       </c>
       <c r="M197" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N197" t="str">
         <v>null</v>
@@ -24471,7 +24471,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/parameter-meetfrequentie</v>
       </c>
       <c r="M198" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N198" t="str">
         <v>null</v>
@@ -24593,7 +24593,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/parameter-meetonzekerheid</v>
       </c>
       <c r="M199" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N199" t="str">
         <v>null</v>
@@ -24715,7 +24715,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/parameter-parameter</v>
       </c>
       <c r="M200" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N200" t="str">
         <v>null</v>
@@ -24837,7 +24837,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-lucht/parameter-soort</v>
       </c>
       <c r="M201" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N201" t="str">
         <v>null</v>
@@ -24959,7 +24959,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/datum</v>
       </c>
       <c r="M202" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N202" t="str">
         <v>null</v>
@@ -25203,7 +25203,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/labo</v>
       </c>
       <c r="M204" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N204" t="str">
         <v>null</v>
@@ -25325,7 +25325,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/labo-id</v>
       </c>
       <c r="M205" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N205" t="str">
         <v>null</v>
@@ -25447,7 +25447,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/labo-naam</v>
       </c>
       <c r="M206" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N206" t="str">
         <v>null</v>
@@ -25569,7 +25569,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/meting</v>
       </c>
       <c r="M207" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N207" t="str">
         <v>null</v>
@@ -25691,7 +25691,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/parameter</v>
       </c>
       <c r="M208" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N208" t="str">
         <v>null</v>
@@ -25813,7 +25813,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/parameter-concentratie</v>
       </c>
       <c r="M209" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N209" t="str">
         <v>null</v>
@@ -25935,7 +25935,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/parameter-meetfrequentie</v>
       </c>
       <c r="M210" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N210" t="str">
         <v>null</v>
@@ -26057,7 +26057,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/parameter-meetonzekerheid</v>
       </c>
       <c r="M211" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N211" t="str">
         <v>null</v>
@@ -26179,7 +26179,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/parameter-parameter</v>
       </c>
       <c r="M212" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N212" t="str">
         <v>null</v>
@@ -26301,7 +26301,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-zelfcontrole-water/parameter-soort</v>
       </c>
       <c r="M213" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N213" t="str">
         <v>null</v>
@@ -27399,7 +27399,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/definitief_uit_dienst</v>
       </c>
       <c r="M222" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N222" t="str">
         <v>null</v>
@@ -27521,7 +27521,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/in_dienst</v>
       </c>
       <c r="M223" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N223" t="str">
         <v>null</v>
@@ -27643,7 +27643,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/ontmanteld</v>
       </c>
       <c r="M224" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N224" t="str">
         <v>null</v>
@@ -27765,7 +27765,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/tijdelijk_uit_dienst</v>
       </c>
       <c r="M225" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N225" t="str">
         <v>null</v>
@@ -27887,7 +27887,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/verkeerde_registratie</v>
       </c>
       <c r="M226" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N226" t="str">
         <v>null</v>
@@ -28009,7 +28009,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/voorgesteld</v>
       </c>
       <c r="M227" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N227" t="str">
         <v>null</v>
@@ -28863,7 +28863,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/uitwisselpunt-type/uitwisselpunt</v>
       </c>
       <c r="M234" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N234" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_type</v>
@@ -29229,7 +29229,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_eigenschappen</v>
       </c>
       <c r="M237" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N237" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_eigenschappen</v>
@@ -29443,7 +29443,7 @@
         <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
       </c>
       <c r="C239" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="D239" t="str">
         <v>null</v>
@@ -29595,7 +29595,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/filter_type</v>
       </c>
       <c r="M240" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N240" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_type</v>
@@ -29717,7 +29717,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_eigenschappen</v>
       </c>
       <c r="M241" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N241" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_eigenschappen</v>
@@ -30083,7 +30083,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/meetpunt_eigenschappen</v>
       </c>
       <c r="M244" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N244" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_eigenschappen</v>
@@ -30205,7 +30205,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/meetpunt_type</v>
       </c>
       <c r="M245" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N245" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_type</v>
@@ -30449,7 +30449,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/onttrekkingspunt_type</v>
       </c>
       <c r="M247" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N247" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_type</v>
@@ -31059,7 +31059,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_grondstoffen</v>
       </c>
       <c r="M252" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N252" t="str">
         <v>null</v>
@@ -31181,7 +31181,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_grondwater</v>
       </c>
       <c r="M253" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N253" t="str">
         <v>null</v>
@@ -31547,7 +31547,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_lucht_emissie</v>
       </c>
       <c r="M256" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N256" t="str">
         <v>null</v>
@@ -31669,7 +31669,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_lucht_rapportering</v>
       </c>
       <c r="M257" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N257" t="str">
         <v>null</v>
@@ -32279,7 +32279,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_toestand_indicator</v>
       </c>
       <c r="M262" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N262" t="str">
         <v>null</v>
@@ -32523,7 +32523,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_water_lozing</v>
       </c>
       <c r="M264" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N264" t="str">
         <v>null</v>
@@ -32767,7 +32767,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_zelfcontrole_lucht_meting</v>
       </c>
       <c r="M266" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N266" t="str">
         <v>null</v>
@@ -33133,7 +33133,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_zelfcontrole_water_meting</v>
       </c>
       <c r="M269" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="N269" t="str">
         <v>null</v>
@@ -33591,7 +33591,7 @@
         <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
       </c>
       <c r="C273" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="D273" t="str">
         <v>null</v>
@@ -33713,7 +33713,7 @@
         <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
       </c>
       <c r="C274" t="str">
-        <v>2026-10-07T13:39:34.912Z</v>
+        <v>2026-10-14T09:25:40.927Z</v>
       </c>
       <c r="D274" t="str">
         <v>null</v>

--- a/src/main/resources/be/vlaanderen/omgeving/data/id/conceptscheme/rie-iepr/rie-iepr.xlsx
+++ b/src/main/resources/be/vlaanderen/omgeving/data/id/conceptscheme/rie-iepr/rie-iepr.xlsx
@@ -538,7 +538,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/collection/rie-iepr/operationeel_parameters_grondwater</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-10-19T13:50:49.562Z</v>
+        <v>2026-10-20T08:43:32.688Z</v>
       </c>
       <c r="E2" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/csor/variabele/V_246|https://data.omgeving.vlaanderen.be/id/concept/csor/variabele/V_247|https://data.omgeving.vlaanderen.be/id/concept/csor/variabele/V_251|https://data.omgeving.vlaanderen.be/id/concept/csor/variabele/V_321|https://data.omgeving.vlaanderen.be/id/concept/csor/variabele/V_329|https://data.omgeving.vlaanderen.be/id/concept/csor/variabele/V_337</v>
@@ -666,7 +666,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/collection/rie-iepr/operationeel_stoffen_lucht</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-10-19T13:50:49.562Z</v>
+        <v>2026-10-20T08:43:32.688Z</v>
       </c>
       <c r="E3" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/csor/variabele/V_1057|https://data.omgeving.vlaanderen.be/id/concept/csor/variabele/V_1060|https://data.omgeving.vlaanderen.be/id/concept/csor/variabele/V_1685|https://data.omgeving.vlaanderen.be/id/concept/csor/variabele/V_1686|https://data.omgeving.vlaanderen.be/id/concept/csor/variabele/V_1901|https://data.omgeving.vlaanderen.be/id/concept/csor/variabele/V_1919</v>
@@ -794,7 +794,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/collection/rie-iepr/operationeel_stoffen_water</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-10-19T13:50:49.562Z</v>
+        <v>2026-10-20T08:43:32.688Z</v>
       </c>
       <c r="E4" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/csor/variabele/V_231|https://data.omgeving.vlaanderen.be/id/concept/csor/variabele/V_316|https://data.omgeving.vlaanderen.be/id/concept/csor/variabele/V_333|https://data.omgeving.vlaanderen.be/id/concept/csor/variabele/V_351|https://data.omgeving.vlaanderen.be/id/concept/csor/variabele/V_424|https://data.omgeving.vlaanderen.be/id/concept/csor/variabele/V_46</v>
@@ -922,7 +922,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/collection/rie-iepr/opslagcapaciteit_eenheden</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-10-19T13:50:49.562Z</v>
+        <v>2026-10-20T08:43:32.688Z</v>
       </c>
       <c r="E5" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/csor/eenheid/E_32|https://data.omgeving.vlaanderen.be/id/concept/csor/eenheid/E_33|https://data.omgeving.vlaanderen.be/id/concept/csor/eenheid/E_41|https://data.omgeving.vlaanderen.be/id/concept/csor/eenheid/E_83</v>
@@ -1050,7 +1050,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/collection/rie-iepr/productiecapaciteit_eenheden</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-10-19T13:50:49.562Z</v>
+        <v>2026-10-20T08:43:32.688Z</v>
       </c>
       <c r="E6" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/csor/eenheid/E_15</v>
@@ -1178,7 +1178,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/collection/rie-iepr/vermogen_eenheden</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-10-19T13:50:49.562Z</v>
+        <v>2026-10-20T08:43:32.688Z</v>
       </c>
       <c r="E7" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/csor/eenheid/E_92</v>
@@ -1306,7 +1306,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/collection/rie-iepr/verwijderingsrendement_stoffen</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-10-19T13:50:49.562Z</v>
+        <v>2026-10-20T08:43:32.688Z</v>
       </c>
       <c r="E8" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/csor/variabele/V_1096|https://data.omgeving.vlaanderen.be/id/concept/csor/variabele/V_2217</v>
@@ -2202,7 +2202,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissie-type/abnormale</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-10-19T13:50:49.562Z</v>
+        <v>2026-10-20T08:43:32.688Z</v>
       </c>
       <c r="E15" t="str">
         <v>null</v>
@@ -2330,7 +2330,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissie-type/geleide</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-10-19T13:50:49.562Z</v>
+        <v>2026-10-20T08:43:32.688Z</v>
       </c>
       <c r="E16" t="str">
         <v>null</v>
@@ -2458,7 +2458,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissie-type/niet-geleide</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-10-19T13:50:49.562Z</v>
+        <v>2026-10-20T08:43:32.688Z</v>
       </c>
       <c r="E17" t="str">
         <v>null</v>
@@ -2586,7 +2586,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissie-type/niet-geleide-fakkel</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-10-19T13:50:49.562Z</v>
+        <v>2026-10-20T08:43:32.688Z</v>
       </c>
       <c r="E18" t="str">
         <v>null</v>
@@ -2714,7 +2714,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissie-type/niet-geleide-lekverlies</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-10-19T13:50:49.562Z</v>
+        <v>2026-10-20T08:43:32.688Z</v>
       </c>
       <c r="E19" t="str">
         <v>null</v>
@@ -2842,7 +2842,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissie-type/niet-geleide-opslagverlies</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-10-19T13:50:49.562Z</v>
+        <v>2026-10-20T08:43:32.688Z</v>
       </c>
       <c r="E20" t="str">
         <v>null</v>
@@ -2970,7 +2970,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissie-type/niet-geleide-overslagverlies</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-10-19T13:50:49.562Z</v>
+        <v>2026-10-20T08:43:32.688Z</v>
       </c>
       <c r="E21" t="str">
         <v>null</v>
@@ -3098,7 +3098,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-eigenschappen-selectiemogelijkheden/collector</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-10-19T13:50:49.562Z</v>
+        <v>2026-10-20T08:43:32.688Z</v>
       </c>
       <c r="E22" t="str">
         <v>null</v>
@@ -3226,7 +3226,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-eigenschappen-selectiemogelijkheden/externe_waterzuivering</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-10-19T13:50:49.562Z</v>
+        <v>2026-10-20T08:43:32.688Z</v>
       </c>
       <c r="E23" t="str">
         <v>null</v>
@@ -3610,7 +3610,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-eigenschappen-selectiemogelijkheden/regenwaterriool</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-10-19T13:50:49.562Z</v>
+        <v>2026-10-20T08:43:32.688Z</v>
       </c>
       <c r="E26" t="str">
         <v>null</v>
@@ -3866,7 +3866,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-eigenschappen/aantal_punten</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-10-19T13:50:49.562Z</v>
+        <v>2026-10-20T08:43:32.688Z</v>
       </c>
       <c r="E28" t="str">
         <v>null</v>
@@ -3994,7 +3994,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-eigenschappen/diameter</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-10-19T13:50:49.562Z</v>
+        <v>2026-10-20T08:43:32.688Z</v>
       </c>
       <c r="E29" t="str">
         <v>null</v>
@@ -4122,7 +4122,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-eigenschappen/hoogte</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-10-19T13:50:49.562Z</v>
+        <v>2026-10-20T08:43:32.688Z</v>
       </c>
       <c r="E30" t="str">
         <v>null</v>
@@ -4378,7 +4378,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/emissiepunt_lucht</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-10-19T13:50:49.562Z</v>
+        <v>2026-10-20T08:43:32.688Z</v>
       </c>
       <c r="E32" t="str">
         <v>null</v>
@@ -4762,7 +4762,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/installatie</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-10-19T13:50:49.562Z</v>
+        <v>2026-10-20T08:43:32.688Z</v>
       </c>
       <c r="E35" t="str">
         <v>null</v>
@@ -5018,7 +5018,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-10-19T13:50:49.562Z</v>
+        <v>2026-10-20T08:43:32.688Z</v>
       </c>
       <c r="E37" t="str">
         <v>null</v>
@@ -5402,7 +5402,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/filter-eigenschappen/diepte</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-10-19T13:50:49.562Z</v>
+        <v>2026-10-20T08:43:32.688Z</v>
       </c>
       <c r="E40" t="str">
         <v>null</v>
@@ -5530,7 +5530,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/filter-eigenschappen/diepte_pomp</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-10-19T13:50:49.562Z</v>
+        <v>2026-10-20T08:43:32.688Z</v>
       </c>
       <c r="E41" t="str">
         <v>null</v>
@@ -5658,7 +5658,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/filter-eigenschappen/lengte</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-10-19T13:50:49.562Z</v>
+        <v>2026-10-20T08:43:32.688Z</v>
       </c>
       <c r="E42" t="str">
         <v>null</v>
@@ -5786,7 +5786,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/filter-eigenschappen/watervoerendeLaag</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-10-19T13:50:49.562Z</v>
+        <v>2026-10-20T08:43:32.688Z</v>
       </c>
       <c r="E43" t="str">
         <v>null</v>
@@ -5914,7 +5914,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/filter-type/filter</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-10-19T13:50:49.562Z</v>
+        <v>2026-10-20T08:43:32.688Z</v>
       </c>
       <c r="E44" t="str">
         <v>null</v>
@@ -6554,7 +6554,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen-selectiemogelijkheden/andere</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-10-19T13:50:49.562Z</v>
+        <v>2026-10-20T08:43:32.688Z</v>
       </c>
       <c r="E49" t="str">
         <v>null</v>
@@ -6682,7 +6682,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen-selectiemogelijkheden/andere_motor</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-10-19T13:50:49.562Z</v>
+        <v>2026-10-20T08:43:32.688Z</v>
       </c>
       <c r="E50" t="str">
         <v>null</v>
@@ -6810,7 +6810,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen-selectiemogelijkheden/andere_stookinstallatie</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-10-19T13:50:49.562Z</v>
+        <v>2026-10-20T08:43:32.688Z</v>
       </c>
       <c r="E51" t="str">
         <v>null</v>
@@ -6938,7 +6938,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen-selectiemogelijkheden/boiler</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-10-19T13:50:49.562Z</v>
+        <v>2026-10-20T08:43:32.688Z</v>
       </c>
       <c r="E52" t="str">
         <v>null</v>
@@ -7066,7 +7066,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen-selectiemogelijkheden/dieselmotor</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-10-19T13:50:49.562Z</v>
+        <v>2026-10-20T08:43:32.688Z</v>
       </c>
       <c r="E53" t="str">
         <v>null</v>
@@ -7194,7 +7194,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen-selectiemogelijkheden/druk</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-10-19T13:50:49.562Z</v>
+        <v>2026-10-20T08:43:32.688Z</v>
       </c>
       <c r="E54" t="str">
         <v>null</v>
@@ -7322,7 +7322,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen-selectiemogelijkheden/dual_fuel_motor</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-10-19T13:50:49.562Z</v>
+        <v>2026-10-20T08:43:32.688Z</v>
       </c>
       <c r="E55" t="str">
         <v>null</v>
@@ -7450,7 +7450,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen-selectiemogelijkheden/elektriciteit</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-10-19T13:50:49.562Z</v>
+        <v>2026-10-20T08:43:32.688Z</v>
       </c>
       <c r="E56" t="str">
         <v>null</v>
@@ -7578,7 +7578,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen-selectiemogelijkheden/gasmotor</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-10-19T13:50:49.562Z</v>
+        <v>2026-10-20T08:43:32.688Z</v>
       </c>
       <c r="E57" t="str">
         <v>null</v>
@@ -7706,7 +7706,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen-selectiemogelijkheden/gasturbine</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-10-19T13:50:49.562Z</v>
+        <v>2026-10-20T08:43:32.688Z</v>
       </c>
       <c r="E58" t="str">
         <v>null</v>
@@ -7834,7 +7834,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen-selectiemogelijkheden/mechanische_energie</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-10-19T13:50:49.562Z</v>
+        <v>2026-10-20T08:43:32.688Z</v>
       </c>
       <c r="E59" t="str">
         <v>null</v>
@@ -7962,7 +7962,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen-selectiemogelijkheden/stoom</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-10-19T13:50:49.562Z</v>
+        <v>2026-10-20T08:43:32.688Z</v>
       </c>
       <c r="E60" t="str">
         <v>null</v>
@@ -8090,7 +8090,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen-selectiemogelijkheden/warm_water</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-10-19T13:50:49.562Z</v>
+        <v>2026-10-20T08:43:32.688Z</v>
       </c>
       <c r="E61" t="str">
         <v>null</v>
@@ -8218,7 +8218,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen-selectiemogelijkheden/warme_lucht</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-10-19T13:50:49.562Z</v>
+        <v>2026-10-20T08:43:32.688Z</v>
       </c>
       <c r="E62" t="str">
         <v>null</v>
@@ -8346,7 +8346,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen-selectiemogelijkheden/wkk</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-10-19T13:50:49.562Z</v>
+        <v>2026-10-20T08:43:32.688Z</v>
       </c>
       <c r="E63" t="str">
         <v>null</v>
@@ -8474,7 +8474,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/geinstalleerde_opslag_overslagcapaciteit</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-10-19T13:50:49.562Z</v>
+        <v>2026-10-20T08:43:32.688Z</v>
       </c>
       <c r="E64" t="str">
         <v>null</v>
@@ -8730,7 +8730,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/geproduceerde_stof_of_product</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-10-19T13:50:49.562Z</v>
+        <v>2026-10-20T08:43:32.688Z</v>
       </c>
       <c r="E66" t="str">
         <v>null</v>
@@ -8986,7 +8986,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/nominaal_thermisch_vermogen</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-10-19T13:50:49.562Z</v>
+        <v>2026-10-20T08:43:32.688Z</v>
       </c>
       <c r="E68" t="str">
         <v>null</v>
@@ -9114,7 +9114,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/omschrijving</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-10-19T13:50:49.562Z</v>
+        <v>2026-10-20T08:43:32.688Z</v>
       </c>
       <c r="E69" t="str">
         <v>null</v>
@@ -9242,7 +9242,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/opslagen_overgeslagen_stof</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-10-19T13:50:49.562Z</v>
+        <v>2026-10-20T08:43:32.688Z</v>
       </c>
       <c r="E70" t="str">
         <v>null</v>
@@ -9370,7 +9370,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/soort_opgewekte_energie</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-10-19T13:50:49.562Z</v>
+        <v>2026-10-20T08:43:32.688Z</v>
       </c>
       <c r="E71" t="str">
         <v>null</v>
@@ -9498,7 +9498,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/technische_kenmerken</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-10-19T13:50:49.562Z</v>
+        <v>2026-10-20T08:43:32.688Z</v>
       </c>
       <c r="E72" t="str">
         <v>null</v>
@@ -9626,7 +9626,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/type_opslag_overslag</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-10-19T13:50:49.562Z</v>
+        <v>2026-10-20T08:43:32.688Z</v>
       </c>
       <c r="E73" t="str">
         <v>null</v>
@@ -9754,7 +9754,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/type_stookinstallatie</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-10-19T13:50:49.562Z</v>
+        <v>2026-10-20T08:43:32.688Z</v>
       </c>
       <c r="E74" t="str">
         <v>null</v>
@@ -10391,10 +10391,10 @@
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C79" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/waterzuiveringstechniek_ingebruikvan</v>
       </c>
       <c r="D79" t="str">
-        <v>null</v>
+        <v>2026-10-20T08:43:32.688Z</v>
       </c>
       <c r="E79" t="str">
         <v>null</v>
@@ -10778,7 +10778,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/fakkel</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-10-19T13:50:49.562Z</v>
+        <v>2026-10-20T08:43:32.688Z</v>
       </c>
       <c r="E82" t="str">
         <v>null</v>
@@ -11162,7 +11162,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/indirecte_stookinstallatie</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-10-19T13:50:49.562Z</v>
+        <v>2026-10-20T08:43:32.688Z</v>
       </c>
       <c r="E85" t="str">
         <v>null</v>
@@ -11546,7 +11546,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/productie_installatie</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-10-19T13:50:49.562Z</v>
+        <v>2026-10-20T08:43:32.688Z</v>
       </c>
       <c r="E88" t="str">
         <v>null</v>
@@ -11930,7 +11930,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-eigenschappen-selectiemogelijkheden/ander_referentiepunt</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-10-19T13:50:49.562Z</v>
+        <v>2026-10-20T08:43:32.688Z</v>
       </c>
       <c r="E91" t="str">
         <v>null</v>
@@ -12058,7 +12058,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-eigenschappen-selectiemogelijkheden/bovenkant_beschermbuis</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-10-19T13:50:49.562Z</v>
+        <v>2026-10-20T08:43:32.688Z</v>
       </c>
       <c r="E92" t="str">
         <v>null</v>
@@ -12186,7 +12186,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-eigenschappen-selectiemogelijkheden/bovenkant_peilbuis</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-10-19T13:50:49.562Z</v>
+        <v>2026-10-20T08:43:32.688Z</v>
       </c>
       <c r="E93" t="str">
         <v>null</v>
@@ -12314,7 +12314,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-eigenschappen-selectiemogelijkheden/bovenkant_straatpot</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-10-19T13:50:49.562Z</v>
+        <v>2026-10-20T08:43:32.688Z</v>
       </c>
       <c r="E94" t="str">
         <v>null</v>
@@ -12442,7 +12442,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-eigenschappen-selectiemogelijkheden/maaiveld</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-10-19T13:50:49.562Z</v>
+        <v>2026-10-20T08:43:32.688Z</v>
       </c>
       <c r="E95" t="str">
         <v>null</v>
@@ -12570,7 +12570,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-eigenschappen-selectiemogelijkheden/onbekend</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-10-19T13:50:49.562Z</v>
+        <v>2026-10-20T08:43:32.688Z</v>
       </c>
       <c r="E96" t="str">
         <v>null</v>
@@ -12826,7 +12826,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-eigenschappen/merk</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-10-19T13:50:49.562Z</v>
+        <v>2026-10-20T08:43:32.688Z</v>
       </c>
       <c r="E98" t="str">
         <v>null</v>
@@ -12954,7 +12954,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-eigenschappen/putnummer</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-10-19T13:50:49.562Z</v>
+        <v>2026-10-20T08:43:32.688Z</v>
       </c>
       <c r="E99" t="str">
         <v>null</v>
@@ -13466,7 +13466,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-eigenschappen/serienummer</v>
       </c>
       <c r="D103" t="str">
-        <v>2026-10-19T13:50:49.562Z</v>
+        <v>2026-10-20T08:43:32.688Z</v>
       </c>
       <c r="E103" t="str">
         <v>null</v>
@@ -13978,7 +13978,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/onttrekkingspunt-eigenschappen/omschrijving</v>
       </c>
       <c r="D107" t="str">
-        <v>2026-10-19T13:50:49.562Z</v>
+        <v>2026-10-20T08:43:32.688Z</v>
       </c>
       <c r="E107" t="str">
         <v>null</v>
@@ -15642,7 +15642,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-contextueel/activiteit</v>
       </c>
       <c r="D120" t="str">
-        <v>2026-10-19T13:50:49.562Z</v>
+        <v>2026-10-20T08:43:32.688Z</v>
       </c>
       <c r="E120" t="str">
         <v>null</v>
@@ -15770,7 +15770,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-contextueel/energieverbruik</v>
       </c>
       <c r="D121" t="str">
-        <v>2026-10-19T13:50:49.562Z</v>
+        <v>2026-10-20T08:43:32.688Z</v>
       </c>
       <c r="E121" t="str">
         <v>null</v>
@@ -15898,7 +15898,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-contextueel/feature</v>
       </c>
       <c r="D122" t="str">
-        <v>2026-10-19T13:50:49.562Z</v>
+        <v>2026-10-20T08:43:32.688Z</v>
       </c>
       <c r="E122" t="str">
         <v>null</v>
@@ -16026,7 +16026,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-contextueel/grondstoffenverbruik</v>
       </c>
       <c r="D123" t="str">
-        <v>2026-10-19T13:50:49.562Z</v>
+        <v>2026-10-20T08:43:32.688Z</v>
       </c>
       <c r="E123" t="str">
         <v>null</v>
@@ -16154,7 +16154,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-contextueel/productievolume</v>
       </c>
       <c r="D124" t="str">
-        <v>2026-10-19T13:50:49.562Z</v>
+        <v>2026-10-20T08:43:32.688Z</v>
       </c>
       <c r="E124" t="str">
         <v>null</v>
@@ -16282,7 +16282,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-contextueel/waterverbruik</v>
       </c>
       <c r="D125" t="str">
-        <v>2026-10-19T13:50:49.562Z</v>
+        <v>2026-10-20T08:43:32.688Z</v>
       </c>
       <c r="E125" t="str">
         <v>null</v>
@@ -16922,7 +16922,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-be</v>
       </c>
       <c r="D130" t="str">
-        <v>2026-10-19T13:50:49.562Z</v>
+        <v>2026-10-20T08:43:32.688Z</v>
       </c>
       <c r="E130" t="str">
         <v>null</v>
@@ -17434,7 +17434,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-buitenland</v>
       </c>
       <c r="D134" t="str">
-        <v>2026-10-19T13:50:49.562Z</v>
+        <v>2026-10-20T08:43:32.688Z</v>
       </c>
       <c r="E134" t="str">
         <v>null</v>
@@ -17818,7 +17818,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-none</v>
       </c>
       <c r="D137" t="str">
-        <v>2026-10-19T13:50:49.562Z</v>
+        <v>2026-10-20T08:43:32.688Z</v>
       </c>
       <c r="E137" t="str">
         <v>null</v>
@@ -18202,7 +18202,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-werf</v>
       </c>
       <c r="D140" t="str">
-        <v>2026-10-19T13:50:49.562Z</v>
+        <v>2026-10-20T08:43:32.688Z</v>
       </c>
       <c r="E140" t="str">
         <v>null</v>
@@ -37146,7 +37146,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/uitwisselpunt-eigenschappen/diepte</v>
       </c>
       <c r="D288" t="str">
-        <v>2026-10-19T13:50:49.562Z</v>
+        <v>2026-10-20T08:43:32.688Z</v>
       </c>
       <c r="E288" t="str">
         <v>null</v>
@@ -37274,7 +37274,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/uitwisselpunt-type/pompput</v>
       </c>
       <c r="D289" t="str">
-        <v>2026-10-19T13:50:49.562Z</v>
+        <v>2026-10-20T08:43:32.688Z</v>
       </c>
       <c r="E289" t="str">
         <v>null</v>
@@ -37658,7 +37658,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissie_type</v>
       </c>
       <c r="D292" t="str">
-        <v>2026-10-19T13:50:49.562Z</v>
+        <v>2026-10-20T08:43:32.688Z</v>
       </c>
       <c r="E292" t="str">
         <v>null</v>
@@ -38042,7 +38042,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/filter_eigenschappen</v>
       </c>
       <c r="D295" t="str">
-        <v>2026-10-19T13:50:49.562Z</v>
+        <v>2026-10-20T08:43:32.688Z</v>
       </c>
       <c r="E295" t="str">
         <v>null</v>
@@ -38426,7 +38426,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_soort_opgewekte_energie</v>
       </c>
       <c r="D298" t="str">
-        <v>2026-10-19T13:50:49.562Z</v>
+        <v>2026-10-20T08:43:32.688Z</v>
       </c>
       <c r="E298" t="str">
         <v>null</v>
@@ -38682,7 +38682,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_type_stookinstallatie</v>
       </c>
       <c r="D300" t="str">
-        <v>2026-10-19T13:50:49.562Z</v>
+        <v>2026-10-20T08:43:32.688Z</v>
       </c>
       <c r="E300" t="str">
         <v>null</v>
@@ -39066,7 +39066,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/meetpunt_referentiepunt_naam</v>
       </c>
       <c r="D303" t="str">
-        <v>2026-10-19T13:50:49.562Z</v>
+        <v>2026-10-20T08:43:32.688Z</v>
       </c>
       <c r="E303" t="str">
         <v>null</v>
@@ -39962,7 +39962,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_contextueel</v>
       </c>
       <c r="D310" t="str">
-        <v>2026-10-19T13:50:49.562Z</v>
+        <v>2026-10-20T08:43:32.688Z</v>
       </c>
       <c r="E310" t="str">
         <v>null</v>
@@ -40090,7 +40090,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_contextueel_iepr</v>
       </c>
       <c r="D311" t="str">
-        <v>2026-10-19T13:50:49.562Z</v>
+        <v>2026-10-20T08:43:32.688Z</v>
       </c>
       <c r="E311" t="str">
         <v>null</v>
@@ -40218,7 +40218,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_contextueel_iepr_activiteit</v>
       </c>
       <c r="D312" t="str">
-        <v>2026-10-19T13:50:49.562Z</v>
+        <v>2026-10-20T08:43:32.688Z</v>
       </c>
       <c r="E312" t="str">
         <v>null</v>
@@ -43162,7 +43162,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_eigenschappen</v>
       </c>
       <c r="D335" t="str">
-        <v>2026-10-19T13:50:49.562Z</v>
+        <v>2026-10-20T08:43:32.688Z</v>
       </c>
       <c r="E335" t="str">
         <v>null</v>
@@ -43290,7 +43290,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_type</v>
       </c>
       <c r="D336" t="str">
-        <v>2026-10-19T13:50:49.562Z</v>
+        <v>2026-10-20T08:43:32.688Z</v>
       </c>
       <c r="E336" t="str">
         <v>null</v>

--- a/src/main/resources/be/vlaanderen/omgeving/data/id/conceptscheme/rie-iepr/rie-iepr.xlsx
+++ b/src/main/resources/be/vlaanderen/omgeving/data/id/conceptscheme/rie-iepr/rie-iepr.xlsx
@@ -538,7 +538,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/collection/rie-iepr/operationeel_parameters_grondwater</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-10-20T08:43:32.688Z</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E2" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/csor/variabele/V_246|https://data.omgeving.vlaanderen.be/id/concept/csor/variabele/V_247|https://data.omgeving.vlaanderen.be/id/concept/csor/variabele/V_251|https://data.omgeving.vlaanderen.be/id/concept/csor/variabele/V_321|https://data.omgeving.vlaanderen.be/id/concept/csor/variabele/V_329|https://data.omgeving.vlaanderen.be/id/concept/csor/variabele/V_337</v>
@@ -666,7 +666,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/collection/rie-iepr/operationeel_stoffen_lucht</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-10-20T08:43:32.688Z</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E3" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/csor/variabele/V_1057|https://data.omgeving.vlaanderen.be/id/concept/csor/variabele/V_1060|https://data.omgeving.vlaanderen.be/id/concept/csor/variabele/V_1685|https://data.omgeving.vlaanderen.be/id/concept/csor/variabele/V_1686|https://data.omgeving.vlaanderen.be/id/concept/csor/variabele/V_1901|https://data.omgeving.vlaanderen.be/id/concept/csor/variabele/V_1919</v>
@@ -794,7 +794,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/collection/rie-iepr/operationeel_stoffen_water</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-10-20T08:43:32.688Z</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E4" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/csor/variabele/V_231|https://data.omgeving.vlaanderen.be/id/concept/csor/variabele/V_316|https://data.omgeving.vlaanderen.be/id/concept/csor/variabele/V_333|https://data.omgeving.vlaanderen.be/id/concept/csor/variabele/V_351|https://data.omgeving.vlaanderen.be/id/concept/csor/variabele/V_424|https://data.omgeving.vlaanderen.be/id/concept/csor/variabele/V_46</v>
@@ -922,7 +922,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/collection/rie-iepr/opslagcapaciteit_eenheden</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-10-20T08:43:32.688Z</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E5" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/csor/eenheid/E_32|https://data.omgeving.vlaanderen.be/id/concept/csor/eenheid/E_33|https://data.omgeving.vlaanderen.be/id/concept/csor/eenheid/E_41|https://data.omgeving.vlaanderen.be/id/concept/csor/eenheid/E_83</v>
@@ -1050,7 +1050,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/collection/rie-iepr/productiecapaciteit_eenheden</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-10-20T08:43:32.688Z</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E6" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/csor/eenheid/E_15</v>
@@ -1178,7 +1178,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/collection/rie-iepr/vermogen_eenheden</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-10-20T08:43:32.688Z</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E7" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/csor/eenheid/E_92</v>
@@ -1306,7 +1306,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/collection/rie-iepr/verwijderingsrendement_stoffen</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-10-20T08:43:32.688Z</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E8" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/csor/variabele/V_1096|https://data.omgeving.vlaanderen.be/id/concept/csor/variabele/V_2217</v>
@@ -2202,7 +2202,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissie-type/abnormale</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-10-20T08:43:32.688Z</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E15" t="str">
         <v>null</v>
@@ -2330,7 +2330,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissie-type/geleide</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-10-20T08:43:32.688Z</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E16" t="str">
         <v>null</v>
@@ -2458,7 +2458,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissie-type/niet-geleide</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-10-20T08:43:32.688Z</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E17" t="str">
         <v>null</v>
@@ -2586,7 +2586,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissie-type/niet-geleide-fakkel</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-10-20T08:43:32.688Z</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E18" t="str">
         <v>null</v>
@@ -2714,7 +2714,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissie-type/niet-geleide-lekverlies</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-10-20T08:43:32.688Z</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E19" t="str">
         <v>null</v>
@@ -2842,7 +2842,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissie-type/niet-geleide-opslagverlies</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-10-20T08:43:32.688Z</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E20" t="str">
         <v>null</v>
@@ -2970,7 +2970,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissie-type/niet-geleide-overslagverlies</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-10-20T08:43:32.688Z</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E21" t="str">
         <v>null</v>
@@ -3098,7 +3098,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-eigenschappen-selectiemogelijkheden/collector</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-10-20T08:43:32.688Z</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E22" t="str">
         <v>null</v>
@@ -3226,7 +3226,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-eigenschappen-selectiemogelijkheden/externe_waterzuivering</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-10-20T08:43:32.688Z</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E23" t="str">
         <v>null</v>
@@ -3610,7 +3610,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-eigenschappen-selectiemogelijkheden/regenwaterriool</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-10-20T08:43:32.688Z</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E26" t="str">
         <v>null</v>
@@ -3866,7 +3866,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-eigenschappen/aantal_punten</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-10-20T08:43:32.688Z</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E28" t="str">
         <v>null</v>
@@ -3994,7 +3994,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-eigenschappen/diameter</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-10-20T08:43:32.688Z</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E29" t="str">
         <v>null</v>
@@ -4122,7 +4122,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-eigenschappen/hoogte</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-10-20T08:43:32.688Z</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E30" t="str">
         <v>null</v>
@@ -4378,7 +4378,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/emissiepunt_lucht</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-10-20T08:43:32.688Z</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E32" t="str">
         <v>null</v>
@@ -4503,10 +4503,10 @@
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C33" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/fakkel</v>
       </c>
       <c r="D33" t="str">
-        <v>null</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E33" t="str">
         <v>null</v>
@@ -4554,7 +4554,7 @@
         <v>null</v>
       </c>
       <c r="T33" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_type</v>
       </c>
       <c r="U33" t="str">
         <v>null</v>
@@ -4631,10 +4631,10 @@
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C34" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/gebouw</v>
       </c>
       <c r="D34" t="str">
-        <v>null</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E34" t="str">
         <v>null</v>
@@ -4682,7 +4682,7 @@
         <v>null</v>
       </c>
       <c r="T34" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_type</v>
       </c>
       <c r="U34" t="str">
         <v>null</v>
@@ -4762,7 +4762,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/installatie</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-10-20T08:43:32.688Z</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E35" t="str">
         <v>null</v>
@@ -4810,7 +4810,7 @@
         <v>null</v>
       </c>
       <c r="T35" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_type</v>
       </c>
       <c r="U35" t="str">
         <v>null</v>
@@ -5018,7 +5018,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-10-20T08:43:32.688Z</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E37" t="str">
         <v>null</v>
@@ -5066,7 +5066,7 @@
         <v>null</v>
       </c>
       <c r="T37" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_type</v>
       </c>
       <c r="U37" t="str">
         <v>null</v>
@@ -5143,10 +5143,10 @@
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C38" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_horizontale_uitstroom</v>
       </c>
       <c r="D38" t="str">
-        <v>null</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E38" t="str">
         <v>null</v>
@@ -5194,7 +5194,7 @@
         <v>null</v>
       </c>
       <c r="T38" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_type</v>
       </c>
       <c r="U38" t="str">
         <v>null</v>
@@ -5271,10 +5271,10 @@
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C39" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_verticale_uitstroom</v>
       </c>
       <c r="D39" t="str">
-        <v>null</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E39" t="str">
         <v>null</v>
@@ -5322,7 +5322,7 @@
         <v>null</v>
       </c>
       <c r="T39" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_type</v>
       </c>
       <c r="U39" t="str">
         <v>null</v>
@@ -5402,7 +5402,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/filter-eigenschappen/diepte</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-10-20T08:43:32.688Z</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E40" t="str">
         <v>null</v>
@@ -5530,7 +5530,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/filter-eigenschappen/diepte_pomp</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-10-20T08:43:32.688Z</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E41" t="str">
         <v>null</v>
@@ -5658,7 +5658,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/filter-eigenschappen/lengte</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-10-20T08:43:32.688Z</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E42" t="str">
         <v>null</v>
@@ -5786,7 +5786,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/filter-eigenschappen/watervoerendeLaag</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-10-20T08:43:32.688Z</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E43" t="str">
         <v>null</v>
@@ -5914,7 +5914,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/filter-type/filter</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-10-20T08:43:32.688Z</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E44" t="str">
         <v>null</v>
@@ -6039,10 +6039,10 @@
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C45" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/filter-type/injectie</v>
       </c>
       <c r="D45" t="str">
-        <v>null</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E45" t="str">
         <v>null</v>
@@ -6090,7 +6090,7 @@
         <v>null</v>
       </c>
       <c r="T45" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_type</v>
       </c>
       <c r="U45" t="str">
         <v>null</v>
@@ -6167,10 +6167,10 @@
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C46" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/filter-type/omkeerbaar</v>
       </c>
       <c r="D46" t="str">
-        <v>null</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E46" t="str">
         <v>null</v>
@@ -6218,7 +6218,7 @@
         <v>null</v>
       </c>
       <c r="T46" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_type</v>
       </c>
       <c r="U46" t="str">
         <v>null</v>
@@ -6295,10 +6295,10 @@
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C47" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/filter-type/peil</v>
       </c>
       <c r="D47" t="str">
-        <v>null</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E47" t="str">
         <v>null</v>
@@ -6346,7 +6346,7 @@
         <v>null</v>
       </c>
       <c r="T47" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_type</v>
       </c>
       <c r="U47" t="str">
         <v>null</v>
@@ -6423,10 +6423,10 @@
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C48" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/filter-type/pomp</v>
       </c>
       <c r="D48" t="str">
-        <v>null</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E48" t="str">
         <v>null</v>
@@ -6474,7 +6474,7 @@
         <v>null</v>
       </c>
       <c r="T48" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_type</v>
       </c>
       <c r="U48" t="str">
         <v>null</v>
@@ -6554,7 +6554,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen-selectiemogelijkheden/andere</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-10-20T08:43:32.688Z</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E49" t="str">
         <v>null</v>
@@ -6682,7 +6682,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen-selectiemogelijkheden/andere_motor</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-10-20T08:43:32.688Z</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E50" t="str">
         <v>null</v>
@@ -6810,7 +6810,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen-selectiemogelijkheden/andere_stookinstallatie</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-10-20T08:43:32.688Z</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E51" t="str">
         <v>null</v>
@@ -6938,7 +6938,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen-selectiemogelijkheden/boiler</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-10-20T08:43:32.688Z</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E52" t="str">
         <v>null</v>
@@ -7066,7 +7066,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen-selectiemogelijkheden/dieselmotor</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-10-20T08:43:32.688Z</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E53" t="str">
         <v>null</v>
@@ -7194,7 +7194,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen-selectiemogelijkheden/druk</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-10-20T08:43:32.688Z</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E54" t="str">
         <v>null</v>
@@ -7322,7 +7322,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen-selectiemogelijkheden/dual_fuel_motor</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-10-20T08:43:32.688Z</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E55" t="str">
         <v>null</v>
@@ -7450,7 +7450,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen-selectiemogelijkheden/elektriciteit</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-10-20T08:43:32.688Z</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E56" t="str">
         <v>null</v>
@@ -7578,7 +7578,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen-selectiemogelijkheden/gasmotor</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-10-20T08:43:32.688Z</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E57" t="str">
         <v>null</v>
@@ -7706,7 +7706,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen-selectiemogelijkheden/gasturbine</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-10-20T08:43:32.688Z</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E58" t="str">
         <v>null</v>
@@ -7834,7 +7834,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen-selectiemogelijkheden/mechanische_energie</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-10-20T08:43:32.688Z</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E59" t="str">
         <v>null</v>
@@ -7962,7 +7962,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen-selectiemogelijkheden/stoom</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-10-20T08:43:32.688Z</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E60" t="str">
         <v>null</v>
@@ -8090,7 +8090,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen-selectiemogelijkheden/warm_water</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-10-20T08:43:32.688Z</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E61" t="str">
         <v>null</v>
@@ -8218,7 +8218,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen-selectiemogelijkheden/warme_lucht</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-10-20T08:43:32.688Z</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E62" t="str">
         <v>null</v>
@@ -8346,7 +8346,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen-selectiemogelijkheden/wkk</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-10-20T08:43:32.688Z</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E63" t="str">
         <v>null</v>
@@ -8474,7 +8474,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/geinstalleerde_opslag_overslagcapaciteit</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-10-20T08:43:32.688Z</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E64" t="str">
         <v>null</v>
@@ -8730,7 +8730,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/geproduceerde_stof_of_product</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-10-20T08:43:32.688Z</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E66" t="str">
         <v>null</v>
@@ -8986,7 +8986,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/nominaal_thermisch_vermogen</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-10-20T08:43:32.688Z</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E68" t="str">
         <v>null</v>
@@ -9114,7 +9114,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/omschrijving</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-10-20T08:43:32.688Z</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E69" t="str">
         <v>null</v>
@@ -9242,7 +9242,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/opslagen_overgeslagen_stof</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-10-20T08:43:32.688Z</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E70" t="str">
         <v>null</v>
@@ -9370,7 +9370,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/soort_opgewekte_energie</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-10-20T08:43:32.688Z</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E71" t="str">
         <v>null</v>
@@ -9498,7 +9498,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/technische_kenmerken</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-10-20T08:43:32.688Z</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E72" t="str">
         <v>null</v>
@@ -9626,7 +9626,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/type_opslag_overslag</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-10-20T08:43:32.688Z</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E73" t="str">
         <v>null</v>
@@ -9754,7 +9754,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/type_stookinstallatie</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-10-20T08:43:32.688Z</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E74" t="str">
         <v>null</v>
@@ -10007,10 +10007,10 @@
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C76" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/verwijderingsrendement_percentage</v>
       </c>
       <c r="D76" t="str">
-        <v>null</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E76" t="str">
         <v>null</v>
@@ -10058,7 +10058,7 @@
         <v>null</v>
       </c>
       <c r="T76" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_eigenschappen</v>
       </c>
       <c r="U76" t="str">
         <v>false</v>
@@ -10135,10 +10135,10 @@
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C77" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/verwijderingsrendement_stof</v>
       </c>
       <c r="D77" t="str">
-        <v>null</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E77" t="str">
         <v>null</v>
@@ -10186,7 +10186,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/luchtzuivering</v>
       </c>
       <c r="T77" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_eigenschappen</v>
       </c>
       <c r="U77" t="str">
         <v>false</v>
@@ -10394,7 +10394,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/waterzuiveringstechniek_ingebruikvan</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-10-20T08:43:32.688Z</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E79" t="str">
         <v>null</v>
@@ -10442,7 +10442,7 @@
         <v>null</v>
       </c>
       <c r="T79" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_eigenschappen</v>
       </c>
       <c r="U79" t="str">
         <v>false</v>
@@ -10519,10 +10519,10 @@
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C80" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/waterzuiveringstechniek_techniek</v>
       </c>
       <c r="D80" t="str">
-        <v>null</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E80" t="str">
         <v>null</v>
@@ -10570,7 +10570,7 @@
         <v>null</v>
       </c>
       <c r="T80" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_eigenschappen</v>
       </c>
       <c r="U80" t="str">
         <v>false</v>
@@ -10647,10 +10647,10 @@
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C81" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/directe_stookinstallatie</v>
       </c>
       <c r="D81" t="str">
-        <v>null</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E81" t="str">
         <v>null</v>
@@ -10698,7 +10698,7 @@
         <v>null</v>
       </c>
       <c r="T81" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_type</v>
       </c>
       <c r="U81" t="str">
         <v>null</v>
@@ -10778,7 +10778,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/fakkel</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-10-20T08:43:32.688Z</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E82" t="str">
         <v>null</v>
@@ -11162,7 +11162,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/indirecte_stookinstallatie</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-10-20T08:43:32.688Z</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E85" t="str">
         <v>null</v>
@@ -11210,7 +11210,7 @@
         <v>null</v>
       </c>
       <c r="T85" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_type</v>
       </c>
       <c r="U85" t="str">
         <v>null</v>
@@ -11546,7 +11546,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/productie_installatie</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-10-20T08:43:32.688Z</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E88" t="str">
         <v>null</v>
@@ -11930,7 +11930,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-eigenschappen-selectiemogelijkheden/ander_referentiepunt</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-10-20T08:43:32.688Z</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E91" t="str">
         <v>null</v>
@@ -12058,7 +12058,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-eigenschappen-selectiemogelijkheden/bovenkant_beschermbuis</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-10-20T08:43:32.688Z</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E92" t="str">
         <v>null</v>
@@ -12186,7 +12186,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-eigenschappen-selectiemogelijkheden/bovenkant_peilbuis</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-10-20T08:43:32.688Z</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E93" t="str">
         <v>null</v>
@@ -12314,7 +12314,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-eigenschappen-selectiemogelijkheden/bovenkant_straatpot</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-10-20T08:43:32.688Z</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E94" t="str">
         <v>null</v>
@@ -12442,7 +12442,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-eigenschappen-selectiemogelijkheden/maaiveld</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-10-20T08:43:32.688Z</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E95" t="str">
         <v>null</v>
@@ -12570,7 +12570,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-eigenschappen-selectiemogelijkheden/onbekend</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-10-20T08:43:32.688Z</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E96" t="str">
         <v>null</v>
@@ -12826,7 +12826,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-eigenschappen/merk</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-10-20T08:43:32.688Z</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E98" t="str">
         <v>null</v>
@@ -12954,7 +12954,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-eigenschappen/putnummer</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-10-20T08:43:32.688Z</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E99" t="str">
         <v>null</v>
@@ -13207,10 +13207,10 @@
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C101" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-eigenschappen/referentiepunt_diepte</v>
       </c>
       <c r="D101" t="str">
-        <v>null</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E101" t="str">
         <v>null</v>
@@ -13258,7 +13258,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-type/peilput</v>
       </c>
       <c r="T101" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_eigenschappen</v>
       </c>
       <c r="U101" t="str">
         <v>false</v>
@@ -13335,10 +13335,10 @@
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C102" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-eigenschappen/referentiepunt_naam</v>
       </c>
       <c r="D102" t="str">
-        <v>null</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E102" t="str">
         <v>null</v>
@@ -13386,7 +13386,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-type/peilput</v>
       </c>
       <c r="T102" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_eigenschappen</v>
       </c>
       <c r="U102" t="str">
         <v>false</v>
@@ -13466,7 +13466,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-eigenschappen/serienummer</v>
       </c>
       <c r="D103" t="str">
-        <v>2026-10-20T08:43:32.688Z</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E103" t="str">
         <v>null</v>
@@ -13978,7 +13978,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/onttrekkingspunt-eigenschappen/omschrijving</v>
       </c>
       <c r="D107" t="str">
-        <v>2026-10-20T08:43:32.688Z</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E107" t="str">
         <v>null</v>
@@ -15642,7 +15642,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-contextueel/activiteit</v>
       </c>
       <c r="D120" t="str">
-        <v>2026-10-20T08:43:32.688Z</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E120" t="str">
         <v>null</v>
@@ -15770,7 +15770,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-contextueel/energieverbruik</v>
       </c>
       <c r="D121" t="str">
-        <v>2026-10-20T08:43:32.688Z</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E121" t="str">
         <v>null</v>
@@ -15898,7 +15898,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-contextueel/feature</v>
       </c>
       <c r="D122" t="str">
-        <v>2026-10-20T08:43:32.688Z</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E122" t="str">
         <v>null</v>
@@ -16026,7 +16026,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-contextueel/grondstoffenverbruik</v>
       </c>
       <c r="D123" t="str">
-        <v>2026-10-20T08:43:32.688Z</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E123" t="str">
         <v>null</v>
@@ -16154,7 +16154,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-contextueel/productievolume</v>
       </c>
       <c r="D124" t="str">
-        <v>2026-10-20T08:43:32.688Z</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E124" t="str">
         <v>null</v>
@@ -16282,7 +16282,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-contextueel/waterverbruik</v>
       </c>
       <c r="D125" t="str">
-        <v>2026-10-20T08:43:32.688Z</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E125" t="str">
         <v>null</v>
@@ -16922,7 +16922,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-be</v>
       </c>
       <c r="D130" t="str">
-        <v>2026-10-20T08:43:32.688Z</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E130" t="str">
         <v>null</v>
@@ -17434,7 +17434,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-buitenland</v>
       </c>
       <c r="D134" t="str">
-        <v>2026-10-20T08:43:32.688Z</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E134" t="str">
         <v>null</v>
@@ -17818,7 +17818,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-none</v>
       </c>
       <c r="D137" t="str">
-        <v>2026-10-20T08:43:32.688Z</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E137" t="str">
         <v>null</v>
@@ -18202,7 +18202,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/operationeel-grondstoffen/bestemmingsidentificatie-werf</v>
       </c>
       <c r="D140" t="str">
-        <v>2026-10-20T08:43:32.688Z</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E140" t="str">
         <v>null</v>
@@ -37146,7 +37146,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/uitwisselpunt-eigenschappen/diepte</v>
       </c>
       <c r="D288" t="str">
-        <v>2026-10-20T08:43:32.688Z</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E288" t="str">
         <v>null</v>
@@ -37274,7 +37274,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/uitwisselpunt-type/pompput</v>
       </c>
       <c r="D289" t="str">
-        <v>2026-10-20T08:43:32.688Z</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E289" t="str">
         <v>null</v>
@@ -37658,7 +37658,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissie_type</v>
       </c>
       <c r="D292" t="str">
-        <v>2026-10-20T08:43:32.688Z</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E292" t="str">
         <v>null</v>
@@ -38042,7 +38042,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/filter_eigenschappen</v>
       </c>
       <c r="D295" t="str">
-        <v>2026-10-20T08:43:32.688Z</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E295" t="str">
         <v>null</v>
@@ -38426,7 +38426,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_soort_opgewekte_energie</v>
       </c>
       <c r="D298" t="str">
-        <v>2026-10-20T08:43:32.688Z</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E298" t="str">
         <v>null</v>
@@ -38682,7 +38682,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_type_stookinstallatie</v>
       </c>
       <c r="D300" t="str">
-        <v>2026-10-20T08:43:32.688Z</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E300" t="str">
         <v>null</v>
@@ -39066,7 +39066,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/meetpunt_referentiepunt_naam</v>
       </c>
       <c r="D303" t="str">
-        <v>2026-10-20T08:43:32.688Z</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E303" t="str">
         <v>null</v>
@@ -39962,7 +39962,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_contextueel</v>
       </c>
       <c r="D310" t="str">
-        <v>2026-10-20T08:43:32.688Z</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E310" t="str">
         <v>null</v>
@@ -40090,7 +40090,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_contextueel_iepr</v>
       </c>
       <c r="D311" t="str">
-        <v>2026-10-20T08:43:32.688Z</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E311" t="str">
         <v>null</v>
@@ -40218,7 +40218,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/operationeel_contextueel_iepr_activiteit</v>
       </c>
       <c r="D312" t="str">
-        <v>2026-10-20T08:43:32.688Z</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E312" t="str">
         <v>null</v>
@@ -43162,7 +43162,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_eigenschappen</v>
       </c>
       <c r="D335" t="str">
-        <v>2026-10-20T08:43:32.688Z</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E335" t="str">
         <v>null</v>
@@ -43276,7 +43276,7 @@
         <v>null</v>
       </c>
       <c r="AP335" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-eigenschappen/aantal_punten|https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_eigenschappen|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-eigenschappen/diameter|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-eigenschappen/hoogte|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-eigenschappen/lozingspunt-lozingsplaats|https://data.omgeving.vlaanderen.be/id/concept/riepr/filter-eigenschappen/diepte|https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/filter_eigenschappen|https://data.omgeving.vlaanderen.be/id/concept/riepr/filter-eigenschappen/diepte_pomp|https://data.omgeving.vlaanderen.be/id/concept/riepr/filter-eigenschappen/lengte|https://data.omgeving.vlaanderen.be/id/concept/riepr/filter-eigenschappen/watervoerendeLaag|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/geinstalleerde_opslag_overslagcapaciteit|https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_eigenschappen|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/geinstalleerde_productiecapaciteit|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/geproduceerde_stof_of_product|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/luchtzuiverings_techniek|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/nominaal_thermisch_vermogen|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/omschrijving|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/opslagen_overgeslagen_stof|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/soort_opgewekte_energie|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/technische_kenmerken|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/type_opslag_overslag|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/type_stookinstallatie|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/verwijderingsrendement|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/waterzuiveringstechniek|https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-eigenschappen/diepte|https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/meetpunt_eigenschappen|https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-eigenschappen/merk|https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-eigenschappen/putnummer|https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-eigenschappen/referentiepunt|https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-eigenschappen/serienummer|https://data.omgeving.vlaanderen.be/id/concept/riepr/onttrekkingspunt-eigenschappen/omschrijving|https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/onttrekkingspunt_eigenschappen|https://data.omgeving.vlaanderen.be/id/concept/riepr/uitwisselpunt-eigenschappen/diepte|https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/uitwisselpunt_eigenschappen</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-eigenschappen/aantal_punten|https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_eigenschappen|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-eigenschappen/diameter|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-eigenschappen/hoogte|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-eigenschappen/lozingspunt-lozingsplaats|https://data.omgeving.vlaanderen.be/id/concept/riepr/filter-eigenschappen/diepte|https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/filter_eigenschappen|https://data.omgeving.vlaanderen.be/id/concept/riepr/filter-eigenschappen/diepte_pomp|https://data.omgeving.vlaanderen.be/id/concept/riepr/filter-eigenschappen/lengte|https://data.omgeving.vlaanderen.be/id/concept/riepr/filter-eigenschappen/watervoerendeLaag|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/geinstalleerde_opslag_overslagcapaciteit|https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_eigenschappen|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/geinstalleerde_productiecapaciteit|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/geproduceerde_stof_of_product|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/luchtzuiverings_techniek|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/nominaal_thermisch_vermogen|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/omschrijving|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/opslagen_overgeslagen_stof|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/soort_opgewekte_energie|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/technische_kenmerken|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/type_opslag_overslag|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/type_stookinstallatie|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/verwijderingsrendement|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/verwijderingsrendement_percentage|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/verwijderingsrendement_stof|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/waterzuiveringstechniek|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/waterzuiveringstechniek_ingebruikvan|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/waterzuiveringstechniek_techniek|https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-eigenschappen/diepte|https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/meetpunt_eigenschappen|https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-eigenschappen/merk|https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-eigenschappen/putnummer|https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-eigenschappen/referentiepunt|https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-eigenschappen/referentiepunt_diepte|https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-eigenschappen/referentiepunt_naam|https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-eigenschappen/serienummer|https://data.omgeving.vlaanderen.be/id/concept/riepr/onttrekkingspunt-eigenschappen/omschrijving|https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/onttrekkingspunt_eigenschappen|https://data.omgeving.vlaanderen.be/id/concept/riepr/uitwisselpunt-eigenschappen/diepte|https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/uitwisselpunt_eigenschappen</v>
       </c>
     </row>
     <row r="336">
@@ -43290,7 +43290,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_type</v>
       </c>
       <c r="D336" t="str">
-        <v>2026-10-20T08:43:32.688Z</v>
+        <v>2026-10-21T11:58:12.462Z</v>
       </c>
       <c r="E336" t="str">
         <v>null</v>
@@ -43404,7 +43404,7 @@
         <v>null</v>
       </c>
       <c r="AP336" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/fakkel|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/opslag_overslag|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/emissiepunt_lucht|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/lozingspunt|https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type|https://data.omgeving.vlaanderen.be/id/concept/riepr/filter-type/filter|https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/filter_type|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/productie_installatie|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/luchtzuivering|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/stookinstallatie|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/waterzuivering|https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_type|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/geothermisch|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/gpbv|https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-type/peilput|https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-type/debietmeter|https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-type/controleinrichting|https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/meetpunt_type|https://data.omgeving.vlaanderen.be/id/concept/riepr/onttrekkingspunt-type/opnamepunt|https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/onttrekkingspunt_type|https://data.omgeving.vlaanderen.be/id/concept/riepr/uitwisselpunt-type/pompput|https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/uitwisselpunt_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/fakkel|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/opslag_overslag|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/emissiepunt_lucht|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/lozingspunt|https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/fakkel|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/gebouw|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/installatie|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_horizontale_uitstroom|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_verticale_uitstroom|https://data.omgeving.vlaanderen.be/id/concept/riepr/filter-type/filter|https://data.omgeving.vlaanderen.be/id/concept/riepr/filter-type/pomp|https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/filter_type|https://data.omgeving.vlaanderen.be/id/concept/riepr/filter-type/injectie|https://data.omgeving.vlaanderen.be/id/concept/riepr/filter-type/omkeerbaar|https://data.omgeving.vlaanderen.be/id/concept/riepr/filter-type/peil|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/productie_installatie|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/luchtzuivering|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/stookinstallatie|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/waterzuivering|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/directe_stookinstallatie|https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_type|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/geothermisch|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/gpbv|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/indirecte_stookinstallatie|https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-type/peilput|https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-type/debietmeter|https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-type/controleinrichting|https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/meetpunt_type|https://data.omgeving.vlaanderen.be/id/concept/riepr/onttrekkingspunt-type/opnamepunt|https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/onttrekkingspunt_type|https://data.omgeving.vlaanderen.be/id/concept/riepr/uitwisselpunt-type/pompput|https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/uitwisselpunt_type</v>
       </c>
     </row>
     <row r="337">
